--- a/Noticias_Calcario_20260819.xlsx
+++ b/Noticias_Calcario_20260819.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D518"/>
+  <dimension ref="A1:D519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,132 +441,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A Mosaic apresenta sua gravel de 32” e cria uma nova marca de componentes para solucionar um de seus grandes problemas - brujulabike.com</t>
+          <t>Prefeitura de Iomerê entrega novo distribuidor de calcário e adubos à Associação da Linha Caravagio - Rádio Tropical FM 99.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19/08/2026 02:41</t>
+          <t>19/08/2026 09:15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLTFBUG8xNmpsV1FITzJfSjlWTlRUT0Itc1N6eTdxQzlXVlNSeWhMYTZUWnBGYlRLUWp1N0tHeHIweTN3eVZEdkd5SUR3cHF3Y2l4MjNQUG0yXzhDREM3QjRUTUlkUU1jbjNzNW9ucjQwenZmM21YWTZDUk9OdWV2Z3RJbzJFbUpiejkyWHJUeGx1cG9mbE1MNlBKZ0VoenlaVXdIUDF2SW9ub2hlOWU4czZYODhSLUt3bW1FR2x0U01KOTNkaUJyNUJqRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOZi1LOHNDUjNfNEFTWjNRZm5ybHZWYTJkVHdoanVVR2xLVkRfaVluSlo2OUNZS24tTUt6Q1k4alJ5STVfQnlzNzBfY2p1M1ZmQ0gyamhEQ25yVEZPZlFnQ2UwWHE3aTdxbkpQdTlVRFNndmloRVB0S0hQS1pSSVV0bFhWVUNwaDhsMmlBN3dlQ2NFdFRScW5aaTlwNHV4aEM2MjBxS0FwQXRNWkFYY1VUT21SSmNLaVVSVUhOSTBEb29WMWl4cjRoSm9qNzBTVTh4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leite com soda cáustica, água e ureia: Homem é condenado a 13 anos de prisão por adulterar produto na Serra - abcmais.com</t>
+          <t>A Mosaic apresenta sua gravel de 32” e cria uma nova marca de componentes para solucionar um de seus grandes problemas - brujulabike.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/08/2026 12:21</t>
+          <t>19/08/2026 02:41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxORmZKalQtNUhHdV80SnhHeGI4RjBDS0FyTFJaMEJOVHdKcG5LNmFuV09WUkRrYS1hNkJ5RmloRDkxUWtBZXNYcktwaXV3OV8zWlQ1RWl1RzBzVDVHYWU0cy1GLUVxV2VQV2RUQy1LU2tNcW5MQTNmOWFjX0s0RWx4ZVA4ZVlreU80SEJCQTMwUGZtUWFncXdQdXlIYU8ycGhDcEZVZjQ2M2tBMUFManI5eURlWmp3S2JnZ3oxYV8tMWdTb3ptSlNEU3R3RWdZWlVQYzBXMzVSOWxPTnd2Z0ZKZndVOHlDZjN5MUx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLTFBUG8xNmpsV1FITzJfSjlWTlRUT0Itc1N6eTdxQzlXVlNSeWhMYTZUWnBGYlRLUWp1N0tHeHIweTN3eVZEdkd5SUR3cHF3Y2l4MjNQUG0yXzhDREM3QjRUTUlkUU1jbjNzNW9ucjQwenZmM21YWTZDUk9OdWV2Z3RJbzJFbUpiejkyWHJUeGx1cG9mbE1MNlBKZ0VoenlaVXdIUDF2SW9ub2hlOWU4czZYODhSLUt3bW1FR2x0U01KOTNkaUJyNUJqRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Complexo de fertilizantes de US$ 1 bilhão em Minas Gerais pode reduzir produção e suspender contratos de 600 trabalhadores após crise global do enxofre ameaçar operação - CPG Click Petróleo e Gás</t>
+          <t>Leite com soda cáustica, água e ureia: Homem é condenado a 13 anos de prisão por adulterar produto na Serra - abcmais.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18/08/2026 11:06</t>
+          <t>18/08/2026 12:21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNXljX3RCd1I3cW9mR2h2TmdMNUt0SmJSM05TX0xVZEJ5ek5icmNINEtSNG5NN2ZUbE42a0N1THdWZW95Z2lzSG5DNEFaNC1lbXMxRDJqaXFqd1VTamVxU0tkdF82cGRVNTY2eVY2SkVsS1dKQVB6Qk9PNWsyV2h1NTJxY2xhRV9OdWVSZFU1NmJzWkF4SFVhTGZzVkVzY3JEN1Uwbzh1ZFJVck9hdGNjZHNfZEVzM0FwZjZkeEd0bm16UVMycjZiUFdncXluZGxTOTJUYXJIb0NtM2EyQ1g3d0FWcG0wLW9JUjAtRDdVbUxHcVJxZlNJc05qSjBpaTFUWXFZcS1OX2VPcDZZRFFRYTNXMzFnSjU3dDRUaEZnNUJubW5pSU5HUmJCZzl0VFdK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxORmZKalQtNUhHdV80SnhHeGI4RjBDS0FyTFJaMEJOVHdKcG5LNmFuV09WUkRrYS1hNkJ5RmloRDkxUWtBZXNYcktwaXV3OV8zWlQ1RWl1RzBzVDVHYWU0cy1GLUVxV2VQV2RUQy1LU2tNcW5MQTNmOWFjX0s0RWx4ZVA4ZVlreU80SEJCQTMwUGZtUWFncXdQdXlIYU8ycGhDcEZVZjQ2M2tBMUFManI5eURlWmp3S2JnZ3oxYV8tMWdTb3ptSlNEU3R3RWdZWlVQYzBXMzVSOWxPTnd2Z0ZKZndVOHlDZjN5MUx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 18 de Agosto de 2026 - RR Mais</t>
+          <t>Complexo de fertilizantes de US$ 1 bilhão em Minas Gerais pode reduzir produção e suspender contratos de 600 trabalhadores após crise global do enxofre ameaçar operação - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18/08/2026 10:46</t>
+          <t>18/08/2026 11:06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYlVNVmtBdVZFQ250cndQUkRRb09xWm1vNHpzOEFHUkFscC0tQ1JVX2MzVUZrajNXNnVKTjlBdkxzYkdQMzV4MGZjS1VicmlSWEFkVEx0ZGkzaVgzQ1VDUVhLN0VqNE5IZy1SS2dhSHd0SXNVUllKVk5VWGF6cDV3UkFuWXBSWmRMZ1JTRklOWnMwckxJM1kyaTlvclBudmtTYkpWMFl2SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNXljX3RCd1I3cW9mR2h2TmdMNUt0SmJSM05TX0xVZEJ5ek5icmNINEtSNG5NN2ZUbE42a0N1THdWZW95Z2lzSG5DNEFaNC1lbXMxRDJqaXFqd1VTamVxU0tkdF82cGRVNTY2eVY2SkVsS1dKQVB6Qk9PNWsyV2h1NTJxY2xhRV9OdWVSZFU1NmJzWkF4SFVhTGZzVkVzY3JEN1Uwbzh1ZFJVck9hdGNjZHNfZEVzM0FwZjZkeEd0bm16UVMycjZiUFdncXluZGxTOTJUYXJIb0NtM2EyQ1g3d0FWcG0wLW9JUjAtRDdVbUxHcVJxZlNJc05qSjBpaTFUWXFZcS1OX2VPcDZZRFFRYTNXMzFnSjU3dDRUaEZnNUJubW5pSU5HUmJCZzl0VFdK?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN na CMOC Chapadão - Zap Catalão</t>
+          <t>Cotações Agrícolas para esta Terça-feira 18 de Agosto de 2026 - RR Mais</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17/08/2026 22:15</t>
+          <t>18/08/2026 10:46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPX09FZWhNd1BTTzA0NlVya3FiVHRzUkpmZ0ozamh1MnVoOTgzbWQ0bXF0a1B2SzR5NEZZd1BramVBRjhfOVpRb1o5MURiQU16U0hwTjFRS1pXd3pWSWJjU3hWMWx0VS03SnJvQ2x4Nm5ZLXhBQkloaFpjTVZfM1A3TGtkcFpVYkcxV0cwb2V1M2w1LW5td3p4NXMwZjdYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYlVNVmtBdVZFQ250cndQUkRRb09xWm1vNHpzOEFHUkFscC0tQ1JVX2MzVUZrajNXNnVKTjlBdkxzYkdQMzV4MGZjS1VicmlSWEFkVEx0ZGkzaVgzQ1VDUVhLN0VqNE5IZy1SS2dhSHd0SXNVUllKVk5VWGF6cDV3UkFuWXBSWmRMZ1JTRklOWnMwckxJM1kyaTlvclBudmtTYkpWMFl2SQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Homem é condenado a 13 anos de prisão por adulterar leite com água e ureia no RS - GZH</t>
+          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN na CMOC Chapadão - Zap Catalão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17/08/2026 19:50</t>
+          <t>17/08/2026 22:15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPRTF1ZGRpdDJmM0RrZFpoSi1QQ3JibjlnUTI1UHg4QUZxVDk5eGl5ek91RUVNd2ROT3B6MzhhZmk4OG52VUJucnN5WUFpdEJLME9HYkh2QXk1d0dFeVY4VUt6QlhVYUxOaU95T3l5S0REeTRnV29xN3J1SEV0WHhER3RWVnJocE4ybGZid1ZfZkJ5b2dEcXdoNURUWXZqMWREX251TGtrUWZUTUp6ZlVyQ0VtMWwxX0pZdTBvUWQwVlhuQWk3SnpSVXBFci1lMnkxNE9NT3lSdm9mQ1Zob0t2cEFVWXZ4ZU5TZ0plLWc3Q1hRRHRxMW04U3lzSU9LUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPX09FZWhNd1BTTzA0NlVya3FiVHRzUkpmZ0ozamh1MnVoOTgzbWQ0bXF0a1B2SzR5NEZZd1BramVBRjhfOVpRb1o5MURiQU16U0hwTjFRS1pXd3pWSWJjU3hWMWx0VS03SnJvQ2x4Nm5ZLXhBQkloaFpjTVZfM1A3TGtkcFpVYkcxV0cwb2V1M2w1LW5td3p4NXMwZjdYQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Homem é condenado a 13 anos por adulterar leite com ureia no RS - Agora RS</t>
+          <t>Homem é condenado a 13 anos de prisão por adulterar leite com água e ureia no RS - GZH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17/08/2026 19:46</t>
+          <t>17/08/2026 19:50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxON0NvdThIRFJaWlY0RlBFdDRkM3V4XzQwc3I1SWoxcXdRSk5TZk1xd2l5WDBtRFI2a2MzWTExdS04bHJmU1g3U29PQUw1VWg4UDFqMjlDMmNUcjJ2NDI3NG83OHBCeEtsNTlMMGwxeWFpU2hjM0trSmF3STRONWV5bGx6cENFOC1ldDFvb3h0cE5fcVY0WmZBcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPRTF1ZGRpdDJmM0RrZFpoSi1QQ3JibjlnUTI1UHg4QUZxVDk5eGl5ek91RUVNd2ROT3B6MzhhZmk4OG52VUJucnN5WUFpdEJLME9HYkh2QXk1d0dFeVY4VUt6QlhVYUxOaU95T3l5S0REeTRnV29xN3J1SEV0WHhER3RWVnJocE4ybGZid1ZfZkJ5b2dEcXdoNURUWXZqMWREX251TGtrUWZUTUp6ZlVyQ0VtMWwxX0pZdTBvUWQwVlhuQWk3SnpSVXBFci1lMnkxNE9NT3lSdm9mQ1Zob0t2cEFVWXZ4ZU5TZ0plLWc3Q1hRRHRxMW04U3lzSU9LUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -600,83 +600,83 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OPERAÇÃO LEITE COMPEN$ADO: Adulteração de Leite com ureia e soda cáustica rende condenação severa no RS - Terra</t>
+          <t>Homem é condenado a 13 anos por adulterar leite com ureia no RS - agorars.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17/08/2026 16:41</t>
+          <t>17/08/2026 19:46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxONTZUOHdXM0RPQ290UllHZ0dKcTd0U185WWRFVXFfSDlERzRyMDhmamZoajBVZmNPOTZlMzg5TG9VYVNFVDIwNDFjT19vWjJILVJQVnFYaFZfUHlCeFBjU2x2MTFIRVRUS0o3TGFrMExXLVhpbE5iY2d0VGFxM1VydzNNNkNWZmk4SW5nSHNfeXFoTUY4Y0xKbEowTUNwckV0bHhSTENzVHFEckVGd2JjRGFLZEx2VHBoRW43SjlvZnFxSzlWMzhQYzk5VkVCRkgyeVZXSjdwTlhLV013U0FZTU82VF9ieXZCb0k2eHQ2WVBxQS1qdFlTT2UxOXVYTjBYcERVMVpxT2lZX0YxTGFoWU5ZNGFvYm50Wmgzd1hhMy00UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxON0NvdThIRFJaWlY0RlBFdDRkM3V4XzQwc3I1SWoxcXdRSk5TZk1xd2l5WDBtRFI2a2MzWTExdS04bHJmU1g3U29PQUw1VWg4UDFqMjlDMmNUcjJ2NDI3NG83OHBCeEtsNTlMMGwxeWFpU2hjM0trSmF3STRONWV5bGx6cENFOC1ldDFvb3h0cE5fcVY0WmZBcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN da CMOC Chapadão - Diante do Fato Catalão</t>
+          <t>OPERAÇÃO LEITE COMPEN$ADO: Adulteração de Leite com ureia e soda cáustica rende condenação severa no RS - Terra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17/08/2026 16:11</t>
+          <t>17/08/2026 16:41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSlNqSXJuUTdPRHk4SkwyaEFyX3QzR0t1WVZWbEEyMVVNODlyZFF2YkQ0SVdCclRMa2pKSTVKSEhnZlp2Q1dJZTJXWi1vWXItVHpic08weGNZVDlheldQY2FTQy01T1FFejYwQWx3NWU0WFhsT2xVWnc3TENRc055TTM4cFpBZnpTOGxpZFZ6d2FzS2lMWDFwV21PMVF1Nlh6SEZMU1hxTktfQTVPZjlz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxONTZUOHdXM0RPQ290UllHZ0dKcTd0U185WWRFVXFfSDlERzRyMDhmamZoajBVZmNPOTZlMzg5TG9VYVNFVDIwNDFjT19vWjJILVJQVnFYaFZfUHlCeFBjU2x2MTFIRVRUS0o3TGFrMExXLVhpbE5iY2d0VGFxM1VydzNNNkNWZmk4SW5nSHNfeXFoTUY4Y0xKbEowTUNwckV0bHhSTENzVHFEckVGd2JjRGFLZEx2VHBoRW43SjlvZnFxSzlWMzhQYzk5VkVCRkgyeVZXSjdwTlhLV013U0FZTU82VF9ieXZCb0k2eHQ2WVBxQS1qdFlTT2UxOXVYTjBYcERVMVpxT2lZX0YxTGFoWU5ZNGFvYm50Wmgzd1hhMy00UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fertilizante mineral com aditivo biológico melhora altura, enxofre e fósforo de cultivos - Canal Rural</t>
+          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN da CMOC Chapadão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17/08/2026 13:19</t>
+          <t>17/08/2026 16:11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNbERxcTZvVkVyNlRzZTVpZ0FTWHhRdG5vclBfcExyT25DVHZ0dVB5ekl5Qm9zRklEeVNMSmVCNktlS1puUVFhQWwzc1MtWmVzSGdSa0R0Q1FlMTItcVNNenpVQU5mVldUc2RCUzdjWV9HdGZfTE9TbVJGbVg3em83RTJPZ2dmU2N1enNVSDhna3VpcGVMNHRYN2JaVDcxYTJackthM2paaDVNQXBKN3h3ajdrZkcxRjVvVTZkTTdYYlZKWjBJMDUwVnpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSlNqSXJuUTdPRHk4SkwyaEFyX3QzR0t1WVZWbEEyMVVNODlyZFF2YkQ0SVdCclRMa2pKSTVKSEhnZlp2Q1dJZTJXWi1vWXItVHpic08weGNZVDlheldQY2FTQy01T1FFejYwQWx3NWU0WFhsT2xVWnc3TENRc055TTM4cFpBZnpTOGxpZFZ6d2FzS2lMWDFwV21PMVF1Nlh6SEZMU1hxTktfQTVPZjlz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mosaic lança enzima para acelerar decomposição de palhada - revistacultivar.com.br</t>
+          <t>Fertilizante mineral com aditivo biológico melhora altura, enxofre e fósforo de cultivos - Canal Rural</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17/08/2026 10:52</t>
+          <t>17/08/2026 13:19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZW5EZGduY2xOc2dITGplZlVNUkxmUll0QndXS3NWandoeHdPd3ZHTHJYWjEwM21yQ1BKMmVlRTFPNXduMHdSdDRuLV9yZ1VUZXE5dEVyaUNOMXluOENvSmpoRnQ0R3NrUVZKOWtjeGFsSG1JRGtFc19IRWFJQWF3UkpWRDhvUERRNjJCUENsQjJxaEt6d2ZWVW5wVnZoLUJETDZN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNbERxcTZvVkVyNlRzZTVpZ0FTWHhRdG5vclBfcExyT25DVHZ0dVB5ekl5Qm9zRklEeVNMSmVCNktlS1puUVFhQWwzc1MtWmVzSGdSa0R0Q1FlMTItcVNNenpVQU5mVldUc2RCUzdjWV9HdGZfTE9TbVJGbVg3em83RTJPZ2dmU2N1enNVSDhna3VpcGVMNHRYN2JaVDcxYTJackthM2paaDVNQXBKN3h3ajdrZkcxRjVvVTZkTTdYYlZKWjBJMDUwVnpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -688,61 +688,61 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mosaic Biosciences lança produto para manejo de resíduos agrícolas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic lança enzima para acelerar decomposição de palhada - Revista Cultivar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17/08/2026 10:49</t>
+          <t>17/08/2026 10:52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcm00Mk9UbFFXWjJNNTlSalFtc05zd09MSHpCYmd0Tk5YUTE5cVUxSjFJQkk0NnQ5YmpTZ0Y2a1VCNGc5ODNPZFRBOXk4LTJIVk5fVmg4S293a2daR3AwRC1yYUs0M21zSGpTOWpRaXp4MnVVM2RYY3dNMnlpdThEb3poQXItem9HTWpYRWtjeFlqWmVyOEt3eDkzMzI1NzBBcng3RDVwYVRLMEhnWmNqdHJDdFFVT3RwQk5VUzdLSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZW5EZGduY2xOc2dITGplZlVNUkxmUll0QndXS3NWandoeHdPd3ZHTHJYWjEwM21yQ1BKMmVlRTFPNXduMHdSdDRuLV9yZ1VUZXE5dEVyaUNOMXluOENvSmpoRnQ0R3NrUVZKOWtjeGFsSG1JRGtFc19IRWFJQWF3UkpWRDhvUERRNjJCUENsQjJxaEt6d2ZWVW5wVnZoLUJETDZN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ureia no jardim: prazos, dosagens e restrições químicas de aplicação</t>
+          <t>Mosaic Biosciences lança produto para manejo de resíduos agrícolas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17/08/2026 09:56</t>
+          <t>17/08/2026 10:49</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85827e8a644b0c9a4b1a51db50d93b&amp;url=https%3a%2f%2fport.pravda.ru%2fnews%2fjardim%2f59671-urea-garden-fertilizer%2f&amp;c=9936539315119883676&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcm00Mk9UbFFXWjJNNTlSalFtc05zd09MSHpCYmd0Tk5YUTE5cVUxSjFJQkk0NnQ5YmpTZ0Y2a1VCNGc5ODNPZFRBOXk4LTJIVk5fVmg4S293a2daR3AwRC1yYUs0M21zSGpTOWpRaXp4MnVVM2RYY3dNMnlpdThEb3poQXItem9HTWpYRWtjeFlqWmVyOEt3eDkzMzI1NzBBcng3RDVwYVRLMEhnWmNqdHJDdFFVT3RwQk5VUzdLSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Limestone Coast Premier League (Australia) Previsoes e Estatisticas para Hoje - AFootballReport</t>
+          <t>Ureia no jardim: prazos, dosagens e restrições químicas de aplicação</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17/08/2026 07:00</t>
+          <t>17/08/2026 09:56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb0RlVHJVWll5Z2FyMk1BaV9sdnVRLWJ2amp3Q2hncnZ2SVVDZDc2RmQzUi1GREhuUkZXX1oySS1POUx4NHdhNVoycXpTWWNTWkllbkFmNGlMWjVfR00zTGdYcGtQM296aWV0bU1waFV5V1pOd2l1SGI3SURjV0ZTTlRRVkR6bzd0eFRYZk1BdklHbzdGTFlBVTRkODZjd3AwbjY5Yg?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b128773b4004a88835396cdba35b&amp;url=https%3a%2f%2fport.pravda.ru%2fnews%2fjardim%2f59671-urea-garden-fertilizer%2f&amp;c=9936539315119883676&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -754,39 +754,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Escavação e realocação dos túmulos de mártires na área de Limestone Hill. - Vietnam.vn</t>
+          <t>Limestone Coast Premier League (Australia) Previsoes e Estatisticas para Hoje - afootballreport.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16/08/2026 05:32</t>
+          <t>17/08/2026 07:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUnl6SEFHNVJZM2RTYmdna0R3RXlPcldqaDViaDZnM1BuUnllTFJmNk5EeWlhVHRkcXNTakQzNENQMW1TeVR3N3hIX2prZUxReHlpdjZWUHB5RDlDSXRTQUJQMF9DYjA2NzdVSkMtRVZPZnFKejREV1JiemI4a3F1aGU0Mm1Id2lza2xSa2JLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb0RlVHJVWll5Z2FyMk1BaV9sdnVRLWJ2amp3Q2hncnZ2SVVDZDc2RmQzUi1GREhuUkZXX1oySS1POUx4NHdhNVoycXpTWWNTWkllbkFmNGlMWjVfR00zTGdYcGtQM296aWV0bU1waFV5V1pOd2l1SGI3SURjV0ZTTlRRVkR6bzd0eFRYZk1BdklHbzdGTFlBVTRkODZjd3AwbjY5Yg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caminhão carregado de ureia tomba na BR-277, no sentido Curitiba, e 4 pessoas são socorridas - G1</t>
+          <t>Escavação e realocação dos túmulos de mártires na área de Limestone Hill. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15/08/2026 17:48</t>
+          <t>16/08/2026 05:32</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOeVZKclFKX3lhRzZsc2Rpc0s4OWhMUzBPU2w2ZkdfNkp6Vm1rcF83ZE5PQVp1VzdSekVnT2NGZHhRSDM4NXVZbzRLM2VETVZwQkpBQ2h0NVlhLXBYWGdkQ0taWTkxOHJQTVNWMTI4bkVlVFlOalU3WEtxLTVyaFN0R3hHc2M4OXUyNVViM9IBmwFBVV95cUxNRW9wRmhBWUk5N1FuZGRsZXFESWs0RzJBOGRGUkNydkhnSnBYTlM3VWFMRExVcXB5aXQweUVJTjVlQmMxU1RjV0lULXZTUjduWDF0a3RrdGJzZ0hLUUJobVQ0UFZJSnNwOERGT3I3RkRxanJCOVNTeVl6ZzZnNVNFTktkVHdBMEVEUWJqdWRoRlAzbE5xSGMwSk42Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUnl6SEFHNVJZM2RTYmdna0R3RXlPcldqaDViaDZnM1BuUnllTFJmNk5EeWlhVHRkcXNTakQzNENQMW1TeVR3N3hIX2prZUxReHlpdjZWUHB5RDlDSXRTQUJQMF9DYjA2NzdVSkMtRVZPZnFKejREV1JiemI4a3F1aGU0Mm1Id2lza2xSa2JLZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -798,237 +798,237 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Conflitos mantêm pressão sobre preços de fertilizantes - Agrolink</t>
+          <t>Caminhão carregado de ureia tomba na BR-277, no sentido Curitiba, e 4 pessoas são socorridas - G1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15/08/2026 11:10</t>
+          <t>15/08/2026 17:48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSEJMWHVMdmp5N2hwb2d0cWNHaFNmaGo2Y2g1QjR1SU5Ldk94M09KMFBDRVA3dUJBQXBzSGktYnpuOEoycWJvY2dCd2J1TnFSZ25sR3g2MFMtdUxTdGNIdHV4bm9kRWtmZ0lDV1JBT2VTbkNZYnpHQzEwaldsZTh2N1F1aEFmSmVwMEFMR2FQWFIzaU9rZVRvZk1oY09JSHkzejVUbFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOeVZKclFKX3lhRzZsc2Rpc0s4OWhMUzBPU2w2ZkdfNkp6Vm1rcF83ZE5PQVp1VzdSekVnT2NGZHhRSDM4NXVZbzRLM2VETVZwQkpBQ2h0NVlhLXBYWGdkQ0taWTkxOHJQTVNWMTI4bkVlVFlOalU3WEtxLTVyaFN0R3hHc2M4OXUyNVViM9IBmwFBVV95cUxNRW9wRmhBWUk5N1FuZGRsZXFESWs0RzJBOGRGUkNydkhnSnBYTlM3VWFMRExVcXB5aXQweUVJTjVlQmMxU1RjV0lULXZTUjduWDF0a3RrdGJzZ0hLUUJobVQ0UFZJSnNwOERGT3I3RkRxanJCOVNTeVl6ZzZnNVNFTktkVHdBMEVEUWJqdWRoRlAzbE5xSGMwSk42Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Poder de compra de fertilizantes melhorou em julho, aponta Mosaic - globorural.globo.com</t>
+          <t>Conflitos mantêm pressão sobre preços de fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15/08/2026 07:30</t>
+          <t>15/08/2026 11:10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPSVhGNU5pNGk4cUxzWEdnMGhuYXlPTm9JRldSTWY3U0pRVE4wR2p3LVNnRk9CMWR3elZ5aFZlWTQ2Z0NGVG1BQVFWM3p0OTYyVW15Q3JjMk1qNmFFZzJwSXhsc1BNbW9VVVZjTFZwc2x5WFoxeU1JQm5HM0RyaHMxeEw1Mmo0dHpEd3hoM19zZFpld180V0xqZWNxbU5Uc2dmTDFkb0N4NjE5eW5kWUZmVjZsS25JTmpxU3M2WHp1UWTSAc8BQVVfeXFMUGN0dmJHa3p6c1JaOGF1ZWl2aFJpaXB2Q3B0M0JzckltQTRUS2VFSy1tWHdES2lnN1NGdEJzX0tnblI5LVAyLW9hQno2WVpyQWZHWW1keTAwVFNxR29BN1Zza0NiakZzeXFEbUlSYXBXMTZaVDNEU0Mxd1ZzYjFlODN2VVFpcm5xX3psRWJxX2tGaU9OckFKVlRzMHQySFhTb20wT2pKNjNKZ2F5ZzJmR1NBOGRkWTJ5bDFZckV5SVBXcng3aDFIQ2dLYldGM2xF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSEJMWHVMdmp5N2hwb2d0cWNHaFNmaGo2Y2g1QjR1SU5Ldk94M09KMFBDRVA3dUJBQXBzSGktYnpuOEoycWJvY2dCd2J1TnFSZ25sR3g2MFMtdUxTdGNIdHV4bm9kRWtmZ0lDV1JBT2VTbkNZYnpHQzEwaldsZTh2N1F1aEFmSmVwMEFMR2FQWFIzaU9rZVRvZk1oY09JSHkzejVUbFlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Martin Marietta emite US$ 5,5 bilhões em notas sênior para aquisição da Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Poder de compra de fertilizantes melhorou em julho, aponta Mosaic - Globo Rural</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14/08/2026 22:48</t>
+          <t>15/08/2026 07:30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNckJSejh2UjRiY1lZbkVXMnVmVmpENVdKSjdvN29BZjlGUUd6WnN0dmF3WkJDWXdRVFFHNmxLUHNFMC1wY19xbmR5bERrcEFVZkpUV202MFlXaktfaTh1NUJRSmJTZVdJcW9rLWM1R19SR2ZSYXN0ODc5cEJSWTV5WElXQlV1TU1VVVBLUHdyQnQ5RHdDajNYejlkalFKbTJOSFUyWWQ3djlnVHlQSlRKY0VCRXVJWXk3YmdzbEZNSzlFSTJZLW95WFY3cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPSVhGNU5pNGk4cUxzWEdnMGhuYXlPTm9JRldSTWY3U0pRVE4wR2p3LVNnRk9CMWR3elZ5aFZlWTQ2Z0NGVG1BQVFWM3p0OTYyVW15Q3JjMk1qNmFFZzJwSXhsc1BNbW9VVVZjTFZwc2x5WFoxeU1JQm5HM0RyaHMxeEw1Mmo0dHpEd3hoM19zZFpld180V0xqZWNxbU5Uc2dmTDFkb0N4NjE5eW5kWUZmVjZsS25JTmpxU3M2WHp1UWTSAc8BQVVfeXFMUGN0dmJHa3p6c1JaOGF1ZWl2aFJpaXB2Q3B0M0JzckltQTRUS2VFSy1tWHdES2lnN1NGdEJzX0tnblI5LVAyLW9hQno2WVpyQWZHWW1keTAwVFNxR29BN1Zza0NiakZzeXFEbUlSYXBXMTZaVDNEU0Mxd1ZzYjFlODN2VVFpcm5xX3psRWJxX2tGaU9OckFKVlRzMHQySFhTb20wT2pKNjNKZ2F5ZzJmR1NBOGRkWTJ5bDFZckV5SVBXcng3aDFIQ2dLYldGM2xF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A alta nos custos dos adubos importados que pode pressionar a próxima safra - CompreRural</t>
+          <t>Martin Marietta emite US$ 5,5 bilhões em notas sênior para aquisição da Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14/08/2026 22:32</t>
+          <t>14/08/2026 22:48</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWFFtYkRfbkRrcXpYRnZGRzZOdlJnLWxBbkFwZUhIbm9BYV9lc3NhZTlHS0V2SEJGRFpGT3d6ZDExb2dwMnJsUTJWWFp2TUtfS3p6aXNNcmpZZ2NVaDBJeFZPcXdCclUzRHN1WE0xdHJLSWpGdXBSYl82WXJUQzEtc09zMjdHb1N6TXJ3WWZsUnQ3UUJDa012eE1sNG9qRzVDaG1xUk9nbXN4ZEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNckJSejh2UjRiY1lZbkVXMnVmVmpENVdKSjdvN29BZjlGUUd6WnN0dmF3WkJDWXdRVFFHNmxLUHNFMC1wY19xbmR5bERrcEFVZkpUV202MFlXaktfaTh1NUJRSmJTZVdJcW9rLWM1R19SR2ZSYXN0ODc5cEJSWTV5WElXQlV1TU1VVVBLUHdyQnQ5RHdDajNYejlkalFKbTJOSFUyWWQ3djlnVHlQSlRKY0VCRXVJWXk3YmdzbEZNSzlFSTJZLW95WFY3cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Com custo de produção em alta, mato-grossenses lançam mão do uso de calcário - MT Econômico</t>
+          <t>A alta nos custos dos adubos importados que pode pressionar a próxima safra - CompreRural</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14/08/2026 10:54</t>
+          <t>14/08/2026 22:32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOeGNDTzBqejdEVW5CdFpuUlVYV1ZrWnFocldwa1BkdjlneXQxdlhOZkxhcDdFLW5JQ3c1VHh4NUVVdDltcktIeWxUaFlRNFRFWnQ4RWl2MFo5NFhwMXZpS3RoY0xQaEVDRGdsYWxOdG1STERia3VGX2R3dHhzVmFTQTNJcS1wZUZhNldSTjhka05ZdkhPY3lYWjdCNmpiQTltaVlWbjY0aV81dW5iNlN6djJrem5BeE1mUXBRcnRvUk5TZWprTnpmMVNVa2RycTRl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWFFtYkRfbkRrcXpYRnZGRzZOdlJnLWxBbkFwZUhIbm9BYV9lc3NhZTlHS0V2SEJGRFpGT3d6ZDExb2dwMnJsUTJWWFp2TUtfS3p6aXNNcmpZZ2NVaDBJeFZPcXdCclUzRHN1WE0xdHJLSWpGdXBSYl82WXJUQzEtc09zMjdHb1N6TXJ3WWZsUnQ3UUJDa012eE1sNG9qRzVDaG1xUk9nbXN4ZEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Índice de Poder de Compra de Fertilizantes encerra julho em queda de 5% - Notícias Agrícolas</t>
+          <t>Com custo de produção em alta, mato-grossenses lançam mão do uso de calcário - MT Econômico</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14/08/2026 09:57</t>
+          <t>14/08/2026 10:54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNRjVDejlibkhQc0tXRUREaXRlTnk3R3pvd0lhN04tOE0yTGNHd1FpSVZwQXFpUTFsUm91NUg2OFdYLXRxN0pBTWhFelFNRjd1eE5IbktUSkFFcDJqckg2US12ME0zT2Q5M2hpX1M1VExQelRiQXFBelJINzRxWnNpSWRGaVBkMWdzV0o5Y2NPTU85VUdjaFpqYkhXODNhR3FsZ1Q5MThnajA1RHdkZGZyWkRmWHZLdGdBZS05YXRaUG5hSnhEUHdfb3o0bmNEYzFjWkhFSE10VdIB3AFBVV95cUxPNTNzZTNTT3oycERERzJvQkVON19iV2lxTVd6d0xrQWxQTHpVX2tHV1JkZDVpZW1POGVPd2VKa3p6ZU9MV1NoaWI4U3dxbjFjdGcxZ1haenRsR2RnUGF3NmEyYWZBbW1seVRfaE45TGJHdmQwMHZ2RUgwX1pBUHExdjNKekVhdWJ2cDhLT3RQZUlVRzZuZ2tmc08yWEhfektNc0FscGNhSkR4Q0JScmdjVEcyaWNXcFIyYk9kcXE3T3ZXQTdUMU1GaXQ4R3p0TGs3c00zUUQxSXRlNkdE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOeGNDTzBqejdEVW5CdFpuUlVYV1ZrWnFocldwa1BkdjlneXQxdlhOZkxhcDdFLW5JQ3c1VHh4NUVVdDltcktIeWxUaFlRNFRFWnQ4RWl2MFo5NFhwMXZpS3RoY0xQaEVDRGdsYWxOdG1STERia3VGX2R3dHhzVmFTQTNJcS1wZUZhNldSTjhka05ZdkhPY3lYWjdCNmpiQTltaVlWbjY0aV81dW5iNlN6djJrem5BeE1mUXBRcnRvUk5TZWprTnpmMVNVa2RycTRl?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Compra de ureia pelo Brasil volta a subir forte em julho - Farmnews</t>
+          <t>Índice de Poder de Compra de Fertilizantes encerra julho em queda de 5% - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14/08/2026 08:24</t>
+          <t>14/08/2026 09:57</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUjBFMHFVU3dlWTRSeFJqcGd2dGxJbURMWXhfU0I4S1AxOUlobVdJb1JIYThheXlkVS1qbE9QSnVhS0Q5VHNXRXc2OXNveUl4dTdhS3NmMnlzT3BzRE1PdXJOenBMOHFXQjRNa2dNRFRMc3c4T3FoLUhlNnROVkhzRGRjNGVUeDdSM3paaURYNDhnOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNRjVDejlibkhQc0tXRUREaXRlTnk3R3pvd0lhN04tOE0yTGNHd1FpSVZwQXFpUTFsUm91NUg2OFdYLXRxN0pBTWhFelFNRjd1eE5IbktUSkFFcDJqckg2US12ME0zT2Q5M2hpX1M1VExQelRiQXFBelJINzRxWnNpSWRGaVBkMWdzV0o5Y2NPTU85VUdjaFpqYkhXODNhR3FsZ1Q5MThnajA1RHdkZGZyWkRmWHZLdGdBZS05YXRaUG5hSnhEUHdfb3o0bmNEYzFjWkhFSE10VdIB3AFBVV95cUxPNTNzZTNTT3oycERERzJvQkVON19iV2lxTVd6d0xrQWxQTHpVX2tHV1JkZDVpZW1POGVPd2VKa3p6ZU9MV1NoaWI4U3dxbjFjdGcxZ1haenRsR2RnUGF3NmEyYWZBbW1seVRfaE45TGJHdmQwMHZ2RUgwX1pBUHExdjNKekVhdWJ2cDhLT3RQZUlVRzZuZ2tmc08yWEhfektNc0FscGNhSkR4Q0JScmdjVEcyaWNXcFIyYk9kcXE3T3ZXQTdUMU1GaXQ4R3p0TGs3c00zUUQxSXRlNkdE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shuumatsu no Harem tem primeiro vídeo promocional revelado - Anime United</t>
+          <t>Compra de ureia pelo Brasil volta a subir forte em julho - farmnews.com.br</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14/08/2026 03:37</t>
+          <t>14/08/2026 08:24</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOXV0NkhyWmNFSlY3TEg4UlNFTmFWRFkzb0RNZkx6UkY2UklFM09oVjdGZmlyem1uSmlfRUF0WkpnRWJKczh1S1pkUWlMWEtSMEs1RFBlb01LWFVMOENDSFZWZ2Y2UzY0VncxZUlRNWZxQkxRYkh3TzFsSTJjUUx3RVI1andIUi1POFNKNHEtWk5NQlpkNG5wclVhUzJybjNvTndOd0pTWUlYc3dsRnZGYW4xdG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUjBFMHFVU3dlWTRSeFJqcGd2dGxJbURMWXhfU0I4S1AxOUlobVdJb1JIYThheXlkVS1qbE9QSnVhS0Q5VHNXRXc2OXNveUl4dTdhS3NmMnlzT3BzRE1PdXJOenBMOHFXQjRNa2dNRFRMc3c4T3FoLUhlNnROVkhzRGRjNGVUeDdSM3paaURYNDhnOUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes | Parceria com Casa dos Ventos - Energia Eólica - Brasil Mineral</t>
+          <t>Shuumatsu no Harem tem primeiro vídeo promocional revelado - Anime United</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14/08/2026 01:26</t>
+          <t>14/08/2026 03:37</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUlhuTXNnNW1pcERBMlB3YkhTOGo4cUVIdzRGb1l3YzVFLUtTckpYZnkxcGxUeUhWLTM4eG1PeFNPdjduaVd3ZkJNZ25YMXhRN1Fxb2gwdDBYaEt4UXlJaXF2OUttWktBanRfS2JHVlVqRHJ3T1dyY0t2WEo0Yl9hQU9tSUVJWlN3RXNvTHBGUGpEVUFGblJRQ3Q3OHBVVVR3YXp3OENCOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOXV0NkhyWmNFSlY3TEg4UlNFTmFWRFkzb0RNZkx6UkY2UklFM09oVjdGZmlyem1uSmlfRUF0WkpnRWJKczh1S1pkUWlMWEtSMEs1RFBlb01LWFVMOENDSFZWZ2Y2UzY0VncxZUlRNWZxQkxRYkh3TzFsSTJjUUx3RVI1andIUi1POFNKNHEtWk5NQlpkNG5wclVhUzJybjNvTndOd0pTWUlYc3dsRnZGYW4xdG4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Importações brasileiras de fertilizantes de julho atingem 2,99 Milhões de toneladas com alta de 31,3% em comparação a junho - GlobalFert</t>
+          <t>Mosaic Fertilizantes | Parceria com Casa dos Ventos - Energia Eólica - Brasil Mineral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13/08/2026 18:54</t>
+          <t>14/08/2026 01:26</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxObzVNMnZtZGV1X3dYWmZxYWduT3JGQ1pnQmFiZVkyZWZHYWEzN054WnhHMVpBNjJQal9qYmJWczRmZXVWNzkxMlpIX3BDTlZDYmNwbXBaNlN1bURneEN6VXJfSUdsdG1kQlBvdlg1N2JRa3hVbFl6Z3pQWFFPMUs4ak9penMwV1o4bGlpSWs0d1BxTWk3cVlsWjZYMU02WndPWjVuZUdOMEY5SDlvRUo5ZEpOSm5aVU9UQnRFZkUyY1dNQy02UENWcGphUTRYaG5aUGFaNmJ1ZTM3TWIxakdmaWxkUkhHNFh0SlFKWEJicXppSUk5ZnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUlhuTXNnNW1pcERBMlB3YkhTOGo4cUVIdzRGb1l3YzVFLUtTckpYZnkxcGxUeUhWLTM4eG1PeFNPdjduaVd3ZkJNZ25YMXhRN1Fxb2gwdDBYaEt4UXlJaXF2OUttWktBanRfS2JHVlVqRHJ3T1dyY0t2WEo0Yl9hQU9tSUVJWlN3RXNvTHBGUGpEVUFGblJRQ3Q3OHBVVVR3YXp3OENCOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tudo sobre: calcário marinho - Portal Piauí Hoje</t>
+          <t>Importações brasileiras de fertilizantes de julho atingem 2,99 Milhões de toneladas com alta de 31,3% em comparação a junho - GlobalFert</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13/08/2026 15:26</t>
+          <t>13/08/2026 18:54</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBodHpUYk5CalBVRkI1XzJOV0pYRS1XN0pLT0xfbEJBV2dmM1FTWG9jODhQanpvWlRzSkxEX1hmZ2pEQ1RpN3Z3a2xLclZmclZELVdPeUhlZFMzMnIxQVRBOTdhcENHLXl1WlMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxObzVNMnZtZGV1X3dYWmZxYWduT3JGQ1pnQmFiZVkyZWZHYWEzN054WnhHMVpBNjJQal9qYmJWczRmZXVWNzkxMlpIX3BDTlZDYmNwbXBaNlN1bURneEN6VXJfSUdsdG1kQlBvdlg1N2JRa3hVbFl6Z3pQWFFPMUs4ak9penMwV1o4bGlpSWs0d1BxTWk3cVlsWjZYMU02WndPWjVuZUdOMEY5SDlvRUo5ZEpOSm5aVU9UQnRFZkUyY1dNQy02UENWcGphUTRYaG5aUGFaNmJ1ZTM3TWIxakdmaWxkUkhHNFh0SlFKWEJicXppSUk5ZnB3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Projeto prevê geração de empregos com exploração de calcário marinho no litoral do Piauí - Portal Piauí Hoje</t>
+          <t>Tudo sobre: calcário marinho - Portal Piauí Hoje</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13/08/2026 13:34</t>
+          <t>13/08/2026 15:26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOSjRKdkN6N1RzVXhKZTVQWjJCVDJqVGFjWlAyQ280LVZoQ0V5a3JaYkNyMnUxYTJTeDBHOUt6b3pYTEIzdWNYNGVJMlFPdzRKam1QVHVlQ2FoZzZHOHNxc1ZTdjVvSzNyZnpNMWdCZ2VHbFhtWjVrNXpuT0tsU0l1OWJveGlHZ0hRSmhGVmZCVm9tTkZ0MTVJY1pxejRsR1pORC1DVVBXQVlnc1pDNEJfZ3JzcmZ1MlRyTktIWmVrNTdQUUg1MlRwVEpQVmVMaHR2cXBNTHRLd9IB3AFBVV95cUxNblAxNVk1MTBkTXEtWmxLSExrSk1kVDZfSGhBRXBOVTFTdW1meUk0VzBvWTd1YUFTODE0djNIVmZCSlg1M3ozSVFKbTZlTlV5NWlqTERSNU5RQ19QQUt4eXNUWHl0MWhSSkVFbVU1SU1xam91YjB1WHdBSkdXekhqeExUX1JLSE5ub1luLWZaa0d0aHNSamk5QS1NZHhHYklMQzROV1FXUFBfcVZIeTVORG81MHR5WDVCUWticW1nRExoS2dvcnBucUhmUDhMWnJhaUtnYnV0alJsZV9W?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBodHpUYk5CalBVRkI1XzJOV0pYRS1XN0pLT0xfbEJBV2dmM1FTWG9jODhQanpvWlRzSkxEX1hmZ2pEQ1RpN3Z3a2xLclZmclZELVdPeUhlZFMzMnIxQVRBOTdhcENHLXl1WlMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aos 64 anos, veterano transformou 113 toneladas de cimento e blocos de calcário em uma casa de 11 cômodos rodeada por 150 esculturas no Kansas - Brasil 247</t>
+          <t>Projeto prevê geração de empregos com exploração de calcário marinho no litoral do Piauí - Portal Piauí Hoje</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13/08/2026 12:15</t>
+          <t>13/08/2026 13:34</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNUGo3a3BhR1hDTXNpSTcyNlhhVGRUajNMUDdqU1BmU2NZR3NqdFEwYXowSXVudDVyOUt6TWoxMFVKNHpaYVdkRjRvYmxDdHVCeXNsS3ROb216eDZuNUVlX1JKNUszMDhtSTNlMGJpdEExRGsyZUFfZUItTmZBdms2OFdjQ2hqMzV2ZjVtTTlBYVJUOVVsOWRLLVVjdHM5ZVI3eVkzYU9iS0s0Y0loNzZHMm56aHY2eVNxZE11ZVBiak51aWlRcmtDYl9RRzQtel9MRXhrTFgyVDhTZVJySXdIZ0o0MU1udlZsNDF4Sk83NngzZVplU01pT1ZpR0RFQ2JqY0t2YmVSM283bkp6WnhtWkNJY0J4eTNTeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOSjRKdkN6N1RzVXhKZTVQWjJCVDJqVGFjWlAyQ280LVZoQ0V5a3JaYkNyMnUxYTJTeDBHOUt6b3pYTEIzdWNYNGVJMlFPdzRKam1QVHVlQ2FoZzZHOHNxc1ZTdjVvSzNyZnpNMWdCZ2VHbFhtWjVrNXpuT0tsU0l1OWJveGlHZ0hRSmhGVmZCVm9tTkZ0MTVJY1pxejRsR1pORC1DVVBXQVlnc1pDNEJfZ3JzcmZ1MlRyTktIWmVrNTdQUUg1MlRwVEpQVmVMaHR2cXBNTHRLd9IB3AFBVV95cUxNblAxNVk1MTBkTXEtWmxLSExrSk1kVDZfSGhBRXBOVTFTdW1meUk0VzBvWTd1YUFTODE0djNIVmZCSlg1M3ozSVFKbTZlTlV5NWlqTERSNU5RQ19QQUt4eXNUWHl0MWhSSkVFbVU1SU1xam91YjB1WHdBSkdXekhqeExUX1JLSE5ub1luLWZaa0d0aHNSamk5QS1NZHhHYklMQzROV1FXUFBfcVZIeTVORG81MHR5WDVCUWticW1nRExoS2dvcnBucUhmUDhMWnJhaUtnYnV0alJsZV9W?oc=5</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Como o calcário virou escudo contra a alta dos fertilizantes em MT - Cliquef5</t>
+          <t>Aos 64 anos, veterano transformou 113 toneladas de cimento e blocos de calcário em uma casa de 11 cômodos rodeada por 150 esculturas no Kansas - Brasil 247</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13/08/2026 10:30</t>
+          <t>13/08/2026 12:15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdVhJZ1c0UmtPcUJaZnBwTGVVYkViMFNjZXVWaGN3cGhzV2pGZFlvQnJTRjdQenUtN3g1QVVfNWVsTEQ3a0gydi1oRzdYaEFQS1BxbXRJQTljQWo2bXh3VDU5NDNHN19BTEVTekxZdTdEd1g5TU1YOGlPbEVldG1mTTN1NFZ5eVpIaWluUGdDQlBUOXRNc1gzenIxYVJxRWRMXzNremlPS3dFaG5MQXVTMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNUGo3a3BhR1hDTXNpSTcyNlhhVGRUajNMUDdqU1BmU2NZR3NqdFEwYXowSXVudDVyOUt6TWoxMFVKNHpaYVdkRjRvYmxDdHVCeXNsS3ROb216eDZuNUVlX1JKNUszMDhtSTNlMGJpdEExRGsyZUFfZUItTmZBdms2OFdjQ2hqMzV2ZjVtTTlBYVJUOVVsOWRLLVVjdHM5ZVI3eVkzYU9iS0s0Y0loNzZHMm56aHY2eVNxZE11ZVBiak51aWlRcmtDYl9RRzQtel9MRXhrTFgyVDhTZVJySXdIZ0o0MU1udlZsNDF4Sk83NngzZVplU01pT1ZpR0RFQ2JqY0t2YmVSM283bkp6WnhtWkNJY0J4eTNTeXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1106,237 +1106,237 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coronel Pacheco entrega calcário a produtores rurais do município - Jornal Panorama Minas</t>
+          <t>Como o calcário virou escudo contra a alta dos fertilizantes em MT - Cliquef5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12/08/2026 14:28</t>
+          <t>13/08/2026 10:30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUnVEMl9ZZTM3RXg0LV9qSlNRYUJWVUpONWlfNzlFV2d3aWZrTFlHclVaaU5hWU1PaS1DRFFJVndlMFZIcFplMEQzcUVpZW5xWXVTU0VjTlJRUHJIOXM2dHlmT3pYQTFhWDI5NXNidTM1VHhtWkpvcjZWTU4yTk1qWFlrUlpNZl9SWXRCdHBOejl3ZGF0QkNSdkJGSlJwWHVpRER3MGVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdVhJZ1c0UmtPcUJaZnBwTGVVYkViMFNjZXVWaGN3cGhzV2pGZFlvQnJTRjdQenUtN3g1QVVfNWVsTEQ3a0gydi1oRzdYaEFQS1BxbXRJQTljQWo2bXh3VDU5NDNHN19BTEVTekxZdTdEd1g5TU1YOGlPbEVldG1mTTN1NFZ5eVpIaWluUGdDQlBUOXRNc1gzenIxYVJxRWRMXzNremlPS3dFaG5MQXVTMQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Entregas de gasóleo com baixo teor de enxofre para agosto caem no vencimento, segundo dados da ICE - tradingview.com</t>
+          <t>Coronel Pacheco entrega calcário a produtores rurais do município - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12/08/2026 13:47</t>
+          <t>12/08/2026 14:28</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9hZF83YUxjdXo4SjBJSlBmbF9CNXYxSFE4aHl5bmtHRldRbnFrMDFIN2JaVkJlQWdSUTVKc09YZnNVLVc2bV9pdVQzTTBNa2laVW03RTMwWW5SQTVvV2tQajExN3d1M2dNWXVhZWJ6VXhONm5kbV9SVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUnVEMl9ZZTM3RXg0LV9qSlNRYUJWVUpONWlfNzlFV2d3aWZrTFlHclVaaU5hWU1PaS1DRFFJVndlMFZIcFplMEQzcUVpZW5xWXVTU0VjTlJRUHJIOXM2dHlmT3pYQTFhWDI5NXNidTM1VHhtWkpvcjZWTU4yTk1qWFlrUlpNZl9SWXRCdHBOejl3ZGF0QkNSdkJGSlJwWHVpRER3MGVn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Perícia confirma presença de veneno agrícola em garrafada que causou morte no Sertão - O Alagoano</t>
+          <t>Entregas de gasóleo com baixo teor de enxofre para agosto caem no vencimento, segundo dados da ICE - TradingView</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12/08/2026 10:08</t>
+          <t>12/08/2026 13:47</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxObjRDcUVsdWFpSi1wVjZobHI4V3hXRUk3VGs0WWVyYVNjVzlOaUJCd0g1UTFub1AtTUJ3clZKRmxfLTlRUnFWOVlIY2o5V25vV2FVYnFsZkFEVGVsUmNFdGdqTEhHUlUtSXdsQlZfSlF0YXZ3TVFsaEVKcDRPVzNzU0NGZkg3QVo3dmQ1NldnVG1mdXpqX21tTzNmT0RCRk5Nd2NMUEQzUnpxRHF6alhZUjV1aXkxaHhXMzNWQktIdE8wWk9DRlhjb1lMYXhtN0JS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9hZF83YUxjdXo4SjBJSlBmbF9CNXYxSFE4aHl5bmtHRldRbnFrMDFIN2JaVkJlQWdSUTVKc09YZnNVLVc2bV9pdVQzTTBNa2laVW03RTMwWW5SQTVvV2tQajExN3d1M2dNWXVhZWJ6VXhONm5kbV9SVA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros elevam custo da safra e fazem calcário ganhar importância em MT</t>
+          <t>Perícia confirma presença de veneno agrícola em garrafada que causou morte no Sertão - O Alagoano</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12/08/2026 07:40</t>
+          <t>12/08/2026 10:08</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fwww.olhardireto.com.br%2fagro-e-negocios%2fnoticias%2ffertilizantes-mais-caros-elevam-custo-da-safra-e-fazem-calcario-ganhar-importancia-em-mt&amp;c=7347040783018588872&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxObjRDcUVsdWFpSi1wVjZobHI4V3hXRUk3VGs0WWVyYVNjVzlOaUJCd0g1UTFub1AtTUJ3clZKRmxfLTlRUnFWOVlIY2o5V25vV2FVYnFsZkFEVGVsUmNFdGdqTEhHUlUtSXdsQlZfSlF0YXZ3TVFsaEVKcDRPVzNzU0NGZkg3QVo3dmQ1NldnVG1mdXpqX21tTzNmT0RCRk5Nd2NMUEQzUnpxRHF6alhZUjV1aXkxaHhXMzNWQktIdE8wWk9DRlhjb1lMYXhtN0JS?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Saiba quem é o empresário alvo da PF por esquema de extração de calcário em MT - O Mato Grosso</t>
+          <t>Fertilizantes mais caros elevam custo da safra e fazem calcário ganhar importância em MT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11/08/2026 23:00</t>
+          <t>12/08/2026 07:40</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUmp3SF9jOFNfMng3cDk3OVhqRDZxeU01WkpveUo5d3MwaC1WZGl4dVlUVUF5N3FyRXdEb2JLUC1QQVhfeUx2ZXRBbU9TeFNiN3VKUF92Q2RabUxodXZMU3RRSUs0RUJOdl95U29qUWN6SEk1Q1k5WlJycXROcnZXbDcwOTNCM2RQZndYUmgtamYzUHVDVjI2TmFLaUtEOUF5LWxwY1hn?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fwww.olhardireto.com.br%2fagro-e-negocios%2fnoticias%2ffertilizantes-mais-caros-elevam-custo-da-safra-e-fazem-calcario-ganhar-importancia-em-mt&amp;c=7347040783018588872&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Informações Relevantes CMOC Group Ltd (PK) (CMCLF) - ADVFN</t>
+          <t>Saiba quem é o empresário alvo da PF por esquema de extração de calcário em MT - O Mato Grosso</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11/08/2026 14:46</t>
+          <t>11/08/2026 23:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1oNGpwREx2MEtWa2tLaWhnT0RaWDFmSTRvMjZxb2ZGaHRGOV9RRnlJbThBME94djJjaXNaYklEZDg1NmgwLUd4VkM4NWh0OVJCblFpbng3WTZHeWVCY3FXY3pUYThOUUpO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUmp3SF9jOFNfMng3cDk3OVhqRDZxeU01WkpveUo5d3MwaC1WZGl4dVlUVUF5N3FyRXdEb2JLUC1QQVhfeUx2ZXRBbU9TeFNiN3VKUF92Q2RabUxodXZMU3RRSUs0RUJOdl95U29qUWN6SEk1Q1k5WlJycXROcnZXbDcwOTNCM2RQZndYUmgtamYzUHVDVjI2TmFLaUtEOUF5LWxwY1hn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Desabamento em mineradora deixa um morto e três feridos em Arcos (MG) - R7</t>
+          <t>Informações Relevantes CMOC Group Ltd (PK) (CMCLF) - ADVFN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10/08/2026 18:33</t>
+          <t>11/08/2026 14:46</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQcnpzVWxxUEJDbVpyX3BaZHNoa2E3NjU1YmhwWll2Mmt6NWhrU1RtOGFJX0ZsMGIydGdtREtSVWNkZVpWQTNlOHpJbEplQnY0aldfS19TR0ZvRVpZRnBfYWpXOU1GSDJWLVlsanVEZ2VUWFJITUM1T1RCNjdSdlQ1SVVuT0FWMUlSSjl1cUd5ZzgtYTNRZ2UxSEdQMVMxRGlqQ1dTbkFrUFlzQlc0cHNPNGMzNG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1oNGpwREx2MEtWa2tLaWhnT0RaWDFmSTRvMjZxb2ZGaHRGOV9RRnlJbThBME94djJjaXNaYklEZDg1NmgwLUd4VkM4NWh0OVJCblFpbng3WTZHeWVCY3FXY3pUYThOUUpO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gallery of Revestimiento porcelánico estilo piedra - Limestone - 3 - ArchDaily</t>
+          <t>Desabamento em mineradora deixa um morto e três feridos em Arcos (MG) - R7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10/08/2026 15:31</t>
+          <t>10/08/2026 18:33</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTC1LN0RJMllDNUJ1SmROMUlDMHVDckMzUG9KejVOR3g4YnVZN19hX1MtdzFKQl8tY1FWNHdPbTVwZWMzeWxZeTRUSUNTYzVSYzI2UWlpQy1MSzA3blhRZWdwcEZjRTlndV9va0U1dmxqLXRCZUdJV1FQRzEtdGNGelROa0ljbjJZV3VKNTdOTElsZ1l0QXB6MWkyOUxNLVZmcllTM2Z0UTVGTnpjSElsRW0tN0ZVLXhRTVFPNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQcnpzVWxxUEJDbVpyX3BaZHNoa2E3NjU1YmhwWll2Mmt6NWhrU1RtOGFJX0ZsMGIydGdtREtSVWNkZVpWQTNlOHpJbEplQnY0aldfS19TR0ZvRVpZRnBfYWpXOU1GSDJWLVlsanVEZ2VUWFJITUM1T1RCNjdSdlQ1SVVuT0FWMUlSSjl1cUd5ZzgtYTNRZ2UxSEdQMVMxRGlqQ1dTbkFrUFlzQlc0cHNPNGMzNG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alckmin: MS terá maior fábrica de ureia da América Latina - Campo Grande News</t>
+          <t>Gallery of Revestimiento porcelánico estilo piedra - Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10/08/2026 11:12</t>
+          <t>10/08/2026 15:31</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQTXhMNmVvcHhfN2g1UVoyOWhTR19CM19XWWhRdC1HMS1ubEJFeDA1dHUtbUNVbXBwZUVQMjJFY2tLaDNuTFZKYmhrMDlldTc0aXBlc2tmUWhvQkFfTUFWenVUMFNBSWVzbXdPR2NmYmJJNk9qbXlyU1NTbzZyZlhFekxBWV9JRVVKQUJBVVpKdnl3bUlJTGJzOW01SG9sNFRtbFVlT3UyQjdnV19HLS1MaGJDVjJYVF9NdjZfeDZR0gG-AUFVX3lxTE5ZeEt2WnBHck1DWEgzeGpFcGtNOHUyZENzQTF6RG14dkoteWtURVFsVHRhRHBmTnIxSnJ4dVRtQlBtWnBtdElrQnJEbVB1cUhQcHljWTFPa0k4d1lqSDlKc0tnYWZDREtQSHBEQV9SMk9MLVZ0aUM2dzR1RVFwWjJ4LU95RXhwaVNrUTVEWnhYcHIwV0lpbURQcjNSU3p3cjRqRFFrX3FjSjNYaWpqWUk5ajJISHlwRkNpT0dJd1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTC1LN0RJMllDNUJ1SmROMUlDMHVDckMzUG9KejVOR3g4YnVZN19hX1MtdzFKQl8tY1FWNHdPbTVwZWMzeWxZeTRUSUNTYzVSYzI2UWlpQy1MSzA3blhRZWdwcEZjRTlndV9va0U1dmxqLXRCZUdJV1FQRzEtdGNGelROa0ljbjJZV3VKNTdOTElsZ1l0QXB6MWkyOUxNLVZmcllTM2Z0UTVGTnpjSElsRW0tN0ZVLXhRTVFPNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Martin Marietta obtém aprovações regulatórias para aquisição da Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Alckmin: MS terá maior fábrica de ureia da América Latina - Campo Grande News</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10/08/2026 10:21</t>
+          <t>10/08/2026 11:12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOGdkZFpnZUhBYlp2b3hCVldUTlFNd2dRNVdEVElDcFFpVmlLQTczN3FNOThLTG9qQ1RyZkxxdk5hcEotemxsSVhUYXFaQzhIU2p0c0tZVzVkZWZZRGxCd2w1YjJEdHJNYjg2djNlUDZhQ0J6cENqaUFOdFcybnpQdzZYSmJ0NnJQUnk3ZUo3bTBfaUctYVBNazV4TXdMWnZxRjZRbnc1S0QzamJVd3d0RzVwTjVfajkyaDR3S0lHSktGRnhTeFp5RmkxbTVkN0pEZ2d4ZGh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQTXhMNmVvcHhfN2g1UVoyOWhTR19CM19XWWhRdC1HMS1ubEJFeDA1dHUtbUNVbXBwZUVQMjJFY2tLaDNuTFZKYmhrMDlldTc0aXBlc2tmUWhvQkFfTUFWenVUMFNBSWVzbXdPR2NmYmJJNk9qbXlyU1NTbzZyZlhFekxBWV9JRVVKQUJBVVpKdnl3bUlJTGJzOW01SG9sNFRtbFVlT3UyQjdnV19HLS1MaGJDVjJYVF9NdjZfeDZR0gG-AUFVX3lxTE5ZeEt2WnBHck1DWEgzeGpFcGtNOHUyZENzQTF6RG14dkoteWtURVFsVHRhRHBmTnIxSnJ4dVRtQlBtWnBtdElrQnJEbVB1cUhQcHljWTFPa0k4d1lqSDlKc0tnYWZDREtQSHBEQV9SMk9MLVZ0aUM2dzR1RVFwWjJ4LU95RXhwaVNrUTVEWnhYcHIwV0lpbURQcjNSU3p3cjRqRFFrX3FjSjNYaWpqWUk5ajJISHlwRkNpT0dJd1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão</t>
+          <t>Martin Marietta obtém aprovações regulatórias para aquisição da Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10/08/2026 04:31</t>
+          <t>10/08/2026 10:21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85827eb4654807b44e6d99538c89b4&amp;url=https%3a%2f%2fgloborural.globo.com%2fnegocios%2fnoticia%2f2026%2f08%2fmosaic-anuncia-compra-de-titulos-de-divida-de-cerca-de-us-14-bilhao.ghtml&amp;c=5616585260663838501&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOGdkZFpnZUhBYlp2b3hCVldUTlFNd2dRNVdEVElDcFFpVmlLQTczN3FNOThLTG9qQ1RyZkxxdk5hcEotemxsSVhUYXFaQzhIU2p0c0tZVzVkZWZZRGxCd2w1YjJEdHJNYjg2djNlUDZhQ0J6cENqaUFOdFcybnpQdzZYSmJ0NnJQUnk3ZUo3bTBfaUctYVBNazV4TXdMWnZxRjZRbnc1S0QzamJVd3d0RzVwTjVfajkyaDR3S0lHSktGRnhTeFp5RmkxbTVkN0pEZ2d4ZGh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1348,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão - globorural.globo.com</t>
+          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10/08/2026 04:00</t>
+          <t>10/08/2026 04:31</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbnVJOHhFUU94Ynd4U0VNd0xCZFNPVGJzWXFoWHMzeEJ6aU5WR0ViODIzQ3ZfaFJGVjlNa0JmcmdyMmMwOGlCQzd1aUI2MDBWbHhFVkhIZGNia0hKM2V4MnhMZ3JWaU8tdDNiTnhpY2RuS05rWktNR0Y4MlB3dWVBRndtOHBReElOM3pQSXYyN3Bua2NueDRhb3U1VTJhWGxmcmI5ejYtbzRVZnBkUWJTYzY2X2NCazJKZUU3Z2RiSVdUNUUzd3fSAdQBQVVfeXFMTkU4WWt6ZDVtWDRDUTJ6c3BYLW9ZckRuWE95SlRocE1RaFF1dnRlTzFmRnpWcmVrZXNQRDlNTmN0dHMzeTd1Rnc4MmplbG1LTHgxWmc5eV93cm5DaEhfc3NtRWs1TEFLdDdsVnVWLWVwN2hsU1E1R0MwdHBvMGxEMF9mWFY2dGRwQ1N6ajQ5UkJ3QVdnVWU5dTB5Zmc1cU5OM0JsUngxOFJrbGNyTnNJaUx2MEtxMmpFRi16cC1aUjFjeHlscUNoemN0dW5LNHg2Z1RCR0o?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b127b0c647e1b7ca2ed025c4fe7c&amp;url=https%3a%2f%2fgloborural.globo.com%2fnegocios%2fnoticia%2f2026%2f08%2fmosaic-anuncia-compra-de-titulos-de-divida-de-cerca-de-us-14-bilhao.ghtml&amp;c=5616585260663838501&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1409,22 +1409,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aos 64 anos, veterano usou 113 toneladas de cimento, empilhou blocos de calcário como se fossem toras e ergueu no próprio quintal, em Lucas, no Kansas, uma cabana de 11 cômodos cercada por 150 esculturas de concreto - CPG Click Petróleo e Gás</t>
+          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão - Globo Rural</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>09/08/2026 17:18</t>
+          <t>10/08/2026 04:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNSS01SVVhYy1zOHRObE1Vc2hZdlNTOXhDTzZoYnByZmFVN0pPV3BjUXNMYUFINmlfcllfN0s3M29nSGZVNlllZ012Y2NBemE1OHRoR19jbGdQVkZDX0lpNEVESVRtRHVQZlZfTE1SbFN3c25CZmtJd2h3RHFZRzBOU0pVM0dpUnhWVmZGUVltcVhwejJtaENWaGNHdmQyR1lPeEZYRmFveUJuVVZMRXp3azdoYVQ5MDg4dTN5cEgzb1JZdGhMcm8zN3k0ZkFfb29OeDNrZW43bEtBV0V0UEJWTlFCYWlRa3BSeThDSGhVdUdTZUloTlhXTktLdmZTVmVpejhZc1pHUkg5QXZ0U21xRnpLcXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbnVJOHhFUU94Ynd4U0VNd0xCZFNPVGJzWXFoWHMzeEJ6aU5WR0ViODIzQ3ZfaFJGVjlNa0JmcmdyMmMwOGlCQzd1aUI2MDBWbHhFVkhIZGNia0hKM2V4MnhMZ3JWaU8tdDNiTnhpY2RuS05rWktNR0Y4MlB3dWVBRndtOHBReElOM3pQSXYyN3Bua2NueDRhb3U1VTJhWGxmcmI5ejYtbzRVZnBkUWJTYzY2X2NCazJKZUU3Z2RiSVdUNUUzd3fSAdQBQVVfeXFMTkU4WWt6ZDVtWDRDUTJ6c3BYLW9ZckRuWE95SlRocE1RaFF1dnRlTzFmRnpWcmVrZXNQRDlNTmN0dHMzeTd1Rnc4MmplbG1LTHgxWmc5eV93cm5DaEhfc3NtRWs1TEFLdDdsVnVWLWVwN2hsU1E1R0MwdHBvMGxEMF9mWFY2dGRwQ1N6ajQ5UkJ3QVdnVWU5dTB5Zmc1cU5OM0JsUngxOFJrbGNyTnNJaUx2MEtxMmpFRi16cC1aUjFjeHlscUNoemN0dW5LNHg2Z1RCR0o?oc=5</t>
         </is>
       </c>
     </row>
@@ -1436,51 +1436,51 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cientistas da UFMG descobrem que o pó de basalto espalhado na lavoura sequestra carbono, substitui parte do calcário e ainda aumenta a produtividade em até 20% - Olhar Digital</t>
+          <t>Aos 64 anos, veterano usou 113 toneladas de cimento, empilhou blocos de calcário como se fossem toras e ergueu no próprio quintal, em Lucas, no Kansas, uma cabana de 11 cômodos cercada por 150 esculturas de concreto - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>08/08/2026 11:47</t>
+          <t>09/08/2026 17:18</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxQT19EbV8tTDZaXzAzYVE0RkJSVUpUdlpPQ3RJXzlhUGhKWU9PU2xvMS0tek02VFBULThkalBIZjZ1YmlHMmFkWUV1ZmVWRmswMy1waGNEZktuTmNYOENCd3hjNC1oRUhFS29uUkFqRWY2V2JjR2VnZnVSNUN0cVlFOUNYaENFNzM5OEhRc0E3MzdrWjdMTWYtVEgwYlVBQWRQUEI1VnJYZW5GVld6SzY5M3F3T25aUk1ZSWRYZE5EUjRNak9nb1VLYkhZdkJVOF9Ma0ltT204bFNqN0h3OVJCVWUyQ3VLMUlUd1FoTDVqMHpNWDN3M2txTWZwaDh2SWNtb3ZBMFppWFJzNjhLVWtBenBibnhfN3lQbW1jVmJhRHlyaWRtd3VTNzZrUEgwMkYzcXZydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNSS01SVVhYy1zOHRObE1Vc2hZdlNTOXhDTzZoYnByZmFVN0pPV3BjUXNMYUFINmlfcllfN0s3M29nSGZVNlllZ012Y2NBemE1OHRoR19jbGdQVkZDX0lpNEVESVRtRHVQZlZfTE1SbFN3c25CZmtJd2h3RHFZRzBOU0pVM0dpUnhWVmZGUVltcVhwejJtaENWaGNHdmQyR1lPeEZYRmFveUJuVVZMRXp3azdoYVQ5MDg4dTN5cEgzb1JZdGhMcm8zN3k0ZkFfb29OeDNrZW43bEtBV0V0UEJWTlFCYWlRa3BSeThDSGhVdUdTZUloTlhXTktLdmZTVmVpejhZc1pHUkg5QXZ0U21xRnpLcXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nitrogenados avançam e potássicos ficam estáveis - Agrolink</t>
+          <t>Cientistas da UFMG descobrem que o pó de basalto espalhado na lavoura sequestra carbono, substitui parte do calcário e ainda aumenta a produtividade em até 20% - Olhar Digital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>08/08/2026 04:00</t>
+          <t>08/08/2026 11:47</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQ29TXzhvV2tZZ1JnZlBnR2NYcDFmSHpMUGYxamVrZnVPY1JlWDBIaE01Y1NtcURKZTdyLUppTnBRSUJSRDdSekN3Y21aeHlvbVZXWnZXYWJ1VHlCY1dKNjZ4dW5neDZCZGFQVUNuSE1JU2Q0dGx6ZF84V0FtMUpNd1BRU1hkdDQycS10VmNQcHFfb2R5R1p4U0RrZEVxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxQT19EbV8tTDZaXzAzYVE0RkJSVUpUdlpPQ3RJXzlhUGhKWU9PU2xvMS0tek02VFBULThkalBIZjZ1YmlHMmFkWUV1ZmVWRmswMy1waGNEZktuTmNYOENCd3hjNC1oRUhFS29uUkFqRWY2V2JjR2VnZnVSNUN0cVlFOUNYaENFNzM5OEhRc0E3MzdrWjdMTWYtVEgwYlVBQWRQUEI1VnJYZW5GVld6SzY5M3F3T25aUk1ZSWRYZE5EUjRNak9nb1VLYkhZdkJVOF9Ma0ltT204bFNqN0h3OVJCVWUyQ3VLMUlUd1FoTDVqMHpNWDN3M2txTWZwaDh2SWNtb3ZBMFppWFJzNjhLVWtBenBibnhfN3lQbW1jVmJhRHlyaWRtd3VTNzZrUEgwMkYzcXZydg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balsa com calcário colide com embarcação que transportava veículos e passageiros no PA - G1</t>
+          <t>Nitrogenados avançam e potássicos ficam estáveis - Agrolink</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1490,73 +1490,73 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOLXU4VVlXLTFOSFF1SlZGZE1QMHdLNkpxVWlTeUM1WXdvRHhVMHBfMVlNSy1JTjUyZ1d0UkxPdzRpWGc3bmFaUWxFMHByby1EZHJQaGJmMjZ5eWlOa1Q0MVlIejNwQV9kQXF0RmhSbG5wbzdxU0F1enVwSUwzMTViaENYSWgwNmRfTjBTSmtMVVhuR3NPWnNibTlZbVd2QkhPQXBjS1JLRzAydUZ3alpmdTlleU9GSmpJcHBCUmlsM1BYX2Q2Tk91T0tCLWpyc0JiSDNDXzNkZGNOX21zNXBLT0RWdU0zRTlTNzA3emNRQkFUWWhLVWctTDlRb9IBigJBVV95cUxNWm9hVy02aXdPX1luVk9zWjhkS0tYVWpVYmZKMDA3ZEtBNk5RaU5Jd3l5V2FzaklHU0pfNGYxby1tRTB4WEVRdEVubUh6dC1zNTNzTDNYSS1WYlZGLVdmZkdIVHJXVG1tZWZuUHMxbnRUUE0xRWNKdHZKakVwQXZpX3lXWUpjd3FYUEZPak1qb01QNHZQWEF1UzJyVGJnU3ZodncySFZSWTFtSHVwaDdmMjNkWG1kNUFtZFc4UVhQVHdvM1NMLUZCMTZfY3g1dVYxVTN1Nkswb3ZRZ1B0YV9rXzhveUUtZ3c5OS1ZZnJKZlhzY1ZCRG1BRW5SU0pwN1N1OURZaGpWamFEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQ29TXzhvV2tZZ1JnZlBnR2NYcDFmSHpMUGYxamVrZnVPY1JlWDBIaE01Y1NtcURKZTdyLUppTnBRSUJSRDdSekN3Y21aeHlvbVZXWnZXYWJ1VHlCY1dKNjZ4dW5neDZCZGFQVUNuSE1JU2Q0dGx6ZF84V0FtMUpNd1BRU1hkdDQycS10VmNQcHFfb2R5R1p4U0RrZEVxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lhoist participa da SIAVS 2026 e apresenta soluções voltadas à produção animal - Arcos Notícias</t>
+          <t>Balsa com calcário colide com embarcação que transportava veículos e passageiros no PA - G1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>07/08/2026 16:37</t>
+          <t>08/08/2026 04:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQmVqTFJJR21ZY2NGRVhsVHJmbTE2X3EzV0pINGJVVFlfN1ZLcWVHQVVLS2dkQk1wMzdlSnIyczFwZGRtVVhXMVpMQkczemREY0VTUVRwN3p2SmxUcnh0dzdKTzNZbThjelEzWWJ1dnJQODR4RWFPdk9yUFhla280bVFSUjVLVnJnRjhwcHdQMGp6ZDJCNlZWYzBTd0dJbkpHX2VxdzYybkJFWUJCenlRQ25SWkxVVEtBZTJIYjdoQlJ3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOLXU4VVlXLTFOSFF1SlZGZE1QMHdLNkpxVWlTeUM1WXdvRHhVMHBfMVlNSy1JTjUyZ1d0UkxPdzRpWGc3bmFaUWxFMHByby1EZHJQaGJmMjZ5eWlOa1Q0MVlIejNwQV9kQXF0RmhSbG5wbzdxU0F1enVwSUwzMTViaENYSWgwNmRfTjBTSmtMVVhuR3NPWnNibTlZbVd2QkhPQXBjS1JLRzAydUZ3alpmdTlleU9GSmpJcHBCUmlsM1BYX2Q2Tk91T0tCLWpyc0JiSDNDXzNkZGNOX21zNXBLT0RWdU0zRTlTNzA3emNRQkFUWWhLVWctTDlRb9IBigJBVV95cUxNWm9hVy02aXdPX1luVk9zWjhkS0tYVWpVYmZKMDA3ZEtBNk5RaU5Jd3l5V2FzaklHU0pfNGYxby1tRTB4WEVRdEVubUh6dC1zNTNzTDNYSS1WYlZGLVdmZkdIVHJXVG1tZWZuUHMxbnRUUE0xRWNKdHZKakVwQXZpX3lXWUpjd3FYUEZPak1qb01QNHZQWEF1UzJyVGJnU3ZodncySFZSWTFtSHVwaDdmMjNkWG1kNUFtZFc4UVhQVHdvM1NMLUZCMTZfY3g1dVYxVTN1Nkswb3ZRZ1B0YV9rXzhveUUtZ3c5OS1ZZnJKZlhzY1ZCRG1BRW5SU0pwN1N1OURZaGpWamFEZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Há milhares de anos, o mar cobriu antigas cavernas de calcário e deixou manchas escuras no meio das águas claras - Revista Oeste</t>
+          <t>Lhoist participa da SIAVS 2026 e apresenta soluções voltadas à produção animal - Arcos Notícias</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>07/08/2026 12:05</t>
+          <t>07/08/2026 16:37</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOVl5a3l5ZE9fakVBVDZmenlqTmJpbTkzSDc0QUhxSE1aRmpYZm1XM1lmVUxkRmhEcE9LdXM4Y3NNcFBoc2dxcHpweEVQQ2MyZlJpcWNkeklRdXlLZC00LXlsUEp3UkVXT0xOcFl3SlZUTnRlam5uZENrVGxfTnNVSWluTTR1ZnJOSFFyX25jN0RnY2wwY3NUM3M2SDg1Q2tVQ2c1dGhkYnBJa2dBM1FXNU8xZWNLYUp5eTlVc2VMS2VxMHVySDBIUGxYVW1pajBpWjBDMUpGSElxZ0tvMjdYWVF4SVp5b2ZCMzVOZ0JpWDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQmVqTFJJR21ZY2NGRVhsVHJmbTE2X3EzV0pINGJVVFlfN1ZLcWVHQVVLS2dkQk1wMzdlSnIyczFwZGRtVVhXMVpMQkczemREY0VTUVRwN3p2SmxUcnh0dzdKTzNZbThjelEzWWJ1dnJQODR4RWFPdk9yUFhla280bVFSUjVLVnJnRjhwcHdQMGp6ZDJCNlZWYzBTd0dJbkpHX2VxdzYybkJFWUJCenlRQ25SWkxVVEtBZTJIYjdoQlJ3Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20 Empresas no mercado de tetrafluoreto de enxofre Tamanho, Compartilhar - Spherical Insights</t>
+          <t>Há milhares de anos, o mar cobriu antigas cavernas de calcário e deixou manchas escuras no meio das águas claras - Revista Oeste</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>07/08/2026 09:13</t>
+          <t>07/08/2026 12:05</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZ3dtM3FvUTVqZFBFSjRiQ1ZTWGZ3UUJ0aW1vQWN0Q0hoc3ljcEY0Z2stS0VxWG5UcXpaZnNtQ1dJSzVybW1Rb1NOME1XYXdxNjAtRkRHb25rOU5hQ3AyRmdTUWhxMG53czVXREtwUkxKb0tONU40Mlc3V0NUdWhHUHNLcGVRTDFPQU9haDFTV09sSWN1cGxUSjJGcXZwd0xsY3diV003UHhuLW5GazRQYnc2SS1vTzNfMGs2emxRQ2Q5YUJFN2k5QXJjbTg4UDQyYmRfZU1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOVl5a3l5ZE9fakVBVDZmenlqTmJpbTkzSDc0QUhxSE1aRmpYZm1XM1lmVUxkRmhEcE9LdXM4Y3NNcFBoc2dxcHpweEVQQ2MyZlJpcWNkeklRdXlLZC00LXlsUEp3UkVXT0xOcFl3SlZUTnRlam5uZENrVGxfTnNVSWluTTR1ZnJOSFFyX25jN0RnY2wwY3NUM3M2SDg1Q2tVQ2c1dGhkYnBJa2dBM1FXNU8xZWNLYUp5eTlVc2VMS2VxMHVySDBIUGxYVW1pajBpWjBDMUpGSElxZ0tvMjdYWVF4SVp5b2ZCMzVOZ0JpWDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1568,139 +1568,139 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crise de enxofre: Como a guerra no Irã pode afetar o tratamento de água no Brasil - UOL Notícias</t>
+          <t>20 Empresas no mercado de tetrafluoreto de enxofre Tamanho, Compartilhar - Spherical Insights</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>07/08/2026 04:00</t>
+          <t>07/08/2026 09:13</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOeEFxbXZ5Z2lLNUhXTTBtMVBiX29ZUnZtVUwxVjRFeW5HU183NExBV1dNNmw0bWZZaFR1Zmc1RDNaQkxUVHhhNTJvTm9UaXl5MXVvbmRGdDc5cEZTbTROaVBWNm5JSDdnek9Xdk5GbWJLM2hrYXQ5TUMyenhOXzlnSFV2Rk1xSlk0TjRubUhEZGd5VDJXXzlOR2JPSEZMLTRjYl8ydzduTnpHYWJzRW9BNkYyU3FieHgxWDVYQnZYNTdsY0hHOTVxTWxhdVhPdVRoSG9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZ3dtM3FvUTVqZFBFSjRiQ1ZTWGZ3UUJ0aW1vQWN0Q0hoc3ljcEY0Z2stS0VxWG5UcXpaZnNtQ1dJSzVybW1Rb1NOME1XYXdxNjAtRkRHb25rOU5hQ3AyRmdTUWhxMG53czVXREtwUkxKb0tONU40Mlc3V0NUdWhHUHNLcGVRTDFPQU9haDFTV09sSWN1cGxUSjJGcXZwd0xsY3diV003UHhuLW5GazRQYnc2SS1vTzNfMGs2emxRQ2Q5YUJFN2k5QXJjbTg4UDQyYmRfZU1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>China avança na liberação de novas cotas de exportação de ureia para 2026 - GlobalFert</t>
+          <t>Crise de enxofre: Como a guerra no Irã pode afetar o tratamento de água no Brasil - UOL Notícias</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>06/08/2026 20:22</t>
+          <t>07/08/2026 04:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVGVseEtZWDh1cHRpRWpVeEZ2YWdjVmIzNHRJNWcwdjhXLUhMU29BM3RPZ25OOW52QjVZajdKRjE4UWF4RmxsdER3ZEFUTWY1UVVYR2dpdmVmNzl3SVplNS1tbGJtSHR4NEY5TjRMZUhWOE5telR0ZGhQOFJrOVJEUXVZOUF6cGpyOFZRajUzNFF2M2NsU3dHTTZwWHpRbV9ZRGp0YkVLbFFMM1BoTVVIaVhfSDY0MDNi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOeEFxbXZ5Z2lLNUhXTTBtMVBiX29ZUnZtVUwxVjRFeW5HU183NExBV1dNNmw0bWZZaFR1Zmc1RDNaQkxUVHhhNTJvTm9UaXl5MXVvbmRGdDc5cEZTbTROaVBWNm5JSDdnek9Xdk5GbWJLM2hrYXQ5TUMyenhOXzlnSFV2Rk1xSlk0TjRubUhEZGd5VDJXXzlOR2JPSEZMLTRjYl8ydzduTnpHYWJzRW9BNkYyU3FieHgxWDVYQnZYNTdsY0hHOTVxTWxhdVhPdVRoSG9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cine CMOC chega a Porteirinha e Riacho dos Machados – 11 a 18/08 - Agenda BH</t>
+          <t>China avança na liberação de novas cotas de exportação de ureia para 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>06/08/2026 19:15</t>
+          <t>06/08/2026 20:22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOWlhtVFh2SXNYRTI0cmRUMGxNV3QzRnFTcXVUcVZhSlZXRWxhRC1tZGV6d09OcktHZXpXQ0l4YVpxbjhQckEwR1U1LUxrcm5hUGVRVHNSc0RnOFd0Q3dfQWx6cjR6aWcxMlFqajMweUVoaGtrbWM0dEhLdFJmMTFZbTFWdDl5REtWaUQzRXR6Vmt1c3hmMFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVGVseEtZWDh1cHRpRWpVeEZ2YWdjVmIzNHRJNWcwdjhXLUhMU29BM3RPZ25OOW52QjVZajdKRjE4UWF4RmxsdER3ZEFUTWY1UVVYR2dpdmVmNzl3SVplNS1tbGJtSHR4NEY5TjRMZUhWOE5telR0ZGhQOFJrOVJEUXVZOUF6cGpyOFZRajUzNFF2M2NsU3dHTTZwWHpRbV9ZRGp0YkVLbFFMM1BoTVVIaVhfSDY0MDNi?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nutrien e Mosaic sofrem pressão à medida que agricultores reduzem uso de fertilizantes após alta nos preços - TradingView</t>
+          <t>Cine CMOC chega a Porteirinha e Riacho dos Machados – 11 a 18/08 - Agenda BH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>06/08/2026 14:17</t>
+          <t>06/08/2026 19:15</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBHMWkzaE5yd0dWOFB5bzdnNEd1R3I1M0N2dUE5bmVOTFdjTDFxWG9LMmI5UGhRaDRQLWZ2aThXZFdob0hDUDRmQTZHQXhCRi1vZEdYRlg0OXhydlRKVC1TRkJzRV9hbFowdmItc3MxUVVITXZ1Y0w4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOWlhtVFh2SXNYRTI0cmRUMGxNV3QzRnFTcXVUcVZhSlZXRWxhRC1tZGV6d09OcktHZXpXQ0l4YVpxbjhQckEwR1U1LUxrcm5hUGVRVHNSc0RnOFd0Q3dfQWx6cjR6aWcxMlFqajMweUVoaGtrbWM0dEhLdFJmMTFZbTFWdDl5REtWaUQzRXR6Vmt1c3hmMFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Programa de Aprendizagem da Lhoist fortalece formação de jovens em São José da Lapa, Matozinhos e Arcos - Arcos Notícias</t>
+          <t>Nutrien e Mosaic sofrem pressão à medida que agricultores reduzem uso de fertilizantes após alta nos preços - TradingView</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06/08/2026 11:18</t>
+          <t>06/08/2026 14:17</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPSjh5SWdvbUp2amhuTkxBLU1Gb2NfSDBvNTItd2VJMktmenZIUXRRQnV5RXpLaEJKZG5QSVlmb01CZHZwQ3FQLVktcmxEQ2h0TDNQZ3duNjdZRVhQb0FNT2F6a1BVdU5mR2ppaDg0VHdXb2xUa3FwMk1YYmo1d1hvQVpDdThzY29kcnY0azFDYzR6X25uallTa0Z2NFBoMlhiME0tNFlHdkYtZ0o1Qm1Uck4xZDQ1SEdwR0NSSTFydG1EZHAxWFkzbEVnOXVweXlPVmg2T3MtSFhCU1hvMEV1OFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBHMWkzaE5yd0dWOFB5bzdnNEd1R3I1M0N2dUE5bmVOTFdjTDFxWG9LMmI5UGhRaDRQLWZ2aThXZFdob0hDUDRmQTZHQXhCRi1vZEdYRlg0OXhydlRKVC1TRkJzRV9hbFowdmItc3MxUVVITXZ1Y0w4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Prefeitura intensifica articulações para reduzir impactos da paralisação da Mosaic em Uberaba - jornaldeuberaba.com.br</t>
+          <t>Programa de Aprendizagem da Lhoist fortalece formação de jovens em São José da Lapa, Matozinhos e Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06/08/2026 04:00</t>
+          <t>06/08/2026 11:18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOc1VaQ2tJd0FBUWE4b3lMLWItSW8yMEltaUdrMERyWkE0SmN6bXp3a3BKNEFtalF0WHRIVzkxMHNXVjVKRlAtOTJnV0tBNmFWbjU1LVRyM1V5YWhFajBGeEVOeXdQRTRtM0NtTlFzNmRrMHhtalRxQ0lqRTI5QllGUFhHTTFaQlo0Skw3MlRBYzROdTJRejV6NzZndG5zRlY1VXU1dTliM3BGd3FZVmwzbVNwSTA4MXZWcHF6aXhtbmJCcmFwNmI5VVByLWdpU25TYjZ4dXdjUzNxeWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPSjh5SWdvbUp2amhuTkxBLU1Gb2NfSDBvNTItd2VJMktmenZIUXRRQnV5RXpLaEJKZG5QSVlmb01CZHZwQ3FQLVktcmxEQ2h0TDNQZ3duNjdZRVhQb0FNT2F6a1BVdU5mR2ppaDg0VHdXb2xUa3FwMk1YYmo1d1hvQVpDdThzY29kcnY0azFDYzR6X25uallTa0Z2NFBoMlhiME0tNFlHdkYtZ0o1Qm1Uck4xZDQ1SEdwR0NSSTFydG1EZHAxWFkzbEVnOXVweXlPVmg2T3MtSFhCU1hvMEV1OFlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Um engenheiro químico explica como limpar o calcário do vidro do chuveiro: "Os produtos de limpeza convencionais geralmente removem bem os resíduos orgânicos, mas não os inorgânicos" - Minha Vida Saúde</t>
+          <t>Prefeitura intensifica articulações para reduzir impactos da paralisação da Mosaic em Uberaba - Jornal de Uberaba</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9pOEpndTExOHJwQUk2SW5JcThtZl9YdFZWeDBsOFJmOXJTTk0zUTFtQlFfeHdEek1PMHZveHlGRnpaVXlPQmo4UVN5OGVxQ3lEci0tRnFlZWpDV1RUNWdZctIBZkFVX3lxTE5hNGg1YUxwS3Z6aDZCbzQyQnVreW1IWEVhWm9CM0RXaWptYUkwWjVBdk5yajBxcWM4S0tMMkItTGtaaktxQTVOVWZSWGYwX0hEb1l2RXU0OUhuZThLUmhIVXRGeWVHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOc1VaQ2tJd0FBUWE4b3lMLWItSW8yMEltaUdrMERyWkE0SmN6bXp3a3BKNEFtalF0WHRIVzkxMHNXVjVKRlAtOTJnV0tBNmFWbjU1LVRyM1V5YWhFajBGeEVOeXdQRTRtM0NtTlFzNmRrMHhtalRxQ0lqRTI5QllGUFhHTTFaQlo0Skw3MlRBYzROdTJRejV6NzZndG5zRlY1VXU1dTliM3BGd3FZVmwzbVNwSTA4MXZWcHF6aXhtbmJCcmFwNmI5VVByLWdpU25TYjZ4dXdjUzNxeWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Calcário Aliança quebra o silêncio sobre as investigações em Rosário Oeste - Pagina1mt</t>
+          <t>Um engenheiro químico explica como limpar o calcário do vidro do chuveiro: "Os produtos de limpeza convencionais geralmente removem bem os resíduos orgânicos, mas não os inorgânicos" - Minha Vida Saúde</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>05/08/2026 14:40</t>
+          <t>06/08/2026 04:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPRUxRQVdoRk52SF9JYXJSVG1MbXJJOS1qTjlpekx6c0J6MzJGb05iSFZYTGFCLXZsSlVtTUdVUk16SGxBU1Faa2RkRjFPOW5adU93V2R1akV0QmNPRHFUN1luX0dzOEt1WW5kOW9DWHlDN21rY1g0R2llZWh1cUtoakt1VFJRbFdLbFlhZF9zT0J4RzJQUjZvOV96TGxVYndQdXEzRzRkbEl5aVVXZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9pOEpndTExOHJwQUk2SW5JcThtZl9YdFZWeDBsOFJmOXJTTk0zUTFtQlFfeHdEek1PMHZveHlGRnpaVXlPQmo4UVN5OGVxQ3lEci0tRnFlZWpDV1RUNWdZctIBZkFVX3lxTE5hNGg1YUxwS3Z6aDZCbzQyQnVreW1IWEVhWm9CM0RXaWptYUkwWjVBdk5yajBxcWM4S0tMMkItTGtaaktxQTVOVWZSWGYwX0hEb1l2RXU0OUhuZThLUmhIVXRGeWVHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1744,73 +1744,73 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alvo de operação sobre mineração ilegal de calcário diz que vai comprovar regularidade - midiajur.com.br</t>
+          <t>Calcário Aliança quebra o silêncio sobre as investigações em Rosário Oeste - pagina1.com.br</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>05/08/2026 11:58</t>
+          <t>05/08/2026 14:40</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOcWM0dGNJNzdwWERlQ2tyLW9Sa1NaLVFwVmlKa0VuTS1UeTNkVGFvaXV0RkhqamRjZFhOeHpYSGNRVFVGSDJVQTZDMjgzcDVCeVpWTzhCdFB5VUFJSGIySUZ6cG1PZFFGSDlEcUtFMXgtcTBGN0RJdDNFMmZ1NWxueF9mNXZCZ0p0d0o5YmdQeFBqQy1yZDVzOEY2U1R2eF93WlcwNWFGSFFEOUxBVW13R09EQXJHX1ZjZTNrdFBCSWJlU1BX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPRUxRQVdoRk52SF9JYXJSVG1MbXJJOS1qTjlpekx6c0J6MzJGb05iSFZYTGFCLXZsSlVtTUdVUk16SGxBU1Faa2RkRjFPOW5adU93V2R1akV0QmNPRHFUN1luX0dzOEt1WW5kOW9DWHlDN21rY1g0R2llZWh1cUtoakt1VFJRbFdLbFlhZF9zT0J4RzJQUjZvOV96TGxVYndQdXEzRzRkbEl5aVVXZlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo de US$ 273 milhões e culpa crise do enxofre - bra1.com.br</t>
+          <t>Alvo de operação sobre mineração ilegal de calcário diz que vai comprovar regularidade - midiajur.com.br</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>05/08/2026 07:40</t>
+          <t>05/08/2026 11:58</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQclIyRGx0aE9SeTIwVFRsS1ZULWJoUHVPaTFqQjBPWGRLS3BYelRsSjRuRHJxcTNrZGZmY3E0czAwUXFNdFVFZC15eS1PLU5HT2l6aHJIU0VPNzFaQUpFNG5ZN2tKVUVfcW1VSktxMEtYeUVoM3ZYX0JxZ0p1U0lkMWJTLWE1YkQ5NVJCb1JhVWlHdi1mdm5DT05VbjR6SnVTeWdLZUVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOcWM0dGNJNzdwWERlQ2tyLW9Sa1NaLVFwVmlKa0VuTS1UeTNkVGFvaXV0RkhqamRjZFhOeHpYSGNRVFVGSDJVQTZDMjgzcDVCeVpWTzhCdFB5VUFJSGIySUZ6cG1PZFFGSDlEcUtFMXgtcTBGN0RJdDNFMmZ1NWxueF9mNXZCZ0p0d0o5YmdQeFBqQy1yZDVzOEY2U1R2eF93WlcwNWFGSFFEOUxBVW13R09EQXJHX1ZjZTNrdFBCSWJlU1BX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - BOL</t>
+          <t>Mosaic tem prejuízo de US$ 273 milhões e culpa crise do enxofre - bra1.com.br</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>05/08/2026 04:00</t>
+          <t>05/08/2026 07:40</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRkwyVXR1MjRKdnZ5eEN3NjlnelRKc0k2TE5OYTI5b2l4ZWNPYlB5LTVfRkE5Wk5rZ01LN1A1NjlsdHEwakpvMTJyVnV6dUZCSHhDWXNuQkY4TFpnVEFFeFBReXA2cDBST1RFeWR4TUJQbmNnem4yTFNIVmhMRFZfSEMyRTRXMGhIWHZNbzRYcnh2ZU53RDQzczRzVWhJVW14b3pJT0dEUmR4dzFiT29lU0JBbl9fcll3Z0J4Q9IBwgFBVV95cUxOSHQzTGlRa2Z3WGlIMk9FdXlWcHpyVk9EdV9wTF9SMHBGYXJaVHZHcUtSaVlKVUlQLW1qLXhQNUJ0WUR5VmQyRnFob3BTM0FNQ2g4T3g1d0VEWG1KMnk0OEgxa3Biajd5OG8yVWNmek91UGdqN2hKU3lvaXQtdXhuZVFLRE1tS2xVQ1Jtb0QyY1V4bmtEOHNaQW5uNDUtaWZMdFMzZHEzdURZWXZzNkVnOHY5bzJiTnhDTU9kbVZqZ1lNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQclIyRGx0aE9SeTIwVFRsS1ZULWJoUHVPaTFqQjBPWGRLS3BYelRsSjRuRHJxcTNrZGZmY3E0czAwUXFNdFVFZC15eS1PLU5HT2l6aHJIU0VPNzFaQUpFNG5ZN2tKVUVfcW1VSktxMEtYeUVoM3ZYX0JxZ0p1U0lkMWJTLWE1YkQ5NVJCb1JhVWlHdi1mdm5DT05VbjR6SnVTeWdLZUVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - UOL Notícias</t>
+          <t>Martin Marietta obtém aprovações regulatórias para negócio com a Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1820,19 +1820,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPVm5vY00ydFNNRFpySGZRdzkxamEyVHZwWm5acTNRN1draHRoWVU2ZXJPYVNJVG1vaFdUcTZGNFVHaV9wWFo1WmVqYkdCWlRvb0YyWmpPOEpram5fYW5GbVo1aGRndG5yc1BKMTR0RVF6amhpTTJFdFQ2d1VDeHRDMUR4dURYRDgweVFQZ2FUUXVhR0Z4ZW9KWlBhQjgzRUNPd3pLRHZnaThlVklJR3dWYU5ObFlZcjZubUZoalZNRXVTZW9xWEpiby1NX2ZONmRGSnJQYlRQV3VEQmxo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdmlEaDJzTXdyWXdBTkRiVlQtNjlZMVY2WG1Fa2pPSVpnRENkNnBSdG9nWTBiVWFXZEdUWHdCSFRWTlgySjA1VUQzVVN6QUxUYWZfUFVFUURWVmtGQ3haUFMyMGZ4a0hVN3d1Z3FpWDlFNVJYMDA1bjNNVXVobXlUWFV2SGVPRUVmZElHTjRsSFNVODVVN3dhNXFqMkcxRGhtRE9peU5tRnZvU3VUejk1RDR6bDVJUkZIOUdheVJTSmwxRGNpaHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Martin Marietta obtém aprovações regulatórias para negócio com a Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Impacto da reabertura da fábrica de ureia para o agro brasileiro - Revista Oeste</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdmlEaDJzTXdyWXdBTkRiVlQtNjlZMVY2WG1Fa2pPSVpnRENkNnBSdG9nWTBiVWFXZEdUWHdCSFRWTlgySjA1VUQzVVN6QUxUYWZfUFVFUURWVmtGQ3haUFMyMGZ4a0hVN3d1Z3FpWDlFNVJYMDA1bjNNVXVobXlUWFV2SGVPRUVmZElHTjRsSFNVODVVN3dhNXFqMkcxRGhtRE9peU5tRnZvU3VUejk1RDR6bDVJUkZIOUdheVJTSmwxRGNpaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOajFPWU1RdTVTdkl6TDRGUE45aFZ0UEJXekRRcjNWSmx5Q0xwZjlsNjBLOHdJYjVWLWw0UlNTRGNJaEp4Xy1qeW9XQ1NSbGxRd3JuaXBCTXhXYUZCNXpBcU80NWZMbk92M1hNWmhOVjJ5Nlp1c0huNlQ3RWUyLTlKNU9RWGthRTBBcnJPZkNGUE5Ga0xKOXlveDczUVduXzAtaF9hNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1871,12 +1871,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EuroChem avalia reduzir produção e adotar layoff em Serra do Salitre por crise global do enxofre - Estadão Blue Studio</t>
+          <t>O peso do enxofre no balanço da Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1886,19 +1886,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQ3RLWHZWbmFLS0RNTTBYaVpNYWdISjVib1ExR0ZfbFhQUUJKT1I2My0xTEhfMnozRlhWcGxuZzlJRUhQMXExaG8wLVZkbzNZSjdUZDRTckc5RmRrZ2RYbWVKUVF2dWxpb2dTd0c1MVdGVldBM3p0LU9ZUXJLYlJXRTlwNU5zRVF3dmYydUttR1RCTkx0QS16X3BjamVIWmhqbGRsd2FPSjUwQzBGemQxNUlhaFpfN3hfMkZ3R2t1VEZYV2JY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNazEyWVlFbVJHbWRMdUtiUDc5aE9nS3E4ZUVZdE1FdjJUeUtuZjVrbDlXV25xTjd4bEM4TzQ5c05nX0s2QmNvRkdPQWpoUm5pZE42NEc3Unh1R3JET0FhV0RjV2NpZTVJdWtITHhzenk5a2luNEswY3VlTFhUZ1JvWE5oWnVCNDVPUXpqWg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mosaic vê queda de 30% no uso de fosfatados no Brasil e risco à produtividade - The AgriBiz</t>
+          <t>EuroChem avalia reduzir produção e adotar layoff em Serra do Salitre por crise global do enxofre - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVjdYZWJTWUpzT0I3RTEzX0YxN1BZbk4yRjJCa1U5OVBtY2xlV043dTg2MVg3emJXd2ladlBfOEdCTkkxQm9tajNDSTZHaUpSRHNPVTBzT3d4VWNTRE9xVFluckZBV1RyMFVzbGhHLWF2Y3ZXMTg5eWlFeUNsblVUb3dKWlhLYnppQXNYZ0tNQVZlZm91dW9QMzJFVWlldTRCa0o3ZF9WNV9nUjdTMXgtMWdVVl9VSVhFOVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQ3RLWHZWbmFLS0RNTTBYaVpNYWdISjVib1ExR0ZfbFhQUUJKT1I2My0xTEhfMnozRlhWcGxuZzlJRUhQMXExaG8wLVZkbzNZSjdUZDRTckc5RmRrZ2RYbWVKUVF2dWxpb2dTd0c1MVdGVldBM3p0LU9ZUXJLYlJXRTlwNU5zRVF3dmYydUttR1RCTkx0QS16X3BjamVIWmhqbGRsd2FPSjUwQzBGemQxNUlhaFpfN3hfMkZ3R2t1VEZYV2JY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>O peso do enxofre no balanço da Mosaic - AgFeed</t>
+          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - BOL</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1930,19 +1930,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNazEyWVlFbVJHbWRMdUtiUDc5aE9nS3E4ZUVZdE1FdjJUeUtuZjVrbDlXV25xTjd4bEM4TzQ5c05nX0s2QmNvRkdPQWpoUm5pZE42NEc3Unh1R3JET0FhV0RjV2NpZTVJdWtITHhzenk5a2luNEswY3VlTFhUZ1JvWE5oWnVCNDVPUXpqWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRkwyVXR1MjRKdnZ5eEN3NjlnelRKc0k2TE5OYTI5b2l4ZWNPYlB5LTVfRkE5Wk5rZ01LN1A1NjlsdHEwakpvMTJyVnV6dUZCSHhDWXNuQkY4TFpnVEFFeFBReXA2cDBST1RFeWR4TUJQbmNnem4yTFNIVmhMRFZfSEMyRTRXMGhIWHZNbzRYcnh2ZU53RDQzczRzVWhJVW14b3pJT0dEUmR4dzFiT29lU0JBbl9fcll3Z0J4Q9IBwgFBVV95cUxOSHQzTGlRa2Z3WGlIMk9FdXlWcHpyVk9EdV9wTF9SMHBGYXJaVHZHcUtSaVlKVUlQLW1qLXhQNUJ0WUR5VmQyRnFob3BTM0FNQ2g4T3g1d0VEWG1KMnk0OEgxa3Biajd5OG8yVWNmek91UGdqN2hKU3lvaXQtdXhuZVFLRE1tS2xVQ1Jtb0QyY1V4bmtEOHNaQW5uNDUtaWZMdFMzZHEzdURZWXZzNkVnOHY5bzJiTnhDTU9kbVZqZ1lNUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Impacto da reabertura da fábrica de ureia para o agro brasileiro - Revista Oeste</t>
+          <t>Mosaic estima redução de 30% na aplicação de fosfatados no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOajFPWU1RdTVTdkl6TDRGUE45aFZ0UEJXekRRcjNWSmx5Q0xwZjlsNjBLOHdJYjVWLWw0UlNTRGNJaEp4Xy1qeW9XQ1NSbGxRd3JuaXBCTXhXYUZCNXpBcU80NWZMbk92M1hNWmhOVjJ5Nlp1c0huNlQ3RWUyLTlKNU9RWGthRTBBcnJPZkNGUE5Ga0xKOXlveDczUVduXzAtaF9hNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNy1DT0ZOaGdiZDJTa012cjFrXy1UUzlTR2djUEMtNDBESlRzMm1saUNfakxkazd6WXBDV0FnSmEzNENJV2xvZDlLTFA2WUxtMUE3bHdoQW5oR3kxdU5iUmR6eXp6dEdZZnZITWJJMFZpdmM1R2V5LTB4UmhNalhwbmJqS085YkNkVUhOUGdDek93Y2V5R0N3NDRybGlPRkVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mosaic estima redução de 30% na aplicação de fosfatados no Brasil - CNN Brasil</t>
+          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - UOL Notícias</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1974,73 +1974,73 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNy1DT0ZOaGdiZDJTa012cjFrXy1UUzlTR2djUEMtNDBESlRzMm1saUNfakxkazd6WXBDV0FnSmEzNENJV2xvZDlLTFA2WUxtMUE3bHdoQW5oR3kxdU5iUmR6eXp6dEdZZnZITWJJMFZpdmM1R2V5LTB4UmhNalhwbmJqS085YkNkVUhOUGdDek93Y2V5R0N3NDRybGlPRkVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPVm5vY00ydFNNRFpySGZRdzkxamEyVHZwWm5acTNRN1draHRoWVU2ZXJPYVNJVG1vaFdUcTZGNFVHaV9wWFo1WmVqYkdCWlRvb0YyWmpPOEpram5fYW5GbVo1aGRndG5yc1BKMTR0RVF6amhpTTJFdFQ2d1VDeHRDMUR4dURYRDgweVFQZ2FUUXVhR0Z4ZW9KWlBhQjgzRUNPd3pLRHZnaThlVklJR3dWYU5ObFlZcjZubUZoalZNRXVTZW9xWEpiby1NX2ZONmRGSnJQYlRQV3VEQmxo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC demonstra avanços na Agenda ESG em relatório - Brasil Mineral</t>
+          <t>Mosaic vê queda de 30% no uso de fosfatados no Brasil e risco à produtividade - theagribiz.com</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>04/08/2026 15:39</t>
+          <t>05/08/2026 04:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSWo1OWtsdTlnZlR0Nzd1bE9fZHdmMDJxdkp6ZHJUemZZRWI5dmlLSERBTEFmNGNoWDEweW1EdVdBdlctdlhORmxqWU9zLUZXZHJjVWZpMElBVVZ2UXAzQmhfOGhWa2NTTVNFYms2WmlfNEJJQ1YzcFNpWFpEUkhiTVBfaHVKeXJ3ZkJ3TW9MZHlXX3hoNUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVjdYZWJTWUpzT0I3RTEzX0YxN1BZbk4yRjJCa1U5OVBtY2xlV043dTg2MVg3emJXd2ladlBfOEdCTkkxQm9tajNDSTZHaUpSRHNPVTBzT3d4VWNTRE9xVFluckZBV1RyMFVzbGhHLWF2Y3ZXMTg5eWlFeUNsblVUb3dKWlhLYnppQXNYZ0tNQVZlZm91dW9QMzJFVWlldTRCa0o3ZF9WNV9nUjdTMXgtMWdVVl9VSVhFOVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Saiba quem é o empresário alvo da PF por esquema de R$ 3 mi com extração de calcário em MT - O Documento</t>
+          <t>Mosaic reverte lucro e registra prejuízo de US$ 272,8 milhões no 2º trimestre - Canal Rural</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>04/08/2026 12:53</t>
+          <t>05/08/2026 04:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNa0VDRjVGZmRZaENMbWU0X1dEOTVCemYwNUtGNmFrb3BzZzMzYjJOc2JkRVhLQmpvOWtSUGF6dEVENUFuMEdzNVhPWG9rVlVKM2Z3LWdLOGFMU2d3Skk0NHBHenNSMTRvOXZSUGdzZU1GZWR4VWt3QU9Rb1pFbmZUaWZIYnlPUWVGU2VObmZkWnRxVFg3YzJsaWpfY2dUUmtURjE5MTNUOG9kOXlxdkJ0TjFVcFFjS0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQlgyRE9JV2x2Z3Q0U0p0Xy10OW9QRXE0T2xXTlJxTm4zLVFibF9xZFlmSTJqa2ZOTmVzT1JoR29sTE9NYjg3dUtOcXh2Vy1HVWlKRXZNUFp4V1ZaRm9BU216SVlPNU9zeTdhQ09ITEYtc1dsbXg1U0NMQkIzYzdyWU1aNHZYUFJ6M0RscnEyOXRCQmJ5NzdicmpyU0I4TzUtUV9MSWdMQnNMMVYySnZ4aWRqeWEtdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PF mira extração ilegal de calcário e investiga prejuízo de R$ 3 milhões à União - Notícia Max</t>
+          <t>SUSTENTABILIDADE | CMOC demonstra avanços na Agenda ESG em relatório - Brasil Mineral</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>04/08/2026 11:18</t>
+          <t>04/08/2026 15:39</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVk9nV1g2TFZPRU1OUFpGYmNQdG5sNkRidC1TZ25SeElET2FoangzdTdCaEJnSXV3NG42aW1CT28ycEl1SlQ3NnQ5X0w4WWh2NUhjMEJvdUVJejFMakp1TXozSXRvVjBvWkpBT25FSmdMTkpmS0t2eWVXVF9xWnN2VldQbUZ0bkptcVVXNlEyVC1ZSjU4TEtacEFZZlBkNk1wbGh1UkdIR0VUcGlEaGFnVzctMjBhVU90eUhxNzU3Uy1MQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSWo1OWtsdTlnZlR0Nzd1bE9fZHdmMDJxdkp6ZHJUemZZRWI5dmlLSERBTEFmNGNoWDEweW1EdVdBdlctdlhORmxqWU9zLUZXZHJjVWZpMElBVVZ2UXAzQmhfOGhWa2NTTVNFYms2WmlfNEJJQ1YzcFNpWFpEUkhiTVBfaHVKeXJ3ZkJ3TW9MZHlXX3hoNUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2052,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 milhões com extração de calcário e cumpre mandados em Cuiabá - O Documento</t>
+          <t>PF mira extração ilegal de calcário e investiga prejuízo de R$ 3 milhões à União - Notícia Max</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>04/08/2026 10:13</t>
+          <t>04/08/2026 11:18</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOV3J0TXI2SGxlVEZOQ2F0aG1FNkxvRE9sY3E2WUdXa3FUTjhiY3h3Wm5aUmUwenI2WDg5ang2bm90aWlZYWdWQnJ3ZnBSUTAtcFJkRUNrdWxDWjVid3dtV0FVaDNIalE1NE1NR1N3czR6am5BcldlSG1EUlRhTDE1UURjVkJHRWY1RHluN3B1U0xCeElzSEh0R3RZa2UzN0Foemtvd3lKU2MwWjM3bUEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNVk9nV1g2TFZPRU1OUFpGYmNQdG5sNkRidC1TZ25SeElET2FoangzdTdCaEJnSXV3NG42aW1CT28ycEl1SlQ3NnQ5X0w4WWh2NUhjMEJvdUVJejFMakp1TXozSXRvVjBvWkpBT25FSmdMTkpmS0t2eWVXVF9xWnN2VldQbUZ0bkptcVVXNlEyVC1ZSjU4TEtacEFZZlBkNk1wbGh1UkdIR0VUcGlEaGFnVzctMjBhVU90eUhxNzU3Uy1MQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2074,51 +2074,51 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - Ponto na Curva</t>
+          <t>PF mira esquema de R$ 3 milhões com extração de calcário e cumpre mandados em Cuiabá - O Documento</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>04/08/2026 09:55</t>
+          <t>04/08/2026 10:13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2F3T08wUWlMVDMza3FGRUJzTUZXenBQM0NWMHZhZk1OZGlKbThTbE9pcFoyM3NkS1RjUDRLS015eTRya2k3SUw0SDhJM3F6STBDY0ctZXRpM2l1YUV2LVlTNG9sVGNuODd6V0MwbU1yNThyQ2I1OXJ6MHF4OFNRZlhKUm1Rc3Q1UUI1cjVOeVhBSE5ZaF9Hc1dWb0xzeUhyNE5nSzJYVW9XWEFlMXMxamVWazBSSTI4NDRoQzVjMVEyQzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOV3J0TXI2SGxlVEZOQ2F0aG1FNkxvRE9sY3E2WUdXa3FUTjhiY3h3Wm5aUmUwenI2WDg5ang2bm90aWlZYWdWQnJ3ZnBSUTAtcFJkRUNrdWxDWjVid3dtV0FVaDNIalE1NE1NR1N3czR6am5BcldlSG1EUlRhTDE1UURjVkJHRWY1RHluN3B1U0xCeElzSEh0R3RZa2UzN0Foemtvd3lKU2MwWjM3bUEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mosaic fecha 2º trimestre com prejuízo de US$ 273 milhões - CNN Brasil</t>
+          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - Ponto na Curva</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>04/08/2026 04:00</t>
+          <t>04/08/2026 09:55</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOYVg3Y3RpTHNrVms5NXBiN2huemhBejE2Tng3VHV5aXI5RmJNazB1WTZUeDFvZmhWd19fU2FQVzRPRlExQnlBQ0J0anRuYWZkWTFlOW9vbGdwNjNxNnhWN2UwM0l3b3VDRWxmSzFWRkw5SUg3aG45YldJeHNhS0FGTG8tMndGY1lPTEZxU1FrNVJkelNnVEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2F3T08wUWlMVDMza3FGRUJzTUZXenBQM0NWMHZhZk1OZGlKbThTbE9pcFoyM3NkS1RjUDRLS015eTRya2k3SUw0SDhJM3F6STBDY0ctZXRpM2l1YUV2LVlTNG9sVGNuODd6V0MwbU1yNThyQ2I1OXJ6MHF4OFNRZlhKUm1Rc3Q1UUI1cjVOeVhBSE5ZaF9Hc1dWb0xzeUhyNE5nSzJYVW9XWEFlMXMxamVWazBSSTI4NDRoQzVjMVEyQzg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - MidiaNews</t>
+          <t>Com alta no enxofre, Mosaic teve prejuízo de US$ 273 milhões no segundo trimestre - Globo Rural</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2128,19 +2128,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeFpET3FNUWdocW04TVhsWXZsQWNvbnpoMWQ0SHhUMWJsMnRvRDk2emRvaGdlYXNEUTlPVUsyaDluRmtTZnk2X3JsT1hKN2t5N2d2X1ZlNDFrVXYxU3hLVVBzcU1WbVJic2VGYkFtSGROX3djTk9oNnB5TWRlR2hGZVpRMEJoYnk2VmdsWHZqU3RnTnJ1S2hVRnpoZ08tYXVXU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdHRoWXh3Q0lLR20zYUtlM1NHaWt3MTB0clZBSnhUclVBQVFTeVpJMXFGSzk0UjVHendGMklEMGc3bWYtQVpKYlhqeV9XU0Y5OFF2Q21nQ1lIcmV5NG5xM2RkRTFIZG5xcmtTTG85UXE3UEphTXZvcDlTa0g1R3RMVDJHZDNJYWxyY3BuRVg1Z2RtZERWemxfQWhNZUZ0ZlEzR2paSE1fS2g5NHotaVlES2wwM0hCVWttaEHSAcgBQVVfeXFMUEYxcF82QU5MR2xGZ2liVnJsVHltSmRlRFZicWFKaWFDQ3RSTEdzLWhEbEg5YUZDbV9IcS1zNGppeE5SVlVBN1FxTk91T3pwdnZPaGRFQnBPUHM3MjVCVEhVMV8zV1RjU0VXVTF2V3dIdThoQ3g2LVdUbzVMWlYwaG1MWnhvc0t4aUtfWHhtVGZNby1Fd29fRVAxcE9Ca25BS2dHeVkwSGVIelFiVmc3eVBGVW1kS0N2NlJrZFdmZy1uVERHYXdYWjc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PF mira esquema que retirou 34 mil toneladas de calcário e causou prejuízo de R$ 3 milhões em MT - Folha 5</t>
+          <t>Fertilizantes: preço da ureia nos portos brasileiros subiu 19% em 5 semanas - InfoMoney</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2150,19 +2150,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOd1BjR0pwSGpfMkZqbGZfb0hPSzJIZmtMV2oyb3pRZ04zMXBnTGZxOHdQTGJoeW9IN25Tczl1bldyWDFHSGRtZXo5Qjh2aU1JRDBLRHFTeEdZYl9CMV9TRmtyeHFQZ0pTSUl5WGo4bVFiQ1ZrZWgzWEVGdXRDd21GV2N4NHpuaFpUTmEyNmJNVTRiRDN2ZUZGdFZvRkNDRnFXckhuNlFKd2xUbVljTHhNV1ptb0J2S2l4SzBHbTdqV3NoZHljdkFJVWNmLW1DTUJX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ1hiVk10Qzl4WTcySEpXZ3BhNmlQdTRBX3dHUDJaam9oeXlVb1pJXzJSWDBwa0RmRW5uXzdzZzR1UTJCM19acXAzRFA4WTZKaXNqNHROeUFacFlzQWFZWktVbFVGVWZyZ0ZTRGs0N1lXdU1BSVRNazRMZHNnM2VuMjk0YzN3ZmhZVFozSTNYSGp6V2ZpeTF4cFhOZmxSQlAxMU5Pcm0yb2owb0NzU3Nkak930gG3AUFVX3lxTE1lZFphRHIyY1BwRko2WjBjWTdPQUdHRzlMZDNXUk9xM0Fvelo2LUhwNHpCWWZmY2UtYU9SV2Z4U2VVSlhoNkZCY0xraWs3NGZHaWJvNGdjWjEyaWIwOTAtSVJqMGpJbzM4c0hXMTZGRk1na1FFVVpwaVJLOGRMN3VHajZBbTRSbEgzTlFuT3ExUGs0OVRQa2RKM3JrczY1OGJzemUwTGVaSmpCTkhsUTF1SmpuaHBHVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fertilizantes: preço da ureia nos portos brasileiros subiu 19% em 5 semanas - InfoMoney</t>
+          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas de calcário em MT - G1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ1hiVk10Qzl4WTcySEpXZ3BhNmlQdTRBX3dHUDJaam9oeXlVb1pJXzJSWDBwa0RmRW5uXzdzZzR1UTJCM19acXAzRFA4WTZKaXNqNHROeUFacFlzQWFZWktVbFVGVWZyZ0ZTRGs0N1lXdU1BSVRNazRMZHNnM2VuMjk0YzN3ZmhZVFozSTNYSGp6V2ZpeTF4cFhOZmxSQlAxMU5Pcm0yb2owb0NzU3Nkak930gG3AUFVX3lxTE1lZFphRHIyY1BwRko2WjBjWTdPQUdHRzlMZDNXUk9xM0Fvelo2LUhwNHpCWWZmY2UtYU9SV2Z4U2VVSlhoNkZCY0xraWs3NGZHaWJvNGdjWjEyaWIwOTAtSVJqMGpJbzM4c0hXMTZGRk1na1FFVVpwaVJLOGRMN3VHajZBbTRSbEgzTlFuT3ExUGs0OVRQa2RKM3JrczY1OGJzemUwTGVaSmpCTkhsUTF1SmpuaHBHVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbmx0djJaNkM2ZkNYMzdMd3JCa2d6N3YxbUZBUDh1YnhQWjRDaDdUMGZWckllV0tTdmlfOXktbEw3SmhEQ2JneVZTX1JIOS16NGRpTXZuSTRwbGVWTkZ3eGdkc2JPQkJDNEdTXzZ2a0pPUDlOeWpaMF9uMU85WTYySmQweEl0VnE3aUpjWDl5M2pDWWNaMlFmUUxqZEFleXNzVHZ5MFRCeEstWDE5OXNyZFgyUkZ4c1daTkNMMmRJa2ptY2ZqNnZzRUowYmtzQUhuQzdmenl0RUYxSXfSAeoBQVVfeXFMTnNOS3RkOHNCWlB6SHpPT2JQZENXNmtYSWNaLXZ2SENYMnFQVkctVndmVnRxUm85cFh4QlNxUXZNNndIZllRc2J2c3F1TE5GNXczRWhyR2Y5SHdPdEdwdGtDM2JSWktZSzZ6OEhaYUE1RGV3MUFJZ2NvTUlielMzUHJ1NFJUcmRGN0Zma3FpdTlwZjFxZGVud2NNbUJrdjZOejVraTJBNmNqVGhaSmdicFdRMUFGLUhjejhmOHpTbVptaTFodE5VSkNkTEc3aEI5dmFway1hamRlUW45ZEVrVHJrYWRDR0gyeGVn?oc=5</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Resultados da Mosaic em foco: as margens do fosfato podem se recuperar? - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic fecha 2º trimestre com prejuízo de US$ 273 milhões - CNN Brasil</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZHJEZGU5dTl1eXd1cHRvN0RUZlpQSk9aVW1qR3JadzVnQmdXZzRqcERLekRqM2JsR1pNSnJLSlplZ3ZIc2JMbkxXNEtJOUxnTk9GQXF6M3dYbk1KTW5MRUpYeGdyX1VqOWRTWEJ3UzFDUWxrd3VLaHB0QXVPUzJaNS04eVg2dW9wbXhiYkZfc0xwU0ZYbVdRSDhSX0F5anc1U3h1aWlyRGNHbTdfYTVwVXlsQjVockJGQ1FYOURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOYVg3Y3RpTHNrVms5NXBiN2huemhBejE2Tng3VHV5aXI5RmJNazB1WTZUeDFvZmhWd19fU2FQVzRPRlExQnlBQ0J0anRuYWZkWTFlOW9vbGdwNjNxNnhWN2UwM0l3b3VDRWxmSzFWRkw5SUg3aG45YldJeHNhS0FGTG8tMndGY1lPTEZxU1FrNVJkelNnVEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - FOLHAMAX</t>
+          <t>Resultados da Mosaic em foco: as margens do fosfato podem se recuperar? - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNMjVPMmg2Y2tPNGx0elVtTUU3Y1M3NFM4cFJ3czFjQndQTWZLOTE5ZmdPd3hkUmtjS3ZlbnZOVngzUnhWRmdRY3EyM0tEbXUzQkxqc2M4cGdoN2VaZ09xaDJmY2c1OTZrSmNNdXJpTm9NYkc4TjFhSFlYNUt1ZFNnWGtjT3FRNWtuQkhsTXIwa0JjNDJIQS1EVlFiTFBGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZHJEZGU5dTl1eXd1cHRvN0RUZlpQSk9aVW1qR3JadzVnQmdXZzRqcERLekRqM2JsR1pNSnJLSlplZ3ZIc2JMbkxXNEtJOUxnTk9GQXF6M3dYbk1KTW5MRUpYeGdyX1VqOWRTWEJ3UzFDUWxrd3VLaHB0QXVPUzJaNS04eVg2dW9wbXhiYkZfc0xwU0ZYbVdRSDhSX0F5anc1U3h1aWlyRGNHbTdfYTVwVXlsQjVockJGQ1FYOURR?oc=5</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas calcário - G1</t>
+          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - MidiaNews</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORE9Qb29mRHg0MjFfN3NkOEV6TVNVaWdmWnRLUGdHZWNBdjQ1ZFZmc2t4RHZqN2pxUUFJMkJKdWJ4bVdidm9Qc0tNeGNLcVlvZ0V6Uk5lMVI3eGlTUFh6d1VmdUZ0MTA3ZDgwcE12dUdmWjRVVGNLOXF6WmdwZHZmVGo0TUR6V2hWMkp0Wm1PUjlIRGx3VnhLeHo4SmVsdDFwYnRPcDA2YVdfVUEyWi1Eek00aUVoeHk5RDJFb1c5ZlNpZVRCTm1vZmhB0gHYAUFVX3lxTE9KLWE5MnBSVjdkS3JheHpGUWdIS09VRkI0ZUxZcnFRRXFFV3dLSDRIdFRkOTlnTTlaRmVqNkJZMGZGdHhuVHI3blNEcEZyNzFubFNCVlNBV2NET1NiVGFqcU9tSDd5ZmJlX3diS1FJNV9SMnhCZ1ZRaDd5NEVoTTNmcnNBYTVLUnVwWmlmbHVMajdfYXNaT1VRdTFfV0lTQ3VwSDZ0QUpfcFBKb2w5aGhyUUVveldzeF9MdzdxRFZqUF9Wa0ZOcXZwRGFtME5tcXVSNmsxQm13dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeFpET3FNUWdocW04TVhsWXZsQWNvbnpoMWQ0SHhUMWJsMnRvRDk2emRvaGdlYXNEUTlPVUsyaDluRmtTZnk2X3JsT1hKN2t5N2d2X1ZlNDFrVXYxU3hLVVBzcU1WbVJic2VGYkFtSGROX3djTk9oNnB5TWRlR2hGZVpRMEJoYnk2VmdsWHZqU3RnTnJ1S2hVRnpoZ08tYXVXU1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Empresário alvo da PF tem empresas em Rosário e Poconé; saiba quem é - Gazeta Digital</t>
+          <t>PF mira esquema que retirou 34 mil toneladas de calcário e causou prejuízo de R$ 3 milhões em MT - Folha 5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVEo3bkRxQnc0emRmZUlWaFptajgxUjR6bXkyZmlSVEJPWW1OYTFzQmVNYlFtMFZ5dkdycTNDaE5QcVkzTmRfZmVQQWVDZUQ0ZnhaOE9YY2laOWFlMm5UZUdid0pQVy1SWTQ1VGtXUWlTVlJRTkc2WlZfZy10d0NYTUszRHVGUnk3aWoyQTNwelVHZW94YVlYQXBzRnRGZWw2dFBfSnA2SURuODltOGNlSmZKb1lSMkJpLWxoM25QaUlJblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOd1BjR0pwSGpfMkZqbGZfb0hPSzJIZmtMV2oyb3pRZ04zMXBnTGZxOHdQTGJoeW9IN25Tczl1bldyWDFHSGRtZXo5Qjh2aU1JRDBLRHFTeEdZYl9CMV9TRmtyeHFQZ0pTSUl5WGo4bVFiQ1ZrZWgzWEVGdXRDd21GV2N4NHpuaFpUTmEyNmJNVTRiRDN2ZUZGdFZvRkNDRnFXckhuNlFKd2xUbVljTHhNV1ptb0J2S2l4SzBHbTdqV3NoZHljdkFJVWNmLW1DTUJX?oc=5</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Saiba quem é o empresário alvo da PF por esquema de R$ 3 milhões com calcário - FOLHAMAX</t>
+          <t>Empresário alvo da PF tem empresas em Rosário e Poconé; saiba quem é - Gazeta Digital</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYUZzUkNXbWxvcGhSWmJIc2xqLTFwY3p0MXNSMks3dHluTGo2VGpDYldtTnVwSWZGTm52SUtvTFRwSWg3UDV3UGZxajFkY1JQQi1SWjRibFp1dkk4RnI4MGw1bzY3QTZSZy1BZk56cEtkVFB0Q3RUMFNnSWhJQ1ViV1Y3OEtYeVB5VFZRaUR6aDZ5RDVmSXUybC1BQktVXzEzT3Z5RzczQ3QxOEF3VGtQR3R5SzNVZ2lT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVEo3bkRxQnc0emRmZUlWaFptajgxUjR6bXkyZmlSVEJPWW1OYTFzQmVNYlFtMFZ5dkdycTNDaE5QcVkzTmRfZmVQQWVDZUQ0ZnhaOE9YY2laOWFlMm5UZUdid0pQVy1SWTQ1VGtXUWlTVlJRTkc2WlZfZy10d0NYTUszRHVGUnk3aWoyQTNwelVHZW94YVlYQXBzRnRGZWw2dFBfSnA2SURuODltOGNlSmZKb1lSMkJpLWxoM25QaUlJblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas de calcário em MT - G1</t>
+          <t>PF investiga extração de calcário com prejuízo de R$ 3 milhões - MINUTO MT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2326,19 +2326,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbmx0djJaNkM2ZkNYMzdMd3JCa2d6N3YxbUZBUDh1YnhQWjRDaDdUMGZWckllV0tTdmlfOXktbEw3SmhEQ2JneVZTX1JIOS16NGRpTXZuSTRwbGVWTkZ3eGdkc2JPQkJDNEdTXzZ2a0pPUDlOeWpaMF9uMU85WTYySmQweEl0VnE3aUpjWDl5M2pDWWNaMlFmUUxqZEFleXNzVHZ5MFRCeEstWDE5OXNyZFgyUkZ4c1daTkNMMmRJa2ptY2ZqNnZzRUowYmtzQUhuQzdmenl0RUYxSXfSAeoBQVVfeXFMTnNOS3RkOHNCWlB6SHpPT2JQZENXNmtYSWNaLXZ2SENYMnFQVkctVndmVnRxUm85cFh4QlNxUXZNNndIZllRc2J2c3F1TE5GNXczRWhyR2Y5SHdPdEdwdGtDM2JSWktZSzZ6OEhaYUE1RGV3MUFJZ2NvTUlielMzUHJ1NFJUcmRGN0Zma3FpdTlwZjFxZGVud2NNbUJrdjZOejVraTJBNmNqVGhaSmdicFdRMUFGLUhjejhmOHpTbVptaTFodE5VSkNkTEc3aEI5dmFway1hamRlUW45ZEVrVHJrYWRDR0gyeGVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOcmlIZnAxbnk3MnhyYmhhcFRYbmR2RU40ZDg3X1FvT09kNDY1NXBha0xVMmozWFd3cDNzMDc2d3NmTWhKczROZk80OVhWcWxfSzc4bkF2V0JfQTBKZ2tpaU9wUkFheVptSEdPOFp4RGtZYjNfTkU4dWRBYUxqekN0NW5XNW1qTFR0U1FZMTg4Z1hVYnJuc0s2cW93?oc=5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Com alta no enxofre, Mosaic teve prejuízo de US$ 273 milhões no segundo trimestre - globorural.globo.com</t>
+          <t>PF deflagra Operação Peso Bruto contra a extração irregular de calcário em Rosário Oeste - pagina1.com.br</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdHRoWXh3Q0lLR20zYUtlM1NHaWt3MTB0clZBSnhUclVBQVFTeVpJMXFGSzk0UjVHendGMklEMGc3bWYtQVpKYlhqeV9XU0Y5OFF2Q21nQ1lIcmV5NG5xM2RkRTFIZG5xcmtTTG85UXE3UEphTXZvcDlTa0g1R3RMVDJHZDNJYWxyY3BuRVg1Z2RtZERWemxfQWhNZUZ0ZlEzR2paSE1fS2g5NHotaVlES2wwM0hCVWttaEHSAcgBQVVfeXFMUEYxcF82QU5MR2xGZ2liVnJsVHltSmRlRFZicWFKaWFDQ3RSTEdzLWhEbEg5YUZDbV9IcS1zNGppeE5SVlVBN1FxTk91T3pwdnZPaGRFQnBPUHM3MjVCVEhVMV8zV1RjU0VXVTF2V3dIdThoQ3g2LVdUbzVMWlYwaG1MWnhvc0t4aUtfWHhtVGZNby1Fd29fRVAxcE9Ca25BS2dHeVkwSGVIelFiVmc3eVBGVW1kS0N2NlJrZFdmZy1uVERHYXdYWjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRE4xNWZFelh4ZUd2Y3djWU5JaHJVeTAwLWs0akJvY09QWC05RXdobWZjSmNMRjlKbUR2SWRWaXFUbTFtclpudnhmWThaNXBZaFJRYWFaSmloY2hNT0NEczhLWUlKVnVSbGpLU3I2U2xSMFUtYTV0ZU4zTk0ydURaTFRGc0g3c1ZRSnVQSVpmUTFYdUFhSGpUajFMcGpfLTM4Zk9HcnNXZUF1Unp6Z2hVenlHVG82T0c1Zkc2WVMwWkQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PF investiga extração de calcário com prejuízo de R$ 3 milhões - MINUTO MT</t>
+          <t>Saiba quem é o empresário alvo da PF por esquema de R$ 3 milhões com calcário - FOLHAMAX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOcmlIZnAxbnk3MnhyYmhhcFRYbmR2RU40ZDg3X1FvT09kNDY1NXBha0xVMmozWFd3cDNzMDc2d3NmTWhKczROZk80OVhWcWxfSzc4bkF2V0JfQTBKZ2tpaU9wUkFheVptSEdPOFp4RGtZYjNfTkU4dWRBYUxqekN0NW5XNW1qTFR0U1FZMTg4Z1hVYnJuc0s2cW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYUZzUkNXbWxvcGhSWmJIc2xqLTFwY3p0MXNSMks3dHluTGo2VGpDYldtTnVwSWZGTm52SUtvTFRwSWg3UDV3UGZxajFkY1JQQi1SWjRibFp1dkk4RnI4MGw1bzY3QTZSZy1BZk56cEtkVFB0Q3RUMFNnSWhJQ1ViV1Y3OEtYeVB5VFZRaUR6aDZ5RDVmSXUybC1BQktVXzEzT3Z5RzczQ3QxOEF3VGtQR3R5SzNVZ2lT?oc=5</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PF deflagra Operação Peso Bruto contra a extração irregular de calcário em Rosário Oeste - Pagina1mt</t>
+          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRE4xNWZFelh4ZUd2Y3djWU5JaHJVeTAwLWs0akJvY09QWC05RXdobWZjSmNMRjlKbUR2SWRWaXFUbTFtclpudnhmWThaNXBZaFJRYWFaSmloY2hNT0NEczhLWUlKVnVSbGpLU3I2U2xSMFUtYTV0ZU4zTk0ydURaTFRGc0g3c1ZRSnVQSVpmUTFYdUFhSGpUajFMcGpfLTM4Zk9HcnNXZUF1Unp6Z2hVenlHVG82T0c1Zkc2WVMwWkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNMjVPMmg2Y2tPNGx0elVtTUU3Y1M3NFM4cFJ3czFjQndQTWZLOTE5ZmdPd3hkUmtjS3ZlbnZOVngzUnhWRmdRY3EyM0tEbXUzQkxqc2M4cGdoN2VaZ09xaDJmY2c1OTZrSmNNdXJpTm9NYkc4TjFhSFlYNUt1ZFNnWGtjT3FRNWtuQkhsTXIwa0JjNDJIQS1EVlFiTFBGUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CUIDANDO DA NOSSA TERRA: Programa é retomado e garante transporte gratuito de calcário para agricultores familiares - REDE BRASIL DE TELEVISÃO</t>
+          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas calcário - G1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03/08/2026 17:36</t>
+          <t>04/08/2026 04:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX0FBcFhWQXB5RnhJTEdZWlVnR0xFSUJjakMtb1A2dWZBa0s5OWVPUlA5WEFKQ0ctbXVENXJ0NHhRamlwYko2Tm51QkR2TE56NFBCSXgwSm45YUU4V0F4YUg5VG1ERzhWWS05cjUxSVNuWmZZd2RZVDlTS1FwV3NVMEJGWEFVQWtaMjBicGU1QWFuaGFYX1pwS2lzM0JUQ2VzZEtkdjlCNHdqWEFvS19XZWZsR0hrNk1renhiNnpERU1ESUh1T1QwZkVFdDJNSUVaSVlva3NTUkZmdHhWR3pZTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORE9Qb29mRHg0MjFfN3NkOEV6TVNVaWdmWnRLUGdHZWNBdjQ1ZFZmc2t4RHZqN2pxUUFJMkJKdWJ4bVdidm9Qc0tNeGNLcVlvZ0V6Uk5lMVI3eGlTUFh6d1VmdUZ0MTA3ZDgwcE12dUdmWjRVVGNLOXF6WmdwZHZmVGo0TUR6V2hWMkp0Wm1PUjlIRGx3VnhLeHo4SmVsdDFwYnRPcDA2YVdfVUEyWi1Eek00aUVoeHk5RDJFb1c5ZlNpZVRCTm1vZmhB0gHYAUFVX3lxTE9KLWE5MnBSVjdkS3JheHpGUWdIS09VRkI0ZUxZcnFRRXFFV3dLSDRIdFRkOTlnTTlaRmVqNkJZMGZGdHhuVHI3blNEcEZyNzFubFNCVlNBV2NET1NiVGFqcU9tSDd5ZmJlX3diS1FJNV9SMnhCZ1ZRaDd5NEVoTTNmcnNBYTVLUnVwWmlmbHVMajdfYXNaT1VRdTFfV0lTQ3VwSDZ0QUpfcFBKb2w5aGhyUUVveldzeF9MdzdxRFZqUF9Wa0ZOcXZwRGFtME5tcXVSNmsxQm13dQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2426,237 +2426,237 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alepi recebe relatório sobre impacto ambiental da exploração de calcário marinho - parlamentopiaui.com.br</t>
+          <t>CUIDANDO DA NOSSA TERRA: Programa é retomado e garante transporte gratuito de calcário para agricultores familiares - REDE BRASIL DE TELEVISÃO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>03/08/2026 17:00</t>
+          <t>03/08/2026 17:36</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPYlJReXZpUXFUN2JRUTVNVjl5SUwzV093MFlSX0dEdTlsN3Ridm9ZdUQ5bEItTFJ0aUNvTS1sWGJwYVJTdDJCcFE1Qjc1allMVXU5SENlNmFyOS1qbnNBblMyejRXQXFzWHVycHctdVFtN2NTVFVnQlNJZjlXVzVoTGZPa20xVDZvWkg0ZF9rcDFfOGF5M3UzSDAzYlhqUjlIbWc3dzdKNld1Y29mMmw2SDFia1lnNEFEVkRTd3RXX0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX0FBcFhWQXB5RnhJTEdZWlVnR0xFSUJjakMtb1A2dWZBa0s5OWVPUlA5WEFKQ0ctbXVENXJ0NHhRamlwYko2Tm51QkR2TE56NFBCSXgwSm45YUU4V0F4YUg5VG1ERzhWWS05cjUxSVNuWmZZd2RZVDlTS1FwV3NVMEJGWEFVQWtaMjBicGU1QWFuaGFYX1pwS2lzM0JUQ2VzZEtkdjlCNHdqWEFvS19XZWZsR0hrNk1renhiNnpERU1ESUh1T1QwZkVFdDJNSUVaSVlva3NTUkZmdHhWR3pZTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - Portal do Agronegócio</t>
+          <t>Alepi recebe relatório sobre impacto ambiental da exploração de calcário marinho - parlamentopiaui.com.br</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>03/08/2026 13:30</t>
+          <t>03/08/2026 17:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQY0VQM29hUjJobThyTXFqR3M0bm5LNXlwTEN0YmJMeEtGaWxZM3p6UHpsdzhJQ2VuZE9DOHdDZ3ppWGREdVpteUNGTGphYXhZejk1X19tMkV1RERPSlU5YWJJMzVYRUJkZlBhWjBNdldhUW5lajhZUkFfX2U4emdjeDdSNUJJZkhnbmN5Y05LU3pQUkZaUHhXX2d6OVk0TlFYbFdGT1AxVUZqWTVHcVVXMEM5YmdhTldXQVhtTVlmYzh3ZnJHY3dDOGdMamh3UmNhZEMxUTZxVDkzaVlUcXZrQWczcHp0YnJsc2NmU1BMQTNrMXRyMnhkMHZNRU5ubFljX3FKZDBXaWN2NlpCQjNUVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPYlJReXZpUXFUN2JRUTVNVjl5SUwzV093MFlSX0dEdTlsN3Ridm9ZdUQ5bEItTFJ0aUNvTS1sWGJwYVJTdDJCcFE1Qjc1allMVXU5SENlNmFyOS1qbnNBblMyejRXQXFzWHVycHctdVFtN2NTVFVnQlNJZjlXVzVoTGZPa20xVDZvWkg0ZF9rcDFfOGF5M3UzSDAzYlhqUjlIbWc3dzdKNld1Y29mMmw2SDFia1lnNEFEVkRTd3RXX0Y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - Jornal Opção</t>
+          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - portaldoagronegocio.com.br</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>02/08/2026 15:00</t>
+          <t>03/08/2026 13:30</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPd2pmTzdLTS1MYzhVMGhjY0VfSlBxZ045aWJZcEZoQ3ZPVkgyZ1FiRWF3T2NwaFhTckh1LVBSVldoUU9sVTg3UkNPcWNXYjJtTzkydmQ1bWZnWG03UXNrSTFaYmZDNVZQWjN6dWVMQ2E3b2tmMVlEYkZIbDlOREIxbkdYN09ZNXRuVjgzVDlyb0MtNzBidmVIaFNPRFM1RndSR1ROa3BsVHBvNUY0X3dYVzhsMEJ4ZTNHVnhsWG1nVUhDTzNKNVdVQ3NFSlRSXzY1aWNubGpxRGk0U2dDSXhoSnE3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQY0VQM29hUjJobThyTXFqR3M0bm5LNXlwTEN0YmJMeEtGaWxZM3p6UHpsdzhJQ2VuZE9DOHdDZ3ppWGREdVpteUNGTGphYXhZejk1X19tMkV1RERPSlU5YWJJMzVYRUJkZlBhWjBNdldhUW5lajhZUkFfX2U4emdjeDdSNUJJZkhnbmN5Y05LU3pQUkZaUHhXX2d6OVk0TlFYbFdGT1AxVUZqWTVHcVVXMEM5YmdhTldXQVhtTVlmYzh3ZnJHY3dDOGdMamh3UmNhZEMxUTZxVDkzaVlUcXZrQWczcHp0YnJsc2NmU1BMQTNrMXRyMnhkMHZNRU5ubFljX3FKZDBXaWN2NlpCQjNUVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Catalão: Prefeito Velomar Rios reforça apoio à Mosaic durante reunião em São Paulo - Portal Serra Dourada News</t>
+          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - Jornal Opção</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>01/08/2026 04:00</t>
+          <t>02/08/2026 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPN1JlMmFtcTVBZGRLNnQ2OVpUN3g2UEFnQzRzQXZyOENDSTZrOWhjLTNmaE50Ql9FNFNfUzR1cnZUR3lGbHpNUXo4NmJyOVVUOW9tM1VqM3pMMjFxbWhPcEprb29qT09UOHlZejNFQTBhVk5sMDI5NndJRWFNZ3lwQkZjRHJxWDZvN2MybGdMbEh5VkE3VVhPREd5cl95Y1ZYUGgxaFlFdThOQXdMWkxjSk1vOGFyMVdVSThUMzFYSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPd2pmTzdLTS1MYzhVMGhjY0VfSlBxZ045aWJZcEZoQ3ZPVkgyZ1FiRWF3T2NwaFhTckh1LVBSVldoUU9sVTg3UkNPcWNXYjJtTzkydmQ1bWZnWG03UXNrSTFaYmZDNVZQWjN6dWVMQ2E3b2tmMVlEYkZIbDlOREIxbkdYN09ZNXRuVjgzVDlyb0MtNzBidmVIaFNPRFM1RndSR1ROa3BsVHBvNUY0X3dYVzhsMEJ4ZTNHVnhsWG1nVUhDTzNKNVdVQ3NFSlRSXzY1aWNubGpxRGk0U2dDSXhoSnE3SQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - CompreRural</t>
+          <t>Catalão: Prefeito Velomar Rios reforça apoio à Mosaic durante reunião em São Paulo - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>31/07/2026 13:59</t>
+          <t>01/08/2026 04:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNa2dNSHBOQmp0SndMbUp2YnpSM2pEVjUtejVHZ0NDOHZVWFRra0xXX1pXUFZnZzlFQVM1THpySWMwS0tERjhSLXdIMVVaVEFYYTBkalRoMTZ4WEdKZ3pEb1FwQTVvN0JFTm4tczJaal9sNUpTSXk4RjRkR1pJR1pGbFcta0VTSkhPNmQxLXhJZllubnZISFR4RTI4QmFEN0tfUWJxYlpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPN1JlMmFtcTVBZGRLNnQ2OVpUN3g2UEFnQzRzQXZyOENDSTZrOWhjLTNmaE50Ql9FNFNfUzR1cnZUR3lGbHpNUXo4NmJyOVVUOW9tM1VqM3pMMjFxbWhPcEprb29qT09UOHlZejNFQTBhVk5sMDI5NndJRWFNZ3lwQkZjRHJxWDZvN2MybGdMbEh5VkE3VVhPREd5cl95Y1ZYUGgxaFlFdThOQXdMWkxjSk1vOGFyMVdVSThUMzFYSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Agricultor adquire 30 toneladas de calcário agrícola com laudo garantindo alta concentração de neutralização, aplica no solo e nota que a acidez da terra permaneceu inalterada, comprometendo o plantio de 10 hectares de feijão - Correio Braziliense</t>
+          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - CompreRural</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>31/07/2026 04:00</t>
+          <t>31/07/2026 13:59</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPb0pYYkloaDlJOW1HRERkUW03XzFaWVBTVXVYRzNiWjhTN0hMWVE0bnNkWlBTSm1FdW42c1NZZXg3QVJqMXE2TW02aFoxUDhCQk5kQ0lSSWVoSF93UnNMS2NLV19qZjJld1dKRjJNdnRZSlNUUVN5c0tlNmhXZGFlWHByajhwNkRtOTBXNHhVMVp1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNa2dNSHBOQmp0SndMbUp2YnpSM2pEVjUtejVHZ0NDOHZVWFRra0xXX1pXUFZnZzlFQVM1THpySWMwS0tERjhSLXdIMVVaVEFYYTBkalRoMTZ4WEdKZ3pEb1FwQTVvN0JFTm4tczJaal9sNUpTSXk4RjRkR1pJR1pGbFcta0VTSkhPNmQxLXhJZllubnZISFR4RTI4QmFEN0tfUWJxYlpR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Clusters ferro-enxofre abrem novas frentes no manejo de pragas - Global Crop Protection</t>
+          <t>Agricultor adquire 30 toneladas de calcário agrícola com laudo garantindo alta concentração de neutralização, aplica no solo e nota que a acidez da terra permaneceu inalterada, comprometendo o plantio de 10 hectares de feijão - Correio Braziliense</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>30/07/2026 11:26</t>
+          <t>31/07/2026 04:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQLXd0RWlHeWpRendDMGNUMklrZlFEWV9PbnNxLWZ0a1NsdXMxS1hQa2lONXRlMk1peWF1Ny1JNWRyYk9Ddk43TTh3MWQ3MUtBU1VreFZGc0tYZjdzZVdlNUU4Ry1OT05lVE1qSEpZZGh3SWYzcjNCV1ZscURkNlpONmFqblY2Z25QdV9WZ3R6d1pZTVB4TlFOOFlnUG16UFpqdHozU0VRRkpoNXI3amRWVVVYOHdRLUhnUVZnUWw2YUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPb0pYYkloaDlJOW1HRERkUW03XzFaWVBTVXVYRzNiWjhTN0hMWVE0bnNkWlBTSm1FdW42c1NZZXg3QVJqMXE2TW02aFoxUDhCQk5kQ0lSSWVoSF93UnNMS2NLV19qZjJld1dKRjJNdnRZSlNUUVN5c0tlNmhXZGFlWHByajhwNkRtOTBXNHhVMVp1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Portal Revista Kdea 360</t>
+          <t>Clusters ferro-enxofre abrem novas frentes no manejo de pragas - Global Crop Protection</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>30/07/2026 11:09</t>
+          <t>30/07/2026 11:26</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQLXd0RWlHeWpRendDMGNUMklrZlFEWV9PbnNxLWZ0a1NsdXMxS1hQa2lONXRlMk1peWF1Ny1JNWRyYk9Ddk43TTh3MWQ3MUtBU1VreFZGc0tYZjdzZVdlNUU4Ry1OT05lVE1qSEpZZGh3SWYzcjNCV1ZscURkNlpONmFqblY2Z25QdV9WZ3R6d1pZTVB4TlFOOFlnUG16UFpqdHozU0VRRkpoNXI3amRWVVVYOHdRLUhnUVZnUWw2YUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
+          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Portal Revista Kdea 360</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>30/07/2026 04:00</t>
+          <t>30/07/2026 11:09</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
+          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>29/07/2026 22:32</t>
+          <t>30/07/2026 04:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 16 - ArchDaily</t>
+          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>29/07/2026 17:56</t>
+          <t>29/07/2026 22:32</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPbTdDNHJBU0ZTWDk5OERHXzBaU1RkdnQwVlZkSHZzVmt5VXdjMnhjSXhLR1N4cWlpUmNVM1p0V1ZtdHRUNTVSVU53c2lzTy1rVWFDOVNFY05GNzFobVE2U3RlWHNxZl9Yb2JCdXE0aGZKVENTZElzQUpZYlRjMGV2N0dwQVZoR0oyN2NOVFdEYjlYdmx4aENJaDNLMWRqTmRLdEVvQWptNXhpNW02aFFKTW9sc1kwRkQ4U2dkMERueVM2UkRZYmo3RG51aHdtWnh5RFZsVFRNblZtY1pQeFRDVlVXR3NZbzRnN1FIR1UxcVNwVWtfTmhQTWZaQ0FtazA1dlR4b1pkaTBxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
         </is>
       </c>
     </row>
@@ -2668,39 +2668,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 21 - ArchDaily</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 16 - ArchDaily</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>29/07/2026 10:36</t>
+          <t>29/07/2026 17:56</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQbmJlajh6WXU1TENBOFk0d2pic3EtLWxPQjRzZGVDVXRMYzlhZ1lId2xNTWVtY0l3V1I1S0pzN0dKSlIxQXNZY29DckdNcWpZLVJXNnA4VWNqTTdRblR5OGI4LVZJUEs2VmxKdTlJV1RKN181alFQbG84elVpY1o3SDJValF2MG5sdmpuNS1vTWFIQTBZUDV1V0EyaGZJT0pNUTlkcndMNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPbTdDNHJBU0ZTWDk5OERHXzBaU1RkdnQwVlZkSHZzVmt5VXdjMnhjSXhLR1N4cWlpUmNVM1p0V1ZtdHRUNTVSVU53c2lzTy1rVWFDOVNFY05GNzFobVE2U3RlWHNxZl9Yb2JCdXE0aGZKVENTZElzQUpZYlRjMGV2N0dwQVZoR0oyN2NOVFdEYjlYdmx4aENJaDNLMWRqTmRLdEVvQWptNXhpNW02aFFKTW9sc1kwRkQ4U2dkMERueVM2UkRZYmo3RG51aHdtWnh5RFZsVFRNblZtY1pQeFRDVlVXR3NZbzRnN1FIR1UxcVNwVWtfTmhQTWZaQ0FtazA1dlR4b1pkaTBxUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crise do enxofre ameaça produção agrícola no Pará e no Brasil - Bacana News</t>
+          <t>Galeria de Limestone, Granite and Travertine - 21 - ArchDaily</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>29/07/2026 07:18</t>
+          <t>29/07/2026 10:36</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQZG1UZUhyT1JFSW1zcC1ySjNRRlpwRVhKbEVrS3RHYTBWdGUtV0NxOWUwTG41Q1FVcF9MbVZMYXBXRkpSN2dvbjdGVU1NdDlEa245amJDTWNRNFlyRnpudEI3ck5SSVl6cjQ4cm5sdzVxVUZBTE81ckFxLUFzblZlRlJIOFBjR3dINEVPN2ZmM3hhQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQbmJlajh6WXU1TENBOFk0d2pic3EtLWxPQjRzZGVDVXRMYzlhZ1lId2xNTWVtY0l3V1I1S0pzN0dKSlIxQXNZY29DckdNcWpZLVJXNnA4VWNqTTdRblR5OGI4LVZJUEs2VmxKdTlJV1RKN181alFQbG84elVpY1o3SDJValF2MG5sdmpuNS1vTWFIQTBZUDV1V0EyaGZJT0pNUTlkcndMNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2712,17 +2712,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Selada por 5,5 milhões de anos, caverna na Romênia abriga vida sem luz solar em água rica em enxofre e ar quase irrespirável - Revista Oeste</t>
+          <t>Crise do enxofre ameaça produção agrícola no Pará e no Brasil - Bacana News</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>29/07/2026 04:00</t>
+          <t>29/07/2026 07:18</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcFJCZGs0N0xZVWhFMDJiSGwyV2NnYVN5dEtLbExqTGJQbldTdmt0Sy1aRHdDSjVkc2lwSC1laTdPUHFjT2tYcERaR1JCNDVWcXpLTHVvRV9ISlZ4dElUQTlwTnNEQzNjUG1oQ1BwSUFpMDBKczluNzI1LTJpZU9SR3RvR203S3RkVEtZRmR6TDJzSG1YVW1vSFZTQ2xKNl9mYndDS2pzNkR1RjB1MXhtZ0o0eWZmbnloZHZuSzRybUFTelZWajBRREszN3BCdGYxNnZLRDJwM1BTMTZERXZod0JKTGpXSFFHak1JOEZ3YnVoVTFMaXFDMmpZeGppXzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQZG1UZUhyT1JFSW1zcC1ySjNRRlpwRVhKbEVrS3RHYTBWdGUtV0NxOWUwTG41Q1FVcF9MbVZMYXBXRkpSN2dvbjdGVU1NdDlEa245amJDTWNRNFlyRnpudEI3ck5SSVl6cjQ4cm5sdzVxVUZBTE81ckFxLUFzblZlRlJIOFBjR3dINEVPN2ZmM3hhQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
+          <t>Selada por 5,5 milhões de anos, caverna na Romênia abriga vida sem luz solar em água rica em enxofre e ar quase irrespirável - Revista Oeste</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxNcFJCZGs0N0xZVWhFMDJiSGwyV2NnYVN5dEtLbExqTGJQbldTdmt0Sy1aRHdDSjVkc2lwSC1laTdPUHFjT2tYcERaR1JCNDVWcXpLTHVvRV9ISlZ4dElUQTlwTnNEQzNjUG1oQ1BwSUFpMDBKczluNzI1LTJpZU9SR3RvR203S3RkVEtZRmR6TDJzSG1YVW1vSFZTQ2xKNl9mYndDS2pzNkR1RjB1MXhtZ0o0eWZmbnloZHZuSzRybUFTelZWajBRREszN3BCdGYxNnZLRDJwM1BTMTZERXZod0JKTGpXSFFHak1JOEZ3YnVoVTFMaXFDMmpZeGppXzA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
+          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2810,19 +2810,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
+          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2832,29 +2832,29 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - Estadão MT</t>
+          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>28/07/2026 21:26</t>
+          <t>29/07/2026 04:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2866,61 +2866,61 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Distribuição de calcário a produtores rurais começa nesta semana em Santa Helena - Universo da Notícia</t>
+          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - Estadão MT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>28/07/2026 14:26</t>
+          <t>28/07/2026 21:26</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSFoxVDBKSzNXdUtXMlplcU5KSWNoX1BxSklMZ2VDTEMwQl9YWlFQRW5NUzN2VDVmVS02aEJ2QnVFajJXYWNRSDEzRGxLRUdHRE83SEo2OFpfMW90a3BMRHprUHpXZzEtam52TE9WaW9TZ281SEgwc0l6em9mZGVpai1ybTRIcUk3S05sVVVNeXNycEQ1SHRKYWRhWHYwZlY1SWNvVk9Rbk1waDlpeXRjb1FOUDNBYTB5bjRyT05ENEd0b1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Quarta semana consecutiva de alta da ureia nos portos brasileiros e os possíveis impactos para as compras da próxima safra - Cana Online</t>
+          <t>Distribuição de calcário a produtores rurais começa nesta semana em Santa Helena - Universo da Notícia</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>28/07/2026 10:20</t>
+          <t>28/07/2026 14:26</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcFdYTUE0NlRaT3ZYc0l2MzBmdjlWQ1Y4VkZhUzJqa0plOVcyeXg0ZEdheWdCb2hXUXRqel9MUFpwNFFPOFh1dDZGcWVPM1NhaHFOTnlZSVV5NUtPYzhVUFh6SUpEaVYtWUJWcGxROFJ6RmdZMkpUWUl1eEl2R2ZOMXpZa0xCMlJ3azZHNWl3Z1Z3M0xmSVNSNlpkT0FIN29vb0Rqc3l3dm8xazRzVWl1OEp3TGpFcjY5dVBRclVFX0ZZSkd5NjkzV29BdkFkVm1OMkF3Z0wyUXZ1OEJsX0NJLTAyeWd5bHJHQm5GbEJ1OGJfOXY5X3JZNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSFoxVDBKSzNXdUtXMlplcU5KSWNoX1BxSklMZ2VDTEMwQl9YWlFQRW5NUzN2VDVmVS02aEJ2QnVFajJXYWNRSDEzRGxLRUdHRE83SEo2OFpfMW90a3BMRHprUHpXZzEtam52TE9WaW9TZ281SEgwc0l6em9mZGVpai1ybTRIcUk3S05sVVVNeXNycEQ1SHRKYWRhWHYwZlY1SWNvVk9Rbk1waDlpeXRjb1FOUDNBYTB5bjRyT05ENEd0b1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Quarta semana consecutiva de alta da ureia nos portos brasileiros e os possíveis impactos para as compras da próxima safra - Cana Online</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>28/07/2026 09:25</t>
+          <t>28/07/2026 10:20</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE8waGNjYVp0Q0tiRlZJQmxiaFhDRlZ6U2tuZEhLcnRMZER4WGw0TndNeUFjVUd4MUVHZVRWOEdiVXRpUU4ydXdHSEZRV1lQa25idnM3ejQ3U2dseldHQWR5c2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcFdYTUE0NlRaT3ZYc0l2MzBmdjlWQ1Y4VkZhUzJqa0plOVcyeXg0ZEdheWdCb2hXUXRqel9MUFpwNFFPOFh1dDZGcWVPM1NhaHFOTnlZSVV5NUtPYzhVUFh6SUpEaVYtWUJWcGxROFJ6RmdZMkpUWUl1eEl2R2ZOMXpZa0xCMlJ3azZHNWl3Z1Z3M0xmSVNSNlpkT0FIN29vb0Rqc3l3dm8xazRzVWl1OEp3TGpFcjY5dVBRclVFX0ZZSkd5NjkzV29BdkFkVm1OMkF3Z0wyUXZ1OEJsX0NJLTAyeWd5bHJHQm5GbEJ1OGJfOXY5X3JZNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2932,17 +2932,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
+          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>28/07/2026 04:00</t>
+          <t>28/07/2026 09:25</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE8waGNjYVp0Q0tiRlZJQmxiaFhDRlZ6U2tuZEhLcnRMZER4WGw0TndNeUFjVUd4MUVHZVRWOEdiVXRpUU4ydXdHSEZRV1lQa25idnM3ejQ3U2dseldHQWR5c2pR?oc=5</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - Blog do Esmael</t>
+          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,19 +2964,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - Brasil Mineral</t>
+          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - Blog do Esmael</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2986,41 +2986,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPcmVCLTNDSlR3bG9veGZHSnZrZThiTExVb2hsQ3dOT2FjbWN1ZG9aMkt3a1YtVWFNRWhPemxaWnpTT3FCQWdTRE9PRG9vVjM3TWduMFhBNFZMaEtVY1VCaC1VRmJBOGJ2LVZJRXNuQXI2TUw5d2VMN2V1amp2UWNwU0J2VlA1WnJnQ3lSTWZ2dFIzdDJPNFNfQlB4YUFOdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Petróleo e ureia aliviam custos no campo gaúcho - Agrolink</t>
+          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - Brasil Mineral</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>27/07/2026 04:00</t>
+          <t>28/07/2026 04:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNUl4M1J3UVd2UTNSUHMxQWVhWEJLMXFsQjZydk9BZ1RaOGxkUVNHdnlydVpYYUkyX25zcnZpcnoyQVlJQnBIdzE3VlFVdS1lNmh4Z3pRNEpsOTJNRzhkYjFiXzBPTXh0cmFyNWM3X0MzTXdSZGVKbkJIRDk0ZzlDM0RMaVdTLTlIellKWGV5RkhuNXRPRHFzamNCcE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPcmVCLTNDSlR3bG9veGZHSnZrZThiTExVb2hsQ3dOT2FjbWN1ZG9aMkt3a1YtVWFNRWhPemxaWnpTT3FCQWdTRE9PRG9vVjM3TWduMFhBNFZMaEtVY1VCaC1VRmJBOGJ2LVZJRXNuQXI2TUw5d2VMN2V1amp2UWNwU0J2VlA1WnJnQ3lSTWZ2dFIzdDJPNFNfQlB4YUFOdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - revistacultivar.com.br</t>
+          <t>Petróleo e ureia aliviam custos no campo gaúcho - Agrolink</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,19 +3030,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNUl4M1J3UVd2UTNSUHMxQWVhWEJLMXFsQjZydk9BZ1RaOGxkUVNHdnlydVpYYUkyX25zcnZpcnoyQVlJQnBIdzE3VlFVdS1lNmh4Z3pRNEpsOTJNRzhkYjFiXzBPTXh0cmFyNWM3X0MzTXdSZGVKbkJIRDk0ZzlDM0RMaVdTLTlIellKWGV5RkhuNXRPRHFzamNCcE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ureia já aumentou 14% em quatro semanas - Correio do Povo</t>
+          <t>Guerra do Irã afeta fornecimento global de enxofre e crise afeta agricultura e até saneamento no Brasil - G1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNRUJhYXZkbF9aU0k2LXYtS0I2aHR2Y3NHWXZDUG5EOGJCQS1fdGViUmhSTkF1dmhMU0xISDNDVU5mcTlITHNWN1NmNzAwbm9ROFhrSUJtMkFHX0JyT0tfZWs3YVdUWTAwSDJwM2JoVHNqbTlreUtQY0RDME5YRHNRZlBwTmZLV3duMms4UlVRTHJUMXh1QXNfWVFuRFNMTTAwQko4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNYmdob2ExRWhKcGxUNVdMM0FDVXFyZ2JKdkxTOGRHV2N5RDhJeDZOazJaeTNEYVpvX2NKLTlPVGdlNWxrUDhWMUk4dDFGajdRYWp1Y3RiQXZpdEVZU1FRQWR2LWZ5endONmdPVjlKalduTkNSclJ5ZHhYVzFFRE1Pdmt2dDlNSWx4UjR5LVhyWGYtd2ZKeUNDUGNBdEhqeV95VUxsX19wMzAtVmV0M1BUS3BaNHJlcTJMalAwZ1Y3R1gtcmp4Zm9ld2RISnFmcE15YmwxLVdyRWhSelpCamhSaDhuVXM2OTNYd0liOHppbXJZaXfSAYICQVVfeXFMTWQzRTd1WXpuenFtT3JYWGtqeE5SRm9GN2ZETjdvbDV4TnpldUJ5MGRMcW9Va0JZbGlzRjF3cXFZU01lajlYN05URmVWU095WE5wbmRuRi16a3FCRVFKemNDVG05X1ZMYmRWTkRjWkFVUVJzYzZTMlRGYldzVzVpV1FQTHQ2UWVzZmJ0MmszWFlxZEJYRHdJRVpnOFpmdmZZN3lPU3dHU0NFUTAtLUxXS3NVNkNBTkFOWnVCQzFUOUhqdE1hU29mQnRmS3lXZG9weDByRlRMb05JbllGXzBHODg2cV9kMGE0N1lGdkotbnlJb2tkU2htMU1TMHFERFItUjB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Guerra do Irã afeta fornecimento global de enxofre e crise afeta agricultura e até saneamento no Brasil - G1</t>
+          <t>Ureia já aumentou 14% em quatro semanas - Correio do Povo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNYmdob2ExRWhKcGxUNVdMM0FDVXFyZ2JKdkxTOGRHV2N5RDhJeDZOazJaeTNEYVpvX2NKLTlPVGdlNWxrUDhWMUk4dDFGajdRYWp1Y3RiQXZpdEVZU1FRQWR2LWZ5endONmdPVjlKalduTkNSclJ5ZHhYVzFFRE1Pdmt2dDlNSWx4UjR5LVhyWGYtd2ZKeUNDUGNBdEhqeV95VUxsX19wMzAtVmV0M1BUS3BaNHJlcTJMalAwZ1Y3R1gtcmp4Zm9ld2RISnFmcE15YmwxLVdyRWhSelpCamhSaDhuVXM2OTNYd0liOHppbXJZaXfSAYICQVVfeXFMTWQzRTd1WXpuenFtT3JYWGtqeE5SRm9GN2ZETjdvbDV4TnpldUJ5MGRMcW9Va0JZbGlzRjF3cXFZU01lajlYN05URmVWU095WE5wbmRuRi16a3FCRVFKemNDVG05X1ZMYmRWTkRjWkFVUVJzYzZTMlRGYldzVzVpV1FQTHQ2UWVzZmJ0MmszWFlxZEJYRHdJRVpnOFpmdmZZN3lPU3dHU0NFUTAtLUxXS3NVNkNBTkFOWnVCQzFUOUhqdE1hU29mQnRmS3lXZG9weDByRlRMb05JbllGXzBHODg2cV9kMGE0N1lGdkotbnlJb2tkU2htMU1TMHFERFItUjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNRUJhYXZkbF9aU0k2LXYtS0I2aHR2Y3NHWXZDUG5EOGJCQS1fdGViUmhSTkF1dmhMU0xISDNDVU5mcTlITHNWN1NmNzAwbm9ROFhrSUJtMkFHX0JyT0tfZWs3YVdUWTAwSDJwM2JoVHNqbTlreUtQY0RDME5YRHNRZlBwTmZLV3duMms4UlVRTHJUMXh1QXNfWVFuRFNMTTAwQko4?oc=5</t>
         </is>
       </c>
     </row>
@@ -3103,66 +3103,66 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
+          <t>Calcário ultrafino melhora microbiologia do solo, diz estudo - Revista Cultivar</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>25/07/2026 04:00</t>
+          <t>27/07/2026 04:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQNXhhYnc0VGZFOEdldDFmUm1iNWRKVENuVGIzRmN3VTl4NG1NajlYRDhBUFY4Y2pQbjNzTDJYdWFEU29tYUs0SnJqekprbTNfTU9DRjR0YmkzT0gwQzROZzJhaDQ0U0pKRWxOQ1lESnNaMU12ZUNIbXBWZ1JxV1llVTlDSFlqM0toX1d3bVYzNHpYZmVMUEswUVJGc3VIRFhu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - nossasenhoradolivramento.mt.gov.br</t>
+          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>25/07/2026 04:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
+          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - Prefeitura de Nossa Senhora do Livramento - MT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>23/07/2026 04:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
+          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3206,29 +3206,29 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
+          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>22/07/2026 04:00</t>
+          <t>23/07/2026 04:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
         </is>
       </c>
     </row>
@@ -3279,34 +3279,34 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
+          <t>Costa do Marfim: Banco Africano de Desenvolvimento concede um financiamento de 200 milhões de euros para reforçar a produção de combustíveis com baixo teor de enxofre - African Development Bank Group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>21/07/2026 04:00</t>
+          <t>22/07/2026 04:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wJBVV95cUxPZ3ltamlDUFg4Z0E1LW9Kak9Ic05rdTN5QmIxczBiR2NPaGctMnpjTEd3NnpmbFNscEdjS2dyUEcxVUlmcnpJbnRJd1YyS1lSTldxUVNYalc2eFpjdXVmcDNhWEVpNzM0cTZYTVZJenhLTzFaOUVZZjB3RzBIamg1cW1ma3BkSUNKNFlsV0ozajloVk9QQ3BNTVhOWVI5NExRXzNWYmhnU2p0QUpNMk5YSHFRbEhvbTE5UEstdktEU1p6UG04R1pqMmxZRHlGYklCc0hKcW9KVDZSamlUWEIyeVhsSEZaWDF3cFpoTjE0aG93RmFlT0VqUFVUNE1TOWNjTGh2ZU5CcXA2dDJmY01abkw0SVg3b0YwUm9CNGJHS2tzbDNKT0lEQV9wZU1nMXotbF9xQnp5cGU2Z3NHb1ctTE5faTcwX2dCenVCSWtTaUUtaFM0SWdZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3316,41 +3316,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8zeWNfMmcyX1J4RksyM1E1SXhSY0E1eU9mckdDNHVJWVhJQkpUcm9vX01jS1kzVVk0eFllcWMzWU9maUpnNl9yTDRIdzZsVWdvNFo0TS1YX2JEMERGLXhLeVBIQ2x0aUZBWHZZbkptUmg1XzVxNGdB0gF8QVVfeXFMUC1GLVE4YWZkRnZJY1BmYUcyc2gtSjdoU0VFOTd5cGI1UnM5enFSZ3RNVmxVUHhJandINXNGUG5rTkpaWVJzSEZCR2FfVVJuamRfRFF3RmsyaDNYdnFUanE0cVhFZTJUc19ZU0pxbGNxMnN0LUhfc3NxaWJfRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
+          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>20/07/2026 04:00</t>
+          <t>21/07/2026 04:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8zeWNfMmcyX1J4RksyM1E1SXhSY0E1eU9mckdDNHVJWVhJQkpUcm9vX01jS1kzVVk0eFllcWMzWU9maUpnNl9yTDRIdzZsVWdvNFo0TS1YX2JEMERGLXhLeVBIQ2x0aUZBWHZZbkptUmg1XzVxNGdB0gF8QVVfeXFMUC1GLVE4YWZkRnZJY1BmYUcyc2gtSjdoU0VFOTd5cGI1UnM5enFSZ3RNVmxVUHhJandINXNGUG5rTkpaWVJzSEZCR2FfVVJuamRfRFF3RmsyaDNYdnFUanE0cVhFZTJUc19ZU0pxbGNxMnN0LUhfc3NxaWJfRA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
+          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,95 +3360,95 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
+          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20/07/2026 03:43</t>
+          <t>20/07/2026 04:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858279b0c74c46b4f2b6a23b838d75&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>19/07/2026 04:00</t>
+          <t>20/07/2026 03:43</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b122981449e2a5cd9221ff2f0bb4&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>17/07/2026 20:39</t>
+          <t>19/07/2026 04:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>17/07/2026 04:00</t>
+          <t>17/07/2026 20:39</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3482,29 +3482,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>17/07/2026 04:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3514,19 +3514,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNWFFMUTRpZHJ3QjRFY3RzSkJiNHhpYnhXX2J0ZVk2Sk1XNEZ5OTFsbmFVekhtR1E5MDd2a2tJdzdFWE1CNUVpczl4cHRDQlp4aHhhbkJtRzhlajhlRU1lTUs1ZXRsdWhTdXN0Wko1em9VUzNqamFCSXBJSmxQUmRVUjJMNlhOWDJ1ZEN6RzNqNEYzdXVIZFlMRnhQNHdBZm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3548,29 +3548,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' - UOL</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - farmnews.com.br</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>15/07/2026 04:00</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTkxyWkdnWjVncmNISHdDSW82bTRtVzQtWUtTdXhENjJpczl4anRSR2htWklCMm1VTVZ6TU5BeTZNQ2UySV9pd3JBdkNXbkZGUnBPYUNkcWttZHNOTk9Xbmo2eVBJZVZXU3ZNcVd4S013a2Y5MjB4eDdYWXcyUFlVNGY0Y2ZGckVhLUltX283Z1lsbjBtbzVkVEJlVk5XSzdXLVl1SmFla3VXRWJtUE8tY2JFTUlTYzBBcktJV2Zra01PNVhneDZwQkVNQW9TNHRyZGE5bUdrVkNLNmQxUHBV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNWFFMUTRpZHJ3QjRFY3RzSkJiNHhpYnhXX2J0ZVk2Sk1XNEZ5OTFsbmFVekhtR1E5MDd2a2tJdzdFWE1CNUVpczl4cHRDQlp4aHhhbkJtRzhlajhlRU1lTUs1ZXRsdWhTdXN0Wko1em9VUzNqamFCSXBJSmxQUmRVUjJMNlhOWDJ1ZEN6RzNqNEYzdXVIZFlMRnhQNHdBZm8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' - UOL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,41 +3580,41 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTkxyWkdnWjVncmNISHdDSW82bTRtVzQtWUtTdXhENjJpczl4anRSR2htWklCMm1VTVZ6TU5BeTZNQ2UySV9pd3JBdkNXbkZGUnBPYUNkcWttZHNOTk9Xbmo2eVBJZVZXU3ZNcVd4S013a2Y5MjB4eDdYWXcyUFlVNGY0Y2ZGckVhLUltX283Z1lsbjBtbzVkVEJlVk5XSzdXLVl1SmFla3VXRWJtUE8tY2JFTUlTYzBBcktJV2Zra01PNVhneDZwQkVNQW9TNHRyZGE5bUdrVkNLNmQxUHBV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>14/07/2026 04:00</t>
+          <t>15/07/2026 04:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - G1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNTUZhRXRNY2trQVZ1YkFrZTVzNEdyX0xBSkZOdGduN080THhRLWNrRzNRV2piY1hPSkNOaDZxcWh0a2NnNzZOR2hGeHR4Rkh2QjdVNDlDdXhlcFhlRVB5R0JEUHp4c1lhRFh6bmdJdWlRU1h1WEhkQ2VONEhrUWZBVnRJRl81SE1sN0Z3dGx6dGxTd2NDUzYxM01oVHdKTVRVMDlXZXMxZmF0SnFrTjNPUjZtZlRtamVwTmZxaG1SLWtMYWxaa1E3OEVFTlBkQkRQb2ZIQ1AtSkdPVXRwQUN4aHBtdmZXVnNQYUtydUxzeXTSAf8BQVVfeXFMUEtWemJJN0VvVFA5R2c0WE43dWdwQW1qaXZBMGZzdUlzVWc3NXI1LWE1cE9ZT05Fb2JRbVAxdUdVSHZhWVpwa2VDU0NVbFBSNHVZZnNFZVdQN0loOVlUeUtKMll4d2xLclh3dXhTYVZSM3dHNXBSWXNMUGhydEcwYU1Lc1B5RHU4cEpQclFNNEZMZXZjeUp6QjVCc3l2anp4Ymw0M0VmNU9kQ2hlaUMtZ1c4VTg5eWF2eXhoMXh0UERTSUdORlcwQ0hCUDZTd21GUEdVYVM4aEFVTi1mWUxzbVZyUnhQdGhfcF9wdmxzSUtDYmh1dGVqX0pFa1g2QnFV?oc=5</t>
         </is>
       </c>
     </row>
@@ -3653,22 +3653,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>14/07/2026 04:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,19 +3690,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
+          <t>Maior demanda pela ureia interrompe movimento de queda em julho - farmnews.com.br</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3763,66 +3763,66 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
+          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12/07/2026 07:11</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>12/07/2026 04:00</t>
+          <t>12/07/2026 07:11</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>11/07/2026 04:00</t>
+          <t>12/07/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3834,17 +3834,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
+          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>11/07/2026 04:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Crise no enxofre leva Mosaic a hibernar unidade em Uberaba - G1</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,19 +3888,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTUFLaTJkNWxYamJpNUFReXhFRG12WFNvQ1A5cnBlZ3VVSGFUVFhXaFhyMEZ1MmtrTzZoeEgxVFFtMTFEV3pUTUdzbWNWMGFTc2RVZ0xwWkpSbVpiQlduSUIwa21VdFhRRUdPZ3N1VVZyYmVWVVJSQkVKWVJ5Zm5ZV2RVdGJyOF9pdGVLNXVGRjhaQjlaZndwZWpIMllJYlgwZWYzdVRMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Dados da importação de ureia em junho e expectativa de preço! - farmnews.com.br</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTUFLaTJkNWxYamJpNUFReXhFRG12WFNvQ1A5cnBlZ3VVSGFUVFhXaFhyMEZ1MmtrTzZoeEgxVFFtMTFEV3pUTUdzbWNWMGFTc2RVZ0xwWkpSbVpiQlduSUIwa21VdFhRRUdPZ3N1VVZyYmVWVVJSQkVKWVJ5Zm5ZV2RVdGJyOF9pdGVLNXVGRjhaQjlaZndwZWpIMllJYlgwZWYzdVRMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,19 +3954,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3988,17 +3988,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
+          <t>Crise no enxofre leva Mosaic a hibernar unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>09/07/2026 11:32</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4010,29 +4010,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>09/07/2026 11:32</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,63 +4130,63 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>08/07/2026 08:08</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85827eb4654807b44e6d99538c89b4&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>08/07/2026 08:08</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b127b0c647e1b7ca2ed025c4fe7c&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Sorriso-MT</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,19 +4218,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - globorural.globo.com</t>
+          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com mineradora que garantem R$ 11 m... - Portal MPGO</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Sorriso-MT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4262,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYnZHVWpuemFFNFNOdGxsMzlYMW9XM2VzVEJMaXhsZ21iQUNnb1l0MUZselA4ZUZoMFExaUxoT0JaSmNUVGJOOEtqMnE0Zjl2VUc3aFJfUXZkRk03NHE5b2VmNmZWNVM5bTlwdXQwbUoydHZMQ2JHdUNnMU1nc1JKZmhVdHFZdHRYZ2NtR2lITkZ1eFpGMFBpU1JTZGZicWQyOFVVazU5VkNPYXBqNnAzbEdIV2g0ZHJDT0tnZ24tSVM5U011V3BGc0hkM2U3U0No?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>MPGO celebra acordos com mineradora que garantem R$ 11 m... - Portal MPGO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYnZHVWpuemFFNFNOdGxsMzlYMW9XM2VzVEJMaXhsZ21iQUNnb1l0MUZselA4ZUZoMFExaUxoT0JaSmNUVGJOOEtqMnE0Zjl2VUc3aFJfUXZkRk03NHE5b2VmNmZWNVM5bTlwdXQwbUoydHZMQ2JHdUNnMU1nc1JKZmhVdHFZdHRYZ2NtR2lITkZ1eFpGMFBpU1JTZGZicWQyOFVVazU5VkNPYXBqNnAzbEdIV2g0ZHJDT0tnZ24tSVM5U011V3BGc0hkM2U3U0No?oc=5</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4306,19 +4306,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4328,51 +4328,51 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4384,39 +4384,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CBN Amazônia - CBN Amazônia</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>05/07/2026 04:00</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBNZ3NjNnFzM1JLVDJucnN3MDV2cFZlZGhFampxb0FpVVpqeTJVZDlMNXoyczFEOXhOYVRhaUNTOFc0clJRWmVDQ3BwNHFfWGVNN2RJWVgyQmR3OHJBSTBWc2FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,19 +4548,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4570,19 +4570,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - brasilagro.com.br</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPLXdYV05kWHpEMFJ2bVVHc19qdmd1MGJOTlRmTFdwUDJxVmZDZXBHa2J0cVZzTmloeGVacHUtMUVDVHdTeHFOOFNaY1NoVUotdk00V1BnbjlCaFdvN3lxU25CMUlkWWh5OWd0MUJ4NE5TYktzdVg4OGxrWnV5WEg0Sy02QWRqUThJWDZ0a0pNRG5xa0FQN3RLcVNrcDZ0UzVxdGFYc0ZNSzFqTkpk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - navegantes.sc.gov.br</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPLXdYV05kWHpEMFJ2bVVHc19qdmd1MGJOTlRmTFdwUDJxVmZDZXBHa2J0cVZzTmloeGVacHUtMUVDVHdTeHFOOFNaY1NoVUotdk00V1BnbjlCaFdvN3lxU25CMUlkWWh5OWd0MUJ4NE5TYktzdVg4OGxrWnV5WEg0Sy02QWRqUThJWDZ0a0pNRG5xa0FQN3RLcVNrcDZ0UzVxdGFYc0ZNSzFqTkpk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - primeirapagina.com.br</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4731,12 +4731,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,19 +4746,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - globorural.globo.com</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,19 +4856,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - farmnews.com.br</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - farmnews.com.br</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - revistacultivar.com.br</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - farmnews.com.br</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,19 +5230,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - andravirtual.com.br</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5391,12 +5391,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>O ‘apagão’ da ureia - VEJA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>O ‘apagão’ da ureia - VEJA</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - globorural.globo.com</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Pó de rocha: alternativa que custa 10% do fertilizante mineral ganha espaço no agro brasileiro - Canal Rural</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOdHF4SF9QR2R4WmlyeDlpNlRmeHQ5TVpJeUd5TTRkME02b2xCNWlVZ2R2bk1ydmtTV0xOMDVHRzBaN29TQlQ1VGZ0dzFuUzNxUnljV1dGM2loM1g5bXdlWlNWWnNpWjhtdWs1cVI1YlVlR1NrbHNMNkx1bDVkSjVkODlwM05ueXhDdHc5UkRtZGxiQ2F1Um9WY0d0TGF2U3ZBR1AyeS1tclExWXZmNjBQbGt0emVTMW50cmFLVjZYdjJpcV82VUJMZ21SWmg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Pó de rocha: alternativa que custa 10% do fertilizante mineral ganha espaço no agro brasileiro - Canal Rural</t>
+          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOdHF4SF9QR2R4WmlyeDlpNlRmeHQ5TVpJeUd5TTRkME02b2xCNWlVZ2R2bk1ydmtTV0xOMDVHRzBaN29TQlQ1VGZ0dzFuUzNxUnljV1dGM2loM1g5bXdlWlNWWnNpWjhtdWs1cVI1YlVlR1NrbHNMNkx1bDVkSjVkODlwM05ueXhDdHc5UkRtZGxiQ2F1Um9WY0d0TGF2U3ZBR1AyeS1tclExWXZmNjBQbGt0emVTMW50cmFLVjZYdjJpcV82VUJMZ21SWmg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - stonex.com</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,19 +5692,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - stonex.com</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,19 +5736,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - clarim.net.br</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - paranacentral.com.br</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5985,12 +5985,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado 'Casa de Mãe' por excesso de enxofre - UOL Notícias</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6022,19 +6022,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxQVnMwaDNyLVBNaDdna1pSSFRYSFlOZVVWRHBIM05JMHhvdnhzRWJhZWlMaDE2YmlkQTE1d0dtZU1xcVFCeW8xX0hDUEhkc0V3Y3FNeThXRzZCUHA5Zkd5cUxSZHJtODlaSzVRVVJjQTBDdkJzSmFBR3pHYUREclBjY3dPaDlIU2ZBVnlESE8tWkdQdUlyTk5IOGFEUnY4MHVuT1NSYWVCUHJIdzdzRllIQmp5MEtBMlUzWG1jU2JMTGJtZUp1WXdZZ1VlZ01JR0w5aXBmdGJHSkJfd1h0MTA3dENrSjJyN0tCMmxCUXJ0VnlKMTUxbURUNGs3blhscHRxLWl3WmthVVF5YWxoQTlfTnVxWk1McUMwMjA1bXZ1MzBYRlZTS3RBcWt4YlEwSEJyZHExbEt1RnVMMXRaWUk4ZU1zZGU4ZTk0c3VuaXU1SGZNRFlDRlJFcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPMWUyNm9mWU9veFpjQzM1YmNFWkdJNGZ3OEtIZXQ2dERuaTRoNnc4ZlJjNG51T2Z5SXJiNlF2UmFmdzdsNTlzRmJXVmRMS3JGLXN4TEhOWFpnal9iNUtLY0hxaW8xRTAxZV95czZwa0Zhdk93N0RFbEdGX0p0STZtX3d5U0Z5QmxhTGZaeEJJejRRRThqWjltdWNQcUY1cU1NQmFuTENIclV4U09NSXBJTGQ1SEZOeU9DWUszMElldEctazNxZHZYakwxVW1XQ1B6YTJ4eE1OMzJVZXFsalZiaHR6UEdfeEJTeXdDaGNUSXBTSlQwbjNHaVA0cmJGTUJDN1FqQjR3RTB5UVdlaHZ1X0FZZDUwVE5hc0VwM09YZDNzMTBOOFNQVmNXUnNEUWRiM2R6ZXhNNHdQSzR2MzVHZEdEaFZFV2lvam9rWkNwWGQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
+          <t>Anvisa manda recolher lote de coco ralado 'Casa de Mãe' por excesso de enxofre - UOL Notícias</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPMWUyNm9mWU9veFpjQzM1YmNFWkdJNGZ3OEtIZXQ2dERuaTRoNnc4ZlJjNG51T2Z5SXJiNlF2UmFmdzdsNTlzRmJXVmRMS3JGLXN4TEhOWFpnal9iNUtLY0hxaW8xRTAxZV95czZwa0Zhdk93N0RFbEdGX0p0STZtX3d5U0Z5QmxhTGZaeEJJejRRRThqWjltdWNQcUY1cU1NQmFuTENIclV4U09NSXBJTGQ1SEZOeU9DWUszMElldEctazNxZHZYakwxVW1XQ1B6YTJ4eE1OMzJVZXFsalZiaHR6UEdfeEJTeXdDaGNUSXBTSlQwbjNHaVA0cmJGTUJDN1FqQjR3RTB5UVdlaHZ1X0FZZDUwVE5hc0VwM09YZDNzMTBOOFNQVmNXUnNEUWRiM2R6ZXhNNHdQSzR2MzVHZEdEaFZFV2lvam9rWkNwWGQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxQVnMwaDNyLVBNaDdna1pSSFRYSFlOZVVWRHBIM05JMHhvdnhzRWJhZWlMaDE2YmlkQTE1d0dtZU1xcVFCeW8xX0hDUEhkc0V3Y3FNeThXRzZCUHA5Zkd5cUxSZHJtODlaSzVRVVJjQTBDdkJzSmFBR3pHYUREclBjY3dPaDlIU2ZBVnlESE8tWkdQdUlyTk5IOGFEUnY4MHVuT1NSYWVCUHJIdzdzRllIQmp5MEtBMlUzWG1jU2JMTGJtZUp1WXdZZ1VlZ01JR0w5aXBmdGJHSkJfd1h0MTA3dENrSjJyN0tCMmxCUXJ0VnlKMTUxbURUNGs3blhscHRxLWl3WmthVVF5YWxoQTlfTnVxWk1McUMwMjA1bXZ1MzBYRlZTS3RBcWt4YlEwSEJyZHExbEt1RnVMMXRaWUk4ZU1zZGU4ZTk0c3VuaXU1SGZNRFlDRlJFcA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6110,19 +6110,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,19 +6176,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,19 +6242,19 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,19 +6264,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT2VhbXd2MmM2OHRBTm5rMDRFUTNaZE1Ed05jWlFibnJwSlNGaDFqOEdZRGk5Ty1XZlZWaFBhLXhiZHRxTkxZMkhvSERqRGVKeHUyMkhtRk1JOHV2MjZIc21RaWJvWVlYS05sM0NORzBZeGFKMEZ0T3lTOTZrdExVVmNnRHBPbS11eWswa01raW9BVm5jUThnRjgtTjlIN1g2allad3VnYl9xZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,19 +6286,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT2VhbXd2MmM2OHRBTm5rMDRFUTNaZE1Ed05jWlFibnJwSlNGaDFqOEdZRGk5Ty1XZlZWaFBhLXhiZHRxTkxZMkhvSERqRGVKeHUyMkhtRk1JOHV2MjZIc21RaWJvWVlYS05sM0NORzBZeGFKMEZ0T3lTOTZrdExVVmNnRHBPbS11eWswa01raW9BVm5jUThnRjgtTjlIN1g2allad3VnYl9xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - stonex.com</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,19 +6330,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6352,19 +6352,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,19 +6374,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - stonex.com</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - primeirapagina.com.br</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6469,12 +6469,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6484,19 +6484,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQemZaZVVoOVdqclY1NnlPVkRYaE9kcEtNMWFfNUhQcElqdlhXSFFjQ0ZzNmVQOXZNQWdJZ2xkWHJqc2VwMnNoUGVBektPWE5VcDJfWE04Y29EdkJscm9WemNWZkFoaWtCNDVzQWFBbmJDclJ0R1F6NVB1YWpRMm4yVGVDcElrR20xUW16VGsySmFiSFJqdkhtUmtBRkxsLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,19 +6638,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQemZaZVVoOVdqclY1NnlPVkRYaE9kcEtNMWFfNUhQcElqdlhXSFFjQ0ZzNmVQOXZNQWdJZ2xkWHJqc2VwMnNoUGVBektPWE5VcDJfWE04Y29EdkJscm9WemNWZkFoaWtCNDVzQWFBbmJDclJ0R1F6NVB1YWpRMm4yVGVDcElrR20xUW16VGsySmFiSFJqdkhtUmtBRkxsLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,19 +6770,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Como encontrar enxofre em Subnautica 2 - insider-gaming.com</t>
+          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - stonex.com</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - stonex.com</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,19 +6858,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Como encontrar enxofre em Subnautica 2 - Insider Gaming</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1DeUNMSGxnbU9GRnk4Y3hGbWNzYldCMzlBd3hfM0N0R1FUcVJoeHRUMWhwYjlMUXhZRktDUU9JMHRIa2E0cTUwWl9Ld201bnF6UmZ1X1hOSl9fQ0xfbV9LVU5jNWdISk0xcE8wcERtaW4xeEZS?oc=5</t>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,19 +6946,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Mais de 330 bairros da Grande BH podem ficar sem água após manutenção emergencial da Copasa - Impactto News</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,19 +7012,19 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcGZFYkFrb1pzVmR0T0t5dzRQclZjZVE2c2E3WnUtX0R6LXM1c1JJcm5taGRqMmpPZ1JTcmwzVk1zVTVFZ3dHb2NnbmtMWGxIbXF6UHYxQVJwcVByYi1xbVZXMVZ6SUpFd29JQml0Ykh2WEdPRXd1RHl2YWpQNzJvWkxjOEVTY1daa2pxSm1yS0o3SHhLZmRuNGkzWVFFWDhRTUw0NTlHNVdrTzJGUmZ0SW5DMkxsSWk4QXFIaDNWSmR6bjNiMWNzUi10OW45V1BS?oc=5</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Mais de 330 bairros da Grande BH podem ficar sem água após manutenção emergencial da Copasa - Impactto News</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - farmnews.com.br</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,19 +7034,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcGZFYkFrb1pzVmR0T0t5dzRQclZjZVE2c2E3WnUtX0R6LXM1c1JJcm5taGRqMmpPZ1JTcmwzVk1zVTVFZ3dHb2NnbmtMWGxIbXF6UHYxQVJwcVByYi1xbVZXMVZ6SUpFd29JQml0Ykh2WEdPRXd1RHl2YWpQNzJvWkxjOEVTY1daa2pxSm1yS0o3SHhLZmRuNGkzWVFFWDhRTUw0NTlHNVdrTzJGUmZ0SW5DMkxsSWk4QXFIaDNWSmR6bjNiMWNzUi10OW45V1BS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - paranagua.pr.gov.br</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,19 +7188,19 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYWdzbE83cTRBT0tNU3R4aTVGY1d0VzVDRW1DOWxzcXNZLXg0NnJVTTZkeWc5LUloOG42VHQ1aENxNXdvUHdvVl80MFNMTElfeTNLbi01aU56RnlRV0hOUmF6eGNXSjJTbk52U2hDRTk0c0VFMDEtNGsxNUtfNHRJbGk5VDZhVUV5OWg3djA1OHpjQVVCcWJWeA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - theagribiz.com</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,19 +7232,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYWdzbE83cTRBT0tNU3R4aTVGY1d0VzVDRW1DOWxzcXNZLXg0NnJVTTZkeWc5LUloOG42VHQ1aENxNXdvUHdvVl80MFNMTElfeTNLbi01aU56RnlRV0hOUmF6eGNXSjJTbk52U2hDRTk0c0VFMDEtNGsxNUtfNHRJbGk5VDZhVUV5OWg3djA1OHpjQVVCcWJWeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Notícias de Arcos - Jornal Correio Centro Oeste Arcos</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,19 +7386,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - farmnews.com.br</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,19 +7430,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Ureia inicia queda global após disparada dos preços - stonex.com</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - globorural.globo.com</t>
+          <t>Ureia inicia queda global após disparada dos preços - stonex.com</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7562,19 +7562,19 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - theagribiz.com</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,19 +7848,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -8031,12 +8031,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,19 +8046,19 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8244,19 +8244,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - radardigitalbrasilia.com.br</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
+          <t>CSN apresenta inovação sustentável no Vale do Café - avozdacidade.com</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8295,12 +8295,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Queda da ureia acompanha alívio geopolítico - Agrolink</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,19 +8354,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQNEppb0R2TFlCUmIzRW0xckJYSWVvQUJ5cTc3MldveFBqTVZtbU95MFVfNVJLYVR1SUhVM1BFTXd1OHZhVzVoVkQtczA4NXVwLTc0VUdpY0RjN002TXk1aDlnM0w5U1ZvWUUySHREcG9LZUZfdFl2QmxubUpnbEJWdUE3UGZZNXRrNmFOWUFwVDUtRkJsVTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>INSCRIÇÃO NO PROGRAMA DE CALCÁRIO ATÉ O FINAL DO MÊS - Prefeitura de Mato Leitão</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPQ2xHNUVCT202aDlGai1PVTBaS0tmbFAyaDVCYThDdVpQdTFhcWlzTGtDWThuWkhVRU5zTDdwOF9ENUlSd2k2TUNuUktNU3Y1WXpMck1qMkVCeHprRVpUZE9KSUNMQ3lfaWRSMkVwS2hEbXVFTDNmZndjZkh1ek9VQU43VV9SR09aUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - globorural.globo.com</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxONTFwXzhWOXJpNGJOcGg0VkE3Q1FBTF96azlkcXJsemtkNm10NG1LVzk2bHJOeE0xaVZrZmdIbFNRMC0wZFBDTEdXa2VSVTJyUTA2LV9RNkNRVWx5NlN0N2RQMVpNcFZWZkt0MXlHSTVBSlUxeEhLYXV3eElfd1hYNVZSTzdfUGNEb1JVbGM1b3dkZXl3Rml2aFhraVMxektyWjhOM0xXQWg3bDhPc2Vrc3hCaW9TVU5qWVZUVE00cXM5NjgyWHE5dWI2cWRPQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
+          <t>Mosaic paralisa operações de fosfatados em Minas Gerais e planeja venda de ativos - agrofy.com.br</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOOUNzOVZUUkhFOWxIU2E0ZFcwUGs1aWlvYVAzOEdtSkt5cFZVY1lkRjdTOWRObDhEMXNwYm85RjFnUFNXb3lYRkFWdVhxUjVLRUJhNS1FZ1pkcWpMUDFXZ1hWVTZ2anMyVGF6V1Z4RWk4RmN0YkRaRGpzMTRybDdWcXR5OGxfMnVOX2h5MWxVZS1CT2pvSExaSHRSUGZHQ1cwejFZVHFzOFFYUDFJanNXcDR5T01xOHcy?oc=5</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações de fosfatados em Minas Gerais e planeja venda de ativos - agrofy.com.br</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - theagribiz.com</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOOUNzOVZUUkhFOWxIU2E0ZFcwUGs1aWlvYVAzOEdtSkt5cFZVY1lkRjdTOWRObDhEMXNwYm85RjFnUFNXb3lYRkFWdVhxUjVLRUJhNS1FZ1pkcWpMUDFXZ1hWVTZ2anMyVGF6V1Z4RWk4RmN0YkRaRGpzMTRybDdWcXR5OGxfMnVOX2h5MWxVZS1CT2pvSExaSHRSUGZHQ1cwejFZVHFzOFFYUDFJanNXcDR5T01xOHcy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxONTFwXzhWOXJpNGJOcGg0VkE3Q1FBTF96azlkcXJsemtkNm10NG1LVzk2bHJOeE0xaVZrZmdIbFNRMC0wZFBDTEdXa2VSVTJyUTA2LV9RNkNRVWx5NlN0N2RQMVpNcFZWZkt0MXlHSTVBSlUxeEhLYXV3eElfd1hYNVZSTzdfUGNEb1JVbGM1b3dkZXl3Rml2aFhraVMxektyWjhOM0xXQWg3bDhPc2Vrc3hCaW9TVU5qWVZUVE00cXM5NjgyWHE5dWI2cWRPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - varzeagrande.mt.gov.br</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8713,12 +8713,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,19 +8728,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para abril sobe quase 65% em março e segue nas máximas! - Farmnews</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbUlXekJnQ0c5T19mQTBMeDBVcnpuS3ZYTGtGdEN6eTFUcmEtMFhsN05GdTVqaERaUy0yelVxaW5HeWFsOHp5aGRyMzhWQ1ZDZWttbjN4OUpkS0xWT1ExczBYeWI3VHY3emJTTG5IekhsM3BiLXRZc29VR2hybFdmSll2TlR3ZjJVSUtKMjA4RTliNjBmOGd2cnZnc2tGbHMyZXpZMUVBUmN2RjBzVmlwV3p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço futuro da ureia para abril sobe quase 65% em março e segue nas máximas! - farmnews.com.br</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbUlXekJnQ0c5T19mQTBMeDBVcnpuS3ZYTGtGdEN6eTFUcmEtMFhsN05GdTVqaERaUy0yelVxaW5HeWFsOHp5aGRyMzhWQ1ZDZWttbjN4OUpkS0xWT1ExczBYeWI3VHY3emJTTG5IekhsM3BiLXRZc29VR2hybFdmSll2TlR3ZjJVSUtKMjA4RTliNjBmOGd2cnZnc2tGbHMyZXpZMUVBUmN2RjBzVmlwV3p3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - jornalcana.com.br</t>
+          <t>Corretivo de solo sustentável entra no RenovaBio e gera Créditos de Descarbonização - JornalCana</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8882,19 +8882,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,19 +8904,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - farmnews.com.br</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8977,12 +8977,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9014,19 +9014,19 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,19 +9036,19 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - globorural.globo.com</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,19 +9124,19 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,19 +9146,19 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9168,19 +9168,19 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - farmnews.com.br</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9417,12 +9417,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9432,19 +9432,19 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9454,19 +9454,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - globorural.globo.com</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9476,19 +9476,19 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - globorural.globo.com</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic anuncia resultados de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Mosaic anuncia resultados de 2025 - revistacultivar.com.br</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9784,19 +9784,19 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5rSk81Mmx6dm5KanJ6ZWY1SDBpYzREOE5FeW1YM28tOWxVWUVSRDZEb2thQjNGeFQxREZWMmFnQ09uRzFSMlVmR2h5VlJGRG1EYXpnMjliTkRGQWhFcjZCTF8ta0JkX2FSZ29ISEtrSWJaOU51UGw4c1E4UTB1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9806,19 +9806,19 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9828,19 +9828,19 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9850,19 +9850,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9872,95 +9872,95 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Preço de importação da ureia pelo Brasil: dados de janeiro, entre 2018 e 2026 - farmnews.com.br</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>17/02/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYWV4SGJFRFVBR0gzSndtTEMtMU1BbEpEQWdnWjhyODcxUHprVVJfblZHdmpaZnI4N1BXTXZ6dkwwWVFCRUUtcnFyei1kRUZfRlBWXzZwdmEySVJXbUIxWWYycjJXQWVWWG5qZ3BoX2hsNGR2T1FWSmc1dlNoRFc2RFhkYmZ1T2VXVHZjYWJVc1FsaVczOXBwSFZOajhjckRXNFVOZTNvX25nTTJlVVZ0WGZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Preço de importação da ureia pelo Brasil: dados de janeiro, entre 2018 e 2026 - Farmnews</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>17/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOYWV4SGJFRFVBR0gzSndtTEMtMU1BbEpEQWdnWjhyODcxUHprVVJfblZHdmpaZnI4N1BXTXZ6dkwwWVFCRUUtcnFyei1kRUZfRlBWXzZwdmEySVJXbUIxWWYycjJXQWVWWG5qZ3BoX2hsNGR2T1FWSmc1dlNoRFc2RFhkYmZ1T2VXVHZjYWJVc1FsaVczOXBwSFZOajhjckRXNFVOZTNvX25nTTJlVVZ0WGZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10016,83 +10016,83 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>CMOC e comunidades rurais se unem para dialogar sobre segurança pública - Zap Catalão</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>05/02/2026 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxORzNlMV9FY0ZlTkJzdXNIa01XckhwU1l3RzlOUWpvdnlMNUEwTm9NN210dHJqVGJYSVM0ZXFWbEVKWnZvS1NLZmdnNE1RRjBHc0s2QVhzRWNtN3JtU0ZocXhjRlNCUjd2NzRmdGQ4MzVYSnlxQUxrMnlROS1iMVBHaHIxcWpSMk9SYWJqZFcyNndsX3FCaUpsdTVuSDZLZ2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>CMOC e comunidades rurais se unem para dialogar sobre segurança pública - Zap Catalão</t>
+          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>05/02/2026 05:00</t>
+          <t>04/02/2026 08:38</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxORzNlMV9FY0ZlTkJzdXNIa01XckhwU1l3RzlOUWpvdnlMNUEwTm9NN210dHJqVGJYSVM0ZXFWbEVKWnZvS1NLZmdnNE1RRjBHc0s2QVhzRWNtN3JtU0ZocXhjRlNCUjd2NzRmdGQ4MzVYSnlxQUxrMnlROS1iMVBHaHIxcWpSMk9SYWJqZFcyNndsX3FCaUpsdTVuSDZLZ2s?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Parceria entre Governo de Minas e Harsco completa dois anos e beneficia mais de 2 mil agricultores familiares</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>04/02/2026 08:38</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
@@ -10126,17 +10126,17 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa na Bahia - G1</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUDF3STREdi1LcFZocWtheHhmQXlnMl9fSHdLZkUtWWJGNWZtUE9XWmJfN1lWNmc2SnRZeHliSUJ3WHJUN1o4MWZrSkFxZHJmRkE3ZUpuaDVIX1lzZUJuNkQ2eTJXNWh0bmtfWWRnUHdlV2VIQTN4dG5HZDY0U3dPLVdVVFR1UUltX3laMGpHLUZpbkk5OG82WnRwQnROY1BLVktrVEdFeGg3UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
+          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQRS03TU11UVFmWXlleDJua2ppdlVwaFRDYll4amFBSVBFNjZpRjZGY1RKaE81SUowSENhVlFQVmotTlltb1NMYlhxZ2diUmFrdDEzNl9vWVhRQ1pjQ3dBajJJNEZSRUlVYnFGeGxVVTY3SkNyU0huU3c1ZENKODVSSm91THktMEVXbXkxcFJ1M1ZfSmxTdTREQ052NGw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
+          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQRS03TU11UVFmWXlleDJua2ppdlVwaFRDYll4amFBSVBFNjZpRjZGY1RKaE81SUowSENhVlFQVmotTlltb1NMYlhxZ2diUmFrdDEzNl9vWVhRQ1pjQ3dBajJJNEZSRUlVYnFGeGxVVTY3SkNyU0huU3c1ZENKODVSSm91THktMEVXbXkxcFJ1M1ZfSmxTdTREQ052NGw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - The AgriBiz</t>
+          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - revistacultivar.com.br</t>
+          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - theagribiz.com</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
+          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - meon.com.br</t>
+          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - avozdacidade.com</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQklGdHRzc09idVgwaFdKZHpPV0RTUldGTkt5NE55VjQ4MV9nQ1M2YnFDTmlqbzRwMExZTkU4dFd5YUJCc19pYXR3SmE4azlqVUxORHBPem1qN1ZUQmk5dDBjTW9QZ3lrZE1Cazk0QnBMT2tCbVRzOElWckxrcndfZHN6SmhtMTRxZ3N2eEZYaXFEelptLUdkcUo2aEJpZ1lVMkxMWXRzeGJvNGtXVGtzd3FZM2FwNEExY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQklGdHRzc09idVgwaFdKZHpPV0RTUldGTkt5NE55VjQ4MV9nQ1M2YnFDTmlqbzRwMExZTkU4dFd5YUJCc19pYXR3SmE4azlqVUxORHBPem1qN1ZUQmk5dDBjTW9QZ3lrZE1Cazk0QnBMT2tCbVRzOElWckxrcndfZHN6SmhtMTRxZ3N2eEZYaXFEelptLUdkcUo2aEJpZ1lVMkxMWXRzeGJvNGtXVGtzd3FZM2FwNEExY1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,19 +10752,19 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,19 +10796,19 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - china2brazil.com.br</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11155,34 +11155,34 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOT0VjaTAtOGdXU3lacjVmM2xreFRNTEZ2VnI2TC1Rd2M2YTI5cjZ1NjBFOEJtRmlsYXJ5Nmk2b3pNenFJcnBxWG5mZy0tU1dQUnBVRjM0UFExSXliQ19aOTdiRDc3Z2xZT0hsdVhfOXFHSFN6OWh5NGoxaHJrUi1UWmhkMUJCNXVMRjJEa2FZZW1MWWwxdzQ1bi13OC0yRy0zUExUUzNldTFWTmFXSEhGc2JR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b122981449e2a5cd9221ff2f0bb4&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - globorural.globo.com</t>
+          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -11192,29 +11192,29 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOT0VjaTAtOGdXU3lacjVmM2xreFRNTEZ2VnI2TC1Rd2M2YTI5cjZ1NjBFOEJtRmlsYXJ5Nmk2b3pNenFJcnBxWG5mZy0tU1dQUnBVRjM0UFExSXliQ19aOTdiRDc3Z2xZT0hsdVhfOXFHSFN6OWh5NGoxaHJrUi1UWmhkMUJCNXVMRjJEa2FZZW1MWWwxdzQ1bi13OC0yRy0zUExUUzNldTFWTmFXSEhGc2JR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
@@ -11226,29 +11226,29 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Zema e Deputado Arantes recebem direção global da Lhoist e destacam importância estratégica da unidade de Arcos - Arcos Notícias</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>25/11/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNVllJNXRFa1g3eGQxRERRMURaVmJhU2lYQXUyS0FSM0VSX0tNQU94Qm85ZVIycTRHV0lYb0J0MTg1NV81d3JycFNRQmpXYkg0OGEtVGctR3NIeTBVUk11ZVdWSTNweHdZRi1PQVFVSS1tMnBmTERnc0tNVHRDQXdNUldxOHdWeXZpLVc4VFU2bklMdUYwdm5Icnl5MFJLZjdtRmxHT0RTR1otY0FNazZVcFpxajRKcWhjZXdoeDNFa2lpVG5aRF9MZUhDQTdDY0hheXk4WHJHR21XdFg0T2FFNzFLWHozNHNWRy16MHBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Mapa libera agregado siderúrgico da CSN para uso agrícola em todo o país - Portal BE News</t>
+          <t>Zema e Deputado Arantes recebem direção global da Lhoist e destacam importância estratégica da unidade de Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNFJ1X0tKZnRvYm1RVFluT3N3d2J1bTR5bUstYlk1Z3RHMENQSVFELTZ2azJwdTVhVUx2Mm5mSldXaE9JekU5dFFUTFRydlBrQ3dVR3N2Z1BzZUxkWW96OEFKSWtfZDhNU0dyWlE3OVloWjNESEI5aVM1VTViUkhha2tocEtXMWlIVVROVWlEb2VDUElCYjNlV3lyOW5JQnpDR1dr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNVllJNXRFa1g3eGQxRERRMURaVmJhU2lYQXUyS0FSM0VSX0tNQU94Qm85ZVIycTRHV0lYb0J0MTg1NV81d3JycFNRQmpXYkg0OGEtVGctR3NIeTBVUk11ZVdWSTNweHdZRi1PQVFVSS1tMnBmTERnc0tNVHRDQXdNUldxOHdWeXZpLVc4VFU2bklMdUYwdm5Icnl5MFJLZjdtRmxHT0RTR1otY0FNazZVcFpxajRKcWhjZXdoeDNFa2lpVG5aRF9MZUhDQTdDY0hheXk4WHJHR21XdFg0T2FFNzFLWHozNHNWRy16MHBR?oc=5</t>
         </is>
       </c>
     </row>
@@ -11270,17 +11270,17 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>Mapa libera agregado siderúrgico da CSN para uso agrícola em todo o país - Portal BE News</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>25/11/2025 05:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNFJ1X0tKZnRvYm1RVFluT3N3d2J1bTR5bUstYlk1Z3RHMENQSVFELTZ2azJwdTVhVUx2Mm5mSldXaE9JekU5dFFUTFRydlBrQ3dVR3N2Z1BzZUxkWW96OEFKSWtfZDhNU0dyWlE3OVloWjNESEI5aVM1VTViUkhha2tocEtXMWlIVVROVWlEb2VDUElCYjNlV3lyOW5JQnpDR1dr?oc=5</t>
         </is>
       </c>
     </row>
@@ -11292,29 +11292,29 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - avozdacidade.com</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -11353,44 +11353,44 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Mosaic Entra no Mercado de Fertirrigação, um Setor de 4 Milhões de Toneladas até 2030 - Forbes Brasil</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ1Z6amZ6SDBLNHYtOGtuMnZ5VnRCQ2lrYjNIQS1WcmdMZE9wZG9TRk80R3ZjWGc1dzE2RTF1LV9EOEdWXzk2LXhMY20yZlFZY2tLREZabFhnTUZhb2x3eEstZVYtcnlyMUdjZFVjTUFHdlF6bW5iMkozY29hUFl0bG5aXzRVbVZrTjB1d3QxR1hMeXBxUVpaeDNGQ0swREQtVFVaT2ZndTRQd2xUT2FRWnA0UEY0TWYzQVBYNjh0QlpoTV84OEE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - itabuna.ba.gov.br</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - itabuna.ba.gov.br</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -11463,34 +11463,34 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Mosaic divulga resultados do terceiro trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>05/11/2025 05:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZUFJNW5SN2Z5Y0M0cDIwaVVfamdqb1FaSTYyT25JQmpFTDB2eE5nR011emxHVDJubWNCN0Mzd0VoMHR3MWhMbndXYU5GbzN3b3JwcTZOQjVQMzdHVUR1bDZ0ak9rczQwOUUtdUhaNDZCaEJwdnZLV0pSMko5M2pLSE1FNVc0UUhKME9OWWRXOE1HeThuMzZPZGczWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11500,117 +11500,117 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858279b0c74c46b4f2b6a23b838d75&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b122981449e2a5cd9221ff2f0bb4&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - itabuna.ba.gov.br</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - jornalcana.com.br</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para o Programa Jovem Aprendiz 2026 em Arcos - Arcos Notícias</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>03/10/2025 08:14</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORnRTMVVoUTk0Q1JIRy1YYVFTWU9VWDlZa2hjS2g3bzFQNkY3aHVLQ1d3eVdoZHJIeENMV3AybG1JaTBuVGFNYjBGS0xlSGowQkEtVkt6X216WHJQNzdKcHR6YlBuQTNXUHJhWFJSVUlfZlZFYWhkRl9MaWZWMWNibi1OSUFjUDA3YWp6NWtINnYyU1FUVmdfVUxXLTdHSTR6cGNUaE1Ra0FyeThvdExFSkNaTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -11622,171 +11622,171 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Lhoist abre inscrições para o Programa Jovem Aprendiz 2026 em Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>03/10/2025 08:14</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORnRTMVVoUTk0Q1JIRy1YYVFTWU9VWDlZa2hjS2g3bzFQNkY3aHVLQ1d3eVdoZHJIeENMV3AybG1JaTBuVGFNYjBGS0xlSGowQkEtVkt6X216WHJQNzdKcHR6YlBuQTNXUHJhWFJSVUlfZlZFYWhkRl9MaWZWMWNibi1OSUFjUDA3YWp6NWtINnYyU1FUVmdfVUxXLTdHSTR6cGNUaE1Ra0FyeThvdExFSkNaTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - revistacultivar.com.br</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>03/09/2025 04:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>03/09/2025 04:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a858278359d413d91274b3e9ba4fce6&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85b12159c6430eb0249a587eedfc0a&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNGMyS0xkbXBrOG1SM3MtS3NCOWRHT1NsTmtZUE5tcklTNGstZkp6al9vLWxTTVdiY1JZWGloVnlic0ZTdE83eG5mQXQ0X3ZLMTQwM18ydUN4RHVjb2tHRjZkWjlvT1M0dVdVMU9JTWtsRkJkR2h6c2pmWHBvNW96SEZZZWRIZGYxNmpDdVN5eFNHQnVoWEJ3ZzNxS2I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -11809,6 +11809,28 @@
       <c r="D518" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CMOC</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>01/09/2025 04:00</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNGMyS0xkbXBrOG1SM3MtS3NCOWRHT1NsTmtZUE5tcklTNGstZkp6al9vLWxTTVdiY1JZWGloVnlic0ZTdE83eG5mQXQ0X3ZLMTQwM18ydUN4RHVjb2tHRjZkWjlvT1M0dVdVMU9JTWtsRkJkR2h6c2pmWHBvNW96SEZZZWRIZGYxNmpDdVN5eFNHQnVoWEJ3ZzNxS2I?oc=5</t>
         </is>
       </c>
     </row>

--- a/Noticias_Calcario_20260819.xlsx
+++ b/Noticias_Calcario_20260819.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prefeitura de Iomerê entrega novo distribuidor de calcário e adubos à Associação da Linha Caravagio - Rádio Tropical FM 99.1</t>
+          <t>Brasil importa menos fertilizantes, mas troca de nutrientes muda a conta da safra - economicnewsbrasil.com.br</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19/08/2026 09:15</t>
+          <t>19/08/2026 15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOZi1LOHNDUjNfNEFTWjNRZm5ybHZWYTJkVHdoanVVR2xLVkRfaVluSlo2OUNZS24tTUt6Q1k4alJ5STVfQnlzNzBfY2p1M1ZmQ0gyamhEQ25yVEZPZlFnQ2UwWHE3aTdxbkpQdTlVRFNndmloRVB0S0hQS1pSSVV0bFhWVUNwaDhsMmlBN3dlQ2NFdFRScW5aaTlwNHV4aEM2MjBxS0FwQXRNWkFYY1VUT21SSmNLaVVSVUhOSTBEb29WMWl4cjRoSm9qNzBTVTh4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNUzJLX3J2TFlBWDcwWmEtY2J0UlRYblVKNTd0d1QteU54S0xCX2xLbkYyMjEtcWtEbUcyRFhBNTdUbWwtQUo3aTNXMnJNQTJYZGJRN29fd0c2RmtaUktaMUZCbWo4MTBmdlExb1hvN1dzeGFPekZnVXZCSnR2WDdNWUdhd3RhcDEyMmJsakFGUVRIdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -468,171 +468,171 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fábrica prevê produção mensal de 900 mil toneladas de calcário - Jornal de Angola</t>
+          <t>Calcário micronizado eleva produtividade da cana em 42,7 toneladas por hectare, aponta estudo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19/08/2026 07:26</t>
+          <t>19/08/2026 13:30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNWTBUZ1VnTjd3OHdSdWFMbS1iQTZhcW1KNEZPaUdpRDZTa1hJaS1rY2pJYTA3NmN0THRabWQ0amhOSjBCY1p1QjdyMXN2Q0xzRG5nb0IzbThLSlotMWQ0TTQtN1FLRmZMVS1ueEhnTnJ5NEdZNW5KRkVUYWdKN0l5elU2Z3lkVnRYdE9PTm5iSGV6SWNwTFhpTm9rLVFKR2JhVWpOSEw5N3V0b2xfd3FpUzRORGtpTm16aUhmRGFYdUdFM3lOX29keDZBNktCNjFMS3dfMXBicUo0MWpGX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPWXZKMjNsMzdXbkQyYlpab2xDX2N1SE5tT0w4YjVaNkNvdzBGRW5HQll1MU40c19EOW9GNHBfa2dwZUZza1lxVjJBMHdFa2NSUkh0QWdGaFZsbHc4T3FVSWJtQmNzUVk2QUVRaEZkNDRjcEpQYjdHd2pJQXZISEI0d3dweFhXNURSWEdzdFNVZ1dSNEVnRGR3czZBT0lzdUY0NjRkX2VUMndEdS1EdDZsZGxhM3BCTFBUal9HN0JEaTBtRlJkWTMtQ2MyanBCWFA1ZUxWZHd6NVBzblJfdG5RRXFQX1BrdURtWkFYbG42TE9QWG0wSC1tc1pmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A Mosaic apresenta sua gravel de 32” e cria uma nova marca de componentes para solucionar um de seus grandes problemas - brujulabike.com</t>
+          <t>Prefeitura de Iomerê entrega novo distribuidor de calcário e adubos à Associação da Linha Caravagio - Rádio Tropical FM 99.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19/08/2026 02:41</t>
+          <t>19/08/2026 09:15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLTFBUG8xNmpsV1FITzJfSjlWTlRUT0Itc1N6eTdxQzlXVlNSeWhMYTZUWnBGYlRLUWp1N0tHeHIweTN3eVZEdkd5SUR3cHF3Y2l4MjNQUG0yXzhDREM3QjRUTUlkUU1jbjNzNW9ucjQwenZmM21YWTZDUk9OdWV2Z3RJbzJFbUpiejkyWHJUeGx1cG9mbE1MNlBKZ0VoenlaVXdIUDF2SW9ub2hlOWU4czZYODhSLUt3bW1FR2x0U01KOTNkaUJyNUJqRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOZi1LOHNDUjNfNEFTWjNRZm5ybHZWYTJkVHdoanVVR2xLVkRfaVluSlo2OUNZS24tTUt6Q1k4alJ5STVfQnlzNzBfY2p1M1ZmQ0gyamhEQ25yVEZPZlFnQ2UwWHE3aTdxbkpQdTlVRFNndmloRVB0S0hQS1pSSVV0bFhWVUNwaDhsMmlBN3dlQ2NFdFRScW5aaTlwNHV4aEM2MjBxS0FwQXRNWkFYY1VUT21SSmNLaVVSVUhOSTBEb29WMWl4cjRoSm9qNzBTVTh4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Leite com soda cáustica, água e ureia: Homem é condenado a 13 anos de prisão por adulterar produto na Serra - abcmais.com</t>
+          <t>Fábrica prevê produção mensal de 900 mil toneladas de calcário - Jornal de Angola</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18/08/2026 12:21</t>
+          <t>19/08/2026 07:26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxORmZKalQtNUhHdV80SnhHeGI4RjBDS0FyTFJaMEJOVHdKcG5LNmFuV09WUkRrYS1hNkJ5RmloRDkxUWtBZXNYcktwaXV3OV8zWlQ1RWl1RzBzVDVHYWU0cy1GLUVxV2VQV2RUQy1LU2tNcW5MQTNmOWFjX0s0RWx4ZVA4ZVlreU80SEJCQTMwUGZtUWFncXdQdXlIYU8ycGhDcEZVZjQ2M2tBMUFManI5eURlWmp3S2JnZ3oxYV8tMWdTb3ptSlNEU3R3RWdZWlVQYzBXMzVSOWxPTnd2Z0ZKZndVOHlDZjN5MUx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNWTBUZ1VnTjd3OHdSdWFMbS1iQTZhcW1KNEZPaUdpRDZTa1hJaS1rY2pJYTA3NmN0THRabWQ0amhOSjBCY1p1QjdyMXN2Q0xzRG5nb0IzbThLSlotMWQ0TTQtN1FLRmZMVS1ueEhnTnJ5NEdZNW5KRkVUYWdKN0l5elU2Z3lkVnRYdE9PTm5iSGV6SWNwTFhpTm9rLVFKR2JhVWpOSEw5N3V0b2xfd3FpUzRORGtpTm16aUhmRGFYdUdFM3lOX29keDZBNktCNjFMS3dfMXBicUo0MWpGX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Complexo de fertilizantes de US$ 1 bilhão em Minas Gerais pode reduzir produção e suspender contratos de 600 trabalhadores após crise global do enxofre ameaçar operação - CPG Click Petróleo e Gás</t>
+          <t>A Mosaic apresenta sua gravel de 32” e cria uma nova marca de componentes para solucionar um de seus grandes problemas - brujulabike.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18/08/2026 11:06</t>
+          <t>19/08/2026 02:41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNXljX3RCd1I3cW9mR2h2TmdMNUt0SmJSM05TX0xVZEJ5ek5icmNINEtSNG5NN2ZUbE42a0N1THdWZW95Z2lzSG5DNEFaNC1lbXMxRDJqaXFqd1VTamVxU0tkdF82cGRVNTY2eVY2SkVsS1dKQVB6Qk9PNWsyV2h1NTJxY2xhRV9OdWVSZFU1NmJzWkF4SFVhTGZzVkVzY3JEN1Uwbzh1ZFJVck9hdGNjZHNfZEVzM0FwZjZkeEd0bm16UVMycjZiUFdncXluZGxTOTJUYXJIb0NtM2EyQ1g3d0FWcG0wLW9JUjAtRDdVbUxHcVJxZlNJc05qSjBpaTFUWXFZcS1OX2VPcDZZRFFRYTNXMzFnSjU3dDRUaEZnNUJubW5pSU5HUmJCZzl0VFdK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLTFBUG8xNmpsV1FITzJfSjlWTlRUT0Itc1N6eTdxQzlXVlNSeWhMYTZUWnBGYlRLUWp1N0tHeHIweTN3eVZEdkd5SUR3cHF3Y2l4MjNQUG0yXzhDREM3QjRUTUlkUU1jbjNzNW9ucjQwenZmM21YWTZDUk9OdWV2Z3RJbzJFbUpiejkyWHJUeGx1cG9mbE1MNlBKZ0VoenlaVXdIUDF2SW9ub2hlOWU4czZYODhSLUt3bW1FR2x0U01KOTNkaUJyNUJqRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 18 de Agosto de 2026 - RR Mais</t>
+          <t>Leite com soda cáustica, água e ureia: Homem é condenado a 13 anos de prisão por adulterar produto na Serra - abcmais.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18/08/2026 10:46</t>
+          <t>18/08/2026 12:21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYlVNVmtBdVZFQ250cndQUkRRb09xWm1vNHpzOEFHUkFscC0tQ1JVX2MzVUZrajNXNnVKTjlBdkxzYkdQMzV4MGZjS1VicmlSWEFkVEx0ZGkzaVgzQ1VDUVhLN0VqNE5IZy1SS2dhSHd0SXNVUllKVk5VWGF6cDV3UkFuWXBSWmRMZ1JTRklOWnMwckxJM1kyaTlvclBudmtTYkpWMFl2SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxORmZKalQtNUhHdV80SnhHeGI4RjBDS0FyTFJaMEJOVHdKcG5LNmFuV09WUkRrYS1hNkJ5RmloRDkxUWtBZXNYcktwaXV3OV8zWlQ1RWl1RzBzVDVHYWU0cy1GLUVxV2VQV2RUQy1LU2tNcW5MQTNmOWFjX0s0RWx4ZVA4ZVlreU80SEJCQTMwUGZtUWFncXdQdXlIYU8ycGhDcEZVZjQ2M2tBMUFManI5eURlWmp3S2JnZ3oxYV8tMWdTb3ptSlNEU3R3RWdZWlVQYzBXMzVSOWxPTnd2Z0ZKZndVOHlDZjN5MUx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN na CMOC Chapadão - Zap Catalão</t>
+          <t>Complexo de fertilizantes de US$ 1 bilhão em Minas Gerais pode reduzir produção e suspender contratos de 600 trabalhadores após crise global do enxofre ameaçar operação - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17/08/2026 22:15</t>
+          <t>18/08/2026 11:06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPX09FZWhNd1BTTzA0NlVya3FiVHRzUkpmZ0ozamh1MnVoOTgzbWQ0bXF0a1B2SzR5NEZZd1BramVBRjhfOVpRb1o5MURiQU16U0hwTjFRS1pXd3pWSWJjU3hWMWx0VS03SnJvQ2x4Nm5ZLXhBQkloaFpjTVZfM1A3TGtkcFpVYkcxV0cwb2V1M2w1LW5td3p4NXMwZjdYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNXljX3RCd1I3cW9mR2h2TmdMNUt0SmJSM05TX0xVZEJ5ek5icmNINEtSNG5NN2ZUbE42a0N1THdWZW95Z2lzSG5DNEFaNC1lbXMxRDJqaXFqd1VTamVxU0tkdF82cGRVNTY2eVY2SkVsS1dKQVB6Qk9PNWsyV2h1NTJxY2xhRV9OdWVSZFU1NmJzWkF4SFVhTGZzVkVzY3JEN1Uwbzh1ZFJVck9hdGNjZHNfZEVzM0FwZjZkeEd0bm16UVMycjZiUFdncXluZGxTOTJUYXJIb0NtM2EyQ1g3d0FWcG0wLW9JUjAtRDdVbUxHcVJxZlNJc05qSjBpaTFUWXFZcS1OX2VPcDZZRFFRYTNXMzFnSjU3dDRUaEZnNUJubW5pSU5HUmJCZzl0VFdK?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Homem é condenado a 13 anos de prisão por adulterar leite com água e ureia no RS - GZH</t>
+          <t>Cotações Agrícolas para esta Terça-feira 18 de Agosto de 2026 - RR Mais</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17/08/2026 19:50</t>
+          <t>18/08/2026 10:46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPRTF1ZGRpdDJmM0RrZFpoSi1QQ3JibjlnUTI1UHg4QUZxVDk5eGl5ek91RUVNd2ROT3B6MzhhZmk4OG52VUJucnN5WUFpdEJLME9HYkh2QXk1d0dFeVY4VUt6QlhVYUxOaU95T3l5S0REeTRnV29xN3J1SEV0WHhER3RWVnJocE4ybGZid1ZfZkJ5b2dEcXdoNURUWXZqMWREX251TGtrUWZUTUp6ZlVyQ0VtMWwxX0pZdTBvUWQwVlhuQWk3SnpSVXBFci1lMnkxNE9NT3lSdm9mQ1Zob0t2cEFVWXZ4ZU5TZ0plLWc3Q1hRRHRxMW04U3lzSU9LUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOYlVNVmtBdVZFQ250cndQUkRRb09xWm1vNHpzOEFHUkFscC0tQ1JVX2MzVUZrajNXNnVKTjlBdkxzYkdQMzV4MGZjS1VicmlSWEFkVEx0ZGkzaVgzQ1VDUVhLN0VqNE5IZy1SS2dhSHd0SXNVUllKVk5VWGF6cDV3UkFuWXBSWmRMZ1JTRklOWnMwckxJM1kyaTlvclBudmtTYkpWMFl2SQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homem é condenado a 13 anos por adulterar leite com ureia no RS - Agora RS</t>
+          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN na CMOC Chapadão - Zap Catalão</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17/08/2026 19:46</t>
+          <t>17/08/2026 22:15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxON0NvdThIRFJaWlY0RlBFdDRkM3V4XzQwc3I1SWoxcXdRSk5TZk1xd2l5WDBtRFI2a2MzWTExdS04bHJmU1g3U29PQUw1VWg4UDFqMjlDMmNUcjJ2NDI3NG83OHBCeEtsNTlMMGwxeWFpU2hjM0trSmF3STRONWV5bGx6cENFOC1ldDFvb3h0cE5fcVY0WmZBcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPX09FZWhNd1BTTzA0NlVya3FiVHRzUkpmZ0ozamh1MnVoOTgzbWQ0bXF0a1B2SzR5NEZZd1BramVBRjhfOVpRb1o5MURiQU16U0hwTjFRS1pXd3pWSWJjU3hWMWx0VS03SnJvQ2x4Nm5ZLXhBQkloaFpjTVZfM1A3TGtkcFpVYkcxV0cwb2V1M2w1LW5td3p4NXMwZjdYQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -644,435 +644,435 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OPERAÇÃO LEITE COMPEN$ADO: Adulteração de Leite com ureia e soda cáustica rende condenação severa no RS - Terra</t>
+          <t>Homem é condenado a 13 anos de prisão por adulterar leite com água e ureia no RS - GZH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17/08/2026 16:41</t>
+          <t>17/08/2026 19:50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxONTZUOHdXM0RPQ290UllHZ0dKcTd0U185WWRFVXFfSDlERzRyMDhmamZoajBVZmNPOTZlMzg5TG9VYVNFVDIwNDFjT19vWjJILVJQVnFYaFZfUHlCeFBjU2x2MTFIRVRUS0o3TGFrMExXLVhpbE5iY2d0VGFxM1VydzNNNkNWZmk4SW5nSHNfeXFoTUY4Y0xKbEowTUNwckV0bHhSTENzVHFEckVGd2JjRGFLZEx2VHBoRW43SjlvZnFxSzlWMzhQYzk5VkVCRkgyeVZXSjdwTlhLV013U0FZTU82VF9ieXZCb0k2eHQ2WVBxQS1qdFlTT2UxOXVYTjBYcERVMVpxT2lZX0YxTGFoWU5ZNGFvYm50Wmgzd1hhMy00UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxPRTF1ZGRpdDJmM0RrZFpoSi1QQ3JibjlnUTI1UHg4QUZxVDk5eGl5ek91RUVNd2ROT3B6MzhhZmk4OG52VUJucnN5WUFpdEJLME9HYkh2QXk1d0dFeVY4VUt6QlhVYUxOaU95T3l5S0REeTRnV29xN3J1SEV0WHhER3RWVnJocE4ybGZid1ZfZkJ5b2dEcXdoNURUWXZqMWREX251TGtrUWZUTUp6ZlVyQ0VtMWwxX0pZdTBvUWQwVlhuQWk3SnpSVXBFci1lMnkxNE9NT3lSdm9mQ1Zob0t2cEFVWXZ4ZU5TZ0plLWc3Q1hRRHRxMW04U3lzSU9LUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN da CMOC Chapadão - Diante do Fato Catalão</t>
+          <t>Homem é condenado a 13 anos por adulterar leite com ureia no RS - Agora RS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17/08/2026 16:11</t>
+          <t>17/08/2026 19:46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSlNqSXJuUTdPRHk4SkwyaEFyX3QzR0t1WVZWbEEyMVVNODlyZFF2YkQ0SVdCclRMa2pKSTVKSEhnZlp2Q1dJZTJXWi1vWXItVHpic08weGNZVDlheldQY2FTQy01T1FFejYwQWx3NWU0WFhsT2xVWnc3TENRc055TTM4cFpBZnpTOGxpZFZ6d2FzS2lMWDFwV21PMVF1Nlh6SEZMU1hxTktfQTVPZjlz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxON0NvdThIRFJaWlY0RlBFdDRkM3V4XzQwc3I1SWoxcXdRSk5TZk1xd2l5WDBtRFI2a2MzWTExdS04bHJmU1g3U29PQUw1VWg4UDFqMjlDMmNUcjJ2NDI3NG83OHBCeEtsNTlMMGwxeWFpU2hjM0trSmF3STRONWV5bGx6cENFOC1ldDFvb3h0cE5fcVY0WmZBcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fertilizante mineral com aditivo biológico melhora altura, enxofre e fósforo de cultivos - Canal Rural</t>
+          <t>OPERAÇÃO LEITE COMPEN$ADO: Adulteração de Leite com ureia e soda cáustica rende condenação severa no RS - Terra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17/08/2026 13:19</t>
+          <t>17/08/2026 16:41</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNbERxcTZvVkVyNlRzZTVpZ0FTWHhRdG5vclBfcExyT25DVHZ0dVB5ekl5Qm9zRklEeVNMSmVCNktlS1puUVFhQWwzc1MtWmVzSGdSa0R0Q1FlMTItcVNNenpVQU5mVldUc2RCUzdjWV9HdGZfTE9TbVJGbVg3em83RTJPZ2dmU2N1enNVSDhna3VpcGVMNHRYN2JaVDcxYTJackthM2paaDVNQXBKN3h3ajdrZkcxRjVvVTZkTTdYYlZKWjBJMDUwVnpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxONTZUOHdXM0RPQ290UllHZ0dKcTd0U185WWRFVXFfSDlERzRyMDhmamZoajBVZmNPOTZlMzg5TG9VYVNFVDIwNDFjT19vWjJILVJQVnFYaFZfUHlCeFBjU2x2MTFIRVRUS0o3TGFrMExXLVhpbE5iY2d0VGFxM1VydzNNNkNWZmk4SW5nSHNfeXFoTUY4Y0xKbEowTUNwckV0bHhSTENzVHFEckVGd2JjRGFLZEx2VHBoRW43SjlvZnFxSzlWMzhQYzk5VkVCRkgyeVZXSjdwTlhLV013U0FZTU82VF9ieXZCb0k2eHQ2WVBxQS1qdFlTT2UxOXVYTjBYcERVMVpxT2lZX0YxTGFoWU5ZNGFvYm50Wmgzd1hhMy00UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mosaic lança enzima para acelerar decomposição de palhada - Revista Cultivar</t>
+          <t>Sindicato Metabase participa da 7ª reunião da CIPAMIN da CMOC Chapadão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17/08/2026 10:52</t>
+          <t>17/08/2026 16:11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZW5EZGduY2xOc2dITGplZlVNUkxmUll0QndXS3NWandoeHdPd3ZHTHJYWjEwM21yQ1BKMmVlRTFPNXduMHdSdDRuLV9yZ1VUZXE5dEVyaUNOMXluOENvSmpoRnQ0R3NrUVZKOWtjeGFsSG1JRGtFc19IRWFJQWF3UkpWRDhvUERRNjJCUENsQjJxaEt6d2ZWVW5wVnZoLUJETDZN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSlNqSXJuUTdPRHk4SkwyaEFyX3QzR0t1WVZWbEEyMVVNODlyZFF2YkQ0SVdCclRMa2pKSTVKSEhnZlp2Q1dJZTJXWi1vWXItVHpic08weGNZVDlheldQY2FTQy01T1FFejYwQWx3NWU0WFhsT2xVWnc3TENRc055TTM4cFpBZnpTOGxpZFZ6d2FzS2lMWDFwV21PMVF1Nlh6SEZMU1hxTktfQTVPZjlz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mosaic Biosciences lança produto para manejo de resíduos agrícolas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Fertilizante mineral com aditivo biológico melhora altura, enxofre e fósforo de cultivos - Canal Rural</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17/08/2026 10:49</t>
+          <t>17/08/2026 13:19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcm00Mk9UbFFXWjJNNTlSalFtc05zd09MSHpCYmd0Tk5YUTE5cVUxSjFJQkk0NnQ5YmpTZ0Y2a1VCNGc5ODNPZFRBOXk4LTJIVk5fVmg4S293a2daR3AwRC1yYUs0M21zSGpTOWpRaXp4MnVVM2RYY3dNMnlpdThEb3poQXItem9HTWpYRWtjeFlqWmVyOEt3eDkzMzI1NzBBcng3RDVwYVRLMEhnWmNqdHJDdFFVT3RwQk5VUzdLSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNbERxcTZvVkVyNlRzZTVpZ0FTWHhRdG5vclBfcExyT25DVHZ0dVB5ekl5Qm9zRklEeVNMSmVCNktlS1puUVFhQWwzc1MtWmVzSGdSa0R0Q1FlMTItcVNNenpVQU5mVldUc2RCUzdjWV9HdGZfTE9TbVJGbVg3em83RTJPZ2dmU2N1enNVSDhna3VpcGVMNHRYN2JaVDcxYTJackthM2paaDVNQXBKN3h3ajdrZkcxRjVvVTZkTTdYYlZKWjBJMDUwVnpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ureia no jardim: prazos, dosagens e restrições químicas de aplicação</t>
+          <t>Mosaic lança enzima para acelerar decomposição de palhada - Revista Cultivar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17/08/2026 09:56</t>
+          <t>17/08/2026 10:52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dac0d83b4406ad0c1e3dad3fb79a&amp;url=https%3a%2f%2fport.pravda.ru%2fnews%2fjardim%2f59671-urea-garden-fertilizer%2f&amp;c=9936539315119883676&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPZW5EZGduY2xOc2dITGplZlVNUkxmUll0QndXS3NWandoeHdPd3ZHTHJYWjEwM21yQ1BKMmVlRTFPNXduMHdSdDRuLV9yZ1VUZXE5dEVyaUNOMXluOENvSmpoRnQ0R3NrUVZKOWtjeGFsSG1JRGtFc19IRWFJQWF3UkpWRDhvUERRNjJCUENsQjJxaEt6d2ZWVW5wVnZoLUJETDZN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Limestone Coast Premier League (Australia) Previsoes e Estatisticas para Hoje - AFootballReport</t>
+          <t>Mosaic Biosciences lança produto para manejo de resíduos agrícolas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17/08/2026 07:00</t>
+          <t>17/08/2026 10:49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb0RlVHJVWll5Z2FyMk1BaV9sdnVRLWJ2amp3Q2hncnZ2SVVDZDc2RmQzUi1GREhuUkZXX1oySS1POUx4NHdhNVoycXpTWWNTWkllbkFmNGlMWjVfR00zTGdYcGtQM296aWV0bU1waFV5V1pOd2l1SGI3SURjV0ZTTlRRVkR6bzd0eFRYZk1BdklHbzdGTFlBVTRkODZjd3AwbjY5Yg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNcm00Mk9UbFFXWjJNNTlSalFtc05zd09MSHpCYmd0Tk5YUTE5cVUxSjFJQkk0NnQ5YmpTZ0Y2a1VCNGc5ODNPZFRBOXk4LTJIVk5fVmg4S293a2daR3AwRC1yYUs0M21zSGpTOWpRaXp4MnVVM2RYY3dNMnlpdThEb3poQXItem9HTWpYRWtjeFlqWmVyOEt3eDkzMzI1NzBBcng3RDVwYVRLMEhnWmNqdHJDdFFVT3RwQk5VUzdLSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Escavação e realocação dos túmulos de mártires na área de Limestone Hill. - Vietnam.vn</t>
+          <t>Ureia no jardim: prazos, dosagens e restrições químicas de aplicação</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16/08/2026 05:32</t>
+          <t>17/08/2026 09:56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUnl6SEFHNVJZM2RTYmdna0R3RXlPcldqaDViaDZnM1BuUnllTFJmNk5EeWlhVHRkcXNTakQzNENQMW1TeVR3N3hIX2prZUxReHlpdjZWUHB5RDlDSXRTQUJQMF9DYjA2NzdVSkMtRVZPZnFKejREV1JiemI4a3F1aGU0Mm1Id2lza2xSa2JLZw?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2673c854d8781bf42da37caf430&amp;url=https%3a%2f%2fport.pravda.ru%2fnews%2fjardim%2f59671-urea-garden-fertilizer%2f&amp;c=9936539315119883676&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caminhão carregado de ureia tomba na BR-277, no sentido Curitiba, e 4 pessoas são socorridas - G1</t>
+          <t>Limestone Coast Premier League (Australia) Previsoes e Estatisticas para Hoje - AFootballReport</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15/08/2026 17:48</t>
+          <t>17/08/2026 07:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOeVZKclFKX3lhRzZsc2Rpc0s4OWhMUzBPU2w2ZkdfNkp6Vm1rcF83ZE5PQVp1VzdSekVnT2NGZHhRSDM4NXVZbzRLM2VETVZwQkpBQ2h0NVlhLXBYWGdkQ0taWTkxOHJQTVNWMTI4bkVlVFlOalU3WEtxLTVyaFN0R3hHc2M4OXUyNVViM9IBmwFBVV95cUxNRW9wRmhBWUk5N1FuZGRsZXFESWs0RzJBOGRGUkNydkhnSnBYTlM3VWFMRExVcXB5aXQweUVJTjVlQmMxU1RjV0lULXZTUjduWDF0a3RrdGJzZ0hLUUJobVQ0UFZJSnNwOERGT3I3RkRxanJCOVNTeVl6ZzZnNVNFTktkVHdBMEVEUWJqdWRoRlAzbE5xSGMwSk42Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOb0RlVHJVWll5Z2FyMk1BaV9sdnVRLWJ2amp3Q2hncnZ2SVVDZDc2RmQzUi1GREhuUkZXX1oySS1POUx4NHdhNVoycXpTWWNTWkllbkFmNGlMWjVfR00zTGdYcGtQM296aWV0bU1waFV5V1pOd2l1SGI3SURjV0ZTTlRRVkR6bzd0eFRYZk1BdklHbzdGTFlBVTRkODZjd3AwbjY5Yg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Conflitos mantêm pressão sobre preços de fertilizantes - Agrolink</t>
+          <t>Escavação e realocação dos túmulos de mártires na área de Limestone Hill. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15/08/2026 11:10</t>
+          <t>16/08/2026 05:32</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSEJMWHVMdmp5N2hwb2d0cWNHaFNmaGo2Y2g1QjR1SU5Ldk94M09KMFBDRVA3dUJBQXBzSGktYnpuOEoycWJvY2dCd2J1TnFSZ25sR3g2MFMtdUxTdGNIdHV4bm9kRWtmZ0lDV1JBT2VTbkNZYnpHQzEwaldsZTh2N1F1aEFmSmVwMEFMR2FQWFIzaU9rZVRvZk1oY09JSHkzejVUbFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNUnl6SEFHNVJZM2RTYmdna0R3RXlPcldqaDViaDZnM1BuUnllTFJmNk5EeWlhVHRkcXNTakQzNENQMW1TeVR3N3hIX2prZUxReHlpdjZWUHB5RDlDSXRTQUJQMF9DYjA2NzdVSkMtRVZPZnFKejREV1JiemI4a3F1aGU0Mm1Id2lza2xSa2JLZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Poder de compra de fertilizantes melhorou em julho, aponta Mosaic - Globo Rural</t>
+          <t>Caminhão carregado de ureia tomba na BR-277, no sentido Curitiba, e 4 pessoas são socorridas - G1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15/08/2026 07:30</t>
+          <t>15/08/2026 17:48</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPSVhGNU5pNGk4cUxzWEdnMGhuYXlPTm9JRldSTWY3U0pRVE4wR2p3LVNnRk9CMWR3elZ5aFZlWTQ2Z0NGVG1BQVFWM3p0OTYyVW15Q3JjMk1qNmFFZzJwSXhsc1BNbW9VVVZjTFZwc2x5WFoxeU1JQm5HM0RyaHMxeEw1Mmo0dHpEd3hoM19zZFpld180V0xqZWNxbU5Uc2dmTDFkb0N4NjE5eW5kWUZmVjZsS25JTmpxU3M2WHp1UWTSAc8BQVVfeXFMUGN0dmJHa3p6c1JaOGF1ZWl2aFJpaXB2Q3B0M0JzckltQTRUS2VFSy1tWHdES2lnN1NGdEJzX0tnblI5LVAyLW9hQno2WVpyQWZHWW1keTAwVFNxR29BN1Zza0NiakZzeXFEbUlSYXBXMTZaVDNEU0Mxd1ZzYjFlODN2VVFpcm5xX3psRWJxX2tGaU9OckFKVlRzMHQySFhTb20wT2pKNjNKZ2F5ZzJmR1NBOGRkWTJ5bDFZckV5SVBXcng3aDFIQ2dLYldGM2xF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOeVZKclFKX3lhRzZsc2Rpc0s4OWhMUzBPU2w2ZkdfNkp6Vm1rcF83ZE5PQVp1VzdSekVnT2NGZHhRSDM4NXVZbzRLM2VETVZwQkpBQ2h0NVlhLXBYWGdkQ0taWTkxOHJQTVNWMTI4bkVlVFlOalU3WEtxLTVyaFN0R3hHc2M4OXUyNVViM9IBmwFBVV95cUxNRW9wRmhBWUk5N1FuZGRsZXFESWs0RzJBOGRGUkNydkhnSnBYTlM3VWFMRExVcXB5aXQweUVJTjVlQmMxU1RjV0lULXZTUjduWDF0a3RrdGJzZ0hLUUJobVQ0UFZJSnNwOERGT3I3RkRxanJCOVNTeVl6ZzZnNVNFTktkVHdBMEVEUWJqdWRoRlAzbE5xSGMwSk42Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Martin Marietta emite US$ 5,5 bilhões em notas sênior para aquisição da Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Conflitos mantêm pressão sobre preços de fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14/08/2026 22:48</t>
+          <t>15/08/2026 11:10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNckJSejh2UjRiY1lZbkVXMnVmVmpENVdKSjdvN29BZjlGUUd6WnN0dmF3WkJDWXdRVFFHNmxLUHNFMC1wY19xbmR5bERrcEFVZkpUV202MFlXaktfaTh1NUJRSmJTZVdJcW9rLWM1R19SR2ZSYXN0ODc5cEJSWTV5WElXQlV1TU1VVVBLUHdyQnQ5RHdDajNYejlkalFKbTJOSFUyWWQ3djlnVHlQSlRKY0VCRXVJWXk3YmdzbEZNSzlFSTJZLW95WFY3cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQSEJMWHVMdmp5N2hwb2d0cWNHaFNmaGo2Y2g1QjR1SU5Ldk94M09KMFBDRVA3dUJBQXBzSGktYnpuOEoycWJvY2dCd2J1TnFSZ25sR3g2MFMtdUxTdGNIdHV4bm9kRWtmZ0lDV1JBT2VTbkNZYnpHQzEwaldsZTh2N1F1aEFmSmVwMEFMR2FQWFIzaU9rZVRvZk1oY09JSHkzejVUbFlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A alta nos custos dos adubos importados que pode pressionar a próxima safra - CompreRural</t>
+          <t>Poder de compra de fertilizantes melhorou em julho, aponta Mosaic - globorural.globo.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14/08/2026 22:32</t>
+          <t>15/08/2026 07:30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWFFtYkRfbkRrcXpYRnZGRzZOdlJnLWxBbkFwZUhIbm9BYV9lc3NhZTlHS0V2SEJGRFpGT3d6ZDExb2dwMnJsUTJWWFp2TUtfS3p6aXNNcmpZZ2NVaDBJeFZPcXdCclUzRHN1WE0xdHJLSWpGdXBSYl82WXJUQzEtc09zMjdHb1N6TXJ3WWZsUnQ3UUJDa012eE1sNG9qRzVDaG1xUk9nbXN4ZEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPSVhGNU5pNGk4cUxzWEdnMGhuYXlPTm9JRldSTWY3U0pRVE4wR2p3LVNnRk9CMWR3elZ5aFZlWTQ2Z0NGVG1BQVFWM3p0OTYyVW15Q3JjMk1qNmFFZzJwSXhsc1BNbW9VVVZjTFZwc2x5WFoxeU1JQm5HM0RyaHMxeEw1Mmo0dHpEd3hoM19zZFpld180V0xqZWNxbU5Uc2dmTDFkb0N4NjE5eW5kWUZmVjZsS25JTmpxU3M2WHp1UWTSAc8BQVVfeXFMUGN0dmJHa3p6c1JaOGF1ZWl2aFJpaXB2Q3B0M0JzckltQTRUS2VFSy1tWHdES2lnN1NGdEJzX0tnblI5LVAyLW9hQno2WVpyQWZHWW1keTAwVFNxR29BN1Zza0NiakZzeXFEbUlSYXBXMTZaVDNEU0Mxd1ZzYjFlODN2VVFpcm5xX3psRWJxX2tGaU9OckFKVlRzMHQySFhTb20wT2pKNjNKZ2F5ZzJmR1NBOGRkWTJ5bDFZckV5SVBXcng3aDFIQ2dLYldGM2xF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Com custo de produção em alta, mato-grossenses lançam mão do uso de calcário - MT Econômico</t>
+          <t>Martin Marietta emite US$ 5,5 bilhões em notas sênior para aquisição da Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14/08/2026 10:54</t>
+          <t>14/08/2026 22:48</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOeGNDTzBqejdEVW5CdFpuUlVYV1ZrWnFocldwa1BkdjlneXQxdlhOZkxhcDdFLW5JQ3c1VHh4NUVVdDltcktIeWxUaFlRNFRFWnQ4RWl2MFo5NFhwMXZpS3RoY0xQaEVDRGdsYWxOdG1STERia3VGX2R3dHhzVmFTQTNJcS1wZUZhNldSTjhka05ZdkhPY3lYWjdCNmpiQTltaVlWbjY0aV81dW5iNlN6djJrem5BeE1mUXBRcnRvUk5TZWprTnpmMVNVa2RycTRl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNckJSejh2UjRiY1lZbkVXMnVmVmpENVdKSjdvN29BZjlGUUd6WnN0dmF3WkJDWXdRVFFHNmxLUHNFMC1wY19xbmR5bERrcEFVZkpUV202MFlXaktfaTh1NUJRSmJTZVdJcW9rLWM1R19SR2ZSYXN0ODc5cEJSWTV5WElXQlV1TU1VVVBLUHdyQnQ5RHdDajNYejlkalFKbTJOSFUyWWQ3djlnVHlQSlRKY0VCRXVJWXk3YmdzbEZNSzlFSTJZLW95WFY3cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Índice de Poder de Compra de Fertilizantes encerra julho em queda de 5% - Notícias Agrícolas</t>
+          <t>A alta nos custos dos adubos importados que pode pressionar a próxima safra - CompreRural</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14/08/2026 09:57</t>
+          <t>14/08/2026 22:32</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNRjVDejlibkhQc0tXRUREaXRlTnk3R3pvd0lhN04tOE0yTGNHd1FpSVZwQXFpUTFsUm91NUg2OFdYLXRxN0pBTWhFelFNRjd1eE5IbktUSkFFcDJqckg2US12ME0zT2Q5M2hpX1M1VExQelRiQXFBelJINzRxWnNpSWRGaVBkMWdzV0o5Y2NPTU85VUdjaFpqYkhXODNhR3FsZ1Q5MThnajA1RHdkZGZyWkRmWHZLdGdBZS05YXRaUG5hSnhEUHdfb3o0bmNEYzFjWkhFSE10VdIB3AFBVV95cUxPNTNzZTNTT3oycERERzJvQkVON19iV2lxTVd6d0xrQWxQTHpVX2tHV1JkZDVpZW1POGVPd2VKa3p6ZU9MV1NoaWI4U3dxbjFjdGcxZ1haenRsR2RnUGF3NmEyYWZBbW1seVRfaE45TGJHdmQwMHZ2RUgwX1pBUHExdjNKekVhdWJ2cDhLT3RQZUlVRzZuZ2tmc08yWEhfektNc0FscGNhSkR4Q0JScmdjVEcyaWNXcFIyYk9kcXE3T3ZXQTdUMU1GaXQ4R3p0TGs3c00zUUQxSXRlNkdE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWFFtYkRfbkRrcXpYRnZGRzZOdlJnLWxBbkFwZUhIbm9BYV9lc3NhZTlHS0V2SEJGRFpGT3d6ZDExb2dwMnJsUTJWWFp2TUtfS3p6aXNNcmpZZ2NVaDBJeFZPcXdCclUzRHN1WE0xdHJLSWpGdXBSYl82WXJUQzEtc09zMjdHb1N6TXJ3WWZsUnQ3UUJDa012eE1sNG9qRzVDaG1xUk9nbXN4ZEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Compra de ureia pelo Brasil volta a subir forte em julho - Farmnews</t>
+          <t>Com custo de produção em alta, mato-grossenses lançam mão do uso de calcário - MT Econômico</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14/08/2026 08:24</t>
+          <t>14/08/2026 10:54</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUjBFMHFVU3dlWTRSeFJqcGd2dGxJbURMWXhfU0I4S1AxOUlobVdJb1JIYThheXlkVS1qbE9QSnVhS0Q5VHNXRXc2OXNveUl4dTdhS3NmMnlzT3BzRE1PdXJOenBMOHFXQjRNa2dNRFRMc3c4T3FoLUhlNnROVkhzRGRjNGVUeDdSM3paaURYNDhnOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOeGNDTzBqejdEVW5CdFpuUlVYV1ZrWnFocldwa1BkdjlneXQxdlhOZkxhcDdFLW5JQ3c1VHh4NUVVdDltcktIeWxUaFlRNFRFWnQ4RWl2MFo5NFhwMXZpS3RoY0xQaEVDRGdsYWxOdG1STERia3VGX2R3dHhzVmFTQTNJcS1wZUZhNldSTjhka05ZdkhPY3lYWjdCNmpiQTltaVlWbjY0aV81dW5iNlN6djJrem5BeE1mUXBRcnRvUk5TZWprTnpmMVNVa2RycTRl?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shuumatsu no Harem tem primeiro vídeo promocional revelado - Anime United</t>
+          <t>Índice de Poder de Compra de Fertilizantes encerra julho em queda de 5% - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14/08/2026 03:37</t>
+          <t>14/08/2026 09:57</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOXV0NkhyWmNFSlY3TEg4UlNFTmFWRFkzb0RNZkx6UkY2UklFM09oVjdGZmlyem1uSmlfRUF0WkpnRWJKczh1S1pkUWlMWEtSMEs1RFBlb01LWFVMOENDSFZWZ2Y2UzY0VncxZUlRNWZxQkxRYkh3TzFsSTJjUUx3RVI1andIUi1POFNKNHEtWk5NQlpkNG5wclVhUzJybjNvTndOd0pTWUlYc3dsRnZGYW4xdG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNRjVDejlibkhQc0tXRUREaXRlTnk3R3pvd0lhN04tOE0yTGNHd1FpSVZwQXFpUTFsUm91NUg2OFdYLXRxN0pBTWhFelFNRjd1eE5IbktUSkFFcDJqckg2US12ME0zT2Q5M2hpX1M1VExQelRiQXFBelJINzRxWnNpSWRGaVBkMWdzV0o5Y2NPTU85VUdjaFpqYkhXODNhR3FsZ1Q5MThnajA1RHdkZGZyWkRmWHZLdGdBZS05YXRaUG5hSnhEUHdfb3o0bmNEYzFjWkhFSE10VdIB3AFBVV95cUxPNTNzZTNTT3oycERERzJvQkVON19iV2lxTVd6d0xrQWxQTHpVX2tHV1JkZDVpZW1POGVPd2VKa3p6ZU9MV1NoaWI4U3dxbjFjdGcxZ1haenRsR2RnUGF3NmEyYWZBbW1seVRfaE45TGJHdmQwMHZ2RUgwX1pBUHExdjNKekVhdWJ2cDhLT3RQZUlVRzZuZ2tmc08yWEhfektNc0FscGNhSkR4Q0JScmdjVEcyaWNXcFIyYk9kcXE3T3ZXQTdUMU1GaXQ4R3p0TGs3c00zUUQxSXRlNkdE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes | Parceria com Casa dos Ventos - Energia Eólica - Brasil Mineral</t>
+          <t>Compra de ureia pelo Brasil volta a subir forte em julho - Farmnews</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14/08/2026 01:26</t>
+          <t>14/08/2026 08:24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUlhuTXNnNW1pcERBMlB3YkhTOGo4cUVIdzRGb1l3YzVFLUtTckpYZnkxcGxUeUhWLTM4eG1PeFNPdjduaVd3ZkJNZ25YMXhRN1Fxb2gwdDBYaEt4UXlJaXF2OUttWktBanRfS2JHVlVqRHJ3T1dyY0t2WEo0Yl9hQU9tSUVJWlN3RXNvTHBGUGpEVUFGblJRQ3Q3OHBVVVR3YXp3OENCOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNUjBFMHFVU3dlWTRSeFJqcGd2dGxJbURMWXhfU0I4S1AxOUlobVdJb1JIYThheXlkVS1qbE9QSnVhS0Q5VHNXRXc2OXNveUl4dTdhS3NmMnlzT3BzRE1PdXJOenBMOHFXQjRNa2dNRFRMc3c4T3FoLUhlNnROVkhzRGRjNGVUeDdSM3paaURYNDhnOUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Importações brasileiras de fertilizantes de julho atingem 2,99 Milhões de toneladas com alta de 31,3% em comparação a junho - GlobalFert</t>
+          <t>Shuumatsu no Harem tem primeiro vídeo promocional revelado - Anime United</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13/08/2026 18:54</t>
+          <t>14/08/2026 03:37</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxObzVNMnZtZGV1X3dYWmZxYWduT3JGQ1pnQmFiZVkyZWZHYWEzN054WnhHMVpBNjJQal9qYmJWczRmZXVWNzkxMlpIX3BDTlZDYmNwbXBaNlN1bURneEN6VXJfSUdsdG1kQlBvdlg1N2JRa3hVbFl6Z3pQWFFPMUs4ak9penMwV1o4bGlpSWs0d1BxTWk3cVlsWjZYMU02WndPWjVuZUdOMEY5SDlvRUo5ZEpOSm5aVU9UQnRFZkUyY1dNQy02UENWcGphUTRYaG5aUGFaNmJ1ZTM3TWIxakdmaWxkUkhHNFh0SlFKWEJicXppSUk5ZnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOXV0NkhyWmNFSlY3TEg4UlNFTmFWRFkzb0RNZkx6UkY2UklFM09oVjdGZmlyem1uSmlfRUF0WkpnRWJKczh1S1pkUWlMWEtSMEs1RFBlb01LWFVMOENDSFZWZ2Y2UzY0VncxZUlRNWZxQkxRYkh3TzFsSTJjUUx3RVI1andIUi1POFNKNHEtWk5NQlpkNG5wclVhUzJybjNvTndOd0pTWUlYc3dsRnZGYW4xdG4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tudo sobre: calcário marinho - Portal Piauí Hoje</t>
+          <t>Mosaic Fertilizantes | Parceria com Casa dos Ventos - Energia Eólica - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13/08/2026 15:26</t>
+          <t>14/08/2026 01:26</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBodHpUYk5CalBVRkI1XzJOV0pYRS1XN0pLT0xfbEJBV2dmM1FTWG9jODhQanpvWlRzSkxEX1hmZ2pEQ1RpN3Z3a2xLclZmclZELVdPeUhlZFMzMnIxQVRBOTdhcENHLXl1WlMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUlhuTXNnNW1pcERBMlB3YkhTOGo4cUVIdzRGb1l3YzVFLUtTckpYZnkxcGxUeUhWLTM4eG1PeFNPdjduaVd3ZkJNZ25YMXhRN1Fxb2gwdDBYaEt4UXlJaXF2OUttWktBanRfS2JHVlVqRHJ3T1dyY0t2WEo0Yl9hQU9tSUVJWlN3RXNvTHBGUGpEVUFGblJRQ3Q3OHBVVVR3YXp3OENCOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Projeto prevê geração de empregos com exploração de calcário marinho no litoral do Piauí - Portal Piauí Hoje</t>
+          <t>Tudo sobre: calcário marinho - Portal Piauí Hoje</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13/08/2026 13:34</t>
+          <t>13/08/2026 15:26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOSjRKdkN6N1RzVXhKZTVQWjJCVDJqVGFjWlAyQ280LVZoQ0V5a3JaYkNyMnUxYTJTeDBHOUt6b3pYTEIzdWNYNGVJMlFPdzRKam1QVHVlQ2FoZzZHOHNxc1ZTdjVvSzNyZnpNMWdCZ2VHbFhtWjVrNXpuT0tsU0l1OWJveGlHZ0hRSmhGVmZCVm9tTkZ0MTVJY1pxejRsR1pORC1DVVBXQVlnc1pDNEJfZ3JzcmZ1MlRyTktIWmVrNTdQUUg1MlRwVEpQVmVMaHR2cXBNTHRLd9IB3AFBVV95cUxNblAxNVk1MTBkTXEtWmxLSExrSk1kVDZfSGhBRXBOVTFTdW1meUk0VzBvWTd1YUFTODE0djNIVmZCSlg1M3ozSVFKbTZlTlV5NWlqTERSNU5RQ19QQUt4eXNUWHl0MWhSSkVFbVU1SU1xam91YjB1WHdBSkdXekhqeExUX1JLSE5ub1luLWZaa0d0aHNSamk5QS1NZHhHYklMQzROV1FXUFBfcVZIeTVORG81MHR5WDVCUWticW1nRExoS2dvcnBucUhmUDhMWnJhaUtnYnV0alJsZV9W?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBodHpUYk5CalBVRkI1XzJOV0pYRS1XN0pLT0xfbEJBV2dmM1FTWG9jODhQanpvWlRzSkxEX1hmZ2pEQ1RpN3Z3a2xLclZmclZELVdPeUhlZFMzMnIxQVRBOTdhcENHLXl1WlMw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aos 64 anos, veterano transformou 113 toneladas de cimento e blocos de calcário em uma casa de 11 cômodos rodeada por 150 esculturas no Kansas - Brasil 247</t>
+          <t>Projeto prevê geração de empregos com exploração de calcário marinho no litoral do Piauí - Portal Piauí Hoje</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13/08/2026 12:15</t>
+          <t>13/08/2026 13:34</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNUGo3a3BhR1hDTXNpSTcyNlhhVGRUajNMUDdqU1BmU2NZR3NqdFEwYXowSXVudDVyOUt6TWoxMFVKNHpaYVdkRjRvYmxDdHVCeXNsS3ROb216eDZuNUVlX1JKNUszMDhtSTNlMGJpdEExRGsyZUFfZUItTmZBdms2OFdjQ2hqMzV2ZjVtTTlBYVJUOVVsOWRLLVVjdHM5ZVI3eVkzYU9iS0s0Y0loNzZHMm56aHY2eVNxZE11ZVBiak51aWlRcmtDYl9RRzQtel9MRXhrTFgyVDhTZVJySXdIZ0o0MU1udlZsNDF4Sk83NngzZVplU01pT1ZpR0RFQ2JqY0t2YmVSM283bkp6WnhtWkNJY0J4eTNTeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOSjRKdkN6N1RzVXhKZTVQWjJCVDJqVGFjWlAyQ280LVZoQ0V5a3JaYkNyMnUxYTJTeDBHOUt6b3pYTEIzdWNYNGVJMlFPdzRKam1QVHVlQ2FoZzZHOHNxc1ZTdjVvSzNyZnpNMWdCZ2VHbFhtWjVrNXpuT0tsU0l1OWJveGlHZ0hRSmhGVmZCVm9tTkZ0MTVJY1pxejRsR1pORC1DVVBXQVlnc1pDNEJfZ3JzcmZ1MlRyTktIWmVrNTdQUUg1MlRwVEpQVmVMaHR2cXBNTHRLd9IB3AFBVV95cUxNblAxNVk1MTBkTXEtWmxLSExrSk1kVDZfSGhBRXBOVTFTdW1meUk0VzBvWTd1YUFTODE0djNIVmZCSlg1M3ozSVFKbTZlTlV5NWlqTERSNU5RQ19QQUt4eXNUWHl0MWhSSkVFbVU1SU1xam91YjB1WHdBSkdXekhqeExUX1JLSE5ub1luLWZaa0d0aHNSamk5QS1NZHhHYklMQzROV1FXUFBfcVZIeTVORG81MHR5WDVCUWticW1nRExoS2dvcnBucUhmUDhMWnJhaUtnYnV0alJsZV9W?oc=5</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Como o calcário virou escudo contra a alta dos fertilizantes em MT - Cliquef5</t>
+          <t>Aos 64 anos, veterano transformou 113 toneladas de cimento e blocos de calcário em uma casa de 11 cômodos rodeada por 150 esculturas no Kansas - Brasil 247</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13/08/2026 10:30</t>
+          <t>13/08/2026 12:15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdVhJZ1c0UmtPcUJaZnBwTGVVYkViMFNjZXVWaGN3cGhzV2pGZFlvQnJTRjdQenUtN3g1QVVfNWVsTEQ3a0gydi1oRzdYaEFQS1BxbXRJQTljQWo2bXh3VDU5NDNHN19BTEVTekxZdTdEd1g5TU1YOGlPbEVldG1mTTN1NFZ5eVpIaWluUGdDQlBUOXRNc1gzenIxYVJxRWRMXzNremlPS3dFaG5MQXVTMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNUGo3a3BhR1hDTXNpSTcyNlhhVGRUajNMUDdqU1BmU2NZR3NqdFEwYXowSXVudDVyOUt6TWoxMFVKNHpaYVdkRjRvYmxDdHVCeXNsS3ROb216eDZuNUVlX1JKNUszMDhtSTNlMGJpdEExRGsyZUFfZUItTmZBdms2OFdjQ2hqMzV2ZjVtTTlBYVJUOVVsOWRLLVVjdHM5ZVI3eVkzYU9iS0s0Y0loNzZHMm56aHY2eVNxZE11ZVBiak51aWlRcmtDYl9RRzQtel9MRXhrTFgyVDhTZVJySXdIZ0o0MU1udlZsNDF4Sk83NngzZVplU01pT1ZpR0RFQ2JqY0t2YmVSM283bkp6WnhtWkNJY0J4eTNTeXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -1150,215 +1150,215 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coronel Pacheco entrega calcário a produtores rurais do município - Jornal Panorama Minas</t>
+          <t>Como o calcário virou escudo contra a alta dos fertilizantes em MT - Cliquef5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12/08/2026 14:28</t>
+          <t>13/08/2026 10:30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUnVEMl9ZZTM3RXg0LV9qSlNRYUJWVUpONWlfNzlFV2d3aWZrTFlHclVaaU5hWU1PaS1DRFFJVndlMFZIcFplMEQzcUVpZW5xWXVTU0VjTlJRUHJIOXM2dHlmT3pYQTFhWDI5NXNidTM1VHhtWkpvcjZWTU4yTk1qWFlrUlpNZl9SWXRCdHBOejl3ZGF0QkNSdkJGSlJwWHVpRER3MGVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdVhJZ1c0UmtPcUJaZnBwTGVVYkViMFNjZXVWaGN3cGhzV2pGZFlvQnJTRjdQenUtN3g1QVVfNWVsTEQ3a0gydi1oRzdYaEFQS1BxbXRJQTljQWo2bXh3VDU5NDNHN19BTEVTekxZdTdEd1g5TU1YOGlPbEVldG1mTTN1NFZ5eVpIaWluUGdDQlBUOXRNc1gzenIxYVJxRWRMXzNremlPS3dFaG5MQXVTMQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Perícia confirma presença de veneno agrícola em garrafada que causou morte no Sertão - O Alagoano</t>
+          <t>Coronel Pacheco entrega calcário a produtores rurais do município - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>12/08/2026 10:08</t>
+          <t>12/08/2026 14:28</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxObjRDcUVsdWFpSi1wVjZobHI4V3hXRUk3VGs0WWVyYVNjVzlOaUJCd0g1UTFub1AtTUJ3clZKRmxfLTlRUnFWOVlIY2o5V25vV2FVYnFsZkFEVGVsUmNFdGdqTEhHUlUtSXdsQlZfSlF0YXZ3TVFsaEVKcDRPVzNzU0NGZkg3QVo3dmQ1NldnVG1mdXpqX21tTzNmT0RCRk5Nd2NMUEQzUnpxRHF6alhZUjV1aXkxaHhXMzNWQktIdE8wWk9DRlhjb1lMYXhtN0JS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQUnVEMl9ZZTM3RXg0LV9qSlNRYUJWVUpONWlfNzlFV2d3aWZrTFlHclVaaU5hWU1PaS1DRFFJVndlMFZIcFplMEQzcUVpZW5xWXVTU0VjTlJRUHJIOXM2dHlmT3pYQTFhWDI5NXNidTM1VHhtWkpvcjZWTU4yTk1qWFlrUlpNZl9SWXRCdHBOejl3ZGF0QkNSdkJGSlJwWHVpRER3MGVn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros elevam custo da safra e fazem calcário ganhar importância em MT</t>
+          <t>Perícia confirma presença de veneno agrícola em garrafada que causou morte no Sertão - oalagoano.com.br</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12/08/2026 07:40</t>
+          <t>12/08/2026 10:08</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fwww.olhardireto.com.br%2fagro-e-negocios%2fnoticias%2ffertilizantes-mais-caros-elevam-custo-da-safra-e-fazem-calcario-ganhar-importancia-em-mt&amp;c=7347040783018588872&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxObjRDcUVsdWFpSi1wVjZobHI4V3hXRUk3VGs0WWVyYVNjVzlOaUJCd0g1UTFub1AtTUJ3clZKRmxfLTlRUnFWOVlIY2o5V25vV2FVYnFsZkFEVGVsUmNFdGdqTEhHUlUtSXdsQlZfSlF0YXZ3TVFsaEVKcDRPVzNzU0NGZkg3QVo3dmQ1NldnVG1mdXpqX21tTzNmT0RCRk5Nd2NMUEQzUnpxRHF6alhZUjV1aXkxaHhXMzNWQktIdE8wWk9DRlhjb1lMYXhtN0JS?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Saiba quem é o empresário alvo da PF por esquema de extração de calcário em MT - O Mato Grosso</t>
+          <t>Fertilizantes mais caros elevam custo da safra e fazem calcário ganhar importância em MT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11/08/2026 23:00</t>
+          <t>12/08/2026 07:40</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUmp3SF9jOFNfMng3cDk3OVhqRDZxeU01WkpveUo5d3MwaC1WZGl4dVlUVUF5N3FyRXdEb2JLUC1QQVhfeUx2ZXRBbU9TeFNiN3VKUF92Q2RabUxodXZMU3RRSUs0RUJOdl95U29qUWN6SEk1Q1k5WlJycXROcnZXbDcwOTNCM2RQZndYUmgtamYzUHVDVjI2TmFLaUtEOUF5LWxwY1hn?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fwww.olhardireto.com.br%2fagro-e-negocios%2fnoticias%2ffertilizantes-mais-caros-elevam-custo-da-safra-e-fazem-calcario-ganhar-importancia-em-mt&amp;c=7347040783018588872&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Informações Relevantes CMOC Group Ltd (PK) (CMCLF) - ADVFN</t>
+          <t>Saiba quem é o empresário alvo da PF por esquema de extração de calcário em MT - omatogrosso.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11/08/2026 14:46</t>
+          <t>11/08/2026 23:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1oNGpwREx2MEtWa2tLaWhnT0RaWDFmSTRvMjZxb2ZGaHRGOV9RRnlJbThBME94djJjaXNaYklEZDg1NmgwLUd4VkM4NWh0OVJCblFpbng3WTZHeWVCY3FXY3pUYThOUUpO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUmp3SF9jOFNfMng3cDk3OVhqRDZxeU01WkpveUo5d3MwaC1WZGl4dVlUVUF5N3FyRXdEb2JLUC1QQVhfeUx2ZXRBbU9TeFNiN3VKUF92Q2RabUxodXZMU3RRSUs0RUJOdl95U29qUWN6SEk1Q1k5WlJycXROcnZXbDcwOTNCM2RQZndYUmgtamYzUHVDVjI2TmFLaUtEOUF5LWxwY1hn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gallery of Revestimiento porcelánico estilo piedra - Limestone - 3 - ArchDaily</t>
+          <t>Informações Relevantes CMOC Group Ltd (PK) (CMCLF) - ADVFN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10/08/2026 15:31</t>
+          <t>11/08/2026 14:46</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTC1LN0RJMllDNUJ1SmROMUlDMHVDckMzUG9KejVOR3g4YnVZN19hX1MtdzFKQl8tY1FWNHdPbTVwZWMzeWxZeTRUSUNTYzVSYzI2UWlpQy1MSzA3blhRZWdwcEZjRTlndV9va0U1dmxqLXRCZUdJV1FQRzEtdGNGelROa0ljbjJZV3VKNTdOTElsZ1l0QXB6MWkyOUxNLVZmcllTM2Z0UTVGTnpjSElsRW0tN0ZVLXhRTVFPNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1oNGpwREx2MEtWa2tLaWhnT0RaWDFmSTRvMjZxb2ZGaHRGOV9RRnlJbThBME94djJjaXNaYklEZDg1NmgwLUd4VkM4NWh0OVJCblFpbng3WTZHeWVCY3FXY3pUYThOUUpO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alckmin: MS terá maior fábrica de ureia da América Latina - Campo Grande News</t>
+          <t>Gallery of Revestimiento porcelánico estilo piedra - Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10/08/2026 11:12</t>
+          <t>10/08/2026 15:31</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQTXhMNmVvcHhfN2g1UVoyOWhTR19CM19XWWhRdC1HMS1ubEJFeDA1dHUtbUNVbXBwZUVQMjJFY2tLaDNuTFZKYmhrMDlldTc0aXBlc2tmUWhvQkFfTUFWenVUMFNBSWVzbXdPR2NmYmJJNk9qbXlyU1NTbzZyZlhFekxBWV9JRVVKQUJBVVpKdnl3bUlJTGJzOW01SG9sNFRtbFVlT3UyQjdnV19HLS1MaGJDVjJYVF9NdjZfeDZR0gG-AUFVX3lxTE5ZeEt2WnBHck1DWEgzeGpFcGtNOHUyZENzQTF6RG14dkoteWtURVFsVHRhRHBmTnIxSnJ4dVRtQlBtWnBtdElrQnJEbVB1cUhQcHljWTFPa0k4d1lqSDlKc0tnYWZDREtQSHBEQV9SMk9MLVZ0aUM2dzR1RVFwWjJ4LU95RXhwaVNrUTVEWnhYcHIwV0lpbURQcjNSU3p3cjRqRFFrX3FjSjNYaWpqWUk5ajJISHlwRkNpT0dJd1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQTC1LN0RJMllDNUJ1SmROMUlDMHVDckMzUG9KejVOR3g4YnVZN19hX1MtdzFKQl8tY1FWNHdPbTVwZWMzeWxZeTRUSUNTYzVSYzI2UWlpQy1MSzA3blhRZWdwcEZjRTlndV9va0U1dmxqLXRCZUdJV1FQRzEtdGNGelROa0ljbjJZV3VKNTdOTElsZ1l0QXB6MWkyOUxNLVZmcllTM2Z0UTVGTnpjSElsRW0tN0ZVLXhRTVFPNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Martin Marietta obtém aprovações regulatórias para aquisição da Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Alckmin: MS terá maior fábrica de ureia da América Latina - Campo Grande News</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10/08/2026 10:21</t>
+          <t>10/08/2026 11:12</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOGdkZFpnZUhBYlp2b3hCVldUTlFNd2dRNVdEVElDcFFpVmlLQTczN3FNOThLTG9qQ1RyZkxxdk5hcEotemxsSVhUYXFaQzhIU2p0c0tZVzVkZWZZRGxCd2w1YjJEdHJNYjg2djNlUDZhQ0J6cENqaUFOdFcybnpQdzZYSmJ0NnJQUnk3ZUo3bTBfaUctYVBNazV4TXdMWnZxRjZRbnc1S0QzamJVd3d0RzVwTjVfajkyaDR3S0lHSktGRnhTeFp5RmkxbTVkN0pEZ2d4ZGh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQTXhMNmVvcHhfN2g1UVoyOWhTR19CM19XWWhRdC1HMS1ubEJFeDA1dHUtbUNVbXBwZUVQMjJFY2tLaDNuTFZKYmhrMDlldTc0aXBlc2tmUWhvQkFfTUFWenVUMFNBSWVzbXdPR2NmYmJJNk9qbXlyU1NTbzZyZlhFekxBWV9JRVVKQUJBVVpKdnl3bUlJTGJzOW01SG9sNFRtbFVlT3UyQjdnV19HLS1MaGJDVjJYVF9NdjZfeDZR0gG-AUFVX3lxTE5ZeEt2WnBHck1DWEgzeGpFcGtNOHUyZENzQTF6RG14dkoteWtURVFsVHRhRHBmTnIxSnJ4dVRtQlBtWnBtdElrQnJEbVB1cUhQcHljWTFPa0k4d1lqSDlKc0tnYWZDREtQSHBEQV9SMk9MLVZ0aUM2dzR1RVFwWjJ4LU95RXhwaVNrUTVEWnhYcHIwV0lpbURQcjNSU3p3cjRqRFFrX3FjSjNYaWpqWUk5ajJISHlwRkNpT0dJd1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão</t>
+          <t>Martin Marietta obtém aprovações regulatórias para aquisição da Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10/08/2026 04:31</t>
+          <t>10/08/2026 10:21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dabfd4e74b3a8f5f8090bd6c12d0&amp;url=https%3a%2f%2fgloborural.globo.com%2fnegocios%2fnoticia%2f2026%2f08%2fmosaic-anuncia-compra-de-titulos-de-divida-de-cerca-de-us-14-bilhao.ghtml&amp;c=5616585260663838501&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOGdkZFpnZUhBYlp2b3hCVldUTlFNd2dRNVdEVElDcFFpVmlLQTczN3FNOThLTG9qQ1RyZkxxdk5hcEotemxsSVhUYXFaQzhIU2p0c0tZVzVkZWZZRGxCd2w1YjJEdHJNYjg2djNlUDZhQ0J6cENqaUFOdFcybnpQdzZYSmJ0NnJQUnk3ZUo3bTBfaUctYVBNazV4TXdMWnZxRjZRbnc1S0QzamJVd3d0RzVwTjVfajkyaDR3S0lHSktGRnhTeFp5RmkxbTVkN0pEZ2d4ZGh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trabalhador morre após estrutura metálica desabar sobre caminhão em mineradora em MG - G1</t>
+          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10/08/2026 04:00</t>
+          <t>10/08/2026 04:31</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNc2ZqdVJHVzVWSFI0ckxwZk5xOWZrZVVZR2hLWDlYNlg1bVBNOHFDVTdXUjNwVDhZT3hHRjk5R09ybjNFM2c5YlN6bm8yVHoyOUJBUjlqamVKSURnNk5YZDZSaWNlTUoyR0NVelQ3cnhMZHVZbTFXTVhIajhnUS1EMkZ4Yl9pN3pDRlNYYWx1a21hVkdQdmkzLUlfOXhubVBIcENDOTRNeVVRV19DMkhKTE9EeUlOMDN0SGc1c0stanFxckdxdkJpbVRDalcyVlcyOXlxdnRGMEJWX1JIc3NV0gHuAUFVX3lxTFBiY1B0TGRZZzc1RnpzWm1xa282LUd3MHY5NkhmNjhGcE9CUmpoR2lPdVJ5R3RWOXJVV2NfeTNMY1Jsa0dDWmxBTTVHeGFRU01mSFdRWDdVWmFrWlI5MVAzU0RpZkQwV2F5cVluaVFzZVlKc2tpdkdwYk1kTmpGTHZmV3loekFjdGhvMmN4eTFLbGRBUWVmVmVsY3FvUG15eHN3TVg5VGhISk1HbTdQNDV3UFdwX2k2MWl5Z0ptOUhhOEtxQkJyWUsyTlNweVN0MkhHQzlPajJGQ1ZURUVhbDFDMXhNVU5MNXBDREpxZmc?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2667e4f4e75bffc6bf9d8437f55&amp;url=https%3a%2f%2fgloborural.globo.com%2fnegocios%2fnoticia%2f2026%2f08%2fmosaic-anuncia-compra-de-titulos-de-divida-de-cerca-de-us-14-bilhao.ghtml&amp;c=5616585260663838501&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão - Globo Rural</t>
+          <t>Mosaic anuncia compra de títulos de dívida de cerca de US$ 1,4 bilhão - globorural.globo.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mosaic anuncia oferta de recompra de dívida de até US$ 1,4 bilhão - CNN Brasil</t>
+          <t>Trabalhador morre após estrutura metálica desabar sobre caminhão em mineradora em MG - G1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1402,73 +1402,73 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNQXpPYnJzdG1YaHRmVGh4SGYxOHNRRkx3UjRTb2V0OVZVbmNucHBQUnROVjlCYlE5aF8xMlliaUItdUZWaXctbE9tZmowMkpaVXc0SWFfcFVobndCazdnZzlvUTdnUVk2d2pvZEtUUzVVUzVQd0tFaGdWcXpXWlh4dWlUbmZnVUpDYnRVYnRod2NrZFB3Z1dxU2tGR0hKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNc2ZqdVJHVzVWSFI0ckxwZk5xOWZrZVVZR2hLWDlYNlg1bVBNOHFDVTdXUjNwVDhZT3hHRjk5R09ybjNFM2c5YlN6bm8yVHoyOUJBUjlqamVKSURnNk5YZDZSaWNlTUoyR0NVelQ3cnhMZHVZbTFXTVhIajhnUS1EMkZ4Yl9pN3pDRlNYYWx1a21hVkdQdmkzLUlfOXhubVBIcENDOTRNeVVRV19DMkhKTE9EeUlOMDN0SGc1c0stanFxckdxdkJpbVRDalcyVlcyOXlxdnRGMEJWX1JIc3NV0gHuAUFVX3lxTFBiY1B0TGRZZzc1RnpzWm1xa282LUd3MHY5NkhmNjhGcE9CUmpoR2lPdVJ5R3RWOXJVV2NfeTNMY1Jsa0dDWmxBTTVHeGFRU01mSFdRWDdVWmFrWlI5MVAzU0RpZkQwV2F5cVluaVFzZVlKc2tpdkdwYk1kTmpGTHZmV3loekFjdGhvMmN4eTFLbGRBUWVmVmVsY3FvUG15eHN3TVg5VGhISk1HbTdQNDV3UFdwX2k2MWl5Z0ptOUhhOEtxQkJyWUsyTlNweVN0MkhHQzlPajJGQ1ZURUVhbDFDMXhNVU5MNXBDREpxZmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aos 64 anos, veterano usou 113 toneladas de cimento, empilhou blocos de calcário como se fossem toras e ergueu no próprio quintal, em Lucas, no Kansas, uma cabana de 11 cômodos cercada por 150 esculturas de concreto - CPG Click Petróleo e Gás</t>
+          <t>Desabamento em mineradora deixa um morto e três feridos em Arcos (MG) - R7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>09/08/2026 17:18</t>
+          <t>10/08/2026 04:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNSS01SVVhYy1zOHRObE1Vc2hZdlNTOXhDTzZoYnByZmFVN0pPV3BjUXNMYUFINmlfcllfN0s3M29nSGZVNlllZ012Y2NBemE1OHRoR19jbGdQVkZDX0lpNEVESVRtRHVQZlZfTE1SbFN3c25CZmtJd2h3RHFZRzBOU0pVM0dpUnhWVmZGUVltcVhwejJtaENWaGNHdmQyR1lPeEZYRmFveUJuVVZMRXp3azdoYVQ5MDg4dTN5cEgzb1JZdGhMcm8zN3k0ZkFfb29OeDNrZW43bEtBV0V0UEJWTlFCYWlRa3BSeThDSGhVdUdTZUloTlhXTktLdmZTVmVpejhZc1pHUkg5QXZ0U21xRnpLcXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQcnpzVWxxUEJDbVpyX3BaZHNoa2E3NjU1YmhwWll2Mmt6NWhrU1RtOGFJX0ZsMGIydGdtREtSVWNkZVpWQTNlOHpJbEplQnY0aldfS19TR0ZvRVpZRnBfYWpXOU1GSDJWLVlsanVEZ2VUWFJITUM1T1RCNjdSdlQ1SVVuT0FWMUlSSjl1cUd5ZzgtYTNRZ2UxSEdQMVMxRGlqQ1dTbkFrUFlzQlc0cHNPNGMzNG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cientistas da UFMG descobrem que o pó de basalto espalhado na lavoura sequestra carbono, substitui parte do calcário e ainda aumenta a produtividade em até 20% - Olhar Digital</t>
+          <t>Mosaic anuncia oferta de recompra de dívida de até US$ 1,4 bilhão - CNN Brasil</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>08/08/2026 11:47</t>
+          <t>10/08/2026 04:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxQT19EbV8tTDZaXzAzYVE0RkJSVUpUdlpPQ3RJXzlhUGhKWU9PU2xvMS0tek02VFBULThkalBIZjZ1YmlHMmFkWUV1ZmVWRmswMy1waGNEZktuTmNYOENCd3hjNC1oRUhFS29uUkFqRWY2V2JjR2VnZnVSNUN0cVlFOUNYaENFNzM5OEhRc0E3MzdrWjdMTWYtVEgwYlVBQWRQUEI1VnJYZW5GVld6SzY5M3F3T25aUk1ZSWRYZE5EUjRNak9nb1VLYkhZdkJVOF9Ma0ltT204bFNqN0h3OVJCVWUyQ3VLMUlUd1FoTDVqMHpNWDN3M2txTWZwaDh2SWNtb3ZBMFppWFJzNjhLVWtBenBibnhfN3lQbW1jVmJhRHlyaWRtd3VTNzZrUEgwMkYzcXZydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNQXpPYnJzdG1YaHRmVGh4SGYxOHNRRkx3UjRTb2V0OVZVbmNucHBQUnROVjlCYlE5aF8xMlliaUItdUZWaXctbE9tZmowMkpaVXc0SWFfcFVobndCazdnZzlvUTdnUVk2d2pvZEtUUzVVUzVQd0tFaGdWcXpXWlh4dWlUbmZnVUpDYnRVYnRod2NrZFB3Z1dxU2tGR0hKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nitrogenados avançam e potássicos ficam estáveis - Agrolink</t>
+          <t>Aos 64 anos, veterano usou 113 toneladas de cimento, empilhou blocos de calcário como se fossem toras e ergueu no próprio quintal, em Lucas, no Kansas, uma cabana de 11 cômodos cercada por 150 esculturas de concreto - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>08/08/2026 04:00</t>
+          <t>09/08/2026 17:18</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQ29TXzhvV2tZZ1JnZlBnR2NYcDFmSHpMUGYxamVrZnVPY1JlWDBIaE01Y1NtcURKZTdyLUppTnBRSUJSRDdSekN3Y21aeHlvbVZXWnZXYWJ1VHlCY1dKNjZ4dW5neDZCZGFQVUNuSE1JU2Q0dGx6ZF84V0FtMUpNd1BRU1hkdDQycS10VmNQcHFfb2R5R1p4U0RrZEVxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNSS01SVVhYy1zOHRObE1Vc2hZdlNTOXhDTzZoYnByZmFVN0pPV3BjUXNMYUFINmlfcllfN0s3M29nSGZVNlllZ012Y2NBemE1OHRoR19jbGdQVkZDX0lpNEVESVRtRHVQZlZfTE1SbFN3c25CZmtJd2h3RHFZRzBOU0pVM0dpUnhWVmZGUVltcVhwejJtaENWaGNHdmQyR1lPeEZYRmFveUJuVVZMRXp3azdoYVQ5MDg4dTN5cEgzb1JZdGhMcm8zN3k0ZkFfb29OeDNrZW43bEtBV0V0UEJWTlFCYWlRa3BSeThDSGhVdUdTZUloTlhXTktLdmZTVmVpejhZc1pHUkg5QXZ0U21xRnpLcXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -1480,39 +1480,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Balsa com calcário colide com embarcação que transportava veículos e passageiros no PA - G1</t>
+          <t>Cientistas da UFMG descobrem que o pó de basalto espalhado na lavoura sequestra carbono, substitui parte do calcário e ainda aumenta a produtividade em até 20% - Olhar Digital</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>08/08/2026 04:00</t>
+          <t>08/08/2026 11:47</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOLXU4VVlXLTFOSFF1SlZGZE1QMHdLNkpxVWlTeUM1WXdvRHhVMHBfMVlNSy1JTjUyZ1d0UkxPdzRpWGc3bmFaUWxFMHByby1EZHJQaGJmMjZ5eWlOa1Q0MVlIejNwQV9kQXF0RmhSbG5wbzdxU0F1enVwSUwzMTViaENYSWgwNmRfTjBTSmtMVVhuR3NPWnNibTlZbVd2QkhPQXBjS1JLRzAydUZ3alpmdTlleU9GSmpJcHBCUmlsM1BYX2Q2Tk91T0tCLWpyc0JiSDNDXzNkZGNOX21zNXBLT0RWdU0zRTlTNzA3emNRQkFUWWhLVWctTDlRb9IBigJBVV95cUxNWm9hVy02aXdPX1luVk9zWjhkS0tYVWpVYmZKMDA3ZEtBNk5RaU5Jd3l5V2FzaklHU0pfNGYxby1tRTB4WEVRdEVubUh6dC1zNTNzTDNYSS1WYlZGLVdmZkdIVHJXVG1tZWZuUHMxbnRUUE0xRWNKdHZKakVwQXZpX3lXWUpjd3FYUEZPak1qb01QNHZQWEF1UzJyVGJnU3ZodncySFZSWTFtSHVwaDdmMjNkWG1kNUFtZFc4UVhQVHdvM1NMLUZCMTZfY3g1dVYxVTN1Nkswb3ZRZ1B0YV9rXzhveUUtZ3c5OS1ZZnJKZlhzY1ZCRG1BRW5SU0pwN1N1OURZaGpWamFEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAJBVV95cUxQT19EbV8tTDZaXzAzYVE0RkJSVUpUdlpPQ3RJXzlhUGhKWU9PU2xvMS0tek02VFBULThkalBIZjZ1YmlHMmFkWUV1ZmVWRmswMy1waGNEZktuTmNYOENCd3hjNC1oRUhFS29uUkFqRWY2V2JjR2VnZnVSNUN0cVlFOUNYaENFNzM5OEhRc0E3MzdrWjdMTWYtVEgwYlVBQWRQUEI1VnJYZW5GVld6SzY5M3F3T25aUk1ZSWRYZE5EUjRNak9nb1VLYkhZdkJVOF9Ma0ltT204bFNqN0h3OVJCVWUyQ3VLMUlUd1FoTDVqMHpNWDN3M2txTWZwaDh2SWNtb3ZBMFppWFJzNjhLVWtBenBibnhfN3lQbW1jVmJhRHlyaWRtd3VTNzZrUEgwMkYzcXZydg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lhoist participa da SIAVS 2026 e apresenta soluções voltadas à produção animal - Arcos Notícias</t>
+          <t>Nitrogenados avançam e potássicos ficam estáveis - Agrolink</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>07/08/2026 16:37</t>
+          <t>08/08/2026 04:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQmVqTFJJR21ZY2NGRVhsVHJmbTE2X3EzV0pINGJVVFlfN1ZLcWVHQVVLS2dkQk1wMzdlSnIyczFwZGRtVVhXMVpMQkczemREY0VTUVRwN3p2SmxUcnh0dzdKTzNZbThjelEzWWJ1dnJQODR4RWFPdk9yUFhla280bVFSUjVLVnJnRjhwcHdQMGp6ZDJCNlZWYzBTd0dJbkpHX2VxdzYybkJFWUJCenlRQ25SWkxVVEtBZTJIYjdoQlJ3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQ29TXzhvV2tZZ1JnZlBnR2NYcDFmSHpMUGYxamVrZnVPY1JlWDBIaE01Y1NtcURKZTdyLUppTnBRSUJSRDdSekN3Y21aeHlvbVZXWnZXYWJ1VHlCY1dKNjZ4dW5neDZCZGFQVUNuSE1JU2Q0dGx6ZF84V0FtMUpNd1BRU1hkdDQycS10VmNQcHFfb2R5R1p4U0RrZEVxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1524,149 +1524,149 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Há milhares de anos, o mar cobriu antigas cavernas de calcário e deixou manchas escuras no meio das águas claras - Revista Oeste</t>
+          <t>Balsa com calcário colide com embarcação que transportava veículos e passageiros no PA - G1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>07/08/2026 12:05</t>
+          <t>08/08/2026 04:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOVl5a3l5ZE9fakVBVDZmenlqTmJpbTkzSDc0QUhxSE1aRmpYZm1XM1lmVUxkRmhEcE9LdXM4Y3NNcFBoc2dxcHpweEVQQ2MyZlJpcWNkeklRdXlLZC00LXlsUEp3UkVXT0xOcFl3SlZUTnRlam5uZENrVGxfTnNVSWluTTR1ZnJOSFFyX25jN0RnY2wwY3NUM3M2SDg1Q2tVQ2c1dGhkYnBJa2dBM1FXNU8xZWNLYUp5eTlVc2VMS2VxMHVySDBIUGxYVW1pajBpWjBDMUpGSElxZ0tvMjdYWVF4SVp5b2ZCMzVOZ0JpWDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOLXU4VVlXLTFOSFF1SlZGZE1QMHdLNkpxVWlTeUM1WXdvRHhVMHBfMVlNSy1JTjUyZ1d0UkxPdzRpWGc3bmFaUWxFMHByby1EZHJQaGJmMjZ5eWlOa1Q0MVlIejNwQV9kQXF0RmhSbG5wbzdxU0F1enVwSUwzMTViaENYSWgwNmRfTjBTSmtMVVhuR3NPWnNibTlZbVd2QkhPQXBjS1JLRzAydUZ3alpmdTlleU9GSmpJcHBCUmlsM1BYX2Q2Tk91T0tCLWpyc0JiSDNDXzNkZGNOX21zNXBLT0RWdU0zRTlTNzA3emNRQkFUWWhLVWctTDlRb9IBigJBVV95cUxNWm9hVy02aXdPX1luVk9zWjhkS0tYVWpVYmZKMDA3ZEtBNk5RaU5Jd3l5V2FzaklHU0pfNGYxby1tRTB4WEVRdEVubUh6dC1zNTNzTDNYSS1WYlZGLVdmZkdIVHJXVG1tZWZuUHMxbnRUUE0xRWNKdHZKakVwQXZpX3lXWUpjd3FYUEZPak1qb01QNHZQWEF1UzJyVGJnU3ZodncySFZSWTFtSHVwaDdmMjNkWG1kNUFtZFc4UVhQVHdvM1NMLUZCMTZfY3g1dVYxVTN1Nkswb3ZRZ1B0YV9rXzhveUUtZ3c5OS1ZZnJKZlhzY1ZCRG1BRW5SU0pwN1N1OURZaGpWamFEZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20 Empresas no mercado de tetrafluoreto de enxofre Tamanho, Compartilhar - Spherical Insights</t>
+          <t>Lhoist participa da SIAVS 2026 e apresenta soluções voltadas à produção animal - Arcos Notícias</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>07/08/2026 09:13</t>
+          <t>07/08/2026 16:37</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZ3dtM3FvUTVqZFBFSjRiQ1ZTWGZ3UUJ0aW1vQWN0Q0hoc3ljcEY0Z2stS0VxWG5UcXpaZnNtQ1dJSzVybW1Rb1NOME1XYXdxNjAtRkRHb25rOU5hQ3AyRmdTUWhxMG53czVXREtwUkxKb0tONU40Mlc3V0NUdWhHUHNLcGVRTDFPQU9haDFTV09sSWN1cGxUSjJGcXZwd0xsY3diV003UHhuLW5GazRQYnc2SS1vTzNfMGs2emxRQ2Q5YUJFN2k5QXJjbTg4UDQyYmRfZU1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQQmVqTFJJR21ZY2NGRVhsVHJmbTE2X3EzV0pINGJVVFlfN1ZLcWVHQVVLS2dkQk1wMzdlSnIyczFwZGRtVVhXMVpMQkczemREY0VTUVRwN3p2SmxUcnh0dzdKTzNZbThjelEzWWJ1dnJQODR4RWFPdk9yUFhla280bVFSUjVLVnJnRjhwcHdQMGp6ZDJCNlZWYzBTd0dJbkpHX2VxdzYybkJFWUJCenlRQ25SWkxVVEtBZTJIYjdoQlJ3Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crise de enxofre: Como a guerra no Irã pode afetar o tratamento de água no Brasil - UOL Notícias</t>
+          <t>Há milhares de anos, o mar cobriu antigas cavernas de calcário e deixou manchas escuras no meio das águas claras - Revista Oeste</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>07/08/2026 04:00</t>
+          <t>07/08/2026 12:05</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOeEFxbXZ5Z2lLNUhXTTBtMVBiX29ZUnZtVUwxVjRFeW5HU183NExBV1dNNmw0bWZZaFR1Zmc1RDNaQkxUVHhhNTJvTm9UaXl5MXVvbmRGdDc5cEZTbTROaVBWNm5JSDdnek9Xdk5GbWJLM2hrYXQ5TUMyenhOXzlnSFV2Rk1xSlk0TjRubUhEZGd5VDJXXzlOR2JPSEZMLTRjYl8ydzduTnpHYWJzRW9BNkYyU3FieHgxWDVYQnZYNTdsY0hHOTVxTWxhdVhPdVRoSG9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQOVl5a3l5ZE9fakVBVDZmenlqTmJpbTkzSDc0QUhxSE1aRmpYZm1XM1lmVUxkRmhEcE9LdXM4Y3NNcFBoc2dxcHpweEVQQ2MyZlJpcWNkeklRdXlLZC00LXlsUEp3UkVXT0xOcFl3SlZUTnRlam5uZENrVGxfTnNVSWluTTR1ZnJOSFFyX25jN0RnY2wwY3NUM3M2SDg1Q2tVQ2c1dGhkYnBJa2dBM1FXNU8xZWNLYUp5eTlVc2VMS2VxMHVySDBIUGxYVW1pajBpWjBDMUpGSElxZ0tvMjdYWVF4SVp5b2ZCMzVOZ0JpWDA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>China avança na liberação de novas cotas de exportação de ureia para 2026 - GlobalFert</t>
+          <t>20 Empresas no mercado de tetrafluoreto de enxofre Tamanho, Compartilhar - Spherical Insights</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>06/08/2026 20:22</t>
+          <t>07/08/2026 09:13</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVGVseEtZWDh1cHRpRWpVeEZ2YWdjVmIzNHRJNWcwdjhXLUhMU29BM3RPZ25OOW52QjVZajdKRjE4UWF4RmxsdER3ZEFUTWY1UVVYR2dpdmVmNzl3SVplNS1tbGJtSHR4NEY5TjRMZUhWOE5telR0ZGhQOFJrOVJEUXVZOUF6cGpyOFZRajUzNFF2M2NsU3dHTTZwWHpRbV9ZRGp0YkVLbFFMM1BoTVVIaVhfSDY0MDNi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZ3dtM3FvUTVqZFBFSjRiQ1ZTWGZ3UUJ0aW1vQWN0Q0hoc3ljcEY0Z2stS0VxWG5UcXpaZnNtQ1dJSzVybW1Rb1NOME1XYXdxNjAtRkRHb25rOU5hQ3AyRmdTUWhxMG53czVXREtwUkxKb0tONU40Mlc3V0NUdWhHUHNLcGVRTDFPQU9haDFTV09sSWN1cGxUSjJGcXZwd0xsY3diV003UHhuLW5GazRQYnc2SS1vTzNfMGs2emxRQ2Q5YUJFN2k5QXJjbTg4UDQyYmRfZU1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cine CMOC chega a Porteirinha e Riacho dos Machados – 11 a 18/08 - Agenda BH</t>
+          <t>Crise de enxofre: Como a guerra no Irã pode afetar o tratamento de água no Brasil - UOL Notícias</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>06/08/2026 19:15</t>
+          <t>07/08/2026 04:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOWlhtVFh2SXNYRTI0cmRUMGxNV3QzRnFTcXVUcVZhSlZXRWxhRC1tZGV6d09OcktHZXpXQ0l4YVpxbjhQckEwR1U1LUxrcm5hUGVRVHNSc0RnOFd0Q3dfQWx6cjR6aWcxMlFqajMweUVoaGtrbWM0dEhLdFJmMTFZbTFWdDl5REtWaUQzRXR6Vmt1c3hmMFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOeEFxbXZ5Z2lLNUhXTTBtMVBiX29ZUnZtVUwxVjRFeW5HU183NExBV1dNNmw0bWZZaFR1Zmc1RDNaQkxUVHhhNTJvTm9UaXl5MXVvbmRGdDc5cEZTbTROaVBWNm5JSDdnek9Xdk5GbWJLM2hrYXQ5TUMyenhOXzlnSFV2Rk1xSlk0TjRubUhEZGd5VDJXXzlOR2JPSEZMLTRjYl8ydzduTnpHYWJzRW9BNkYyU3FieHgxWDVYQnZYNTdsY0hHOTVxTWxhdVhPdVRoSG9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nutrien e Mosaic sofrem pressão à medida que agricultores reduzem uso de fertilizantes após alta nos preços - TradingView</t>
+          <t>China avança na liberação de novas cotas de exportação de ureia para 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>06/08/2026 14:17</t>
+          <t>06/08/2026 20:22</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBHMWkzaE5yd0dWOFB5bzdnNEd1R3I1M0N2dUE5bmVOTFdjTDFxWG9LMmI5UGhRaDRQLWZ2aThXZFdob0hDUDRmQTZHQXhCRi1vZEdYRlg0OXhydlRKVC1TRkJzRV9hbFowdmItc3MxUVVITXZ1Y0w4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPVGVseEtZWDh1cHRpRWpVeEZ2YWdjVmIzNHRJNWcwdjhXLUhMU29BM3RPZ25OOW52QjVZajdKRjE4UWF4RmxsdER3ZEFUTWY1UVVYR2dpdmVmNzl3SVplNS1tbGJtSHR4NEY5TjRMZUhWOE5telR0ZGhQOFJrOVJEUXVZOUF6cGpyOFZRajUzNFF2M2NsU3dHTTZwWHpRbV9ZRGp0YkVLbFFMM1BoTVVIaVhfSDY0MDNi?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Programa de Aprendizagem da Lhoist fortalece formação de jovens em São José da Lapa, Matozinhos e Arcos - Arcos Notícias</t>
+          <t>Cine CMOC chega a Porteirinha e Riacho dos Machados – 11 a 18/08 - Agenda BH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>06/08/2026 11:18</t>
+          <t>06/08/2026 19:15</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPSjh5SWdvbUp2amhuTkxBLU1Gb2NfSDBvNTItd2VJMktmenZIUXRRQnV5RXpLaEJKZG5QSVlmb01CZHZwQ3FQLVktcmxEQ2h0TDNQZ3duNjdZRVhQb0FNT2F6a1BVdU5mR2ppaDg0VHdXb2xUa3FwMk1YYmo1d1hvQVpDdThzY29kcnY0azFDYzR6X25uallTa0Z2NFBoMlhiME0tNFlHdkYtZ0o1Qm1Uck4xZDQ1SEdwR0NSSTFydG1EZHAxWFkzbEVnOXVweXlPVmg2T3MtSFhCU1hvMEV1OFlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOWlhtVFh2SXNYRTI0cmRUMGxNV3QzRnFTcXVUcVZhSlZXRWxhRC1tZGV6d09OcktHZXpXQ0l4YVpxbjhQckEwR1U1LUxrcm5hUGVRVHNSc0RnOFd0Q3dfQWx6cjR6aWcxMlFqajMweUVoaGtrbWM0dEhLdFJmMTFZbTFWdDl5REtWaUQzRXR6Vmt1c3hmMFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -1678,39 +1678,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Prefeitura intensifica articulações para reduzir impactos da paralisação da Mosaic em Uberaba - jornaldeuberaba.com.br</t>
+          <t>Nutrien e Mosaic sofrem pressão à medida que agricultores reduzem uso de fertilizantes após alta nos preços - TradingView</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06/08/2026 04:00</t>
+          <t>06/08/2026 14:17</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOc1VaQ2tJd0FBUWE4b3lMLWItSW8yMEltaUdrMERyWkE0SmN6bXp3a3BKNEFtalF0WHRIVzkxMHNXVjVKRlAtOTJnV0tBNmFWbjU1LVRyM1V5YWhFajBGeEVOeXdQRTRtM0NtTlFzNmRrMHhtalRxQ0lqRTI5QllGUFhHTTFaQlo0Skw3MlRBYzROdTJRejV6NzZndG5zRlY1VXU1dTliM3BGd3FZVmwzbVNwSTA4MXZWcHF6aXhtbmJCcmFwNmI5VVByLWdpU25TYjZ4dXdjUzNxeWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBHMWkzaE5yd0dWOFB5bzdnNEd1R3I1M0N2dUE5bmVOTFdjTDFxWG9LMmI5UGhRaDRQLWZ2aThXZFdob0hDUDRmQTZHQXhCRi1vZEdYRlg0OXhydlRKVC1TRkJzRV9hbFowdmItc3MxUVVITXZ1Y0w4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Um engenheiro químico explica como limpar o calcário do vidro do chuveiro: "Os produtos de limpeza convencionais geralmente removem bem os resíduos orgânicos, mas não os inorgânicos" - minhavida.com.br</t>
+          <t>Programa de Aprendizagem da Lhoist fortalece formação de jovens em São José da Lapa, Matozinhos e Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>06/08/2026 04:00</t>
+          <t>06/08/2026 11:18</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9pOEpndTExOHJwQUk2SW5JcThtZl9YdFZWeDBsOFJmOXJTTk0zUTFtQlFfeHdEek1PMHZveHlGRnpaVXlPQmo4UVN5OGVxQ3lEci0tRnFlZWpDV1RUNWdZctIBZkFVX3lxTE5hNGg1YUxwS3Z6aDZCbzQyQnVreW1IWEVhWm9CM0RXaWptYUkwWjVBdk5yajBxcWM4S0tMMkItTGtaaktxQTVOVWZSWGYwX0hEb1l2RXU0OUhuZThLUmhIVXRGeWVHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPSjh5SWdvbUp2amhuTkxBLU1Gb2NfSDBvNTItd2VJMktmenZIUXRRQnV5RXpLaEJKZG5QSVlmb01CZHZwQ3FQLVktcmxEQ2h0TDNQZ3duNjdZRVhQb0FNT2F6a1BVdU5mR2ppaDg0VHdXb2xUa3FwMk1YYmo1d1hvQVpDdThzY29kcnY0azFDYzR6X25uallTa0Z2NFBoMlhiME0tNFlHdkYtZ0o1Qm1Uck4xZDQ1SEdwR0NSSTFydG1EZHAxWFkzbEVnOXVweXlPVmg2T3MtSFhCU1hvMEV1OFlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alvo de operação sobre mineração ilegal de calcário diz que vai comprovar regularidade - midiajur.com.br</t>
+          <t>Um engenheiro químico explica como limpar o calcário do vidro do chuveiro: "Os produtos de limpeza convencionais geralmente removem bem os resíduos orgânicos, mas não os inorgânicos" - Minha Vida Saúde</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>05/08/2026 11:58</t>
+          <t>06/08/2026 04:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOcWM0dGNJNzdwWERlQ2tyLW9Sa1NaLVFwVmlKa0VuTS1UeTNkVGFvaXV0RkhqamRjZFhOeHpYSGNRVFVGSDJVQTZDMjgzcDVCeVpWTzhCdFB5VUFJSGIySUZ6cG1PZFFGSDlEcUtFMXgtcTBGN0RJdDNFMmZ1NWxueF9mNXZCZ0p0d0o5YmdQeFBqQy1yZDVzOEY2U1R2eF93WlcwNWFGSFFEOUxBVW13R09EQXJHX1ZjZTNrdFBCSWJlU1BX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9pOEpndTExOHJwQUk2SW5JcThtZl9YdFZWeDBsOFJmOXJTTk0zUTFtQlFfeHdEek1PMHZveHlGRnpaVXlPQmo4UVN5OGVxQ3lEci0tRnFlZWpDV1RUNWdZctIBZkFVX3lxTE5hNGg1YUxwS3Z6aDZCbzQyQnVreW1IWEVhWm9CM0RXaWptYUkwWjVBdk5yajBxcWM4S0tMMkItTGtaaktxQTVOVWZSWGYwX0hEb1l2RXU0OUhuZThLUmhIVXRGeWVHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1744,51 +1744,51 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - BOL</t>
+          <t>Prefeitura intensifica articulações para reduzir impactos da paralisação da Mosaic em Uberaba - Jornal de Uberaba</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>05/08/2026 04:00</t>
+          <t>06/08/2026 04:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRkwyVXR1MjRKdnZ5eEN3NjlnelRKc0k2TE5OYTI5b2l4ZWNPYlB5LTVfRkE5Wk5rZ01LN1A1NjlsdHEwakpvMTJyVnV6dUZCSHhDWXNuQkY4TFpnVEFFeFBReXA2cDBST1RFeWR4TUJQbmNnem4yTFNIVmhMRFZfSEMyRTRXMGhIWHZNbzRYcnh2ZU53RDQzczRzVWhJVW14b3pJT0dEUmR4dzFiT29lU0JBbl9fcll3Z0J4Q9IBwgFBVV95cUxOSHQzTGlRa2Z3WGlIMk9FdXlWcHpyVk9EdV9wTF9SMHBGYXJaVHZHcUtSaVlKVUlQLW1qLXhQNUJ0WUR5VmQyRnFob3BTM0FNQ2g4T3g1d0VEWG1KMnk0OEgxa3Biajd5OG8yVWNmek91UGdqN2hKU3lvaXQtdXhuZVFLRE1tS2xVQ1Jtb0QyY1V4bmtEOHNaQW5uNDUtaWZMdFMzZHEzdURZWXZzNkVnOHY5bzJiTnhDTU9kbVZqZ1lNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOc1VaQ2tJd0FBUWE4b3lMLWItSW8yMEltaUdrMERyWkE0SmN6bXp3a3BKNEFtalF0WHRIVzkxMHNXVjVKRlAtOTJnV0tBNmFWbjU1LVRyM1V5YWhFajBGeEVOeXdQRTRtM0NtTlFzNmRrMHhtalRxQ0lqRTI5QllGUFhHTTFaQlo0Skw3MlRBYzROdTJRejV6NzZndG5zRlY1VXU1dTliM3BGd3FZVmwzbVNwSTA4MXZWcHF6aXhtbmJCcmFwNmI5VVByLWdpU25TYjZ4dXdjUzNxeWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Martin Marietta obtém aprovações regulatórias para negócio com a Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Alvo de operação sobre mineração ilegal de calcário diz que vai comprovar regularidade - midiajur.com.br</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>05/08/2026 04:00</t>
+          <t>05/08/2026 11:58</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdmlEaDJzTXdyWXdBTkRiVlQtNjlZMVY2WG1Fa2pPSVpnRENkNnBSdG9nWTBiVWFXZEdUWHdCSFRWTlgySjA1VUQzVVN6QUxUYWZfUFVFUURWVmtGQ3haUFMyMGZ4a0hVN3d1Z3FpWDlFNVJYMDA1bjNNVXVobXlUWFV2SGVPRUVmZElHTjRsSFNVODVVN3dhNXFqMkcxRGhtRE9peU5tRnZvU3VUejk1RDR6bDVJUkZIOUdheVJTSmwxRGNpaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOcWM0dGNJNzdwWERlQ2tyLW9Sa1NaLVFwVmlKa0VuTS1UeTNkVGFvaXV0RkhqamRjZFhOeHpYSGNRVFVGSDJVQTZDMjgzcDVCeVpWTzhCdFB5VUFJSGIySUZ6cG1PZFFGSDlEcUtFMXgtcTBGN0RJdDNFMmZ1NWxueF9mNXZCZ0p0d0o5YmdQeFBqQy1yZDVzOEY2U1R2eF93WlcwNWFGSFFEOUxBVW13R09EQXJHX1ZjZTNrdFBCSWJlU1BX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Impacto da reabertura da fábrica de ureia para o agro brasileiro - Revista Oeste</t>
+          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - UOL Notícias</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOajFPWU1RdTVTdkl6TDRGUE45aFZ0UEJXekRRcjNWSmx5Q0xwZjlsNjBLOHdJYjVWLWw0UlNTRGNJaEp4Xy1qeW9XQ1NSbGxRd3JuaXBCTXhXYUZCNXpBcU80NWZMbk92M1hNWmhOVjJ5Nlp1c0huNlQ3RWUyLTlKNU9RWGthRTBBcnJPZkNGUE5Ga0xKOXlveDczUVduXzAtaF9hNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPVm5vY00ydFNNRFpySGZRdzkxamEyVHZwWm5acTNRN1draHRoWVU2ZXJPYVNJVG1vaFdUcTZGNFVHaV9wWFo1WmVqYkdCWlRvb0YyWmpPOEpram5fYW5GbVo1aGRndG5yc1BKMTR0RVF6amhpTTJFdFQ2d1VDeHRDMUR4dURYRDgweVFQZ2FUUXVhR0Z4ZW9KWlBhQjgzRUNPd3pLRHZnaThlVklJR3dWYU5ObFlZcjZubUZoalZNRXVTZW9xWEpiby1NX2ZONmRGSnJQYlRQV3VEQmxo?oc=5</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mosaic reverte lucro e registra prejuízo de US$ 272,8 milhões no 2º trimestre - Canal Rural</t>
+          <t>Mosaic estima redução de 30% na aplicação de fosfatados no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1820,19 +1820,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQlgyRE9JV2x2Z3Q0U0p0Xy10OW9QRXE0T2xXTlJxTm4zLVFibF9xZFlmSTJqa2ZOTmVzT1JoR29sTE9NYjg3dUtOcXh2Vy1HVWlKRXZNUFp4V1ZaRm9BU216SVlPNU9zeTdhQ09ITEYtc1dsbXg1U0NMQkIzYzdyWU1aNHZYUFJ6M0RscnEyOXRCQmJ5NzdicmpyU0I4TzUtUV9MSWdMQnNMMVYySnZ4aWRqeWEtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNy1DT0ZOaGdiZDJTa012cjFrXy1UUzlTR2djUEMtNDBESlRzMm1saUNfakxkazd6WXBDV0FnSmEzNENJV2xvZDlLTFA2WUxtMUE3bHdoQW5oR3kxdU5iUmR6eXp6dEdZZnZITWJJMFZpdmM1R2V5LTB4UmhNalhwbmJqS085YkNkVUhOUGdDek93Y2V5R0N3NDRybGlPRkVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>O peso do enxofre no balanço da Mosaic - AgFeed</t>
+          <t>EuroChem avalia reduzir produção e adotar layoff em Serra do Salitre por crise global do enxofre - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1842,19 +1842,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNazEyWVlFbVJHbWRMdUtiUDc5aE9nS3E4ZUVZdE1FdjJUeUtuZjVrbDlXV25xTjd4bEM4TzQ5c05nX0s2QmNvRkdPQWpoUm5pZE42NEc3Unh1R3JET0FhV0RjV2NpZTVJdWtITHhzenk5a2luNEswY3VlTFhUZ1JvWE5oWnVCNDVPUXpqWg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQ3RLWHZWbmFLS0RNTTBYaVpNYWdISjVib1ExR0ZfbFhQUUJKT1I2My0xTEhfMnozRlhWcGxuZzlJRUhQMXExaG8wLVZkbzNZSjdUZDRTckc5RmRrZ2RYbWVKUVF2dWxpb2dTd0c1MVdGVldBM3p0LU9ZUXJLYlJXRTlwNU5zRVF3dmYydUttR1RCTkx0QS16X3BjamVIWmhqbGRsd2FPSjUwQzBGemQxNUlhaFpfN3hfMkZ3R2t1VEZYV2JY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mosaic estima redução de 30% na aplicação de fosfatados no Brasil - CNN Brasil</t>
+          <t>Martin Marietta obtém aprovações regulatórias para negócio com a Lhoist - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNy1DT0ZOaGdiZDJTa012cjFrXy1UUzlTR2djUEMtNDBESlRzMm1saUNfakxkazd6WXBDV0FnSmEzNENJV2xvZDlLTFA2WUxtMUE3bHdoQW5oR3kxdU5iUmR6eXp6dEdZZnZITWJJMFZpdmM1R2V5LTB4UmhNalhwbmJqS085YkNkVUhOUGdDek93Y2V5R0N3NDRybGlPRkVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdmlEaDJzTXdyWXdBTkRiVlQtNjlZMVY2WG1Fa2pPSVpnRENkNnBSdG9nWTBiVWFXZEdUWHdCSFRWTlgySjA1VUQzVVN6QUxUYWZfUFVFUURWVmtGQ3haUFMyMGZ4a0hVN3d1Z3FpWDlFNVJYMDA1bjNNVXVobXlUWFV2SGVPRUVmZElHTjRsSFNVODVVN3dhNXFqMkcxRGhtRE9peU5tRnZvU3VUejk1RDR6bDVJUkZIOUdheVJTSmwxRGNpaHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação de operações em Araxá e suspensão da mineração em Patrocínio após alta histórica do enxofre - gazetaptc.com.br</t>
+          <t>Impacto da reabertura da fábrica de ureia para o agro brasileiro - Revista Oeste</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQalVuOXA0a09JRWNabGJaNnptaFBqYUxoN0Q0eWtINWxDM2t1WnF5bDZSaG4tS1pnY2trTXYxZ3UwSEJxdHZETUVMay1odHpNV0dWTlpWaGdwWE5ZYnhIUlBlSjRlNWFvM2pGY2NXY0lkVHpJakpkYW05YmNoNGRhdmZhX0VRQUViZUVwSjdNaVFkMlhrUjlVVjlmbW51alhCVUJsR2FTMVBkZl9pcVJIczJzMklGMW9OR2ZEZ2xKU19VYjBLWThsRW1zUHh2QTVfY29KeF9BbVZrSWszWkY4Q1FsXzBIVm9GV3VhNGx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOajFPWU1RdTVTdkl6TDRGUE45aFZ0UEJXekRRcjNWSmx5Q0xwZjlsNjBLOHdJYjVWLWw0UlNTRGNJaEp4Xy1qeW9XQ1NSbGxRd3JuaXBCTXhXYUZCNXpBcU80NWZMbk92M1hNWmhOVjJ5Nlp1c0huNlQ3RWUyLTlKNU9RWGthRTBBcnJPZkNGUE5Ga0xKOXlveDczUVduXzAtaF9hNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - UOL Notícias</t>
+          <t>Mosaic reverte lucro e tem prejuízo de US$ 272,8 milhões no 2º trimestre - BOL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPVm5vY00ydFNNRFpySGZRdzkxamEyVHZwWm5acTNRN1draHRoWVU2ZXJPYVNJVG1vaFdUcTZGNFVHaV9wWFo1WmVqYkdCWlRvb0YyWmpPOEpram5fYW5GbVo1aGRndG5yc1BKMTR0RVF6amhpTTJFdFQ2d1VDeHRDMUR4dURYRDgweVFQZ2FUUXVhR0Z4ZW9KWlBhQjgzRUNPd3pLRHZnaThlVklJR3dWYU5ObFlZcjZubUZoalZNRXVTZW9xWEpiby1NX2ZONmRGSnJQYlRQV3VEQmxo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRkwyVXR1MjRKdnZ5eEN3NjlnelRKc0k2TE5OYTI5b2l4ZWNPYlB5LTVfRkE5Wk5rZ01LN1A1NjlsdHEwakpvMTJyVnV6dUZCSHhDWXNuQkY4TFpnVEFFeFBReXA2cDBST1RFeWR4TUJQbmNnem4yTFNIVmhMRFZfSEMyRTRXMGhIWHZNbzRYcnh2ZU53RDQzczRzVWhJVW14b3pJT0dEUmR4dzFiT29lU0JBbl9fcll3Z0J4Q9IBwgFBVV95cUxOSHQzTGlRa2Z3WGlIMk9FdXlWcHpyVk9EdV9wTF9SMHBGYXJaVHZHcUtSaVlKVUlQLW1qLXhQNUJ0WUR5VmQyRnFob3BTM0FNQ2g4T3g1d0VEWG1KMnk0OEgxa3Biajd5OG8yVWNmek91UGdqN2hKU3lvaXQtdXhuZVFLRE1tS2xVQ1Jtb0QyY1V4bmtEOHNaQW5uNDUtaWZMdFMzZHEzdURZWXZzNkVnOHY5bzJiTnhDTU9kbVZqZ1lNUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mosaic vê queda de 30% no uso de fosfatados no Brasil e risco à produtividade - The AgriBiz</t>
+          <t>Mosaic anuncia paralisação de operações em Araxá e suspensão da mineração em Patrocínio após alta histórica do enxofre - Gazeta de Patrocínio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1930,19 +1930,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVjdYZWJTWUpzT0I3RTEzX0YxN1BZbk4yRjJCa1U5OVBtY2xlV043dTg2MVg3emJXd2ladlBfOEdCTkkxQm9tajNDSTZHaUpSRHNPVTBzT3d4VWNTRE9xVFluckZBV1RyMFVzbGhHLWF2Y3ZXMTg5eWlFeUNsblVUb3dKWlhLYnppQXNYZ0tNQVZlZm91dW9QMzJFVWlldTRCa0o3ZF9WNV9nUjdTMXgtMWdVVl9VSVhFOVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQalVuOXA0a09JRWNabGJaNnptaFBqYUxoN0Q0eWtINWxDM2t1WnF5bDZSaG4tS1pnY2trTXYxZ3UwSEJxdHZETUVMay1odHpNV0dWTlpWaGdwWE5ZYnhIUlBlSjRlNWFvM2pGY2NXY0lkVHpJakpkYW05YmNoNGRhdmZhX0VRQUViZUVwSjdNaVFkMlhrUjlVVjlmbW51alhCVUJsR2FTMVBkZl9pcVJIczJzMklGMW9OR2ZEZ2xKU19VYjBLWThsRW1zUHh2QTVfY29KeF9BbVZrSWszWkY4Q1FsXzBIVm9GV3VhNGx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EuroChem avalia reduzir produção e adotar layoff em Serra do Salitre por crise global do enxofre - Estadão Blue Studio</t>
+          <t>O peso do enxofre no balanço da Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1952,51 +1952,51 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQ3RLWHZWbmFLS0RNTTBYaVpNYWdISjVib1ExR0ZfbFhQUUJKT1I2My0xTEhfMnozRlhWcGxuZzlJRUhQMXExaG8wLVZkbzNZSjdUZDRTckc5RmRrZ2RYbWVKUVF2dWxpb2dTd0c1MVdGVldBM3p0LU9ZUXJLYlJXRTlwNU5zRVF3dmYydUttR1RCTkx0QS16X3BjamVIWmhqbGRsd2FPSjUwQzBGemQxNUlhaFpfN3hfMkZ3R2t1VEZYV2JY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNazEyWVlFbVJHbWRMdUtiUDc5aE9nS3E4ZUVZdE1FdjJUeUtuZjVrbDlXV25xTjd4bEM4TzQ5c05nX0s2QmNvRkdPQWpoUm5pZE42NEc3Unh1R3JET0FhV0RjV2NpZTVJdWtITHhzenk5a2luNEswY3VlTFhUZ1JvWE5oWnVCNDVPUXpqWg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC demonstra avanços na Agenda ESG em relatório - Brasil Mineral</t>
+          <t>Mosaic vê queda de 30% no uso de fosfatados no Brasil e risco à produtividade - The AgriBiz</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>04/08/2026 15:39</t>
+          <t>05/08/2026 04:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSWo1OWtsdTlnZlR0Nzd1bE9fZHdmMDJxdkp6ZHJUemZZRWI5dmlLSERBTEFmNGNoWDEweW1EdVdBdlctdlhORmxqWU9zLUZXZHJjVWZpMElBVVZ2UXAzQmhfOGhWa2NTTVNFYms2WmlfNEJJQ1YzcFNpWFpEUkhiTVBfaHVKeXJ3ZkJ3TW9MZHlXX3hoNUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVjdYZWJTWUpzT0I3RTEzX0YxN1BZbk4yRjJCa1U5OVBtY2xlV043dTg2MVg3emJXd2ladlBfOEdCTkkxQm9tajNDSTZHaUpSRHNPVTBzT3d4VWNTRE9xVFluckZBV1RyMFVzbGhHLWF2Y3ZXMTg5eWlFeUNsblVUb3dKWlhLYnppQXNYZ0tNQVZlZm91dW9QMzJFVWlldTRCa0o3ZF9WNV9nUjdTMXgtMWdVVl9VSVhFOVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 milhões com extração de calcário e cumpre mandados em Cuiabá - O Documento</t>
+          <t>SUSTENTABILIDADE | CMOC demonstra avanços na Agenda ESG em relatório - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>04/08/2026 10:13</t>
+          <t>04/08/2026 15:39</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOV3J0TXI2SGxlVEZOQ2F0aG1FNkxvRE9sY3E2WUdXa3FUTjhiY3h3Wm5aUmUwenI2WDg5ang2bm90aWlZYWdWQnJ3ZnBSUTAtcFJkRUNrdWxDWjVid3dtV0FVaDNIalE1NE1NR1N3czR6am5BcldlSG1EUlRhTDE1UURjVkJHRWY1RHluN3B1U0xCeElzSEh0R3RZa2UzN0Foemtvd3lKU2MwWjM3bUEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSWo1OWtsdTlnZlR0Nzd1bE9fZHdmMDJxdkp6ZHJUemZZRWI5dmlLSERBTEFmNGNoWDEweW1EdVdBdlctdlhORmxqWU9zLUZXZHJjVWZpMElBVVZ2UXAzQmhfOGhWa2NTTVNFYms2WmlfNEJJQ1YzcFNpWFpEUkhiTVBfaHVKeXJ3ZkJ3TW9MZHlXX3hoNUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - Ponto na Curva</t>
+          <t>PF mira esquema de R$ 3 milhões com extração de calcário e cumpre mandados em Cuiabá - O Documento</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>04/08/2026 09:55</t>
+          <t>04/08/2026 10:13</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2F3T08wUWlMVDMza3FGRUJzTUZXenBQM0NWMHZhZk1OZGlKbThTbE9pcFoyM3NkS1RjUDRLS015eTRya2k3SUw0SDhJM3F6STBDY0ctZXRpM2l1YUV2LVlTNG9sVGNuODd6V0MwbU1yNThyQ2I1OXJ6MHF4OFNRZlhKUm1Rc3Q1UUI1cjVOeVhBSE5ZaF9Hc1dWb0xzeUhyNE5nSzJYVW9XWEFlMXMxamVWazBSSTI4NDRoQzVjMVEyQzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOV3J0TXI2SGxlVEZOQ2F0aG1FNkxvRE9sY3E2WUdXa3FUTjhiY3h3Wm5aUmUwenI2WDg5ang2bm90aWlZYWdWQnJ3ZnBSUTAtcFJkRUNrdWxDWjVid3dtV0FVaDNIalE1NE1NR1N3czR6am5BcldlSG1EUlRhTDE1UURjVkJHRWY1RHluN3B1U0xCeElzSEh0R3RZa2UzN0Foemtvd3lKU2MwWjM3bUEw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2030,17 +2030,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PF mira esquema que retirou 34 mil toneladas de calcário e causou prejuízo de R$ 3 milhões em MT - Folha 5</t>
+          <t>PF apura extração irregular de calcário e cumpre mandados em investigação - Ponto na Curva</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>04/08/2026 04:00</t>
+          <t>04/08/2026 09:55</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOd1BjR0pwSGpfMkZqbGZfb0hPSzJIZmtMV2oyb3pRZ04zMXBnTGZxOHdQTGJoeW9IN25Tczl1bldyWDFHSGRtZXo5Qjh2aU1JRDBLRHFTeEdZYl9CMV9TRmtyeHFQZ0pTSUl5WGo4bVFiQ1ZrZWgzWEVGdXRDd21GV2N4NHpuaFpUTmEyNmJNVTRiRDN2ZUZGdFZvRkNDRnFXckhuNlFKd2xUbVljTHhNV1ptb0J2S2l4SzBHbTdqV3NoZHljdkFJVWNmLW1DTUJX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPV2F3T08wUWlMVDMza3FGRUJzTUZXenBQM0NWMHZhZk1OZGlKbThTbE9pcFoyM3NkS1RjUDRLS015eTRya2k3SUw0SDhJM3F6STBDY0ctZXRpM2l1YUV2LVlTNG9sVGNuODd6V0MwbU1yNThyQ2I1OXJ6MHF4OFNRZlhKUm1Rc3Q1UUI1cjVOeVhBSE5ZaF9Hc1dWb0xzeUhyNE5nSzJYVW9XWEFlMXMxamVWazBSSTI4NDRoQzVjMVEyQzg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mosaic fecha 2º trimestre com prejuízo de US$ 273 milhões - CNN Brasil</t>
+          <t>Resultados da Mosaic em foco: as margens do fosfato podem se recuperar? - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOYVg3Y3RpTHNrVms5NXBiN2huemhBejE2Tng3VHV5aXI5RmJNazB1WTZUeDFvZmhWd19fU2FQVzRPRlExQnlBQ0J0anRuYWZkWTFlOW9vbGdwNjNxNnhWN2UwM0l3b3VDRWxmSzFWRkw5SUg3aG45YldJeHNhS0FGTG8tMndGY1lPTEZxU1FrNVJkelNnVEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZHJEZGU5dTl1eXd1cHRvN0RUZlpQSk9aVW1qR3JadzVnQmdXZzRqcERLekRqM2JsR1pNSnJLSlplZ3ZIc2JMbkxXNEtJOUxnTk9GQXF6M3dYbk1KTW5MRUpYeGdyX1VqOWRTWEJ3UzFDUWxrd3VLaHB0QXVPUzJaNS04eVg2dW9wbXhiYkZfc0xwU0ZYbVdRSDhSX0F5anc1U3h1aWlyRGNHbTdfYTVwVXlsQjVockJGQ1FYOURR?oc=5</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - MidiaNews</t>
+          <t>PF deflagra Operação Peso Bruto contra a extração irregular de calcário em Rosário Oeste - Pagina1mt</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeFpET3FNUWdocW04TVhsWXZsQWNvbnpoMWQ0SHhUMWJsMnRvRDk2emRvaGdlYXNEUTlPVUsyaDluRmtTZnk2X3JsT1hKN2t5N2d2X1ZlNDFrVXYxU3hLVVBzcU1WbVJic2VGYkFtSGROX3djTk9oNnB5TWRlR2hGZVpRMEJoYnk2VmdsWHZqU3RnTnJ1S2hVRnpoZ08tYXVXU1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRE4xNWZFelh4ZUd2Y3djWU5JaHJVeTAwLWs0akJvY09QWC05RXdobWZjSmNMRjlKbUR2SWRWaXFUbTFtclpudnhmWThaNXBZaFJRYWFaSmloY2hNT0NEczhLWUlKVnVSbGpLU3I2U2xSMFUtYTV0ZU4zTk0ydURaTFRGc0g3c1ZRSnVQSVpmUTFYdUFhSGpUajFMcGpfLTM4Zk9HcnNXZUF1Unp6Z2hVenlHVG82T0c1Zkc2WVMwWkQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PF investiga extração de calcário com prejuízo de R$ 3 milhões - MINUTO MT</t>
+          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - MidiaNews</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOcmlIZnAxbnk3MnhyYmhhcFRYbmR2RU40ZDg3X1FvT09kNDY1NXBha0xVMmozWFd3cDNzMDc2d3NmTWhKczROZk80OVhWcWxfSzc4bkF2V0JfQTBKZ2tpaU9wUkFheVptSEdPOFp4RGtZYjNfTkU4dWRBYUxqekN0NW5XNW1qTFR0U1FZMTg4Z1hVYnJuc0s2cW93?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeFpET3FNUWdocW04TVhsWXZsQWNvbnpoMWQ0SHhUMWJsMnRvRDk2emRvaGdlYXNEUTlPVUsyaDluRmtTZnk2X3JsT1hKN2t5N2d2X1ZlNDFrVXYxU3hLVVBzcU1WbVJic2VGYkFtSGROX3djTk9oNnB5TWRlR2hGZVpRMEJoYnk2VmdsWHZqU3RnTnJ1S2hVRnpoZ08tYXVXU1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Saiba quem é o empresário alvo da PF por esquema de R$ 3 milhões com calcário - FOLHAMAX</t>
+          <t>PF mira esquema que retirou 34 mil toneladas de calcário e causou prejuízo de R$ 3 milhões em MT - Folha 5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2128,19 +2128,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYUZzUkNXbWxvcGhSWmJIc2xqLTFwY3p0MXNSMks3dHluTGo2VGpDYldtTnVwSWZGTm52SUtvTFRwSWg3UDV3UGZxajFkY1JQQi1SWjRibFp1dkk4RnI4MGw1bzY3QTZSZy1BZk56cEtkVFB0Q3RUMFNnSWhJQ1ViV1Y3OEtYeVB5VFZRaUR6aDZ5RDVmSXUybC1BQktVXzEzT3Z5RzczQ3QxOEF3VGtQR3R5SzNVZ2lT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOd1BjR0pwSGpfMkZqbGZfb0hPSzJIZmtMV2oyb3pRZ04zMXBnTGZxOHdQTGJoeW9IN25Tczl1bldyWDFHSGRtZXo5Qjh2aU1JRDBLRHFTeEdZYl9CMV9TRmtyeHFQZ0pTSUl5WGo4bVFiQ1ZrZWgzWEVGdXRDd21GV2N4NHpuaFpUTmEyNmJNVTRiRDN2ZUZGdFZvRkNDRnFXckhuNlFKd2xUbVljTHhNV1ptb0J2S2l4SzBHbTdqV3NoZHljdkFJVWNmLW1DTUJX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mosaic volta ao negativo e registra prejuízo de US$ 273 milhões no trimestre - AgFeed</t>
+          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas de calcário em MT - G1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNN25Wc0JsVHdYM1JaNFVsbkM1TEtibExtb0ZxcmFxZnhuT1BVVFRRSnQ1bnljdHNUcFBZRmRUX293SXJWa3RiYUdjLW83Vk43Rm44Z2x0Q3AxYk5OZFhMWXdPUk9VdFA3OExCV19fN25pamNCZTQ1a3RET3JUQ1M1SFUwWE4xZXFadTdER29yUTVxelhUOXc1cEtibnFQamtfNng5eHJSSzY4VVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbmx0djJaNkM2ZkNYMzdMd3JCa2d6N3YxbUZBUDh1YnhQWjRDaDdUMGZWckllV0tTdmlfOXktbEw3SmhEQ2JneVZTX1JIOS16NGRpTXZuSTRwbGVWTkZ3eGdkc2JPQkJDNEdTXzZ2a0pPUDlOeWpaMF9uMU85WTYySmQweEl0VnE3aUpjWDl5M2pDWWNaMlFmUUxqZEFleXNzVHZ5MFRCeEstWDE5OXNyZFgyUkZ4c1daTkNMMmRJa2ptY2ZqNnZzRUowYmtzQUhuQzdmenl0RUYxSXfSAeoBQVVfeXFMTnNOS3RkOHNCWlB6SHpPT2JQZENXNmtYSWNaLXZ2SENYMnFQVkctVndmVnRxUm85cFh4QlNxUXZNNndIZllRc2J2c3F1TE5GNXczRWhyR2Y5SHdPdEdwdGtDM2JSWktZSzZ6OEhaYUE1RGV3MUFJZ2NvTUlielMzUHJ1NFJUcmRGN0Zma3FpdTlwZjFxZGVud2NNbUJrdjZOejVraTJBNmNqVGhaSmdicFdRMUFGLUhjejhmOHpTbVptaTFodE5VSkNkTEc3aEI5dmFway1hamRlUW45ZEVrVHJrYWRDR0gyeGVn?oc=5</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Empresário alvo da PF tem empresas em Rosário e Poconé; saiba quem é - Gazeta Digital</t>
+          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas calcário - G1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVEo3bkRxQnc0emRmZUlWaFptajgxUjR6bXkyZmlSVEJPWW1OYTFzQmVNYlFtMFZ5dkdycTNDaE5QcVkzTmRfZmVQQWVDZUQ0ZnhaOE9YY2laOWFlMm5UZUdid0pQVy1SWTQ1VGtXUWlTVlJRTkc2WlZfZy10d0NYTUszRHVGUnk3aWoyQTNwelVHZW94YVlYQXBzRnRGZWw2dFBfSnA2SURuODltOGNlSmZKb1lSMkJpLWxoM25QaUlJblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORE9Qb29mRHg0MjFfN3NkOEV6TVNVaWdmWnRLUGdHZWNBdjQ1ZFZmc2t4RHZqN2pxUUFJMkJKdWJ4bVdidm9Qc0tNeGNLcVlvZ0V6Uk5lMVI3eGlTUFh6d1VmdUZ0MTA3ZDgwcE12dUdmWjRVVGNLOXF6WmdwZHZmVGo0TUR6V2hWMkp0Wm1PUjlIRGx3VnhLeHo4SmVsdDFwYnRPcDA2YVdfVUEyWi1Eek00aUVoeHk5RDJFb1c5ZlNpZVRCTm1vZmhB0gHYAUFVX3lxTE9KLWE5MnBSVjdkS3JheHpGUWdIS09VRkI0ZUxZcnFRRXFFV3dLSDRIdFRkOTlnTTlaRmVqNkJZMGZGdHhuVHI3blNEcEZyNzFubFNCVlNBV2NET1NiVGFqcU9tSDd5ZmJlX3diS1FJNV9SMnhCZ1ZRaDd5NEVoTTNmcnNBYTVLUnVwWmlmbHVMajdfYXNaT1VRdTFfV0lTQ3VwSDZ0QUpfcFBKb2w5aGhyUUVveldzeF9MdzdxRFZqUF9Wa0ZOcXZwRGFtME5tcXVSNmsxQm13dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Com alta no enxofre, Mosaic teve prejuízo de US$ 273 milhões no segundo trimestre - Globo Rural</t>
+          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2194,19 +2194,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdHRoWXh3Q0lLR20zYUtlM1NHaWt3MTB0clZBSnhUclVBQVFTeVpJMXFGSzk0UjVHendGMklEMGc3bWYtQVpKYlhqeV9XU0Y5OFF2Q21nQ1lIcmV5NG5xM2RkRTFIZG5xcmtTTG85UXE3UEphTXZvcDlTa0g1R3RMVDJHZDNJYWxyY3BuRVg1Z2RtZERWemxfQWhNZUZ0ZlEzR2paSE1fS2g5NHotaVlES2wwM0hCVWttaEHSAcgBQVVfeXFMUEYxcF82QU5MR2xGZ2liVnJsVHltSmRlRFZicWFKaWFDQ3RSTEdzLWhEbEg5YUZDbV9IcS1zNGppeE5SVlVBN1FxTk91T3pwdnZPaGRFQnBPUHM3MjVCVEhVMV8zV1RjU0VXVTF2V3dIdThoQ3g2LVdUbzVMWlYwaG1MWnhvc0t4aUtfWHhtVGZNby1Fd29fRVAxcE9Ca25BS2dHeVkwSGVIelFiVmc3eVBGVW1kS0N2NlJrZFdmZy1uVERHYXdYWjc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNMjVPMmg2Y2tPNGx0elVtTUU3Y1M3NFM4cFJ3czFjQndQTWZLOTE5ZmdPd3hkUmtjS3ZlbnZOVngzUnhWRmdRY3EyM0tEbXUzQkxqc2M4cGdoN2VaZ09xaDJmY2c1OTZrSmNNdXJpTm9NYkc4TjFhSFlYNUt1ZFNnWGtjT3FRNWtuQkhsTXIwa0JjNDJIQS1EVlFiTFBGUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PF mira esquema de R$ 3 mi com extração de calcário em MT - FOLHAMAX</t>
+          <t>Mosaic volta ao negativo e registra prejuízo de US$ 273 milhões no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2216,19 +2216,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNMjVPMmg2Y2tPNGx0elVtTUU3Y1M3NFM4cFJ3czFjQndQTWZLOTE5ZmdPd3hkUmtjS3ZlbnZOVngzUnhWRmdRY3EyM0tEbXUzQkxqc2M4cGdoN2VaZ09xaDJmY2c1OTZrSmNNdXJpTm9NYkc4TjFhSFlYNUt1ZFNnWGtjT3FRNWtuQkhsTXIwa0JjNDJIQS1EVlFiTFBGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNN25Wc0JsVHdYM1JaNFVsbkM1TEtibExtb0ZxcmFxZnhuT1BVVFRRSnQ1bnljdHNUcFBZRmRUX293SXJWa3RiYUdjLW83Vk43Rm44Z2x0Q3AxYk5OZFhMWXdPUk9VdFA3OExCV19fN25pamNCZTQ1a3RET3JUQ1M1SFUwWE4xZXFadTdER29yUTVxelhUOXc1cEtibnFQamtfNng5eHJSSzY4VVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas calcário - G1</t>
+          <t>Fertilizantes: preço da ureia nos portos brasileiros subiu 19% em 5 semanas - InfoMoney</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2238,19 +2238,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxORE9Qb29mRHg0MjFfN3NkOEV6TVNVaWdmWnRLUGdHZWNBdjQ1ZFZmc2t4RHZqN2pxUUFJMkJKdWJ4bVdidm9Qc0tNeGNLcVlvZ0V6Uk5lMVI3eGlTUFh6d1VmdUZ0MTA3ZDgwcE12dUdmWjRVVGNLOXF6WmdwZHZmVGo0TUR6V2hWMkp0Wm1PUjlIRGx3VnhLeHo4SmVsdDFwYnRPcDA2YVdfVUEyWi1Eek00aUVoeHk5RDJFb1c5ZlNpZVRCTm1vZmhB0gHYAUFVX3lxTE9KLWE5MnBSVjdkS3JheHpGUWdIS09VRkI0ZUxZcnFRRXFFV3dLSDRIdFRkOTlnTTlaRmVqNkJZMGZGdHhuVHI3blNEcEZyNzFubFNCVlNBV2NET1NiVGFqcU9tSDd5ZmJlX3diS1FJNV9SMnhCZ1ZRaDd5NEVoTTNmcnNBYTVLUnVwWmlmbHVMajdfYXNaT1VRdTFfV0lTQ3VwSDZ0QUpfcFBKb2w5aGhyUUVveldzeF9MdzdxRFZqUF9Wa0ZOcXZwRGFtME5tcXVSNmsxQm13dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ1hiVk10Qzl4WTcySEpXZ3BhNmlQdTRBX3dHUDJaam9oeXlVb1pJXzJSWDBwa0RmRW5uXzdzZzR1UTJCM19acXAzRFA4WTZKaXNqNHROeUFacFlzQWFZWktVbFVGVWZyZ0ZTRGs0N1lXdU1BSVRNazRMZHNnM2VuMjk0YzN3ZmhZVFozSTNYSGp6V2ZpeTF4cFhOZmxSQlAxMU5Pcm0yb2owb0NzU3Nkak930gG3AUFVX3lxTE1lZFphRHIyY1BwRko2WjBjWTdPQUdHRzlMZDNXUk9xM0Fvelo2LUhwNHpCWWZmY2UtYU9SV2Z4U2VVSlhoNkZCY0xraWs3NGZHaWJvNGdjWjEyaWIwOTAtSVJqMGpJbzM4c0hXMTZGRk1na1FFVVpwaVJLOGRMN3VHajZBbTRSbEgzTlFuT3ExUGs0OVRQa2RKM3JrczY1OGJzemUwTGVaSmpCTkhsUTF1SmpuaHBHVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fertilizantes: preço da ureia nos portos brasileiros subiu 19% em 5 semanas - InfoMoney</t>
+          <t>Saiba quem é o empresário alvo da PF por esquema de R$ 3 milhões com calcário - FOLHAMAX</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ1hiVk10Qzl4WTcySEpXZ3BhNmlQdTRBX3dHUDJaam9oeXlVb1pJXzJSWDBwa0RmRW5uXzdzZzR1UTJCM19acXAzRFA4WTZKaXNqNHROeUFacFlzQWFZWktVbFVGVWZyZ0ZTRGs0N1lXdU1BSVRNazRMZHNnM2VuMjk0YzN3ZmhZVFozSTNYSGp6V2ZpeTF4cFhOZmxSQlAxMU5Pcm0yb2owb0NzU3Nkak930gG3AUFVX3lxTE1lZFphRHIyY1BwRko2WjBjWTdPQUdHRzlMZDNXUk9xM0Fvelo2LUhwNHpCWWZmY2UtYU9SV2Z4U2VVSlhoNkZCY0xraWs3NGZHaWJvNGdjWjEyaWIwOTAtSVJqMGpJbzM4c0hXMTZGRk1na1FFVVpwaVJLOGRMN3VHajZBbTRSbEgzTlFuT3ExUGs0OVRQa2RKM3JrczY1OGJzemUwTGVaSmpCTkhsUTF1SmpuaHBHVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYUZzUkNXbWxvcGhSWmJIc2xqLTFwY3p0MXNSMks3dHluTGo2VGpDYldtTnVwSWZGTm52SUtvTFRwSWg3UDV3UGZxajFkY1JQQi1SWjRibFp1dkk4RnI4MGw1bzY3QTZSZy1BZk56cEtkVFB0Q3RUMFNnSWhJQ1ViV1Y3OEtYeVB5VFZRaUR6aDZ5RDVmSXUybC1BQktVXzEzT3Z5RzczQ3QxOEF3VGtQR3R5SzNVZ2lT?oc=5</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Operação da PF investiga retirada ilegal de mais de 34 toneladas de calcário em MT - G1</t>
+          <t>Empresário alvo da PF tem empresas em Rosário e Poconé; saiba quem é - Gazeta Digital</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbmx0djJaNkM2ZkNYMzdMd3JCa2d6N3YxbUZBUDh1YnhQWjRDaDdUMGZWckllV0tTdmlfOXktbEw3SmhEQ2JneVZTX1JIOS16NGRpTXZuSTRwbGVWTkZ3eGdkc2JPQkJDNEdTXzZ2a0pPUDlOeWpaMF9uMU85WTYySmQweEl0VnE3aUpjWDl5M2pDWWNaMlFmUUxqZEFleXNzVHZ5MFRCeEstWDE5OXNyZFgyUkZ4c1daTkNMMmRJa2ptY2ZqNnZzRUowYmtzQUhuQzdmenl0RUYxSXfSAeoBQVVfeXFMTnNOS3RkOHNCWlB6SHpPT2JQZENXNmtYSWNaLXZ2SENYMnFQVkctVndmVnRxUm85cFh4QlNxUXZNNndIZllRc2J2c3F1TE5GNXczRWhyR2Y5SHdPdEdwdGtDM2JSWktZSzZ6OEhaYUE1RGV3MUFJZ2NvTUlielMzUHJ1NFJUcmRGN0Zma3FpdTlwZjFxZGVud2NNbUJrdjZOejVraTJBNmNqVGhaSmdicFdRMUFGLUhjejhmOHpTbVptaTFodE5VSkNkTEc3aEI5dmFway1hamRlUW45ZEVrVHJrYWRDR0gyeGVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQVEo3bkRxQnc0emRmZUlWaFptajgxUjR6bXkyZmlSVEJPWW1OYTFzQmVNYlFtMFZ5dkdycTNDaE5QcVkzTmRfZmVQQWVDZUQ0ZnhaOE9YY2laOWFlMm5UZUdid0pQVy1SWTQ1VGtXUWlTVlJRTkc2WlZfZy10d0NYTUszRHVGUnk3aWoyQTNwelVHZW94YVlYQXBzRnRGZWw2dFBfSnA2SURuODltOGNlSmZKb1lSMkJpLWxoM25QaUlJblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Resultados da Mosaic em foco: as margens do fosfato podem se recuperar? - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com alta no enxofre, Mosaic teve prejuízo de US$ 273 milhões no segundo trimestre - globorural.globo.com</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZHJEZGU5dTl1eXd1cHRvN0RUZlpQSk9aVW1qR3JadzVnQmdXZzRqcERLekRqM2JsR1pNSnJLSlplZ3ZIc2JMbkxXNEtJOUxnTk9GQXF6M3dYbk1KTW5MRUpYeGdyX1VqOWRTWEJ3UzFDUWxrd3VLaHB0QXVPUzJaNS04eVg2dW9wbXhiYkZfc0xwU0ZYbVdRSDhSX0F5anc1U3h1aWlyRGNHbTdfYTVwVXlsQjVockJGQ1FYOURR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdHRoWXh3Q0lLR20zYUtlM1NHaWt3MTB0clZBSnhUclVBQVFTeVpJMXFGSzk0UjVHendGMklEMGc3bWYtQVpKYlhqeV9XU0Y5OFF2Q21nQ1lIcmV5NG5xM2RkRTFIZG5xcmtTTG85UXE3UEphTXZvcDlTa0g1R3RMVDJHZDNJYWxyY3BuRVg1Z2RtZERWemxfQWhNZUZ0ZlEzR2paSE1fS2g5NHotaVlES2wwM0hCVWttaEHSAcgBQVVfeXFMUEYxcF82QU5MR2xGZ2liVnJsVHltSmRlRFZicWFKaWFDQ3RSTEdzLWhEbEg5YUZDbV9IcS1zNGppeE5SVlVBN1FxTk91T3pwdnZPaGRFQnBPUHM3MjVCVEhVMV8zV1RjU0VXVTF2V3dIdThoQ3g2LVdUbzVMWlYwaG1MWnhvc0t4aUtfWHhtVGZNby1Fd29fRVAxcE9Ca25BS2dHeVkwSGVIelFiVmc3eVBGVW1kS0N2NlJrZFdmZy1uVERHYXdYWjc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PF deflagra Operação Peso Bruto contra a extração irregular de calcário em Rosário Oeste - Pagina1mt</t>
+          <t>Mosaic fecha 2º trimestre com prejuízo de US$ 273 milhões - CNN Brasil</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRE4xNWZFelh4ZUd2Y3djWU5JaHJVeTAwLWs0akJvY09QWC05RXdobWZjSmNMRjlKbUR2SWRWaXFUbTFtclpudnhmWThaNXBZaFJRYWFaSmloY2hNT0NEczhLWUlKVnVSbGpLU3I2U2xSMFUtYTV0ZU4zTk0ydURaTFRGc0g3c1ZRSnVQSVpmUTFYdUFhSGpUajFMcGpfLTM4Zk9HcnNXZUF1Unp6Z2hVenlHVG82T0c1Zkc2WVMwWkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOYVg3Y3RpTHNrVms5NXBiN2huemhBejE2Tng3VHV5aXI5RmJNazB1WTZUeDFvZmhWd19fU2FQVzRPRlExQnlBQ0J0anRuYWZkWTFlOW9vbGdwNjNxNnhWN2UwM0l3b3VDRWxmSzFWRkw5SUg3aG45YldJeHNhS0FGTG8tMndGY1lPTEZxU1FrNVJkelNnVEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CUIDANDO DA NOSSA TERRA: Programa é retomado e garante transporte gratuito de calcário para agricultores familiares - REDE BRASIL DE TELEVISÃO</t>
+          <t>PF investiga extração de calcário com prejuízo de R$ 3 milhões - MINUTO MT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>03/08/2026 17:36</t>
+          <t>04/08/2026 04:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX0FBcFhWQXB5RnhJTEdZWlVnR0xFSUJjakMtb1A2dWZBa0s5OWVPUlA5WEFKQ0ctbXVENXJ0NHhRamlwYko2Tm51QkR2TE56NFBCSXgwSm45YUU4V0F4YUg5VG1ERzhWWS05cjUxSVNuWmZZd2RZVDlTS1FwV3NVMEJGWEFVQWtaMjBicGU1QWFuaGFYX1pwS2lzM0JUQ2VzZEtkdjlCNHdqWEFvS19XZWZsR0hrNk1renhiNnpERU1ESUh1T1QwZkVFdDJNSUVaSVlva3NTUkZmdHhWR3pZTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOcmlIZnAxbnk3MnhyYmhhcFRYbmR2RU40ZDg3X1FvT09kNDY1NXBha0xVMmozWFd3cDNzMDc2d3NmTWhKczROZk80OVhWcWxfSzc4bkF2V0JfQTBKZ2tpaU9wUkFheVptSEdPOFp4RGtZYjNfTkU4dWRBYUxqekN0NW5XNW1qTFR0U1FZMTg4Z1hVYnJuc0s2cW93?oc=5</t>
         </is>
       </c>
     </row>
@@ -2382,237 +2382,237 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Alepi recebe relatório sobre impacto ambiental da exploração de calcário marinho - parlamentopiaui.com.br</t>
+          <t>CUIDANDO DA NOSSA TERRA: Programa é retomado e garante transporte gratuito de calcário para agricultores familiares - REDE BRASIL DE TELEVISÃO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>03/08/2026 17:00</t>
+          <t>03/08/2026 17:36</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPYlJReXZpUXFUN2JRUTVNVjl5SUwzV093MFlSX0dEdTlsN3Ridm9ZdUQ5bEItTFJ0aUNvTS1sWGJwYVJTdDJCcFE1Qjc1allMVXU5SENlNmFyOS1qbnNBblMyejRXQXFzWHVycHctdVFtN2NTVFVnQlNJZjlXVzVoTGZPa20xVDZvWkg0ZF9rcDFfOGF5M3UzSDAzYlhqUjlIbWc3dzdKNld1Y29mMmw2SDFia1lnNEFEVkRTd3RXX0Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPX0FBcFhWQXB5RnhJTEdZWlVnR0xFSUJjakMtb1A2dWZBa0s5OWVPUlA5WEFKQ0ctbXVENXJ0NHhRamlwYko2Tm51QkR2TE56NFBCSXgwSm45YUU4V0F4YUg5VG1ERzhWWS05cjUxSVNuWmZZd2RZVDlTS1FwV3NVMEJGWEFVQWtaMjBicGU1QWFuaGFYX1pwS2lzM0JUQ2VzZEtkdjlCNHdqWEFvS19XZWZsR0hrNk1renhiNnpERU1ESUh1T1QwZkVFdDJNSUVaSVlva3NTUkZmdHhWR3pZTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - Portal do Agronegócio</t>
+          <t>Alepi recebe relatório sobre impacto ambiental da exploração de calcário marinho - parlamentopiaui.com.br</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>03/08/2026 13:30</t>
+          <t>03/08/2026 17:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQY0VQM29hUjJobThyTXFqR3M0bm5LNXlwTEN0YmJMeEtGaWxZM3p6UHpsdzhJQ2VuZE9DOHdDZ3ppWGREdVpteUNGTGphYXhZejk1X19tMkV1RERPSlU5YWJJMzVYRUJkZlBhWjBNdldhUW5lajhZUkFfX2U4emdjeDdSNUJJZkhnbmN5Y05LU3pQUkZaUHhXX2d6OVk0TlFYbFdGT1AxVUZqWTVHcVVXMEM5YmdhTldXQVhtTVlmYzh3ZnJHY3dDOGdMamh3UmNhZEMxUTZxVDkzaVlUcXZrQWczcHp0YnJsc2NmU1BMQTNrMXRyMnhkMHZNRU5ubFljX3FKZDBXaWN2NlpCQjNUVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPYlJReXZpUXFUN2JRUTVNVjl5SUwzV093MFlSX0dEdTlsN3Ridm9ZdUQ5bEItTFJ0aUNvTS1sWGJwYVJTdDJCcFE1Qjc1allMVXU5SENlNmFyOS1qbnNBblMyejRXQXFzWHVycHctdVFtN2NTVFVnQlNJZjlXVzVoTGZPa20xVDZvWkg0ZF9rcDFfOGF5M3UzSDAzYlhqUjlIbWc3dzdKNld1Y29mMmw2SDFia1lnNEFEVkRTd3RXX0Y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - Jornal Opção</t>
+          <t>Mosaic e Elicit Plant unem forças para desenvolver tecnologia contra estresse hídrico na canola da América do Norte - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>02/08/2026 15:00</t>
+          <t>03/08/2026 13:30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPd2pmTzdLTS1MYzhVMGhjY0VfSlBxZ045aWJZcEZoQ3ZPVkgyZ1FiRWF3T2NwaFhTckh1LVBSVldoUU9sVTg3UkNPcWNXYjJtTzkydmQ1bWZnWG03UXNrSTFaYmZDNVZQWjN6dWVMQ2E3b2tmMVlEYkZIbDlOREIxbkdYN09ZNXRuVjgzVDlyb0MtNzBidmVIaFNPRFM1RndSR1ROa3BsVHBvNUY0X3dYVzhsMEJ4ZTNHVnhsWG1nVUhDTzNKNVdVQ3NFSlRSXzY1aWNubGpxRGk0U2dDSXhoSnE3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQY0VQM29hUjJobThyTXFqR3M0bm5LNXlwTEN0YmJMeEtGaWxZM3p6UHpsdzhJQ2VuZE9DOHdDZ3ppWGREdVpteUNGTGphYXhZejk1X19tMkV1RERPSlU5YWJJMzVYRUJkZlBhWjBNdldhUW5lajhZUkFfX2U4emdjeDdSNUJJZkhnbmN5Y05LU3pQUkZaUHhXX2d6OVk0TlFYbFdGT1AxVUZqWTVHcVVXMEM5YmdhTldXQVhtTVlmYzh3ZnJHY3dDOGdMamh3UmNhZEMxUTZxVDkzaVlUcXZrQWczcHp0YnJsc2NmU1BMQTNrMXRyMnhkMHZNRU5ubFljX3FKZDBXaWN2NlpCQjNUVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Catalão: Prefeito Velomar Rios reforça apoio à Mosaic durante reunião em São Paulo - Portal Serra Dourada News</t>
+          <t>Dependência externa expõe vulnerabilidade do agro goiano após crise do enxofre, alerta Fecomex - Jornal Opção</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>01/08/2026 04:00</t>
+          <t>02/08/2026 15:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPN1JlMmFtcTVBZGRLNnQ2OVpUN3g2UEFnQzRzQXZyOENDSTZrOWhjLTNmaE50Ql9FNFNfUzR1cnZUR3lGbHpNUXo4NmJyOVVUOW9tM1VqM3pMMjFxbWhPcEprb29qT09UOHlZejNFQTBhVk5sMDI5NndJRWFNZ3lwQkZjRHJxWDZvN2MybGdMbEh5VkE3VVhPREd5cl95Y1ZYUGgxaFlFdThOQXdMWkxjSk1vOGFyMVdVSThUMzFYSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPd2pmTzdLTS1MYzhVMGhjY0VfSlBxZ045aWJZcEZoQ3ZPVkgyZ1FiRWF3T2NwaFhTckh1LVBSVldoUU9sVTg3UkNPcWNXYjJtTzkydmQ1bWZnWG03UXNrSTFaYmZDNVZQWjN6dWVMQ2E3b2tmMVlEYkZIbDlOREIxbkdYN09ZNXRuVjgzVDlyb0MtNzBidmVIaFNPRFM1RndSR1ROa3BsVHBvNUY0X3dYVzhsMEJ4ZTNHVnhsWG1nVUhDTzNKNVdVQ3NFSlRSXzY1aWNubGpxRGk0U2dDSXhoSnE3SQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - CompreRural</t>
+          <t>Catalão: Prefeito Velomar Rios reforça apoio à Mosaic durante reunião em São Paulo - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>31/07/2026 13:59</t>
+          <t>01/08/2026 04:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNa2dNSHBOQmp0SndMbUp2YnpSM2pEVjUtejVHZ0NDOHZVWFRra0xXX1pXUFZnZzlFQVM1THpySWMwS0tERjhSLXdIMVVaVEFYYTBkalRoMTZ4WEdKZ3pEb1FwQTVvN0JFTm4tczJaal9sNUpTSXk4RjRkR1pJR1pGbFcta0VTSkhPNmQxLXhJZllubnZISFR4RTI4QmFEN0tfUWJxYlpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPN1JlMmFtcTVBZGRLNnQ2OVpUN3g2UEFnQzRzQXZyOENDSTZrOWhjLTNmaE50Ql9FNFNfUzR1cnZUR3lGbHpNUXo4NmJyOVVUOW9tM1VqM3pMMjFxbWhPcEprb29qT09UOHlZejNFQTBhVk5sMDI5NndJRWFNZ3lwQkZjRHJxWDZvN2MybGdMbEh5VkE3VVhPREd5cl95Y1ZYUGgxaFlFdThOQXdMWkxjSk1vOGFyMVdVSThUMzFYSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Agricultor adquire 30 toneladas de calcário agrícola com laudo garantindo alta concentração de neutralização, aplica no solo e nota que a acidez da terra permaneceu inalterada, comprometendo o plantio de 10 hectares de feijão - Correio Braziliense</t>
+          <t>Enxofre dispara para US$ 1.200 e pressiona custo dos fertilizantes no campo - CompreRural</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>31/07/2026 04:00</t>
+          <t>31/07/2026 13:59</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPb0pYYkloaDlJOW1HRERkUW03XzFaWVBTVXVYRzNiWjhTN0hMWVE0bnNkWlBTSm1FdW42c1NZZXg3QVJqMXE2TW02aFoxUDhCQk5kQ0lSSWVoSF93UnNMS2NLV19qZjJld1dKRjJNdnRZSlNUUVN5c0tlNmhXZGFlWHByajhwNkRtOTBXNHhVMVp1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNa2dNSHBOQmp0SndMbUp2YnpSM2pEVjUtejVHZ0NDOHZVWFRra0xXX1pXUFZnZzlFQVM1THpySWMwS0tERjhSLXdIMVVaVEFYYTBkalRoMTZ4WEdKZ3pEb1FwQTVvN0JFTm4tczJaal9sNUpTSXk4RjRkR1pJR1pGbFcta0VTSkhPNmQxLXhJZllubnZISFR4RTI4QmFEN0tfUWJxYlpR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Clusters ferro-enxofre abrem novas frentes no manejo de pragas - Global Crop Protection</t>
+          <t>Agricultor adquire 30 toneladas de calcário agrícola com laudo garantindo alta concentração de neutralização, aplica no solo e nota que a acidez da terra permaneceu inalterada, comprometendo o plantio de 10 hectares de feijão - Correio Braziliense</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>30/07/2026 11:26</t>
+          <t>31/07/2026 04:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQLXd0RWlHeWpRendDMGNUMklrZlFEWV9PbnNxLWZ0a1NsdXMxS1hQa2lONXRlMk1peWF1Ny1JNWRyYk9Ddk43TTh3MWQ3MUtBU1VreFZGc0tYZjdzZVdlNUU4Ry1OT05lVE1qSEpZZGh3SWYzcjNCV1ZscURkNlpONmFqblY2Z25QdV9WZ3R6d1pZTVB4TlFOOFlnUG16UFpqdHozU0VRRkpoNXI3amRWVVVYOHdRLUhnUVZnUWw2YUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPb0pYYkloaDlJOW1HRERkUW03XzFaWVBTVXVYRzNiWjhTN0hMWVE0bnNkWlBTSm1FdW42c1NZZXg3QVJqMXE2TW02aFoxUDhCQk5kQ0lSSWVoSF93UnNMS2NLV19qZjJld1dKRjJNdnRZSlNUUVN5c0tlNmhXZGFlWHByajhwNkRtOTBXNHhVMVp1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - Portal Revista Kdea 360</t>
+          <t>Clusters ferro-enxofre abrem novas frentes no manejo de pragas - Global Crop Protection</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>30/07/2026 11:09</t>
+          <t>30/07/2026 11:26</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQLXd0RWlHeWpRendDMGNUMklrZlFEWV9PbnNxLWZ0a1NsdXMxS1hQa2lONXRlMk1peWF1Ny1JNWRyYk9Ddk43TTh3MWQ3MUtBU1VreFZGc0tYZjdzZVdlNUU4Ry1OT05lVE1qSEpZZGh3SWYzcjNCV1ZscURkNlpONmFqblY2Z25QdV9WZ3R6d1pZTVB4TlFOOFlnUG16UFpqdHozU0VRRkpoNXI3amRWVVVYOHdRLUhnUVZnUWw2YUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
+          <t>Mosaic transforma inovação agronômica em campanha para aproximar tecnologia do produtor rural - revistakdea360.com.br</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>30/07/2026 04:00</t>
+          <t>30/07/2026 11:09</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelhhdmFxT0ZKRG5MenJyRElINW5HVGVVLVZOVWJJY3RVaXRKeXRTMHZHcHhQeVVZNlY3bXFYa0RiUHFQbWRDVWlJTm5RSmR4R3NVak04Zk40ZHB4cG1oZG9jNzA1d1ByMjVSVWIzWkY5blRvM3F3OGZUR1dsNk1yX2xtVTlHeUxuZ25MUHd1bGxYUWtNcTNoY19TSnAyV1kydXZJblhMSjJGdXZaTWQ2aWhrMk5rYmx2M2ZlRDZGRGtBaS1UdU9ETnI1X2VsZTFfMGlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
+          <t>EuroChem pode paralisar e implementar layoff em Serra do Salitre devido à crise do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>29/07/2026 22:32</t>
+          <t>30/07/2026 04:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1FUmpCMjBWeG01TDVyOEZqbWI3Tk83SjVvdjA4ajBzVWtZTTFTZjA2Qi1HU2RMOUtab3dWelVzbjE4dTUtS3NGSEZ6Rms0SDd3T1I0eUpXVmNGaFJHdlFkdW1SZHM2MDZQM2wtZ0xKcnI3a0lCZ01FNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 16 - ArchDaily</t>
+          <t>Nova fábrica de ureia na índia terá capacidade de 1,27 milhão de toneladas por ano - GlobalFert</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>29/07/2026 17:56</t>
+          <t>29/07/2026 22:32</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPbTdDNHJBU0ZTWDk5OERHXzBaU1RkdnQwVlZkSHZzVmt5VXdjMnhjSXhLR1N4cWlpUmNVM1p0V1ZtdHRUNTVSVU53c2lzTy1rVWFDOVNFY05GNzFobVE2U3RlWHNxZl9Yb2JCdXE0aGZKVENTZElzQUpZYlRjMGV2N0dwQVZoR0oyN2NOVFdEYjlYdmx4aENJaDNLMWRqTmRLdEVvQWptNXhpNW02aFFKTW9sc1kwRkQ4U2dkMERueVM2UkRZYmo3RG51aHdtWnh5RFZsVFRNblZtY1pQeFRDVlVXR3NZbzRnN1FIR1UxcVNwVWtfTmhQTWZaQ0FtazA1dlR4b1pkaTBxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdWlvSWxaY3E2VEpHZUtQM1dMRUlBUlhzaTZQVTEwY29wa0lKZldWMXBiaW5BVlBjZkh3WmdNVVMxRlRSRmotRzFDbHRCVVZQMldyMVJ0WWljVE0wb19sM3d1NmRObzBzWW03THF5ZG4zTE5obU9lTVFQZ0lkemVoOG1sLTdTaEpURjZTd2hlODN5NW5hTzVnaGYteExpSlFmd0lsVGhuMEVHbFd1TE81RFdLZEpzSjFTX2hKdzgtbjFoNDNP?oc=5</t>
         </is>
       </c>
     </row>
@@ -2624,39 +2624,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 21 - ArchDaily</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 16 - ArchDaily</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>29/07/2026 10:36</t>
+          <t>29/07/2026 17:56</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQbmJlajh6WXU1TENBOFk0d2pic3EtLWxPQjRzZGVDVXRMYzlhZ1lId2xNTWVtY0l3V1I1S0pzN0dKSlIxQXNZY29DckdNcWpZLVJXNnA4VWNqTTdRblR5OGI4LVZJUEs2VmxKdTlJV1RKN181alFQbG84elVpY1o3SDJValF2MG5sdmpuNS1vTWFIQTBZUDV1V0EyaGZJT0pNUTlkcndMNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPbTdDNHJBU0ZTWDk5OERHXzBaU1RkdnQwVlZkSHZzVmt5VXdjMnhjSXhLR1N4cWlpUmNVM1p0V1ZtdHRUNTVSVU53c2lzTy1rVWFDOVNFY05GNzFobVE2U3RlWHNxZl9Yb2JCdXE0aGZKVENTZElzQUpZYlRjMGV2N0dwQVZoR0oyN2NOVFdEYjlYdmx4aENJaDNLMWRqTmRLdEVvQWptNXhpNW02aFFKTW9sc1kwRkQ4U2dkMERueVM2UkRZYmo3RG51aHdtWnh5RFZsVFRNblZtY1pQeFRDVlVXR3NZbzRnN1FIR1UxcVNwVWtfTmhQTWZaQ0FtazA1dlR4b1pkaTBxUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
+          <t>Galeria de Limestone, Granite and Travertine - 21 - ArchDaily</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>29/07/2026 04:00</t>
+          <t>29/07/2026 10:36</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQbmJlajh6WXU1TENBOFk0d2pic3EtLWxPQjRzZGVDVXRMYzlhZ1lId2xNTWVtY0l3V1I1S0pzN0dKSlIxQXNZY29DckdNcWpZLVJXNnA4VWNqTTdRblR5OGI4LVZJUEs2VmxKdTlJV1RKN181alFQbG84elVpY1o3SDJValF2MG5sdmpuNS1vTWFIQTBZUDV1V0EyaGZJT0pNUTlkcndMNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Aumento da tensão no Oriente Médio faz ureia subir quase 14% em um mês - brasilagro.com.br</t>
+          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2678,19 +2678,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPV0ttektrOWVWbUNQcndLWHlINjhWUUIzek1DQ18tNWJST1RBMGFCandldlJhNmdUeUdOUkx6VkhNSjdvNkhLVjJRQndkNlQwalVfQVRkd1ZpQUdDcmcta3RobEtoOXIxUzVvekJTc2l0ZHlhbEl2dGdlUWlEckRrWWFoX2xLUloyVDQ3VUV2dUoza2d2VFJZTWVEYkNGRzNhVHdMNUF4TFdVdkstX1F4NGhaaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ureia cai forte e muda a conta para a próxima safra - Agrolink</t>
+          <t>Chinesa CMOC fecha acordo para comprar minério de ferro da brasileira Itaminas - InvestNews</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPLUtOVnNuaHlwVThqUERlWVNWNWYzOE9sSk96YnkxSndhelBJQXBremtlVjRldTdMTTNYTjJSb3FGb04tLURZdjlBZk1QZ1BMaWVXN1B3ZVBJREctc21HMnRxZkJtSjUyS205c2hYeUJ2dE9kOUpla2t3TXdNOTRuYXRzMGY1MWxwcUpYWVVZeXpDR3VER2lZNUJvdmg4RVYxdmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5DT2VnclhuTHNCOFlEd05PUHRSdU9BU3gwVUhDaHpmVzBQSHEwV3Fub2hBbkREMEl5N2E2TzNDbVplZ3dudkptZHU4WXFNdEdmWENvT19zeFVSYTlhUWdLc2Q3V2tDdXBqTkZVVjk1aUxzQdIBd0FVX3lxTE9EMUJSRjJpOWxNRGhVVnFDS0F5NW9wNlFPSGNGcnp2RmxTOS1PRXBzbzY3N2wzVHpRU2d0aEJuSkhQNmJMMGRzcGxuc3lYOE1vUEtEeTVjLUhtMkNveFZrOHQtQlNsZWh3NGUxTERKYkg1eE9ZaFVz?oc=5</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - Brasil Mineral</t>
+          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2722,19 +2722,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPWExkNkZWSHNlQ2xZeEVSNlY5Ul82MThzN3pSUXpEZTJ4VGNXS1UyZXJIODFrdXJWSm5YdGtXSWVnOXVVYzRDY0dHR0llNV9KaG9IVUpNdnpnU2NTRnYwNmtuYm93Z25QbXkyTU9lUmFndVoxRWN6MENxbjZSME1CMjc2UHZVaGVXT3hxQTBIVS02RFda?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ormuz pressiona fertilizantes: enxofre sobe 322% em um ano, fosfatados perdem demanda e ureia volta a avançar - Money Times</t>
+          <t>Aumento da tensão no Oriente Médio faz ureia subir quase 14% em um mês - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2744,29 +2744,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPX1FwemdXWEhUWnBFTkt4NkRMQ1p2aU1zVHB6aVJlbkh5WWJrWURlbkVZa0w3ZG9mLWl2VHZjY3gtekJsSWVrellJX29fRGJvMy1YZlotM3VVR3J5a05pc01UcEx1MjNSUkNVUDdieUx3eTR4RU5PdEEzMlYwVnQ5Yzdja0R1QlRnY1A2T0ZlNUFGTzdiRTY4ek50U0RKRDJtZXoyMlJWQTNGeTdwYlBHQVdYclRhVnFSUHIxRl9QXzBrazB2UGVoWGRaZkJ6SXdaaXBkSUJoeFVDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPV0ttektrOWVWbUNQcndLWHlINjhWUUIzek1DQ18tNWJST1RBMGFCandldlJhNmdUeUdOUkx6VkhNSjdvNkhLVjJRQndkNlQwalVfQVRkd1ZpQUdDcmcta3RobEtoOXIxUzVvekJTc2l0ZHlhbEl2dGdlUWlEckRrWWFoX2xLUloyVDQ3VUV2dUoza2d2VFJZTWVEYkNGRzNhVHdMNUF4TFdVdkstX1F4NGhaaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - estadaomatogrosso.com.br</t>
+          <t>EXCLUSIVO | O que está acontecendo na cadeia de valor do enxofre? - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>28/07/2026 21:26</t>
+          <t>29/07/2026 04:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPWExkNkZWSHNlQ2xZeEVSNlY5Ul82MThzN3pSUXpEZTJ4VGNXS1UyZXJIODFrdXJWSm5YdGtXSWVnOXVVYzRDY0dHR0llNV9KaG9IVUpNdnpnU2NTRnYwNmtuYm93Z25QbXkyTU9lUmFndVoxRWN6MENxbjZSME1CMjc2UHZVaGVXT3hxQTBIVS02RFda?oc=5</t>
         </is>
       </c>
     </row>
@@ -2778,61 +2778,61 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Distribuição de calcário a produtores rurais começa nesta semana em Santa Helena - Universo da Notícia</t>
+          <t>Pesquisa aponta que calcário ultrafino melhora microbiologia do solo - Estadão MT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>28/07/2026 14:26</t>
+          <t>28/07/2026 21:26</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSFoxVDBKSzNXdUtXMlplcU5KSWNoX1BxSklMZ2VDTEMwQl9YWlFQRW5NUzN2VDVmVS02aEJ2QnVFajJXYWNRSDEzRGxLRUdHRE83SEo2OFpfMW90a3BMRHprUHpXZzEtam52TE9WaW9TZ281SEgwc0l6em9mZGVpai1ybTRIcUk3S05sVVVNeXNycEQ1SHRKYWRhWHYwZlY1SWNvVk9Rbk1waDlpeXRjb1FOUDNBYTB5bjRyT05ENEd0b1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNMkhNdkktcm9mVHc3Vk5vSVl3LW5kTjN6REdMZ0lPZ3N4ZDZfejJQRUpIcmZEX1NORWpFNUV5VWFjVC16S0t2RnBxTnhVSVRuZkFvMy1zRkVyUWZvQ3NxV0tncmU2YUVYWjd2V29sbElsWE9rTHlhajgtNnZFNE9KanRIaGRaelRQMlRJbXRnZW5MUWpLWS1zbDFEMWo3bTdmaEZKMlNOckYxSGxnaTBjZUJxU3BYRzJpUXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Quarta semana consecutiva de alta da ureia nos portos brasileiros e os possíveis impactos para as compras da próxima safra - Cana Online</t>
+          <t>Distribuição de calcário a produtores rurais começa nesta semana em Santa Helena - Universo da Notícia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>28/07/2026 10:20</t>
+          <t>28/07/2026 14:26</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcFdYTUE0NlRaT3ZYc0l2MzBmdjlWQ1Y4VkZhUzJqa0plOVcyeXg0ZEdheWdCb2hXUXRqel9MUFpwNFFPOFh1dDZGcWVPM1NhaHFOTnlZSVV5NUtPYzhVUFh6SUpEaVYtWUJWcGxROFJ6RmdZMkpUWUl1eEl2R2ZOMXpZa0xCMlJ3azZHNWl3Z1Z3M0xmSVNSNlpkT0FIN29vb0Rqc3l3dm8xazRzVWl1OEp3TGpFcjY5dVBRclVFX0ZZSkd5NjkzV29BdkFkVm1OMkF3Z0wyUXZ1OEJsX0NJLTAyeWd5bHJHQm5GbEJ1OGJfOXY5X3JZNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNSFoxVDBKSzNXdUtXMlplcU5KSWNoX1BxSklMZ2VDTEMwQl9YWlFQRW5NUzN2VDVmVS02aEJ2QnVFajJXYWNRSDEzRGxLRUdHRE83SEo2OFpfMW90a3BMRHprUHpXZzEtam52TE9WaW9TZ281SEgwc0l6em9mZGVpai1ybTRIcUk3S05sVVVNeXNycEQ1SHRKYWRhWHYwZlY1SWNvVk9Rbk1waDlpeXRjb1FOUDNBYTB5bjRyT05ENEd0b1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Quarta semana consecutiva de alta da ureia nos portos brasileiros e os possíveis impactos para as compras da próxima safra - Cana Online</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>28/07/2026 09:25</t>
+          <t>28/07/2026 10:20</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE8waGNjYVp0Q0tiRlZJQmxiaFhDRlZ6U2tuZEhLcnRMZER4WGw0TndNeUFjVUd4MUVHZVRWOEdiVXRpUU4ydXdHSEZRV1lQa25idnM3ejQ3U2dseldHQWR5c2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcFdYTUE0NlRaT3ZYc0l2MzBmdjlWQ1Y4VkZhUzJqa0plOVcyeXg0ZEdheWdCb2hXUXRqel9MUFpwNFFPOFh1dDZGcWVPM1NhaHFOTnlZSVV5NUtPYzhVUFh6SUpEaVYtWUJWcGxROFJ6RmdZMkpUWUl1eEl2R2ZOMXpZa0xCMlJ3azZHNWl3Z1Z3M0xmSVNSNlpkT0FIN29vb0Rqc3l3dm8xazRzVWl1OEp3TGpFcjY5dVBRclVFX0ZZSkd5NjkzV29BdkFkVm1OMkF3Z0wyUXZ1OEJsX0NJLTAyeWd5bHJHQm5GbEJ1OGJfOXY5X3JZNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2844,29 +2844,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
+          <t>Crise do enxofre põe em risco setor de fertilizantes e preocupa o Brasil - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>28/07/2026 04:00</t>
+          <t>28/07/2026 09:25</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE8waGNjYVp0Q0tiRlZJQmxiaFhDRlZ6U2tuZEhLcnRMZER4WGw0TndNeUFjVUd4MUVHZVRWOEdiVXRpUU4ydXdHSEZRV1lQa25idnM3ejQ3U2dseldHQWR5c2pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - Blog do Esmael</t>
+          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPcmVCLTNDSlR3bG9veGZHSnZrZThiTExVb2hsQ3dOT2FjbWN1ZG9aMkt3a1YtVWFNRWhPemxaWnpTT3FCQWdTRE9PRG9vVjM3TWduMFhBNFZMaEtVY1VCaC1VRmJBOGJ2LVZJRXNuQXI2TUw5d2VMN2V1amp2UWNwU0J2VlA1WnJnQ3lSTWZ2dFIzdDJPNFNfQlB4YUFOdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ENERGIA RENOVÁVEL | Mosaic e Casa dos Ventos ampliam parceria para autoprodução - Brasil Mineral</t>
+          <t>Enxofre caro ameaça fertilizantes da safra do Paraná - esmaelmorais.com.br</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPcmVCLTNDSlR3bG9veGZHSnZrZThiTExVb2hsQ3dOT2FjbWN1ZG9aMkt3a1YtVWFNRWhPemxaWnpTT3FCQWdTRE9PRG9vVjM3TWduMFhBNFZMaEtVY1VCaC1VRmJBOGJ2LVZJRXNuQXI2TUw5d2VMN2V1amp2UWNwU0J2VlA1WnJnQ3lSTWZ2dFIzdDJPNFNfQlB4YUFOdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5Yb2lTdDUxanVKZE1qVWxFb0twbzAtTlJ6Z0g4TkJucEJsOWpvS1hZQVQtbGJYal9TN2ZJNXVGWFNiR0NURFIyQ1RyTnMwUnVLQ1kydXJKZ2JVM3R3Tl9aOHRLQzFtUHItYjNmYWdBNU1PMVBTMWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -2910,17 +2910,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Guerra do Irã afeta fornecimento global de enxofre e crise afeta agricultura e até saneamento no Brasil - G1</t>
+          <t>Com guerra no Irã, estoque brasileiro de enxofre pode não alcançar setembro, afirma Ibram - Valor Econômico</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>27/07/2026 04:00</t>
+          <t>28/07/2026 04:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNYmdob2ExRWhKcGxUNVdMM0FDVXFyZ2JKdkxTOGRHV2N5RDhJeDZOazJaeTNEYVpvX2NKLTlPVGdlNWxrUDhWMUk4dDFGajdRYWp1Y3RiQXZpdEVZU1FRQWR2LWZ5endONmdPVjlKalduTkNSclJ5ZHhYVzFFRE1Pdmt2dDlNSWx4UjR5LVhyWGYtd2ZKeUNDUGNBdEhqeV95VUxsX19wMzAtVmV0M1BUS3BaNHJlcTJMalAwZ1Y3R1gtcmp4Zm9ld2RISnFmcE15YmwxLVdyRWhSelpCamhSaDhuVXM2OTNYd0liOHppbXJZaXfSAYICQVVfeXFMTWQzRTd1WXpuenFtT3JYWGtqeE5SRm9GN2ZETjdvbDV4TnpldUJ5MGRMcW9Va0JZbGlzRjF3cXFZU01lajlYN05URmVWU095WE5wbmRuRi16a3FCRVFKemNDVG05X1ZMYmRWTkRjWkFVUVJzYzZTMlRGYldzVzVpV1FQTHQ2UWVzZmJ0MmszWFlxZEJYRHdJRVpnOFpmdmZZN3lPU3dHU0NFUTAtLUxXS3NVNkNBTkFOWnVCQzFUOUhqdE1hU29mQnRmS3lXZG9weDByRlRMb05JbllGXzBHODg2cV9kMGE0N1lGdkotbnlJb2tkU2htMU1TMHFERFItUjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWHRWcEVlMmJVOEtOTFhYSUFrbkxvNVcxcTBXNXkwb3VFaXJ1NE5yMXNSZ3cxR0RPT1RhbGRLeTZvc3NFUGJHRDh1LTR5TU5YdXN3U0dtdVJTMElMUGlzUHJQeEVMVWhYbGVSa1BzQ2twNkxpZHZ0dUNVSjBBU1VYOTI1Vk9RUThBZ2xtbWJ4UGRBOHhNMk5Sc1M1QkR3Yk1MbHlSNGhvUU1CcjY2ZENpTTY2OW5yaGJra3pqXzc3ajE0SDZ2Vlczdk5weE54bjlsWml6ZWJwYl96QdIB6AFBVV95cUxQVENsWFVQaUIwTTNGaFItb2sxd1BoX2hLZ1cwTlpUYXJFUHVSd1RoUFFnMTFxR0sxTUJ5aHJVcXJyZXZ0NFpOcUEyTVRNOXlkWFA4ZVlyaW9TZ2JELTJpZ3owZ2k2QjE0SFIxS2wwVUxDWHRPb2s1cGNmTWhzWGxsUUxMbGlfcXlYWlFXakVxNWxkMzdGRkg1YUVfa3lnel9WQjFCUktvM1FoaUxBblVod013Y2dsX1ZPNk1Edkdpb3dkZDFmYlBQYmZza3pOQ3ZZRDVRQWlYR2tfSTFaNTJFd19IMGNlUWV3?oc=5</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2971,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ureia já aumentou 14% em quatro semanas - Correio do Povo</t>
+          <t>Guerra do Irã afeta fornecimento global de enxofre e crise afeta agricultura e até saneamento no Brasil - G1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNRUJhYXZkbF9aU0k2LXYtS0I2aHR2Y3NHWXZDUG5EOGJCQS1fdGViUmhSTkF1dmhMU0xISDNDVU5mcTlITHNWN1NmNzAwbm9ROFhrSUJtMkFHX0JyT0tfZWs3YVdUWTAwSDJwM2JoVHNqbTlreUtQY0RDME5YRHNRZlBwTmZLV3duMms4UlVRTHJUMXh1QXNfWVFuRFNMTTAwQko4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNYmdob2ExRWhKcGxUNVdMM0FDVXFyZ2JKdkxTOGRHV2N5RDhJeDZOazJaeTNEYVpvX2NKLTlPVGdlNWxrUDhWMUk4dDFGajdRYWp1Y3RiQXZpdEVZU1FRQWR2LWZ5endONmdPVjlKalduTkNSclJ5ZHhYVzFFRE1Pdmt2dDlNSWx4UjR5LVhyWGYtd2ZKeUNDUGNBdEhqeV95VUxsX19wMzAtVmV0M1BUS3BaNHJlcTJMalAwZ1Y3R1gtcmp4Zm9ld2RISnFmcE15YmwxLVdyRWhSelpCamhSaDhuVXM2OTNYd0liOHppbXJZaXfSAYICQVVfeXFMTWQzRTd1WXpuenFtT3JYWGtqeE5SRm9GN2ZETjdvbDV4TnpldUJ5MGRMcW9Va0JZbGlzRjF3cXFZU01lajlYN05URmVWU095WE5wbmRuRi16a3FCRVFKemNDVG05X1ZMYmRWTkRjWkFVUVJzYzZTMlRGYldzVzVpV1FQTHQ2UWVzZmJ0MmszWFlxZEJYRHdJRVpnOFpmdmZZN3lPU3dHU0NFUTAtLUxXS3NVNkNBTkFOWnVCQzFUOUhqdE1hU29mQnRmS3lXZG9weDByRlRMb05JbllGXzBHODg2cV9kMGE0N1lGdkotbnlJb2tkU2htMU1TMHFERFItUjB3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3015,44 +3015,44 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
+          <t>Ureia já aumentou 14% em quatro semanas - Correio do Povo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>25/07/2026 04:00</t>
+          <t>27/07/2026 04:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNRUJhYXZkbF9aU0k2LXYtS0I2aHR2Y3NHWXZDUG5EOGJCQS1fdGViUmhSTkF1dmhMU0xISDNDVU5mcTlITHNWN1NmNzAwbm9ROFhrSUJtMkFHX0JyT0tfZWs3YVdUWTAwSDJwM2JoVHNqbTlreUtQY0RDME5YRHNRZlBwTmZLV3duMms4UlVRTHJUMXh1QXNfWVFuRFNMTTAwQko4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - Prefeitura de Nossa Senhora do Livramento - MT</t>
+          <t>Mosaic e Elicit Plant desenvolvem solução para canola na América do Norte - CNN Brasil</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>23/07/2026 13:15</t>
+          <t>25/07/2026 04:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOVDJpQWxoSVUzaEhaVTBvY3ZVelozNHgzSUdiR19SWFZUamFLZG1USl9RZUd2aFJBM2lOZnBsa3QxY2VrTkdrU2JCUDhLNTdJZkhpNUtTbFZobWRJdVVEYVY3LUM4OXpMZ1NlTnZfelduVFBoaU5kT1RKQ2lUWEhTUzRGTFRBNVVVdDVnd3lpYmlNNXJmNFdDT0stOWZBTV96Y1FoM0JNeEJFQUVp?oc=5</t>
         </is>
       </c>
     </row>
@@ -3064,29 +3064,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
+          <t>SEADERMA fortalece agricultura familiar com projetos de piscicultura, distribuição de calcário e novos investimentos em Livramento - Prefeitura de Nossa Senhora do Livramento - MT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>23/07/2026 04:00</t>
+          <t>23/07/2026 13:15</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxNUDh6cS1zSTl3a3JGRTRnT05DYklpQjBwYnVtOERvakhweEtIU3V0NzJQeExpRkxuc3Jjai1zeUdmem1hbFRaM0l0MUlSTG1mTFhvbDYwTEVuZ2dFYUo1TU42X0pBQWxBRVZEU2FwWVU1cVFabkJ3YUttOFRhMGlEN2FKYVdBM0wxNk9yRlJPZGU0VEEwQXBJOFpzVzVNTVJSTUgzd0JhQm9MTW9kd0Q4MzI3SjdGbXhSVjdwcGRfQmNlS0czTlVDQmx4d3JoNVBOc1JIM0Z6czJEM1loY2pnYTVubmNoMFpkdTJkWGZxNVNwMnFXaVg4VEVXV3pIeHBpN05lcUVGTGI0eS1HeW9qOWJtZWVmMmNwbXFnT1ZvOFJ5MC1zWjRjTm1sWXZfZnFrNmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
+          <t>Justiça dá 3 dias para "baronesa do calcário" pagar R$ 41 milhões a advogados em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNdmUtWUVyak1ITk92eG04bmpRaEJndjJaMWJ2LVdKVXlnbHE4bXJJQXRCYWh3ck03ZDAxUElfNWxRSkI4cEZYVEJtdW10dzY0MG43cnZ2VUQwb3VLTW9aMXNFMjdOaGpwNVQ3NFl0NGp3ZEI4bWxEckhKOFFhc3h4Y1ItMEdUTHVEOXVFM1d4YXJQSEpodXd4VC1KWFZlQUp1NWo4MTlQdXhrSXhtR3ptb1Y0c1QySmM3TFRlcDdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
+          <t>Estudos sobre materiais para baterias de enxofre abrem possibilidades de otimização da tecnologia - Agência FAPESP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>22/07/2026 04:00</t>
+          <t>23/07/2026 04:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQSnVhNTZSSGVGTmx0dUtpeXBqaXFOWkw2UGQ5bll0S2EyWEVwa3dObWE1am1rc3pGNHhQdWhPdEFGNHR3Y1dTalFKU2hCa19QU21iTDdXRnF2c1ZqSUplTF9ZY282M3RWb2pOSExQbDI5cmxmbmtZdEM3bUp3azlmR2RoNWFzNjRPYXdMUTJSaG1RRy15OVd2dGpBZlU1bnBGZHJ0LVNBcGFfWlBwcVpDY2hLOFp0Sk02SjBZZ2ZWYUhZT09sRElrVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3147,34 +3147,34 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
+          <t>Escassez global de enxofre paralisa indústria de fertilizantes em Goiás e ameaça mais de 600 empregos - G1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>21/07/2026 04:00</t>
+          <t>22/07/2026 04:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQazVGaElwb0d2SFd0bjRwZE9yM2E3VEt3UzVZaV9TRUUtNGtsQ2tTS21jbVRNdXk0M3ZQd3Vhc3BtakpoN2JOZEh0UllpNFNNU1RBQVZLb0otVnN0cnRUMHNROTFVYWNzMDJ4bmNIbjhsaGhZZVFDcFllcV9oZ3dFa25HaWdtdDJWQ01jeEllTnRYYi0zMFhfMEJ3ekRuNl8xOTlUN2dWbGdkX1p3NnQ1N2FHbFRUWjJSUlNla3lTSFpFSlV6U2w3QVlrNW1OVm5HVjVtQllSaTN0d3ptWjdObnVSWUY2bDRWUGltadIB-wFBVV95cUxPallYVTZnVk1ndHB4SGlqWGVwUWxla2RjRlh3SWtrMy1hWFU4Zkk3czd0ejhral9ha3FKV3Y5Mk9YNDBmejdTVXc0eDZRdGdORDRENFRIZjdkQzhLTUl0Sl80Z1dRQm9HdGlRTGxDT19xTTV1OVZrbHlGWGV1ZUpEaEh6Z055NHZlTS1vblFhVWJuNm5VWGE2WE5KNElrdGJTbEdMSnJVWTVrMUNrNGE1NU9QaVAwRkwxYUtvMFh4Mm4wRzVPay1EdnVTUjZhV1J1Si1KSHYwYm9DcGVVdmZ1OHZNM3hicWttR21GV3BscHp6VlBpd2ljRTJZaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - CNN Brasil</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8zeWNfMmcyX1J4RksyM1E1SXhSY0E1eU9mckdDNHVJWVhJQkpUcm9vX01jS1kzVVk0eFllcWMzWU9maUpnNl9yTDRIdzZsVWdvNFo0TS1YX2JEMERGLXhLeVBIQ2x0aUZBWHZZbkptUmg1XzVxNGdB0gF8QVVfeXFMUC1GLVE4YWZkRnZJY1BmYUcyc2gtSjdoU0VFOTd5cGI1UnM5enFSZ3RNVmxVUHhJandINXNGUG5rTkpaWVJzSEZCR2FfVVJuamRfRFF3RmsyaDNYdnFUanE0cVhFZTJUc19ZU0pxbGNxMnN0LUhfc3NxaWJfRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQMGtJYlMwLWUzVkNubGpBZjAzUTNhY1lUWjN0aHd2ZGxVLUxRS0NmbDZIRXJzRFk2VnFCaUVrVFlodHdYSmJzVWZjelV1WFJhVGZOdXVzN083N2xVb24wakFhTjRWUWw5ZGRTeG5PNkt1MVo3T0VNbGxxVUliVUtvRDBaYU1zZU1Rc2VnbHFudUJMaFk4eExyNUhqV0stdXkxRFE3WC1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,29 +3196,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
+          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20/07/2026 04:00</t>
+          <t>21/07/2026 04:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8zeWNfMmcyX1J4RksyM1E1SXhSY0E1eU9mckdDNHVJWVhJQkpUcm9vX01jS1kzVVk0eFllcWMzWU9maUpnNl9yTDRIdzZsVWdvNFo0TS1YX2JEMERGLXhLeVBIQ2x0aUZBWHZZbkptUmg1XzVxNGdB0gF8QVVfeXFMUC1GLVE4YWZkRnZJY1BmYUcyc2gtSjdoU0VFOTd5cGI1UnM5enFSZ3RNVmxVUHhJandINXNGUG5rTkpaWVJzSEZCR2FfVVJuamRfRFF3RmsyaDNYdnFUanE0cVhFZTJUc19ZU0pxbGNxMnN0LUhfc3NxaWJfRA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
+          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,95 +3228,95 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
+          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>20/07/2026 03:43</t>
+          <t>20/07/2026 04:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dabac85b4fd8acb9fd4faa2408fe&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>19/07/2026 04:00</t>
+          <t>20/07/2026 03:43</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f26262804d03a352f3432f58a419&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - jmonline.com.br</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>17/07/2026 20:39</t>
+          <t>19/07/2026 04:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Sol, sombras e mistérios: eclipse à espreita - Férias no Museu - verão 2026 - Museu Nacional de História Natural e da Ciência</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>17/07/2026 04:00</t>
+          <t>17/07/2026 20:39</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPSUJWQ3J3amRKdUlCVnV5ZFdSaVc5WUFVSFBMRjN0REZURkRZLXJ5aTZrX0Uwd0JWQUF6ZE0wZWJ5dVZLalU1UDlvVjcwLVlJVmhCamFMcG9yTEdEU1MzSnBCLTFlVkxlcUo5MkNOVzY1dzdRU2NLTmRFNUpVdmU2QkdrTjBKN1BET3hNMk9zZk9SSmswN0tQQnJCdnJKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3345,44 +3345,44 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 7 - ArchDaily</t>
+          <t>Sol, sombras e mistérios: eclipse à espreita - Férias no Museu - verão 2026 - Museu Nacional de História Natural e da Ciência</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>16/07/2026 18:05</t>
+          <t>17/07/2026 04:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQmhPZldYZ3JacFd0MjRpamZDenBUVVo1V3NDM2JCdXZpVmp5TTNjS2VvSWZacTlVYlc5TjRmcHRULXlBcTIzdjR0Nk9tampZUDRxcDl4aUhSOXZHcWFmR0JxOUVNQjBJQVpFc2pZZUJXc1h5T2M4Zi1ISDBrcUNNNlR4OFFuQ1lVUWkyVlRXRGFQcy1iME8tYTJ3c3VFUTQyVXQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPSUJWQ3J3amRKdUlCVnV5ZFdSaVc5WUFVSFBMRjN0REZURkRZLXJ5aTZrX0Uwd0JWQUF6ZE0wZWJ5dVZLalU1UDlvVjcwLVlJVmhCamFMcG9yTEdEU1MzSnBCLTFlVkxlcUo5MkNOVzY1dzdRU2NLTmRFNUpVdmU2QkdrTjBKN1BET3hNMk9zZk9SSmswN0tQQnJCdnJKUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>São José: inscrições abertas para programa de transporte de calcário - PortalR3</t>
+          <t>Galeria de Limestone, Granite and Travertine - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 18:05</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQmhPZldYZ3JacFd0MjRpamZDenBUVVo1V3NDM2JCdXZpVmp5TTNjS2VvSWZacTlVYlc5TjRmcHRULXlBcTIzdjR0Nk9tampZUDRxcDl4aUhSOXZHcWFmR0JxOUVNQjBJQVpFc2pZZUJXc1h5T2M4Zi1ISDBrcUNNNlR4OFFuQ1lVUWkyVlRXRGFQcy1iME8tYTJ3c3VFUTQyVXQw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNWFFMUTRpZHJ3QjRFY3RzSkJiNHhpYnhXX2J0ZVk2Sk1XNEZ5OTFsbmFVekhtR1E5MDd2a2tJdzdFWE1CNUVpczl4cHRDQlp4aHhhbkJtRzhlajhlRU1lTUs1ZXRsdWhTdXN0Wko1em9VUzNqamFCSXBJSmxQUmRVUjJMNlhOWDJ1ZEN6RzNqNEYzdXVIZFlMRnhQNHdBZm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNWFFMUTRpZHJ3QjRFY3RzSkJiNHhpYnhXX2J0ZVk2Sk1XNEZ5OTFsbmFVekhtR1E5MDd2a2tJdzdFWE1CNUVpczl4cHRDQlp4aHhhbkJtRzhlajhlRU1lTUs1ZXRsdWhTdXN0Wko1em9VUzNqamFCSXBJSmxQUmRVUjJMNlhOWDJ1ZEN6RzNqNEYzdXVIZFlMRnhQNHdBZm8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' - UOL</t>
+          <t>São José: inscrições abertas para programa de transporte de calcário - portalr3.com.br</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>15/07/2026 04:00</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTkxyWkdnWjVncmNISHdDSW82bTRtVzQtWUtTdXhENjJpczl4anRSR2htWklCMm1VTVZ6TU5BeTZNQ2UySV9pd3JBdkNXbkZGUnBPYUNkcWttZHNOTk9Xbmo2eVBJZVZXU3ZNcVd4S013a2Y5MjB4eDdYWXcyUFlVNGY0Y2ZGckVhLUltX283Z1lsbjBtbzVkVEJlVk5XSzdXLVl1SmFla3VXRWJtUE8tY2JFTUlTYzBBcktJV2Zra01PNVhneDZwQkVNQW9TNHRyZGE5bUdrVkNLNmQxUHBV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVG5tTDNLd2owRzFfRWszRVRWNzJXUXd6S0dHdEp4Z1EtLV8xSmhzV0wyaHFKUnduUnZLRVo1UHViSkUyNi1lbU9TWUpXT3d1Q0Jwdjg3eWg4cXVWSXFFR0VZdDZpUnV4RnYwTzRIVW5ielUtdFloRnVHQnpoclVqM29TbnJYYV9lQnRLT3lVcHpxbl9OMkFPWXU2LUF1T0t2Y0I5RHA0SWNjdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3482,17 +3482,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' - UOL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>14/07/2026 04:00</t>
+          <t>15/07/2026 04:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTkxyWkdnWjVncmNISHdDSW82bTRtVzQtWUtTdXhENjJpczl4anRSR2htWklCMm1VTVZ6TU5BeTZNQ2UySV9pd3JBdkNXbkZGUnBPYUNkcWttZHNOTk9Xbmo2eVBJZVZXU3ZNcVd4S013a2Y5MjB4eDdYWXcyUFlVNGY0Y2ZGckVhLUltX283Z1lsbjBtbzVkVEJlVk5XSzdXLVl1SmFla3VXRWJtUE8tY2JFTUlTYzBBcktJV2Zra01PNVhneDZwQkVNQW9TNHRyZGE5bUdrVkNLNmQxUHBV?oc=5</t>
         </is>
       </c>
     </row>
@@ -3548,29 +3548,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Antigos asteroides podem explicar cristais de enxofre encontrados por Curiosity - Aventuras na História</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>14/07/2026 04:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPbk15WHdxRElHSUFTYmRCSDBMQ3hMN3gyY05ZNmo0SlV1ZFp1WnpsZHNFTHNtelcwWi1oemJLaFB6MHhzWnRudEZPajFLVks2aElOUGVDNVhmY3NFcndPZEUxaURaZm14d0daT0MwVEF3TVY4aGlPQ0hFNWY1dkJGSFk0RFhXMGFncEx0enk2WHU4ZTdkeFc3ZkNQRTZuT2JQOEV1TURqRjh4NjZ4Q1Y2cnQxYm1lTGZvUTBiZjh5SU83cW9pdkRCbkRyT3d1Q1IzOVVxYWN5SXM2Y3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,19 +3580,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRkZqTUNpUk1iTjlPTDZNUlVPSnlPNUgyUGp4cHk3amtEOWsxckdBTE85Z3hrT05OaDVNLXFsdUprclFWckRkU1Z6LVZwM0FObWRWTXZsNFNVODlkTTR2ZjlTc3VINFJ0MzdId3NpZHZPUVhWZTlGcHgtWGNGeEpZYmpONEExOHVsS1JfSHkxcFlibkVYUzJtSHIwQXA5ckJyTHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Transição energética pode reduzir oferta de enxofre e encarecer fertilizantes - CompreRural</t>
+          <t>Maior demanda pela ureia interrompe movimento de queda em julho - Farmnews</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMVowY3hvZ3VyTlU3QkR6YlVZMVk3Y3paOW5UbUxqMV9pSDFydmV2NzU0QmcwZGtoajR1OGtfcC1QM291bXpSc29yRVAxS2k0OXJYSDM4UHJOMVNmcWVOTUJzdzBfNWhfUUJtZlpqYTRkRHR2dGlwMmV5SF83OTl4Nnp0RHhIbVVaY1Z4WmFLYjhuVWRDZXhTYm8xcTZIQ0pwbVNXZXN4OFNfdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRkZqTUNpUk1iTjlPTDZNUlVPSnlPNUgyUGp4cHk3amtEOWsxckdBTE85Z3hrT05OaDVNLXFsdUprclFWckRkU1Z6LVZwM0FObWRWTXZsNFNVODlkTTR2ZjlTc3VINFJ0MzdId3NpZHZPUVhWZTlGcHgtWGNGeEpZYmpONEExOHVsS1JfSHkxcFlibkVYUzJtSHIwQXA5ckJyTHc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3653,66 +3653,66 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>12/07/2026 07:11</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12/07/2026 04:00</t>
+          <t>12/07/2026 07:11</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
+          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>11/07/2026 04:00</t>
+          <t>12/07/2026 04:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3724,17 +3724,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Demissão Mosaic Bahia: 500 funcionários serão demitidos - Associação Comercial e Industrial de Araçatuba</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>11/07/2026 04:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFB2bXdPVjU4Rmg1U1NwYk9rUnpnbHBSZEgxc3VxcGdabmRCMVVBRXpfMnB5eHRUUFJXT3R5Q3lEWS1YQlNGTnNmZ05OSlEweDljT2lyUkVXYnRiQ2hPdTJnZHQ5cHJUbFoxdEFEbjFn?oc=5</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
+          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Crise no enxofre leva Mosaic a hibernar unidade em Uberaba - G1</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,19 +3800,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fosfato no Brasil por restrições no fornecimento de enxofre - Canal Rural</t>
+          <t>Após tombo nos preços, ureia entra em fase de recuperação - Agrolink</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3822,19 +3822,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPeG9YelAzMGdHdy0zZUNKcE9xYUczeVNvb3cxZTVPMEkyLXhUeTNHOUhDRU5hRjdZMzdZT2JzYlNGRW1oUzBPbHRKSnV2WXVlZFRYZ0F2Y3I0RHZxUWpMM3JKMEk5SG4yLTcyTk1PcjhpZFEwYmhKekVEY25razQyeEJURU5SMmE1NGIybVozNTJ2dldsemk4elE4LXhNa3BOeUdDZzBiWi03R0FaWWhYa3ctb1pEcEZhaWgwcldUVTl0MUtoV2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOWTRuMG5FVXRzbW5lbTZ4Q182YW9hSUFwWUphaDFuZHlISXZHNEhtX1drcjdFTDZlYWpCNFNqR2l6cDlsMjRrbGxVRnViZWNIZWJ1Q0h4RzRmbzZoVVczNEpyQ0MzZ0FqeUQ3VWw3QjFCdU1qdlJrdmV5WlpSTlJHZ3ZUOFptXzhqR3hqbEV1UTZ4TzYzZExLX0hnSWZLekdacmJMbEtiME1rUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3844,19 +3844,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTUFLaTJkNWxYamJpNUFReXhFRG12WFNvQ1A5cnBlZ3VVSGFUVFhXaFhyMEZ1MmtrTzZoeEgxVFFtMTFEV3pUTUdzbWNWMGFTc2RVZ0xwWkpSbVpiQlduSUIwa21VdFhRRUdPZ3N1VVZyYmVWVVJSQkVKWVJ5Zm5ZV2RVdGJyOF9pdGVLNXVGRjhaQjlaZndwZWpIMllJYlgwZWYzdVRMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTUFLaTJkNWxYamJpNUFReXhFRG12WFNvQ1A5cnBlZ3VVSGFUVFhXaFhyMEZ1MmtrTzZoeEgxVFFtMTFEV3pUTUdzbWNWMGFTc2RVZ0xwWkpSbVpiQlduSUIwa21VdFhRRUdPZ3N1VVZyYmVWVVJSQkVKWVJ5Zm5ZV2RVdGJyOF9pdGVLNXVGRjhaQjlaZndwZWpIMllJYlgwZWYzdVRMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,17 +3878,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - jmonline.com.br</t>
+          <t>Crise no enxofre leva Mosaic a hibernar unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>09/07/2026 11:32</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN3?oc=5</t>
         </is>
       </c>
     </row>
@@ -3900,29 +3900,29 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Mosaic hiberna fábrica de fertilizantes em Uberaba por falta de enxofre - JM Online</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>09/07/2026 11:32</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQYV84dmVwc0JzTXIyZ0JpTHpucWJaaWZ6bnkzdjVDUmFJZnhVWExfb1QwckthUnRWVnFtR3k3NzZjYTE2dC1JSGJhSDJtSWpSSlQxUlo5Z2xFZkZ4RE0xYndWM1NnZ3N1ZE16N2J1NU0xNWlZc2tCbldBVjU5Skx0aDg4UjB4RXZza2YzS1ZxbXdWRnpNdmh1SXNkT0Z0SmNzV05sRGdXN1o4TThuNTRoM1FnONIBuwFBVV95cUxNaFl6YW9uc2hKWG1QYTVYMllncWZ2TXRvSENGRzJuR0RwbDk3NUR4bmJOS25IU0owc3BZcHFPN280eWV4cG5FWXF6Z3Y2YXhtenZfWndNdE1JVDBwQXI0LU4yV004dko2dVZidmo0R2FXb2w0Z3FERHYtdURrVGRVQkVYZWY0SUh4U0pLRmlETngwRnJqdDJqY05FazNXaTNNRmx0MVRqSmN2bkMwVUE5TUtPVURCaEpUSlo0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Dano ambiental em Catalão leva mineradora a fazer acordo milionário - Mais Goiás</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,19 +3954,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPSldVaDI4S0tmbkFoaXp5UUZ2WUJuNlZOM1Q2RGJEbkJ6RW9ERXk5VjAwV3p2QjkyODF6Ni0wZk0wbEJxdlZueFhKMWJHQlU0RHRlUnU2RVdmM2ZKaHAzZU5LdUNoWlNxc0pTX2JCOU1vRWljaGpyemx2SG1pUU1UbWpkeXdEd2JLTWd2SGRoRnBRZjdKR3JpcDZTb25YUllJWnFEVUZkN0hoSFladUJ1ZFdGend1YVpmd0FxNVlONkdXeU9ZaVdIdTRTWkZTNGw1dkdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -4032,51 +4032,51 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>08/07/2026 08:08</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dabfd4e74b3a8f5f8090bd6c12d0&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - Jornal de Patrocínio</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>08/07/2026 08:08</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2667e4f4e75bffc6bf9d8437f55&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil - CNN Brasil</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,19 +4130,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNcUJxWVBXU2s0ODBmWkpuckdwbG1wa0p1T1ZnRDkta25heDI5VVZZWC1hb3JfeEhzUTJHWUlJUnBScVJYSGFQWXdYRE1rU0JTYjJzQ21JODBlMlpfU3NJdy10UVo0NDRrejRvNGRBSUlZZUl5Zl8wMlV1VXROUi05VjZoZVVSckpWN2hRUHVvaE55WHM1RWJGdkE2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
+          <t>SEM ENXOFRE, MINERADORAS PARALISAM E ADUBO PODE SER VILÃO DA PRODUÇÃO DE ALIMENTOS - jornaldepatrocinio.com</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQaG84bm5LOWVYb0lLb0d2QmZTWkNQUzQ5a1pZVzZVZkMxTmFzaUhwclV6MFBxLWo0WE9hZkJINkkxWjlWMGVMZE9QYkVtXzhoRzRTYWwxdWFpRnN1N1ZQV3hBaVNNWVhpMXN0cVlRc3hGbEc0dFA3aXBaam1UUThoR3YxbUtuUUo3TXFRN2I2SkJxVnZJWTNuRlNtNEVfZzdhNnBUZlFyN0ZhM1VsVHJNR0RTemxzNEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4196,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com mineradora que garantem R$ 11 m... - Portal MPGO</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - globorural.globo.com</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,51 +4218,51 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYnZHVWpuemFFNFNOdGxsMzlYMW9XM2VzVEJMaXhsZ21iQUNnb1l0MUZselA4ZUZoMFExaUxoT0JaSmNUVGJOOEtqMnE0Zjl2VUc3aFJfUXZkRk03NHE5b2VmNmZWNVM5bTlwdXQwbUoydHZMQ2JHdUNnMU1nc1JKZmhVdHFZdHRYZ2NtR2lITkZ1eFpGMFBpU1JTZGZicWQyOFVVazU5VkNPYXBqNnAzbEdIV2g0ZHJDT0tnZ24tSVM5U011V3BGc0hkM2U3U0No?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>MPGO celebra acordos com mineradora que garantem R$ 11 m... - Portal MPGO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYnZHVWpuemFFNFNOdGxsMzlYMW9XM2VzVEJMaXhsZ21iQUNnb1l0MUZselA4ZUZoMFExaUxoT0JaSmNUVGJOOEtqMnE0Zjl2VUc3aFJfUXZkRk03NHE5b2VmNmZWNVM5bTlwdXQwbUoydHZMQ2JHdUNnMU1nc1JKZmhVdHFZdHRYZ2NtR2lITkZ1eFpGMFBpU1JTZGZicWQyOFVVazU5VkNPYXBqNnAzbEdIV2g0ZHJDT0tnZ24tSVM5U011V3BGc0hkM2U3U0No?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4274,127 +4274,127 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil | Empresas - Valor Econômico</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>02/07/2026 04:00</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>01/07/2026 04:00</t>
+          <t>02/07/2026 04:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>01/07/2026 04:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -4423,34 +4423,34 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic enfrenta pressão após Casa Branca suspender tarifas sobre Marrocos - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQU1JyUHczQlZyM01aNnp4dHJSLWNUNHRvU3FfY0ZYWHRNUkVpRkM1V3VOcVZhME1Kb2Q1a0ZwUXNzUDNDeDBKSUhGdVoxOUxCUjZkb2pKOFI5OC1aUGdQbVVRSGY4RjRfZVJZV0xxSXd0U3o1VmtGeHAxYl94eHVQOFlMQm5nRk1qX0g3MW5YUWdnV0JlTGVvZy1ibDI1OFhoVmt0RmZiaFRRTDBLMW1lNl8tM1U0LVVRVV9ESURZcGhuMThaeWpFcDQ1blR0ZzA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - brasilagro.com.br</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,19 +4460,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPLXdYV05kWHpEMFJ2bVVHc19qdmd1MGJOTlRmTFdwUDJxVmZDZXBHa2J0cVZzTmloeGVacHUtMUVDVHdTeHFOOFNaY1NoVUotdk00V1BnbjlCaFdvN3lxU25CMUlkWWh5OWd0MUJ4NE5TYktzdVg4OGxrWnV5WEg0Sy02QWRqUThJWDZ0a0pNRG5xa0FQN3RLcVNrcDZ0UzVxdGFYc0ZNSzFqTkpk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,19 +4482,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - navegantes.sc.gov.br</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Programa Terra Boa 2026 garante distribuição gratuita de calcário para fortalecer a agricultura em Navegantes - Prefeitura de Navegantes -</t>
+          <t>Ureia, MAP e potássio registram queda no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,19 +4526,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQYlpYdmcxN2o2cDRhamVVcW5PQjNBTDdLd05XZDIzUDJrd0ZuOTVwUHg1SUlqb2pXamZGMXZmODZjRTlSOU11YnpINUk1bnhkUjhrWjFZX1RlQWUxVDV2UEIzbU83N09lWTBadmlEdnJVcm1uZ2d3a1pGeFFLcGlGYndtLUJHWVJjSS1Bc0UwRHdpNlJMbzJJTjREVm5ocDhHay16VTdrbVZ1NWhzb0dPOHFkWTAza25ENVZSSDFDdk94dnFYZGZMcVFNNDktekVwMjhvQVN2Zk9UVHppem5vcFl2SEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQckZkR0twcU1KM1hzRlBoYnlKaEVXbERoOEJfSk5zLVJHSlFXc2pVS0hqRlQ0djV0b2o5NDY0azg3REJLbnBlaVJ2VWZ6Y2lzaVF4STlrWlh4TDcteXBGN29xWDdTc0hmU1pROF9UZ2d4UlR0bGFtNjd6UzZqakxCeGlHTEZRTUVReHllcG5NOFV4OFRXZ05YZTIySlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil recebe inscrições para o Edital Seminário de Parceria 2026 - Brasil Mineral</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4548,19 +4548,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNN0NKNG1LSlpXM21pMXBPY3NuV05oa1BETlBObTdjMDBOYkpVQ2RSc0d3V2VoY0lyUnpjLVhoM25SYlNJZ2ltZkpNY2VSMnlXR2E0ZkI0aGdNSXl4T1hCUTl0YVVyYU4zeWxMaVVwSS1QcGNBRTlIN1p0eVUwVVd1dUVUMXg3QWJRZmdpeEl0TW5MYWcyRHZLbE1rQkg2QWFBZldZZ1BmaUhNTGl6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>COMUNIDADES | CMOC Brasil recebe inscrições para o Edital Seminário de Parceria 2026 - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNN0NKNG1LSlpXM21pMXBPY3NuV05oa1BETlBObTdjMDBOYkpVQ2RSc0d3V2VoY0lyUnpjLVhoM25SYlNJZ2ltZkpNY2VSMnlXR2E0ZkI0aGdNSXl4T1hCUTl0YVVyYU4zeWxMaVVwSS1QcGNBRTlIN1p0eVUwVVd1dUVUMXg3QWJRZmdpeEl0TW5MYWcyRHZLbE1rQkg2QWFBZldZZ1BmaUhNTGl6?oc=5</t>
         </is>
       </c>
     </row>
@@ -4582,51 +4582,51 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - primeirapagina.com.br</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPLXdYV05kWHpEMFJ2bVVHc19qdmd1MGJOTlRmTFdwUDJxVmZDZXBHa2J0cVZzTmloeGVacHUtMUVDVHdTeHFOOFNaY1NoVUotdk00V1BnbjlCaFdvN3lxU25CMUlkWWh5OWd0MUJ4NE5TYktzdVg4OGxrWnV5WEg0Sy02QWRqUThJWDZ0a0pNRG5xa0FQN3RLcVNrcDZ0UzVxdGFYc0ZNSzFqTkpk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,29 +4680,29 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4731,22 +4731,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - globorural.globo.com</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -4775,34 +4775,34 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,29 +4834,29 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - serranewsrj.com.br</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbW80OVNNUDM3c3ZHckJOajRBMkhlUTVEaGV4a3FLejNoellXeWwxY3JaZ3ZYaUVSWmhacHZHN2U1NEE5Ny1UcWdsbWRHdW8tS3daRUE2ZnkzTTM3X1BHc2wxcGFrRWpyZ3FTMGI0WDNsNzA3STh0MU9udXM0ZE5qdjBWbFhmVlk4RkNXTmtIaERXU0NweV9oZzBGRU9lTWZLdE5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4885,154 +4885,154 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbW80OVNNUDM3c3ZHckJOajRBMkhlUTVEaGV4a3FLejNoellXeWwxY3JaZ3ZYaUVSWmhacHZHN2U1NEE5Ny1UcWdsbWRHdW8tS3daRUE2ZnkzTTM3X1BHc2wxcGFrRWpyZ3FTMGI0WDNsNzA3STh0MU9udXM0ZE5qdjBWbFhmVlk4RkNXTmtIaERXU0NweV9oZzBGRU9lTWZLdE5n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Prefeituras têm até 30 de junho para retirar agrosilício - AMM | Associação Mineira de Municípios</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNa2hNNldIOFhaOUVZS1JtcTJwUWRXT1dkU2F6NWwxR29SUmJCa2d2dUxNdnROS2RfQTFsSml2TUlaX3VZTXZzYWJCWTkyZlJuWVhnM2JqS3RiVGRwb21xbVR6dmlHQWdJM1dFdkgyUXBrR2NOVFZwUVgtcUdFMWhNa2ZleDZyV1FsOERLZElmb0I5amdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Shuumatsu no Harem tem data de estreia confirmada - Anime United</t>
+          <t>Prefeituras têm até 30 de junho para retirar agrosilício - AMM | Associação Mineira de Municípios</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>17/06/2026 22:54</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPbVJGa0dnX2FWNmUtSFhFSkRFd2tQWlozWk9wa3B6dm9rVGMyaTlGWm44U01mdGpEdFA2YmU2THQ2S0F3VUZIUlh6R2RlZUhpQnRQQnVvRXJ3X2g0SlBuNXlsS014WXdad083TFNSSmVWZ2VwTnRGcTMxUUVJZFJwVGY5MGdqeUprTDlUYTE0X3NmblBy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNa2hNNldIOFhaOUVZS1JtcTJwUWRXT1dkU2F6NWwxR29SUmJCa2d2dUxNdnROS2RfQTFsSml2TUlaX3VZTXZzYWJCWTkyZlJuWVhnM2JqS3RiVGRwb21xbVR6dmlHQWdJM1dFdkgyUXBrR2NOVFZwUVgtcUdFMWhNa2ZleDZyV1FsOERLZElmb0I5amdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Shuumatsu no Harem tem data de estreia confirmada - Anime United</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>17/06/2026 22:54</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPbVJGa0dnX2FWNmUtSFhFSkRFd2tQWlozWk9wa3B6dm9rVGMyaTlGWm44U01mdGpEdFA2YmU2THQ2S0F3VUZIUlh6R2RlZUhpQnRQQnVvRXJ3X2g0SlBuNXlsS014WXdad083TFNSSmVWZ2VwTnRGcTMxUUVJZFJwVGY5MGdqeUprTDlUYTE0X3NmblBy?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5066,29 +5066,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,19 +5098,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Calcário ganha espaço no campo após alta dos fertilizantes e pode beneficiar produtores do Nordeste - Paraíba Business</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdHRzWEdaMFMwRjhjQ2w2Z2I0VkNic0xRT2w5dTVkUVpUOWRVRkxFRG1sa3Yxbk80cGlrcWhiVExVVG15M3Npb2FyUU1tekhiSjZiOHV6ZGRqR2NOVzN3MTN1cUQ2SEZqTWI2Y3VGTEM3dVI2dnBHOU5pZ1Q5MVVKX2dueHF1RkoyTVRnamExN1ktcmoybUhtT2Q0WmZqYUZYb2NGaXNMUUtjWXFMdzFqYzhKTWFmZWpvb2YwUlN2TVRValViS1E1RnJtZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5149,66 +5149,66 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>O ‘apagão’ da ureia - VEJA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>O ‘apagão’ da ureia - VEJA</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,51 +5296,51 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - globorural.globo.com</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - serranewsrj.com.br</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,19 +5384,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Empresas ampliam vagas e buscam talentos - Terra</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQVlV3clMtbWtWX1RVVWlfSUpxbm1YaW1oNk9MR3h1WDMyaWExaTNQZUVzTHR6TWdxOFJkVnVvTGI5cnVkRGpTeHJkV1hKNG5TZW52aGZlREEyUDZFTUJmcGM5TjJSTVhnN0c2dGFBZDlVcm9FelE5LW02VVVJSEZaU3JHeWxNaUNaVHFGYjNiZ0ozT2lTbVpORUF2UFhudWxENDI1QnJ6ekNKSmtBTFozckxkNXlCaHVoRjFSQg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,17 +5418,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5440,95 +5440,95 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>02/06/2026 12:15</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>02/06/2026 12:15</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - serranewsrj.com.br</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - stonex.com</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,19 +5582,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - stonex.com</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,19 +5626,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário mais nutritivo resistente à umidade e ao vento - Paraná Central</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,73 +5736,73 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdk56ZUFYa2pGdWtqdzRMRjJNTmRzNExlY3pPSnpmZjVsQ2ZCT3pJeDl1UGk1dzR1bmRJYjB0akk5alp1YW83empGWHY2TVhzWXdfRHlrenRSRFNHUmx5dS1pLW83YXhWX3ZsSldMM3luSXNScEJRUUpNdTVBM3hTV2tFdDdnRkZvTkowU3IxbU1ZWTBiNVRKSXRhWi05QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>29/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>29/05/2026 04:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPWmY3TXBIbWxobnFjUi1mTUozS2xCbTlaSGxKX2o0QTExdWszWk5USkR4ZVk0Zk5vcTIxSm9HZDRzazlGVjBDLVE4a2NTTnQ4eHpQM3cyNTFDVDd1aGs0cFhxUVBmbXlaUTNLMjljT0FSRWlMRm1iVkxMYk1uc2Nvd0JZencteGFkLXNFSWxySlhTNkdpemo2Y2N4ZlFOclJPMkNLUDdGU2FrYTJsRjIzdTE3RWVQUnhGbXJpVkJhcWhjclZJaWdXM2dueTFYRjNfMWE5WjBEWEFxUdIB3wFBVV95cUxOdGxrd3ZlRXQ3X0k0Rkx5VDk0OW5yQ0FyZ1A1QW5wTGhXZDA3blVtaVdobkM5YVFBcEhsUUlYRGYwVlVodlF1UmxsbVZaY0c2Z2lScV9hWnlOdlpZYzZDNXVLWWdiU0FvRExxZlQzQ2d3N3lTbk9tY3pXZEpJOWtZaDhOYVhVOXFFWExTVkYyMU5jUnk3VURmS0dMazRJUERGYS1BS2p5MFo5bXg3eFlPcVJtZ1NMQjBYRDFrWmRRbnpRdWlMU0VmaHI3T2tHUGp2b3I3bFZZYk9oWWhDX3pN?oc=5</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,19 +5868,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPMWUyNm9mWU9veFpjQzM1YmNFWkdJNGZ3OEtIZXQ2dERuaTRoNnc4ZlJjNG51T2Z5SXJiNlF2UmFmdzdsNTlzRmJXVmRMS3JGLXN4TEhOWFpnal9iNUtLY0hxaW8xRTAxZV95czZwa0Zhdk93N0RFbEdGX0p0STZtX3d5U0Z5QmxhTGZaeEJJejRRRThqWjltdWNQcUY1cU1NQmFuTENIclV4U09NSXBJTGQ1SEZOeU9DWUszMElldEctazNxZHZYakwxVW1XQ1B6YTJ4eE1OMzJVZXFsalZiaHR6UEdfeEJTeXdDaGNUSXBTSlQwbjNHaVA0cmJGTUJDN1FqQjR3RTB5UVdlaHZ1X0FZZDUwVE5hc0VwM09YZDNzMTBOOFNQVmNXUnNEUWRiM2R6ZXhNNHdQSzR2MzVHZEdEaFZFV2lvam9rWkNwWGQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Grand Prix SENAI 2026 conecta estudantes e grandes indústrias em maratona nacional de inovação - Agência de Notícias da Indústria</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNazFuZVlIdUdWeE55Y1hySHEyQnpEazJfaU1ING1DVlNVQ21nUWNVb2pBTE43ZlVwc0NkWGdnbnFicm9zVkwyei1aWVpkSk5pdDNZS3ZtV21EeHRXZlppU3ZHT21VWmhiYTlsc1g4WENhWVNTdWFLc3g0c0FHbGNpaFcyYmo1bmluVFk2ZTBPdy01LVhyZ0cyb1JuYUxlNHVhYXY3YTFPeDdQd29paDAzWHF2TE9wTmVfb0Rrak9rRk80dm9IdXJDYU9XLXhxdi1JeEJWaG5jV2x1RjJmZktqeXU0dXNiTHJXTHpn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Anvisa recolhe lote de coco ralado da Qualicoco por excesso de enxofre - UOL Notícias</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPMWUyNm9mWU9veFpjQzM1YmNFWkdJNGZ3OEtIZXQ2dERuaTRoNnc4ZlJjNG51T2Z5SXJiNlF2UmFmdzdsNTlzRmJXVmRMS3JGLXN4TEhOWFpnal9iNUtLY0hxaW8xRTAxZV95czZwa0Zhdk93N0RFbEdGX0p0STZtX3d5U0Z5QmxhTGZaeEJJejRRRThqWjltdWNQcUY1cU1NQmFuTENIclV4U09NSXBJTGQ1SEZOeU9DWUszMElldEctazNxZHZYakwxVW1XQ1B6YTJ4eE1OMzJVZXFsalZiaHR6UEdfeEJTeXdDaGNUSXBTSlQwbjNHaVA0cmJGTUJDN1FqQjR3RTB5UVdlaHZ1X0FZZDUwVE5hc0VwM09YZDNzMTBOOFNQVmNXUnNEUWRiM2R6ZXhNNHdQSzR2MzVHZEdEaFZFV2lvam9rWkNwWGQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6000,41 +6000,41 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - saude.abril.com.br</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,19 +6044,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT2VhbXd2MmM2OHRBTm5rMDRFUTNaZE1Ed05jWlFibnJwSlNGaDFqOEdZRGk5Ty1XZlZWaFBhLXhiZHRxTkxZMkhvSERqRGVKeHUyMkhtRk1JOHV2MjZIc21RaWJvWVlYS05sM0NORzBZeGFKMEZ0T3lTOTZrdExVVmNnRHBPbS11eWswa01raW9BVm5jUThnRjgtTjlIN1g2allad3VnYl9xZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,29 +6066,29 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOT2VhbXd2MmM2OHRBTm5rMDRFUTNaZE1Ed05jWlFibnJwSlNGaDFqOEdZRGk5Ty1XZlZWaFBhLXhiZHRxTkxZMkhvSERqRGVKeHUyMkhtRk1JOHV2MjZIc21RaWJvWVlYS05sM0NORzBZeGFKMEZ0T3lTOTZrdExVVmNnRHBPbS11eWswa01raW9BVm5jUThnRjgtTjlIN1g2allad3VnYl9xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - stonex.com</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,63 +6198,63 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - primeirapagina.com.br</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - stonex.com</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,19 +6264,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Terra</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,19 +6286,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQblBlQWhYdmdqY2MyeGdKeVd1SnZySzcwSWpoRDlKRVNhZ1JaZjBRUUI5cXE3S284eXVYZVRDTHl4RkxneEFIdE1mbVkzWlQtZ0gxcHJnclVQTEhSZkRMLXQ2d3RvaHBwb3hKd0VwMGtRcjNRcmJaUC1FTmF4Z0FkYjEwSXR6eWE0Rmo3cHpSbkh0T3VuRGZDMVFIVjFaWGd6Yl9kUy1hVGdSWXJQYlljV1lrUlNPZS1rN2RKZFNld3Z3VlNzaS1MY1AzLTE1MU9ON2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,19 +6308,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,41 +6330,41 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,41 +6374,41 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQemZaZVVoOVdqclY1NnlPVkRYaE9kcEtNMWFfNUhQcElqdlhXSFFjQ0ZzNmVQOXZNQWdJZ2xkWHJqc2VwMnNoUGVBektPWE5VcDJfWE04Y29EdkJscm9WemNWZkFoaWtCNDVzQWFBbmJDclJ0R1F6NVB1YWpRMm4yVGVDcElrR20xUW16VGsySmFiSFJqdkhtUmtBRkxsLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQemZaZVVoOVdqclY1NnlPVkRYaE9kcEtNMWFfNUhQcElqdlhXSFFjQ0ZzNmVQOXZNQWdJZ2xkWHJqc2VwMnNoUGVBektPWE5VcDJfWE04Y29EdkJscm9WemNWZkFoaWtCNDVzQWFBbmJDclJ0R1F6NVB1YWpRMm4yVGVDcElrR20xUW16VGsySmFiSFJqdkhtUmtBRkxsLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6506,41 +6506,41 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6550,19 +6550,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6572,63 +6572,63 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBHa202S0l0T0JzM296SVZMU18yeENtQzl5VV96M1BNSll0UVZHRzNncWhVNHZlR2hhNHZTVjk3XzI2NFRFdko4ZlZBYy1pOWV1MDh1bm1WMkY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>18/05/2026 14:18</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBHa202S0l0T0JzM296SVZMU18yeENtQzl5VV96M1BNSll0UVZHRzNncWhVNHZlR2hhNHZTVjk3XzI2NFRFdko4ZlZBYy1pOWV1MDh1bm1WMkY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>18/05/2026 14:18</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - stonex.com</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,29 +6638,29 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
+          <t>Ureia recua 14% em 4 semanas com demanda global enfraquecida - stonex.com</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>17/05/2026 18:07</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOZ0Z5WTFwOXBJc0NMYzFPcGRCWmRzVU1sc3ViLXNJVmJVelhDZE5jNkxZRGJSLU8zb3pUYWVpYWxJVDdLOGpzU0pzSWd5VExmeGF0SVhJLTZsMExmN194V3dONHF5cmdrVGE4WlRETVB4RklMbllPQnRlODctRE1FTlFKRHcyU1h0Tkw2WVYzWTJzN2lDcTNtcEdFdFZGLWgyT1FvdUZOekQzUTNINlAzMjI0TFQtRGtLd3FtQi10N2JUVUc5cGZxNXZSMnZHNUlQd3NVOFhuM0ZzcnF0ZDVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>17/05/2026 18:07</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6733,44 +6733,44 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Mais de 330 bairros da Grande BH podem ficar sem água após manutenção emergencial da Copasa - Impactto News</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcGZFYkFrb1pzVmR0T0t5dzRQclZjZVE2c2E3WnUtX0R6LXM1c1JJcm5taGRqMmpPZ1JTcmwzVk1zVTVFZ3dHb2NnbmtMWGxIbXF6UHYxQVJwcVByYi1xbVZXMVZ6SUpFd29JQml0Ykh2WEdPRXd1RHl2YWpQNzJvWkxjOEVTY1daa2pxSm1yS0o3SHhLZmRuNGkzWVFFWDhRTUw0NTlHNVdrTzJGUmZ0SW5DMkxsSWk4QXFIaDNWSmR6bjNiMWNzUi10OW45V1BS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6799,34 +6799,34 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Mais de 330 bairros da Grande BH podem ficar sem água após manutenção emergencial da Copasa - Impactto News</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPcGZFYkFrb1pzVmR0T0t5dzRQclZjZVE2c2E3WnUtX0R6LXM1c1JJcm5taGRqMmpPZ1JTcmwzVk1zVTVFZ3dHb2NnbmtMWGxIbXF6UHYxQVJwcVByYi1xbVZXMVZ6SUpFd29JQml0Ykh2WEdPRXd1RHl2YWpQNzJvWkxjOEVTY1daa2pxSm1yS0o3SHhLZmRuNGkzWVFFWDhRTUw0NTlHNVdrTzJGUmZ0SW5DMkxsSWk4QXFIaDNWSmR6bjNiMWNzUi10OW45V1BS?oc=5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - jmonline.com.br</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,51 +6858,51 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Secultur</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYWdzbE83cTRBT0tNU3R4aTVGY1d0VzVDRW1DOWxzcXNZLXg0NnJVTTZkeWc5LUloOG42VHQ1aENxNXdvUHdvVl80MFNMTElfeTNLbi01aU56RnlRV0hOUmF6eGNXSjJTbk52U2hDRTk0c0VFMDEtNGsxNUtfNHRJbGk5VDZhVUV5OWg3djA1OHpjQVVCcWJWeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,19 +6924,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,19 +6968,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Notícias de Arcos - Jornal Correio Centro Oeste Arcos</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,19 +6990,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPYWdzbE83cTRBT0tNU3R4aTVGY1d0VzVDRW1DOWxzcXNZLXg0NnJVTTZkeWc5LUloOG42VHQ1aENxNXdvUHdvVl80MFNMTElfeTNLbi01aU56RnlRV0hOUmF6eGNXSjJTbk52U2hDRTk0c0VFMDEtNGsxNUtfNHRJbGk5VDZhVUV5OWg3djA1OHpjQVVCcWJWeA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Notícias de Arcos - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,51 +7034,51 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7107,56 +7107,56 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,19 +7166,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ureia inicia queda global após disparada dos preços - stonex.com</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,19 +7276,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7320,19 +7320,19 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Preços da ureia cedem após dois meses em alta - globorural.globo.com</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7342,19 +7342,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7376,17 +7376,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Ureia inicia queda global após disparada dos preços - stonex.com</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNUMtNEYyR21sTTRYZ2Z5UE9XNGJfMmJvYkJaMjc5em5ZVmx5U3hINmg1MVpHZUdHS2hqbzVnOWN2T0tKV0dmeGFvamdFazhzQ0I3RU9Oa2xEbXBGRDNlUHFfemNTLXpOWUpLeVNCMkZjeWxuS3lDdWE0bEpNLTdBNTRzRDQ0QThrWE9sNDdDdW10ZkZfVFVBUE5zb2E5M29EbkdvLUdSOXRlTTEyZkJ2T0l1aw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7398,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,19 +7452,19 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7552,39 +7552,39 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7613,34 +7613,34 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7650,19 +7650,19 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7672,19 +7672,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7782,19 +7782,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Vereador fiscaliza poda, limpeza e iluminação na rua do Enxofre - camarapiracicaba.sp.gov.br</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMmlXendqSU95eU95LVd3eFVTZ0lmZTJsZXlmeWpTYnhzcnJMZ0ZMQzdIaGRrOWJGLTY1MlZvT3Y1cURXX0Flb1Y3M1gzR0pKOFpuOG5EbGs2WmZkWTdZQVRKMFFrMmRZeEJIUk81dkRNQm8tX1dkSlZRZ2VQbzJ6enpYb1dTd1NwaXZHdG9FM3JFTWVURG9CRVIxY3hObVNleHJKZ2U4Z1hWRWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,19 +8002,19 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,19 +8024,19 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,19 +8200,19 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - Brasil Mineral</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxONTFwXzhWOXJpNGJOcGg0VkE3Q1FBTF96azlkcXJsemtkNm10NG1LVzk2bHJOeE0xaVZrZmdIbFNRMC0wZFBDTEdXa2VSVTJyUTA2LV9RNkNRVWx5NlN0N2RQMVpNcFZWZkt0MXlHSTVBSlUxeEhLYXV3eElfd1hYNVZSTzdfUGNEb1JVbGM1b3dkZXl3Rml2aFhraVMxektyWjhOM0xXQWg3bDhPc2Vrc3hCaW9TVU5qWVZUVE00cXM5NjgyWHE5dWI2cWRPQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - globorural.globo.com</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic paralisa operações de fosfatados em Minas Gerais e planeja venda de ativos - agrofy.com.br</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,19 +8354,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOOUNzOVZUUkhFOWxIU2E0ZFcwUGs1aWlvYVAzOEdtSkt5cFZVY1lkRjdTOWRObDhEMXNwYm85RjFnUFNXb3lYRkFWdVhxUjVLRUJhNS1FZ1pkcWpMUDFXZ1hWVTZ2anMyVGF6V1Z4RWk4RmN0YkRaRGpzMTRybDdWcXR5OGxfMnVOX2h5MWxVZS1CT2pvSExaSHRSUGZHQ1cwejFZVHFzOFFYUDFJanNXcDR5T01xOHcy?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>FERTILIZANTES | Mosaic anuncia paralisação das instalações de Araxá e Patrocínio e busca vender ativos de Araxá - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxONTFwXzhWOXJpNGJOcGg0VkE3Q1FBTF96azlkcXJsemtkNm10NG1LVzk2bHJOeE0xaVZrZmdIbFNRMC0wZFBDTEdXa2VSVTJyUTA2LV9RNkNRVWx5NlN0N2RQMVpNcFZWZkt0MXlHSTVBSlUxeEhLYXV3eElfd1hYNVZSTzdfUGNEb1JVbGM1b3dkZXl3Rml2aFhraVMxektyWjhOM0xXQWg3bDhPc2Vrc3hCaW9TVU5qWVZUVE00cXM5NjgyWHE5dWI2cWRPQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações de fosfatados em Minas Gerais e planeja venda de ativos - agrofy.com.br</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOOUNzOVZUUkhFOWxIU2E0ZFcwUGs1aWlvYVAzOEdtSkt5cFZVY1lkRjdTOWRObDhEMXNwYm85RjFnUFNXb3lYRkFWdVhxUjVLRUJhNS1FZ1pkcWpMUDFXZ1hWVTZ2anMyVGF6V1Z4RWk4RmN0YkRaRGpzMTRybDdWcXR5OGxfMnVOX2h5MWxVZS1CT2pvSExaSHRSUGZHQ1cwejFZVHFzOFFYUDFJanNXcDR5T01xOHcy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,19 +8508,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - bemparana.com.br</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço futuro da ureia para abril sobe quase 65% em março e segue nas máximas! - Farmnews</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbUlXekJnQ0c5T19mQTBMeDBVcnpuS3ZYTGtGdEN6eTFUcmEtMFhsN05GdTVqaERaUy0yelVxaW5HeWFsOHp5aGRyMzhWQ1ZDZWttbjN4OUpkS0xWT1ExczBYeWI3VHY3emJTTG5IekhsM3BiLXRZc29VR2hybFdmSll2TlR3ZjJVSUtKMjA4RTliNjBmOGd2cnZnc2tGbHMyZXpZMUVBUmN2RjBzVmlwV3p3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para abril sobe quase 65% em março e segue nas máximas! - Farmnews</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQbUlXekJnQ0c5T19mQTBMeDBVcnpuS3ZYTGtGdEN6eTFUcmEtMFhsN05GdTVqaERaUy0yelVxaW5HeWFsOHp5aGRyMzhWQ1ZDZWttbjN4OUpkS0xWT1ExczBYeWI3VHY3emJTTG5IekhsM3BiLXRZc29VR2hybFdmSll2TlR3ZjJVSUtKMjA4RTliNjBmOGd2cnZnc2tGbHMyZXpZMUVBUmN2RjBzVmlwV3p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8662,19 +8662,19 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8684,19 +8684,19 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,19 +8772,19 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,19 +8794,19 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - globorural.globo.com</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8845,12 +8845,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,19 +8860,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
+          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,19 +8882,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,19 +8904,19 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8926,19 +8926,19 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Cobertura linear ganha novo andar e vira duplex de 400 m² no Rio - Casa Cor</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado Federal</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNM3ZSSWI2SU5GM19FMFIza3l0dEFFUXZjUUZzaDBBaVRWYWg2MWtvenB1S3dOUG1qRjVod0lTR1JReENZelpid0tYY1dyQk9kWl9HVUlFQTA0dVBpUlluS3J2b0NkVjFmZGs0OXJ5azJEWHRSaFNwckxWeDJLLVpXMjdCVFhOQ3dMX1Fia256eVNYcVB5Y2pXRmo0aEZ0c0dkdy16YmhkVmcxb2FyQkVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9131,12 +9131,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,19 +9146,19 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - ocp.news</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9212,19 +9212,19 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9234,19 +9234,19 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - globorural.globo.com</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9256,19 +9256,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - globorural.globo.com</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9388,19 +9388,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9410,19 +9410,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9432,19 +9432,19 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9608,19 +9608,19 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - gazetadopovo.com.br</t>
+          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9630,19 +9630,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado Federal</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9652,19 +9652,19 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9762,19 +9762,19 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fdiariodocomercio.com.br%2fagronegocio%2fparceria-entre-governo-minas-harsco-completa-dois-anos%2f&amp;c=8635377947739043430&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9960,19 +9960,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUDF3STREdi1LcFZocWtheHhmQXlnMl9fSHdLZkUtWWJGNWZtUE9XWmJfN1lWNmc2SnRZeHliSUJ3WHJUN1o4MWZrSkFxZHJmRkE3ZUpuaDVIX1lzZUJuNkQ2eTJXNWh0bmtfWWRnUHdlV2VIQTN4dG5HZDY0U3dPLVdVVFR1UUltX3laMGpHLUZpbkk5OG82WnRwQnROY1BLVktrVEdFeGg3UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
+          <t>CBPM reage à venda indevida de operação da Equinox Gold na Bahia - Bahia Notícias</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -9982,19 +9982,19 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOb0dyblk0a1dSem1LdjFxOThPbld2Snp3VEd3RjU3WWVLRVJwc18wU2FLVUZ6U0tZMUlJbDNjb1FycDRNWFdMemF0T0ZvUGNZYl9CeGlZeWpHYWZRakJuMHlzSWVVeUk0dFQ5MUlnZk1vZHRlLTR3d0U5Y3M1OVpTUkFYNlJmOV9ka2NDS2pLMGtqN21mcE9BUlR1dDAwNHdhdzhQM05IOWlKQjNoZmZ1b3V3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado Federal</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNUDF3STREdi1LcFZocWtheHhmQXlnMl9fSHdLZkUtWWJGNWZtUE9XWmJfN1lWNmc2SnRZeHliSUJ3WHJUN1o4MWZrSkFxZHJmRkE3ZUpuaDVIX1lzZUJuNkQ2eTJXNWh0bmtfWWRnUHdlV2VIQTN4dG5HZDY0U3dPLVdVVFR1UUltX3laMGpHLUZpbkk5OG82WnRwQnROY1BLVktrVEdFeGg3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
+          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - The AgriBiz</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
+          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - The AgriBiz</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,19 +10488,19 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10642,19 +10642,19 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQklGdHRzc09idVgwaFdKZHpPV0RTUldGTkt5NE55VjQ4MV9nQ1M2YnFDTmlqbzRwMExZTkU4dFd5YUJCc19pYXR3SmE4azlqVUxORHBPem1qN1ZUQmk5dDBjTW9QZ3lrZE1Cazk0QnBMT2tCbVRzOElWckxrcndfZHN6SmhtMTRxZ3N2eEZYaXFEelptLUdkcUo2aEJpZ1lVMkxMWXRzeGJvNGtXVGtzd3FZM2FwNEExY1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10664,19 +10664,19 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPQklGdHRzc09idVgwaFdKZHpPV0RTUldGTkt5NE55VjQ4MV9nQ1M2YnFDTmlqbzRwMExZTkU4dFd5YUJCc19pYXR3SmE4azlqVUxORHBPem1qN1ZUQmk5dDBjTW9QZ3lrZE1Cazk0QnBMT2tCbVRzOElWckxrcndfZHN6SmhtMTRxZ3N2eEZYaXFEelptLUdkcUo2aEJpZ1lVMkxMWXRzeGJvNGtXVGtzd3FZM2FwNEExY1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10708,19 +10708,19 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
+          <t>FOSFATADOS | Mosaic vai paralisar produção de SSP no Brasil - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,19 +10730,19 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOUWJBdTFfTVFMWEt0c1FadWR5eDZVTXdRSm9RWTNQalhhM1kxd2xSRG1kOTE3Z1RERGhFR3FnWm1zMGRMS1p0dTViNk0yWWg4VWhQSWdfeVdab1o4U09CTlota1FGcWp6d3pqZ3BiS2dQWk8tbkhzMXgycEpMRVVuQUh0WnV6MDNod1c1YQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - jn.pt</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,19 +10752,19 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>FOSFATADOS | Mosaic vai paralisar produção de SSP no Brasil - Brasil Mineral</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10774,19 +10774,19 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOUWJBdTFfTVFMWEt0c1FadWR5eDZVTXdRSm9RWTNQalhhM1kxd2xSRG1kOTE3Z1RERGhFR3FnWm1zMGRMS1p0dTViNk0yWWg4VWhQSWdfeVdab1o4U09CTlota1FGcWp6d3pqZ3BiS2dQWk8tbkhzMXgycEpMRVVuQUh0WnV6MDNod1c1YQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,19 +10796,19 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - globorural.globo.com</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10818,19 +10818,19 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10840,19 +10840,19 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - china2brazil.com.br</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbGh4T3dJSy1zbzZZbXJaN01fM2FDeTgzVXFBWFZlZjFVbnRFaTNBdUVpcHJYWXU2MFpJYTV1TmRoSjByMm8wSlVpcnkzdjZIVko0UkdWeVQzSUdKdWNCQnAtTXdDcGRGUVlRTnFfR25WS1dzX19xUUp0QW1LUmxDVjBRanVrQ2taTFBtZkZWUjJkSWRBaUVvb1h4aXVJWGRPZ193VUt0UnFlVDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNbGh4T3dJSy1zbzZZbXJaN01fM2FDeTgzVXFBWFZlZjFVbnRFaTNBdUVpcHJYWXU2MFpJYTV1TmRoSjByMm8wSlVpcnkzdjZIVko0UkdWeVQzSUdKdWNCQnAtTXdDcGRGUVlRTnFfR25WS1dzX19xUUp0QW1LUmxDVjBRanVrQ2taTFBtZkZWUjJkSWRBaUVvb1h4aXVJWGRPZ193VUt0UnFlVDQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - Brasil Mineral</t>
+          <t>SUSTENTABILIDADE | CMOC Brasil é reconhecida pelo Selo ODS Brasil 2025 - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - globorural.globo.com</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
+          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura Municipal de Itararé</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - itarare.sp.gov.br</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11507,22 +11507,22 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Mosaic divulga resultados do terceiro trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>05/11/2025 05:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNZUFJNW5SN2Z5Y0M0cDIwaVVfamdqb1FaSTYyT25JQmpFTDB2eE5nR011emxHVDJubWNCN0Mzd0VoMHR3MWhMbndXYU5GbzN3b3JwcTZOQjVQMzdHVUR1bDZ0ak9rczQwOUUtdUhaNDZCaEJwdnZLV0pSMko5M2pLSE1FNVc0UUhKME9OWWRXOE1HeThuMzZPZGczWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11551,132 +11551,132 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dabac85b4fd8acb9fd4faa2408fe&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f26262804d03a352f3432f58a419&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para o Programa Jovem Aprendiz 2026 em Arcos - Arcos Notícias</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>03/10/2025 08:14</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORnRTMVVoUTk0Q1JIRy1YYVFTWU9VWDlZa2hjS2g3bzFQNkY3aHVLQ1d3eVdoZHJIeENMV3AybG1JaTBuVGFNYjBGS0xlSGowQkEtVkt6X216WHJQNzdKcHR6YlBuQTNXUHJhWFJSVUlfZlZFYWhkRl9MaWZWMWNibi1OSUFjUDA3YWp6NWtINnYyU1FUVmdfVUxXLTdHSTR6cGNUaE1Ra0FyeThvdExFSkNaTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -11688,171 +11688,171 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Lhoist abre inscrições para o Programa Jovem Aprendiz 2026 em Arcos - Arcos Notícias</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>03/10/2025 08:14</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORnRTMVVoUTk0Q1JIRy1YYVFTWU9VWDlZa2hjS2g3bzFQNkY3aHVLQ1d3eVdoZHJIeENMV3AybG1JaTBuVGFNYjBGS0xlSGowQkEtVkt6X216WHJQNzdKcHR6YlBuQTNXUHJhWFJSVUlfZlZFYWhkRl9MaWZWMWNibi1OSUFjUDA3YWp6NWtINnYyU1FUVmdfVUxXLTdHSTR6cGNUaE1Ra0FyeThvdExFSkNaTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPOGs0MF9ObWVia181OG5TRmxlNmswYjA4LVZUNjdNSko5akptRGRFX2w4R3Yzam9aM24xazdsUU1PbjRqOXFNbDF6LWhscllMYWJYVUlPVExVSWptRUNrY3J6YWZYdEtqUjNyR0tIb1B2bkVLRGdrMzg5NzJ2SVpzYzVhdlhFUm1uNHRWY2xYX1VOSUp5dkVqc1hUX01GWjFaQWxYTzRRMUdOOTIxb0I4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>03/09/2025 04:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Fundação Dirce Figueiredo chega a Arcos com escola de música gratuita para crianças e jovens - Portal Arcos</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>03/09/2025 04:00</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85dab83c354b4eb73ed58a782bf46f&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNaWNLMVJaSWN0MFp5MEstSjZfU1RwZkF3NmxtYjVGRHdRMmllcVJUZTk1enJDdkQ2OGp6Y1A2VHBaeUlyclhMdlFSaHBMVnRqR2RYaHF2Vmx6M0FHZjU3ZnkyUWlxYkJ3TWZRdmxFYmFFTUcyYlEzOGVHSmNScnhhbHZxXzc4aUUxTXhYZjd5Q3lsb01XQTliSS00c053NGk4MnlYYlFpMzdCVU4wTGpVMTZuT1cySEtYLVVRQ3BGakJGa3lUS1Y4dWtJQy1nNHpGd0pF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a85f2617f724ddab8a01329aa3fe55c&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - brasilmineral.com.br</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -11875,6 +11875,28 @@
       <c r="D521" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNNGMyS0xkbXBrOG1SM3MtS3NCOWRHT1NsTmtZUE5tcklTNGstZkp6al9vLWxTTVdiY1JZWGloVnlic0ZTdE83eG5mQXQ0X3ZLMTQwM18ydUN4RHVjb2tHRjZkWjlvT1M0dVdVMU9JTWtsRkJkR2h6c2pmWHBvNW96SEZZZWRIZGYxNmpDdVN5eFNHQnVoWEJ3ZzNxS2I?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>CMOC</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>01/09/2025 04:00</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
